--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author &amp; Lead Architect: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1869,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1893,7 +1894,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author &amp; Lead Architect: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -1904,6 +1905,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2112,6 +2114,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2754,7 +2757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2781,6 +2784,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3032,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3059,6 +3063,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3377,7 +3382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3404,6 +3409,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3780,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3807,6 +3813,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4050,7 +4057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4077,6 +4084,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4212,6 +4220,8 @@
       </c>
       <c r="H7" s="9" t="n"/>
     </row>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4223,7 +4233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4247,6 +4257,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1870,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1894,7 +1893,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1904,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2114,7 +2112,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2757,7 +2754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2784,7 +2781,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3036,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3063,7 +3059,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3382,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3409,7 +3404,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3786,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3813,7 +3807,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4057,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4084,7 +4077,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4220,8 +4212,6 @@
       </c>
       <c r="H7" s="9" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4233,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4257,7 +4247,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1869,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1893,7 +1894,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Comclark Network &amp; Technology Corp. / TelTech | Author &amp; Lead Architect: OLIVER TUNGOL</t>
+          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author: OLIVER TUNGOL</t>
         </is>
       </c>
     </row>
@@ -1904,6 +1905,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2112,6 +2114,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2754,7 +2757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2781,6 +2784,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3021,6 +3025,15 @@
       </c>
       <c r="H10" s="9" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3032,7 +3045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3059,6 +3072,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3366,6 +3380,12 @@
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="16" t="n"/>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3377,7 +3397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3404,6 +3424,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3769,6 +3790,10 @@
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="16" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3780,7 +3805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3807,6 +3832,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4039,6 +4065,15 @@
       </c>
       <c r="H10" s="16" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4050,7 +4085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4077,6 +4112,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4212,6 +4248,18 @@
       </c>
       <c r="H7" s="9" t="n"/>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4223,7 +4271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4247,6 +4295,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4445,6 +4494,12 @@
       <c r="D13" s="8" t="inlineStr"/>
       <c r="E13" s="9" t="n"/>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1870,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1905,7 +1904,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2114,7 +2112,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2757,7 +2754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2784,7 +2781,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2868,12 +2864,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>48V / 150Ah LiFePO4 Battery Bank</t>
+          <t>48V LiFePO4 Battery Bank</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>LFP chemistry, &gt;=4,000 cycles @ 80% DoD, smart BMS, &gt;=4h autonomy</t>
+          <t>Guaranteed &gt;=4.0h autonomy @ 3.0 kW load (min 300 Ah / 15 kWh nominal @ 80% DoD)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -3025,15 +3021,6 @@
       </c>
       <c r="H10" s="9" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3045,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3072,7 +3059,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3380,12 +3366,6 @@
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="16" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3397,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3424,7 +3404,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3790,10 +3769,6 @@
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="16" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3805,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3832,7 +3807,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3893,7 +3867,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>99.95% Availability</t>
+          <t>99.95% Target (99.70% Min SLA)</t>
         </is>
       </c>
       <c r="E5" s="15" t="n"/>
@@ -4065,15 +4039,6 @@
       </c>
       <c r="H10" s="16" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4085,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4112,7 +4077,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4248,18 +4212,6 @@
       </c>
       <c r="H7" s="9" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4271,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4295,7 +4247,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -4494,12 +4445,6 @@
       <c r="D13" s="8" t="inlineStr"/>
       <c r="E13" s="9" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Lot 2 - Power &amp; Passive" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Lot 3 - 5G Core" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Lot 4 - OSS-BSS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Lot 6 - Managed Services" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Lot 7 - 5G CPE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Form D - Vendor Financing" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Lot 5 - Site Acq &amp; Civils" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Lot 6 - Managed Services" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Lot 7 - 5G CPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Form D - Vendor Financing" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,8 +25,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +63,29 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -86,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -108,11 +135,39 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +187,44 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1863,13 +1956,246 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FORM D: MANDATORY VENDOR FINANCING PROPOSAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Official Bidding Terms — Enter Proposed Binding Financing Terms in Column D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Parameter Ref</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Financing Term / Condition</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Operator Mandatory Requirement</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Bidder Binding Offer [Bidder Input]</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Compliance / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>FIN-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Financing Structure</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>OEM Vendor Financing, Buyer's Credit, or ECA-backed facility</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>FIN-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Financing Quantum (% of Capex)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Minimum 80.0% of total eligible Capex (Lots 1, 3, Turnkey Services)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>FIN-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Equity Downpayment (% of Capex)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Maximum 20.0% downpayment upon contract signing</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>FIN-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Total Facility Tenor</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Minimum 4 to 5 Years total facility duration</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>FIN-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Principal Grace Period</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Minimum 12 to 18 Months grace period from first disbursement</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>FIN-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Indicative Annual Interest Rate</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Fixed commercial rate &lt;= 6.50% p.a. (or SOFR + competitive spread)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>FIN-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Repayment Schedule</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Equal quarterly or semi-annual principal &amp; interest amortizations</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>FIN-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Collateral / Asset Pledge</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Pledge on acquired telecom hardware without restrictive corporate liens</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>FIN-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Credit Committee Status</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Board or Credit Committee approved term sheet attached with bid</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2037,36 +2363,48 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Lot 6: Managed Services &amp; 24/7 First Line Maintenance</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Lot 6 - Managed Services</t>
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Lot 5: Site Acquisition, Detailed Site Survey (TSSR), RF Design &amp; Civil Works</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Lot 7: 5G High-Gain Customer Premises Equipment (CPE)</t>
+          <t>Lot 6: Managed Services &amp; 24/7 First Line Maintenance</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lot 7 - 5G CPE</t>
+          <t>Lot 6 - Managed Services</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Lot 7: 5G High-Gain Customer Premises Equipment (CPE)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Lot 7 - 5G CPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Form D: Mandatory Vendor Financing Proposal</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Form D - Vendor Financing</t>
         </is>
@@ -3780,6 +4118,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOT 5: SITE ACQUISITION, DETAILED SITE SURVEY (TSSR), RF DESIGN &amp; CIVIL WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Official Bidding Bill of Quantities — Enter Quoted Rates in Column F</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Service / Works Description</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Detailed Scope &amp; Technical Specification</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Unit Rate (USD) [Bidder Input]</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Unit Rate (PHP @ 55)</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Detailed Site Survey Report (TSSR)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Tower structural load audit, 360-degree drone photo sweep, power/grounding audit, civil layout sketch, and PE endorsement.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>All Sites (Co-loc &amp; Greenfield)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25">
+        <f>F5*55</f>
+        <v/>
+      </c>
+      <c r="H5" s="23" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-02</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Site Acquisition &amp; Permitting Support</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>LGU building permit processing, Barangay clearance, CAAP height clearance, and environmental compliance documentation.</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="25">
+        <f>F6*55</f>
+        <v/>
+      </c>
+      <c r="H6" s="23" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-03</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Equipment Pad Foundation &amp; Cable Gantry</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Reinforced concrete plinth for outdoor DC power cabinet/battery, elevated cable tray/gantry, and AC interconnect point.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Leased TowerCo Sites</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="25">
+        <f>F7*55</f>
+        <v/>
+      </c>
+      <c r="H7" s="23" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-04</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Compound Civil Works &amp; Foundation</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>8m x 8m compound grading, perimeter chain-link security fence, crushed gravel bedding, and reinforced foundation slab.</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="25">
+        <f>F8*55</f>
+        <v/>
+      </c>
+      <c r="H8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-05</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Grounding Grid &amp; Lightning Protection System</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Exothermically welded copper ground ring (Cadweld), ground rods, copper busbar, and air terminal (&lt;= 5.0 Ohms).</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>All Sites (Co-loc &amp; Greenfield)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="25">
+        <f>F9*55</f>
+        <v/>
+      </c>
+      <c r="H9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-06</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>30m Galvanized Steel Monopole Tower</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>ASTM A572 steel monopole, 250 km/h Category 5 wind rating, climbing ladder with fall arrest, rigging, erection, and certification.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="25">
+        <f>F10*55</f>
+        <v/>
+      </c>
+      <c r="H10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-07</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>40m Galvanized Steel Monopole Tower</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>ASTM A572 steel monopole, 250 km/h Category 5 wind rating, fall arrest, rigging, erection, and structural PE certification.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Terrain Challenged)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="25">
+        <f>F11*55</f>
+        <v/>
+      </c>
+      <c r="H11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-08</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>RF Propagation Modeling &amp; Siting Optimization</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>High-resolution 3D ray-tracing simulation, local clutter calibration, candidate search ring generation, and nominal design.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Macro Network Footprint</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="25">
+        <f>F12*55</f>
+        <v/>
+      </c>
+      <c r="H12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>CIV-SVC-09</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Cluster RF Optimization &amp; Drive Testing Services</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Multi-site cluster drive testing, antenna tilt/azimuth physical optimization, pilot pollution removal, and handover tuning.</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Multi-Site Clusters (per site share)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="25">
+        <f>F13*55</f>
+        <v/>
+      </c>
+      <c r="H13" s="23" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL-LOT5</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL LOT 5 TURNKEY CIVIL &amp; SITE SCOPE</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Total Site Acquisition, TSSR &amp; Civil Infrastructure per Site</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Full Scope Evaluation</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F14" s="28">
+        <f>SUM(F5:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>SUM(G5:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>Evaluated Rate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4044,7 +4799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4215,237 +4970,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FORM D: MANDATORY VENDOR FINANCING PROPOSAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Official Bidding Terms — Enter Proposed Binding Financing Terms in Column D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Parameter Ref</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Financing Term / Condition</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Operator Mandatory Requirement</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Bidder Binding Offer [Bidder Input]</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Compliance / Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>FIN-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Financing Structure</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>OEM Vendor Financing, Buyer's Credit, or ECA-backed facility</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>FIN-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Financing Quantum (% of Capex)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Minimum 80.0% of total eligible Capex (Lots 1, 3, Turnkey Services)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>FIN-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Equity Downpayment (% of Capex)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Maximum 20.0% downpayment upon contract signing</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>FIN-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Total Facility Tenor</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Minimum 4 to 5 Years total facility duration</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>FIN-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Principal Grace Period</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Minimum 12 to 18 Months grace period from first disbursement</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>FIN-06</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Indicative Annual Interest Rate</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Fixed commercial rate &lt;= 6.50% p.a. (or SOFR + competitive spread)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>FIN-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Repayment Schedule</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Equal quarterly or semi-annual principal &amp; interest amortizations</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>FIN-08</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Collateral / Asset Pledge</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Pledge on acquired telecom hardware without restrictive corporate liens</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>FIN-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Credit Committee Status</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Board or Credit Committee approved term sheet attached with bid</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -225,6 +225,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Version: Official Bidding Version (Blank BoQ) | Date: October 6, 2026</t>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Version: Official Bidding Version (Blank BoQ) | Date: October 14, 2026</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1014,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Component name (6.0 kW DC Rectifier, 150Ah LiFePO4 battery, 15kVA genset, 30m monopole).</t>
+          <t>Component name (6.0 kW DC Rectifier, LiFePO4 battery bank &gt;=4h @ 3.0 kW autonomy, 15kVA genset, 30m monopole).</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1608,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Mandatory SLA metric: 99.95% radio availability, MTTR &lt;= 2h Urban / &lt;= 4h Rural, 100% PM completion.</t>
+          <t>SLA metric: 99.95% Target (99.70% Min Contractual Floor), MTTR &lt;= 2h Urban / &lt;= 4h Rural, 100% PM completion.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1797,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 baseline volume order: 350,000 subscriber terminals for initial commercial rollout.</t>
+          <t>Phase 1 baseline volume order: 350,000 indoor + 15,000 outdoor units (365,000 total terminals).</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2095,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Minimum 4 to 5 Years total facility duration</t>
+          <t>Minimum 4 Years total facility duration (5 Years Preferred)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -2102,7 +2114,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Minimum 12 to 18 Months grace period from first disbursement</t>
+          <t>Minimum 12 Months grace period from first disbursement (18 Months Preferred)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
@@ -2121,7 +2133,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Fixed commercial rate &lt;= 6.50% p.a. (or SOFR + competitive spread)</t>
+          <t>Fixed commercial rate (preferred &lt;= 6.50% p.a.) or competitive benchmark to SOFR + spread</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
@@ -3092,17 +3104,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3120,244 +3134,355 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Equipment Description</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Technical Specification</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Application</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>Phase 1 Qty</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Unit Rate (USD) [Bidder Input]</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>Unit Rate (PHP @ 55)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Phase 1 Total (USD)</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>Remarks / Bidder Model</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>PWR-01</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>6.0 kW Modular DC Rectifier Plant</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>19" 3U subrack, 3x 3.0 kW modules (N+1), SMPS controller, 96% eff</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Co-loc &amp; Greenfield</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="6">
+      <c r="F5" s="31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="24">
         <f>F5*55</f>
         <v/>
       </c>
-      <c r="H5" s="9" t="n"/>
+      <c r="H5" s="25">
+        <f>G5*55</f>
+        <v/>
+      </c>
+      <c r="I5" s="32">
+        <f>F5*G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="23" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>PWR-02</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>48V LiFePO4 Battery Bank</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Guaranteed &gt;=4.0h autonomy @ 3.0 kW load (min 300 Ah / 15 kWh nominal @ 80% DoD)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Sized for &gt;= 12.0 kWh usable energy over 4.0h @ 3.0 kW load, &lt;=80% DoD, 80% SoH retention (min &gt;=19.0 to 20.0 kWh nominal)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Co-loc &amp; Greenfield</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="6">
+      <c r="F6" s="31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="24">
         <f>F6*55</f>
         <v/>
       </c>
-      <c r="H6" s="9" t="n"/>
+      <c r="H6" s="25">
+        <f>G6*55</f>
+        <v/>
+      </c>
+      <c r="I6" s="32">
+        <f>F6*G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="23" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>PWR-03</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>TowerCo DC Tap-Off Box &amp; Submeter</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Enclosure, Class 1.0 revenue kWh meter, RS485 telemetry, SPD Type 2</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Leased TowerCo Sites</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="6">
+      <c r="F7" s="31" t="n">
+        <v>897</v>
+      </c>
+      <c r="G7" s="24">
         <f>F7*55</f>
         <v/>
       </c>
-      <c r="H7" s="9" t="n"/>
+      <c r="H7" s="25">
+        <f>G7*55</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>F7*G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="23" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>PWR-04</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>15 kVA Soundproof Standby Genset</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Diesel, 230V 60Hz, 500L-1000L sub-base tank, ATS auto-transfer, &lt;68dBA</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Greenfield Sites</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="6">
+      <c r="F8" s="31" t="n">
+        <v>103</v>
+      </c>
+      <c r="G8" s="24">
         <f>F8*55</f>
         <v/>
       </c>
-      <c r="H8" s="9" t="n"/>
+      <c r="H8" s="25">
+        <f>G8*55</f>
+        <v/>
+      </c>
+      <c r="I8" s="32">
+        <f>F8*G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="23" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>CIV-01</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>30m Monopole Tower &amp; Foundation</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>ASTM A572 steel, 250 km/h wind rating, 8x8m compound, pad foundation</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Greenfield Sites</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="6">
+      <c r="F9" s="31" t="n">
+        <v>103</v>
+      </c>
+      <c r="G9" s="24">
         <f>F9*55</f>
         <v/>
       </c>
-      <c r="H9" s="9" t="n"/>
+      <c r="H9" s="25">
+        <f>G9*55</f>
+        <v/>
+      </c>
+      <c r="I9" s="32">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>CIV-02</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Grounding Grid &amp; Lightning System</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Copper earth ring, Cadweld, ground rods, air terminal (&lt;=5 Ohms)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Greenfield Sites</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="6">
+      <c r="F10" s="31" t="n">
+        <v>103</v>
+      </c>
+      <c r="G10" s="24">
         <f>F10*55</f>
         <v/>
       </c>
-      <c r="H10" s="9" t="n"/>
+      <c r="H10" s="25">
+        <f>G10*55</f>
+        <v/>
+      </c>
+      <c r="I10" s="32">
+        <f>F10*G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL-LOT2</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL POWER &amp; PASSIVE INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Total Phase 1 Capital Expenditure for Lot 2</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>1,000 Sites Footprint</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="33" t="inlineStr"/>
+      <c r="H11" s="33" t="inlineStr"/>
+      <c r="I11" s="28">
+        <f>SUM(I5:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>Evaluated Lot 2 Total</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4805,7 +4930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4875,97 +5000,132 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>CPE-01</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Indoor 5G High-Gain FWA Router</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Band n50 native, 8-10 dBi internal antenna, Wi-Fi 6 AX1800, 2.5GE port, TR-069</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>Band n50 native, &gt;=8.0 dBi internal antenna, Wi-Fi 6 AX1800/AX3000, 1x 2.5GE + 2x 1GE ports, TR-069/TR-369</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="n">
         <v>350000</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="6">
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="36">
         <f>D5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="9" t="n"/>
+      <c r="H5" s="34" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>CPE-02</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Outdoor 5G High-Gain FWA Terminal</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Band n50 native, 12 dBi directional antenna, IP67 enclosure, PoE, 2.5GE port</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Outdoor 5G High-Gain FWA Terminal Package</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>Band n50, IP67 enclosure, &gt;=12.0 dBi directional antenna, 1x 2.5GE PoE, bundled indoor Wi-Fi 6 router &amp; PoE injector</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="6">
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="36">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="9" t="n"/>
+      <c r="H6" s="34" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>CPE-SVC</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Device Staging, Pre-Configuration &amp; SIM Locking</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Firmware customization, operator APN &amp; SIM locking, custom packaging</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Firmware customization, operator APN &amp; SIM locking, custom retail packaging for all Phase 1 terminals</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>365000</v>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="6">
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="36">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="9" t="n"/>
+      <c r="H7" s="34" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL-LOT7</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL 5G CUSTOMER PREMISES EQUIPMENT (CPE)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Total Initial Terminal Supply &amp; Staging (365,000 Total Devices)</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>365000</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr"/>
+      <c r="G8" s="28">
+        <f>SUM(G5:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>Evaluated Lot 7 Total</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -16,7 +16,8 @@
     <sheet name="Lot 5 - Site Acq &amp; Civils" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Lot 6 - Managed Services" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Lot 7 - 5G CPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Form D - Vendor Financing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Form C - 10-Year TCO Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Form D - Vendor Financing" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +87,15 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +118,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A192F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,6 +255,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1974,6 +1994,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Telecommunications Technology Solutions Incorporated (TelTech)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Form C: 10-Year Total Cost of Ownership (TCO) &amp; Expansion Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Bidding Entity: [Bidder Company Name]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Cost Category / Lifecycle Element</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Phase 1 Capex (Yr 1)</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 2</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 3</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 4</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 5</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Yrs 6-10 Cumulative</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>10-Year Total TCO (USD)</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Notes &amp; Pricing Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. 5G RAN Network Capex (Lots 1, 2, 5)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'Lot 1 - RAN &amp; Rollout'!H19+'Lot 2 - Power &amp; Passive'!I11</f>
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>SUM(B6:G6)</f>
+        <v/>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Initial 1,000 sites turnkey roll-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2. 5G Core Network &amp; Cloud Infrastructure (Lot 3)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'Lot 3 - 5G Core'!F13</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>SUM(B7:G7)</f>
+        <v/>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.0M subscriber capacity Day-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3. Digital OSS/BSS &amp; Automation (Lot 4)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>'Lot 4 - OSS-BSS'!F15</f>
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>SUM(B8:G8)</f>
+        <v/>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Charging, billing, and field dispatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4. 5G CPE Terminals Supply (Lot 7)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>'Lot 7 - 5G CPE'!G8</f>
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>SUM(B9:G9)</f>
+        <v/>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>365,000 Phase 1 indoor/outdoor terminals</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5. Annual Software Support &amp; AMC (5GC + OSS/BSS)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>(('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10))*5</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(B10:G10)</f>
+        <v/>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Standard 10% SLA &amp; feature maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6. Managed Services &amp; Field Operations (Lot 6)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>'Lot 6 - Managed Services'!G10*1000*5</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(B11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24/7 Tier-1/2 FLM &amp; NOC surveillance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7. Spare Parts Float &amp; RMA Replenishment</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>B6*0.02</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>B6*0.05</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(B12:G12)</f>
+        <v/>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2% initial spares float, 1% annual replenishment</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EVALUATED 10-YEAR TCO (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>SUM(B6:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>SUM(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>SUM(E6:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>SUM(F6:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>SUM(G6:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>SUM(H6:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38" t="inlineStr">
+        <is>
+          <t>Evaluated Total Lifecycle Cost of Ownership</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3129,7 +3530,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Official Bidding Bill of Quantities — Enter Quoted Rates in Column F</t>
+          <t>Official Bidding Bill of Quantities — Enter Quoted Unit Rates in Column G (USD)</t>
         </is>
       </c>
     </row>
@@ -3214,10 +3615,7 @@
       <c r="F5" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="G5" s="24">
-        <f>F5*55</f>
-        <v/>
-      </c>
+      <c r="G5" s="24" t="n"/>
       <c r="H5" s="25">
         <f>G5*55</f>
         <v/>
@@ -3257,10 +3655,7 @@
       <c r="F6" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="G6" s="24">
-        <f>F6*55</f>
-        <v/>
-      </c>
+      <c r="G6" s="24" t="n"/>
       <c r="H6" s="25">
         <f>G6*55</f>
         <v/>
@@ -3300,10 +3695,7 @@
       <c r="F7" s="31" t="n">
         <v>897</v>
       </c>
-      <c r="G7" s="24">
-        <f>F7*55</f>
-        <v/>
-      </c>
+      <c r="G7" s="24" t="n"/>
       <c r="H7" s="25">
         <f>G7*55</f>
         <v/>
@@ -3343,10 +3735,7 @@
       <c r="F8" s="31" t="n">
         <v>103</v>
       </c>
-      <c r="G8" s="24">
-        <f>F8*55</f>
-        <v/>
-      </c>
+      <c r="G8" s="24" t="n"/>
       <c r="H8" s="25">
         <f>G8*55</f>
         <v/>
@@ -3386,10 +3775,7 @@
       <c r="F9" s="31" t="n">
         <v>103</v>
       </c>
-      <c r="G9" s="24">
-        <f>F9*55</f>
-        <v/>
-      </c>
+      <c r="G9" s="24" t="n"/>
       <c r="H9" s="25">
         <f>G9*55</f>
         <v/>
@@ -3429,10 +3815,7 @@
       <c r="F10" s="31" t="n">
         <v>103</v>
       </c>
-      <c r="G10" s="24">
-        <f>F10*55</f>
-        <v/>
-      </c>
+      <c r="G10" s="24" t="n"/>
       <c r="H10" s="25">
         <f>G10*55</f>
         <v/>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Minimum 4 Years total facility duration (5 Years Preferred)</t>
+          <t>Flexible facility tenor up to 20 Years (minimum 4 Years, 5+ Years Preferred)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Minimum 12 Months grace period from first disbursement (18 Months Preferred)</t>
+          <t>Deferred payment / principal grace period up to 10 Years (minimum 12 Months, 18+ Months Preferred)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -3594,12 +3594,12 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>6.0 kW Modular DC Rectifier Plant</t>
+          <t>12.0 kW Modular DC Rectifier Plant</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>19" 3U subrack, 3x 3.0 kW modules (N+1), SMPS controller, 96% eff</t>
+          <t>19" 3U subrack, 4x 3.0 kW modules (N+1), SMPS controller, 96% eff</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +94,36 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0078350F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -130,8 +158,26 @@
         <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -181,11 +227,26 @@
         <color rgb="001F4E79"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,6 +318,33 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -688,1298 +776,2081 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Tender Summary &amp; Instructions</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Instructions &amp; Summary</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Text / Matrix</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Overview of bidding currency (USD/PHP), 180-day price validity, scope boundaries, and lot descriptions.</t>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>Overview of bidding currency (USD/PHP), 180-day price validity, scope boundaries, yellow input cell guidelines, and lot descriptions.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="46" t="inlineStr">
         <is>
           <t>Unique reference identifier for RAN hardware and services (e.g. RAN-HW-01 for BBU, RAN-SVC-01 for TSSR).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Item Description</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>Commercial name of the access equipment subsystem or turnkey rollout engineering activity.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Detailed Technical Specification</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>Compliance Basis</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>Mandatory technical standards (e.g., Band n50, 60 MHz TDD, 8T8R 320W RF power, eCPRI interfaces).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Qty / Site</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>Dimensioning</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>Standard quantity deployed per macro site (e.g., 1 BBU, 3 RRUs, 3 Antennas per 3-sector macro BTS).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>Unit of Measure</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr">
         <is>
           <t>Standard UoM</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="46" t="inlineStr">
         <is>
           <t>Commercial billing unit: set, lot, site, or system.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>Unit Rate (USD)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Firm, fixed unit price quoted by Bidder in US Dollars (Yellow input cells).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>Total per Site (USD)</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="44" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="45" t="inlineStr">
         <is>
           <t>Formula (=Qty*Rate)</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="46" t="inlineStr">
         <is>
           <t>Turnkey total access Capex per individual BTS site.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>Phase 1 Total (1,000 Sites)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>Formula (=Site*1,000)</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>Aggregate Year-1 Capex commitment for Phase 1 priority rollout (1,000 BTS sites).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Program Total (5,000 Sites)</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>Formula (=Site*5,000)</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="46" t="inlineStr">
         <is>
           <t>Full 5-year nationwide network Capex commitment across all 5,000 macro sites.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Lot 1 - RAN &amp; Rollout</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Remarks / Bidder Model</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Text / Alphanumeric</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>Bidder Notes</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>Bidder equipment model numbers, hardware datasheets, and compliance cross-references.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="46" t="inlineStr">
         <is>
           <t>Reference identifier for power systems, batteries, standby generators, and civil monopoles (PWR-01, CIV-01).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Equipment Description</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Component name (6.0 kW DC Rectifier, LiFePO4 battery bank &gt;=4h @ 3.0 kW autonomy, 15kVA genset, 30m monopole).</t>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>Component name (12.0 kW DC Rectifier Plant, LiFePO4 battery bank &gt;=4h @ 3.0 kW autonomy [&gt;=20.0 kWh nom / 400 Ah @ 48V], 15kVA genset, 30m monopole).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Technical Specification</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Compliance Basis</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Performance benchmarks: 96% rectifier efficiency, &gt;=4h battery autonomy, ASTM A572 250 km/h wind rating.</t>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>Performance benchmarks: 96% rectifier efficiency (4x 3.0 kW, N+1), &gt;=4h battery autonomy at 3.0 kW load, ASTM A572 250 km/h wind rating.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>Application</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>Siting Condition</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Applicable site typology: Co-location (Classes T1-T3) vs Greenfield (Class T4).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>Unit of Measure</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>Standard UoM</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="46" t="inlineStr">
         <is>
           <t>Billing unit: set, site, or lot.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Phase 1 Qty</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>Volume Quantity</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Phase 1 target deployment quantity (1,000 rectifiers/batteries, 897 tap boxes, 103 gensets/monopoles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Lot 2 - Power &amp; Passive</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>Unit Rate (USD)</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="44" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Firm unit rate quoted by Bidder in US Dollars.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>Firm unit rate quoted by Bidder in US Dollars (Yellow input cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Unit Rate (PHP @ 55)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>Currency (PHP ₱)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="41" t="inlineStr">
         <is>
           <t>Formula (=USD*55)</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="42" t="inlineStr">
         <is>
           <t>Equivalent local currency amount converted at baseline foreign exchange rate of 55.00 PHP/USD.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Lot 2 - Power &amp; Passive</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Phase 1 Total (USD)</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Formula (=Qty*Rate)</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>Total Phase 1 capital expenditure for Lot 2 power and passive infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Lot 2 - Power &amp; Passive</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>Remarks / Bidder Model</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>Bidder Notes</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Manufacturer make, model, dimensions, and battery cycle life curves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="E27" s="42" t="inlineStr">
+        <is>
+          <t>Manufacturer make, model, physical dimensions, and battery cycle life curves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D28" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="46" t="inlineStr">
         <is>
           <t>Core hardware and software component code (5GC-HW-01 servers, 5GC-SW-01 1M sub license).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>Core Subsystem</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D29" s="41" t="inlineStr">
         <is>
           <t>Subsystem Name</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E29" s="42" t="inlineStr">
         <is>
           <t>Functional domain: Compute servers, UPF line-rate nodes, DC leaf-spine fabric, or 5GC SBA software.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>Functional Description &amp; Sizing</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="45" t="inlineStr">
         <is>
           <t>Dimensioning</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E30" s="46" t="inlineStr">
         <is>
           <t>Capacity requirements: 80 Gbps usable throughput/node, inline CG-NAT, 1,000,000 registered subscribers.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Licensing / Delivery</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="40" t="inlineStr">
         <is>
           <t>Commercial Type</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="41" t="inlineStr">
         <is>
           <t>License Model</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E31" s="42" t="inlineStr">
         <is>
           <t>Commercial model: Hardware Purchase, Perpetual Software License, or Professional Services.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="inlineStr">
+        <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="inlineStr">
+        <is>
+          <t>Standard UoM</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>Billing unit: lot, system, or perpetual license.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>Lot 3 - 5G Core</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>Year 1 Price (USD)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C33" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>Total Year-1 turnkey price quoted by Bidder for dual-datacenter active-active deployment.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>Lot 3 - 5G Core</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>Annual AMC %</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E34" s="46" t="inlineStr">
         <is>
           <t>Annual Maintenance Contract support percentage quoted by Bidder for software &amp; hardware.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>Lot 3 - 5G Core</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Model</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="inlineStr">
+        <is>
+          <t>Server hardware specifications, VNF/CNF container architecture, and throughput benchmarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C36" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D36" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E36" s="46" t="inlineStr">
         <is>
           <t>OSS/BSS module code (BSS-01 CRM, BSS-02 CHF Charging, OSS-01 Field Force FMS, OSS-03 WMS).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>OSS/BSS Functional Module</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D37" s="41" t="inlineStr">
         <is>
           <t>Module Name</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E37" s="42" t="inlineStr">
         <is>
           <t>Subsystem functional title: CRM, Rating Engine, Payment Gateway, FMS, or Fault Management.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>Functional Scope &amp; Volume Driver</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C38" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D38" s="45" t="inlineStr">
         <is>
           <t>Volume Sizing</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E38" s="46" t="inlineStr">
         <is>
           <t>Scale driver: 4 retail tariffs + SME, real-time Nchf charging, 3,500 daily work orders, 70% CPE reverse logistics.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>License Type</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
         <is>
           <t>Commercial Type</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D39" s="41" t="inlineStr">
         <is>
           <t>License Model</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E39" s="42" t="inlineStr">
         <is>
           <t>Licensing model: Perpetual Enterprise, Integration Module, or Professional Services.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="inlineStr">
+        <is>
+          <t>Standard UoM</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="inlineStr">
+        <is>
+          <t>Billing unit: lot, platform, or enterprise license.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>Lot 4 - OSS-BSS</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>Year 1 Price (USD)</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C41" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D41" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E41" s="42" t="inlineStr">
         <is>
           <t>Turnkey Year-1 Capex quoted by Bidder for 1,000,000 registered subscribers.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
         <is>
           <t>Lot 4 - OSS-BSS</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>Annual AMC %</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C42" s="44" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D42" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E42" s="46" t="inlineStr">
         <is>
           <t>Annual software support fee percentage quoted by Bidder.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>Lot 4 - OSS-BSS</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Model</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E43" s="42" t="inlineStr">
+        <is>
+          <t>Architecture framework, TM Forum Open API compliance, and cloud deployment requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>Alphanumeric Code</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>Mandatory Code</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>Reference code for site acquisition, permitting, pad foundation, compound fencing, grounding grid, monopole, and RF optimization (CIV-SVC-01 to CIV-SVC-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Service / Works Description</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>Specification</t>
+        </is>
+      </c>
+      <c r="E45" s="42" t="inlineStr">
+        <is>
+          <t>Scope title for site engineering, permitting, civil construction, and RF design optimization works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Detailed Scope &amp; Technical Specification</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>Scope Definition</t>
+        </is>
+      </c>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>Mandatory engineering parameters: TSSR structural audit, 8x8m compound, pad foundations, 250 km/h wind rating, &lt;=5 Ohm ground ring, 3D ray-tracing design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>Siting Typology</t>
+        </is>
+      </c>
+      <c r="E47" s="42" t="inlineStr">
+        <is>
+          <t>Siting condition: Leased TowerCo co-locations (897 sites), Greenfield Monopoles (103 Class T4 sites), or All Sites (1,000 footprint).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="D48" s="45" t="inlineStr">
+        <is>
+          <t>Standard UoM</t>
+        </is>
+      </c>
+      <c r="E48" s="46" t="inlineStr">
+        <is>
+          <t>Commercial billing unit: site, set, or lot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>Phase 1 Qty</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D49" s="41" t="inlineStr">
+        <is>
+          <t>Volume Quantity</t>
+        </is>
+      </c>
+      <c r="E49" s="42" t="inlineStr">
+        <is>
+          <t>Total quantity deployed in Phase 1 (e.g. 1,000 TSSRs, 103 greenfield compounds, 897 equipment pads).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>Unit Rate (USD)</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>BIDDER TO QUOTE</t>
+        </is>
+      </c>
+      <c r="E50" s="46" t="inlineStr">
+        <is>
+          <t>Firm turnkey service or civil unit rate quoted by Bidder in US Dollars (Yellow input cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>Unit Rate (PHP @ 55)</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>Currency (PHP ₱)</t>
+        </is>
+      </c>
+      <c r="D51" s="41" t="inlineStr">
+        <is>
+          <t>Formula (=USD*55)</t>
+        </is>
+      </c>
+      <c r="E51" s="42" t="inlineStr">
+        <is>
+          <t>Equivalent Philippine Peso rate calculated at baseline exchange rate of 55.00 PHP/USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
+        <is>
+          <t>Phase 1 Total (USD)</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="inlineStr">
+        <is>
+          <t>Formula (=Qty*Rate)</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>Total Phase 1 capital expenditure for site civil and acquisition services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>Lot 5 - Site Acq &amp; Civils</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Methodology</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E53" s="42" t="inlineStr">
+        <is>
+          <t>Contractor mobilization strategy, civil construction timeline, and local subcontractor references.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C54" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D54" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Managed services operational scope code (MS-01 NOC, MS-02 FLM, MS-03 PM, MS-04 SPMS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>Managed services operational scope code (MS-01 NOC, MS-02 FLM, MS-03 PM, MS-04 SPMS, MS-05 Genset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>Service Domain</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C55" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr">
         <is>
           <t>Scope Area</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E55" s="42" t="inlineStr">
         <is>
           <t>Operational responsibility domain: 24/7 NOC surveillance, field maintenance, preventive checks, spares.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>Operational Scope of Work</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C56" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D56" s="45" t="inlineStr">
         <is>
           <t>Service Scope</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E56" s="46" t="inlineStr">
         <is>
           <t>Detailed SLA scope: Continuous alarm monitoring, 2-4 hr MTTR, quarterly site audits, NBD spares delivery.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B57" s="39" t="inlineStr">
         <is>
           <t>SLA Target</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C57" s="40" t="inlineStr">
         <is>
           <t>SLA Target</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D57" s="41" t="inlineStr">
         <is>
           <t>Binding Metric</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E57" s="42" t="inlineStr">
         <is>
           <t>SLA metric: 99.95% Target (99.70% Min Contractual Floor), MTTR &lt;= 2h Urban / &lt;= 4h Rural, 100% PM completion.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="43" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>Monthly Rate / Site (PHP)</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C58" s="44" t="inlineStr">
         <is>
           <t>Currency (PHP ₱)</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D58" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E58" s="46" t="inlineStr">
         <is>
           <t>Firm monthly operational managed service fee per active BTS site quoted by Bidder in PHP.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="39" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B59" s="39" t="inlineStr">
         <is>
           <t>Monthly Rate (USD @ 55)</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C59" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D59" s="41" t="inlineStr">
         <is>
           <t>Formula (=PHP/55)</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E59" s="42" t="inlineStr">
         <is>
           <t>Monthly rate per site converted to USD at 55.00 baseline FX.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
         <is>
           <t>Lot 6 - Managed Services</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>Annual Cost / Site (USD)</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D60" s="45" t="inlineStr">
         <is>
           <t>Formula (=USD*12)</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E60" s="46" t="inlineStr">
         <is>
           <t>Annualized active telecom O&amp;M cost per site.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>Lot 6 - Managed Services</t>
+        </is>
+      </c>
+      <c r="B61" s="39" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E61" s="42" t="inlineStr">
+        <is>
+          <t>Staffing dimensioning, field depot locations, and escalation management details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C62" s="44" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D62" s="45" t="inlineStr">
         <is>
           <t>Mandatory Code</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>CPE terminal model reference code (CPE-01 Indoor Wi-Fi 6, CPE-02 Outdoor high gain).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>CPE terminal model reference code (CPE-01 Indoor Wi-Fi 6, CPE-02 Outdoor high gain, CPE-SVC Staging).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>CPE Terminal Model</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C63" s="40" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>Device Model</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Commercial terminal description (Indoor 5G High-Gain Router, Outdoor IP67 Unit).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="E63" s="42" t="inlineStr">
+        <is>
+          <t>Commercial terminal description (Indoor 5G High-Gain Router, Outdoor IP67 Package with PoE and bundled Wi-Fi 6 router).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>Technical Specifications</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C64" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D64" s="45" t="inlineStr">
         <is>
           <t>Device Spec</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>3GPP R16 5G NR Band n50 native, 8-10 dBi internal antenna, Wi-Fi 6 AX1800, 2.5GE port, TR-069 / TR-369.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>3GPP R16 5G NR Band n50 native, 8-10 dBi internal antenna (&gt;=12 dBi outdoor), Wi-Fi 6 AX1800, 2.5GE port, TR-069 / TR-369.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>Target Order Qty (P1)</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C65" s="40" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D65" s="41" t="inlineStr">
         <is>
           <t>Volume Quantity</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E65" s="42" t="inlineStr">
         <is>
           <t>Phase 1 baseline volume order: 350,000 indoor + 15,000 outdoor units (365,000 total terminals).</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="43" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B66" s="43" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="inlineStr">
+        <is>
+          <t>Standard UoM</t>
+        </is>
+      </c>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>Billing unit: units or devices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="inlineStr">
+        <is>
+          <t>Lot 7 - 5G CPE</t>
+        </is>
+      </c>
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>Unit Rate (USD)</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C67" s="40" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D67" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO QUOTE</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Firm unit purchase price quoted by Bidder in volume packaging in USD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="E67" s="42" t="inlineStr">
+        <is>
+          <t>Firm unit purchase price quoted by Bidder in volume packaging in USD (Yellow input cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="43" t="inlineStr">
         <is>
           <t>Lot 7 - 5G CPE</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B68" s="43" t="inlineStr">
         <is>
           <t>Total Phase 1 Cost (USD)</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C68" s="44" t="inlineStr">
         <is>
           <t>Currency ($ USD)</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D68" s="45" t="inlineStr">
         <is>
           <t>Formula (=Qty*Rate)</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E68" s="46" t="inlineStr">
         <is>
           <t>Total initial CPE capital expenditure calculated from Bidder quoted unit rate.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t>Lot 7 - 5G CPE</t>
+        </is>
+      </c>
+      <c r="B69" s="39" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Model</t>
+        </is>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E69" s="42" t="inlineStr">
+        <is>
+          <t>Offered manufacturer make, product model number, chipset platform, and lead times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>Cost Category / Lifecycle Element</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="inlineStr">
+        <is>
+          <t>Category Identifier</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>High-level Capex and Opex lifecycle cost domain covering RAN, Core, OSS/BSS, CPE, Tower Leases, Fiber Transmission, Spares, and Managed Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B71" s="39" t="inlineStr">
+        <is>
+          <t>Phase 1 Capex (Yr 1)</t>
+        </is>
+      </c>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E71" s="42" t="inlineStr">
+        <is>
+          <t>Initial Phase 1 capital investment committed for Day-1 network launch across 1,000 macro sites and 365,000 subscribers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="43" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B72" s="43" t="inlineStr">
+        <is>
+          <t>Yr 2</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D72" s="45" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>Year 2 network expansion capex, subscriber terminal additions, and operational lifecycle expenditure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B73" s="39" t="inlineStr">
+        <is>
+          <t>Yr 3</t>
+        </is>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D73" s="41" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E73" s="42" t="inlineStr">
+        <is>
+          <t>Year 3 network expansion capex, subscriber terminal additions, and operational lifecycle expenditure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="43" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B74" s="43" t="inlineStr">
+        <is>
+          <t>Yr 4</t>
+        </is>
+      </c>
+      <c r="C74" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D74" s="45" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>Year 4 network expansion capex, subscriber terminal additions, and operational lifecycle expenditure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>Yr 5</t>
+        </is>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E75" s="42" t="inlineStr">
+        <is>
+          <t>Year 5 network expansion capex reaching nationwide 5,000 sites and commercial terminal additions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B76" s="43" t="inlineStr">
+        <is>
+          <t>Yrs 6-10 Cumulative</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D76" s="45" t="inlineStr">
+        <is>
+          <t>Formula / Bidder Input</t>
+        </is>
+      </c>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>Total cumulative lifecycle OPEX, hardware refresh, and software maintenance support across Years 6 through 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B77" s="39" t="inlineStr">
+        <is>
+          <t>10-Year Total TCO (USD)</t>
+        </is>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>Currency ($ USD)</t>
+        </is>
+      </c>
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>Formula (=SUM(Y1:Y10))</t>
+        </is>
+      </c>
+      <c r="E77" s="42" t="inlineStr">
+        <is>
+          <t>Complete 10-year Total Cost of Ownership evaluating turnkey lifecycle economics for QCBS financial scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
+        <is>
+          <t>Form C - 10-Year TCO Schedule</t>
+        </is>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>Notes &amp; Pricing Assumptions</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D78" s="45" t="inlineStr">
+        <is>
+          <t>Bidder Assumptions</t>
+        </is>
+      </c>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>Underlying cost drivers, expansion pacing, discount structures, inflation assumptions, and software lifecycle renewals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="inlineStr">
         <is>
           <t>Form D - Vendor Financing</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B79" s="39" t="inlineStr">
         <is>
           <t>Parameter Ref</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>Alphanumeric Code</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D79" s="41" t="inlineStr">
         <is>
           <t>Reference ID</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Financing covenant parameter identifier (FIN-01 to FIN-09).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="E79" s="42" t="inlineStr">
+        <is>
+          <t>Financing covenant parameter identifier from FIN-01 to FIN-09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
         <is>
           <t>Form D - Vendor Financing</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B80" s="43" t="inlineStr">
         <is>
           <t>Financing Term / Condition</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C80" s="44" t="inlineStr">
         <is>
           <t>Text Description</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D80" s="45" t="inlineStr">
         <is>
           <t>Term Name</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Financing term name: Structure, Financing Quantum, Downpayment, Tenor, Grace Period, Interest Rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>Mandatory financing parameter: Structure, Quantum (% Capex), Downpayment, Tenor, Grace Period, Interest Rate, Repayment Cadence, Security/Pledge, Committee Approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="inlineStr">
         <is>
           <t>Form D - Vendor Financing</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Operator Requirement</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>Operator Mandatory Requirement</t>
+        </is>
+      </c>
+      <c r="C81" s="40" t="inlineStr">
         <is>
           <t>Text / Benchmark</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>Mandatory Rule</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Mandatory parameters: &gt;=80% Capex debt, &lt;=20% downpayment, 4-5 year tenor, 12-18m grace, competitive interest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="E81" s="42" t="inlineStr">
+        <is>
+          <t>Mandatory parameters: &gt;=80.0% Capex debt, &lt;=20.0% downpayment, flexible facility tenor up to 20 years (minimum 4 years, 5+ years preferred), deferred principal repayment / grace period up to 10 years (minimum 12 months, 18+ months preferred), competitive benchmark to SOFR + spread or fixed &lt;= 6.50% p.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
         <is>
           <t>Form D - Vendor Financing</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Bidder Binding Offer</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="B82" s="43" t="inlineStr">
+        <is>
+          <t>Bidder Binding Offer [Bidder Input]</t>
+        </is>
+      </c>
+      <c r="C82" s="44" t="inlineStr">
         <is>
           <t>Text / Values</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D82" s="47" t="inlineStr">
         <is>
           <t>BIDDER TO COMPLETE</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Contractually binding financing terms proposed by the Bidder and financing syndicate.</t>
+      <c r="E82" s="46" t="inlineStr">
+        <is>
+          <t>Contractually binding financing terms proposed by the Bidder and financing syndicate (Yellow input cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>Form D - Vendor Financing</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Compliance / Notes</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>Text Description</t>
+        </is>
+      </c>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>Bidder Notes</t>
+        </is>
+      </c>
+      <c r="E83" s="42" t="inlineStr">
+        <is>
+          <t>Compliance confirmation (Compliant / Minor Deviation / Exception), ECA facility details (e.g. Sinosure, EKN, Finnvera, JBIC), term sheet references, and drawdown conditions.</t>
         </is>
       </c>
     </row>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -26,11 +26,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,8 +123,14 @@
       <color rgb="0078350F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -174,6 +181,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -246,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,6 +358,61 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1149,7 +1217,7 @@
       </c>
       <c r="E20" s="46" t="inlineStr">
         <is>
-          <t>Performance benchmarks: 96% rectifier efficiency (4x 3.0 kW, N+1), &gt;=4h battery autonomy at 3.0 kW load, ASTM A572 250 km/h wind rating.</t>
+          <t>Performance benchmarks: 96% rectifier efficiency (4x 3.0 kW, N+1 12.0 kW total), &gt;= 20.0 kWh nominal LiFePO4 battery storage delivering 4.0h autonomy at 3.0 kW load (&lt;=80% DoD, 80% EOL SoH, loss-based calculation), 15 kVA genset with 72h fuel tank, Class 1.0 revenue submeter.</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2594,7 @@
       </c>
       <c r="E71" s="42" t="inlineStr">
         <is>
-          <t>Initial Phase 1 capital investment committed for Day-1 network launch across 1,000 macro sites and 365,000 subscribers.</t>
+          <t>Initial Phase 1 capital investment committed for Day-1 network footprint (1,000 macro BTS sites turnkey rollout across Lots 1, 2, and 5).</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2878,14 +2946,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Form C: 10-Year Total Cost of Ownership (TCO) &amp; Expansion Schedule</t>
+          <t>Form C: Phase 1 (1,000 Sites) 10-Year Baseline Lifecycle Total Cost of Ownership (TCO)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Bidding Entity: [Bidder Company Name]</t>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Baseline Evaluation: Committed 1,000 Sites (Lots 1, 2, 5 Turnkey) | Expansion Yrs 2-5 Call-Off</t>
         </is>
       </c>
     </row>
@@ -2943,7 +3011,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>'Lot 1 - RAN &amp; Rollout'!H19+'Lot 2 - Power &amp; Passive'!I11</f>
+        <f>'Lot 1 - RAN &amp; Rollout'!H19+'Lot 2 - Power &amp; Passive'!I9+'Lot 5 - Site Acq &amp; Civils'!I14</f>
         <v/>
       </c>
       <c r="C6" t="n">
@@ -2967,7 +3035,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Initial 1,000 sites turnkey roll-out</t>
+          <t>[Evaluated Tender Input] Initial 1,000 sites turnkey rollout (Lots 1, 2, 5 Phase 1 Totals). Expansion Yrs 2-5 Capex evaluated via contractual call-off rate card.</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3070,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0M subscriber capacity Day-1</t>
+          <t>[Evaluated Tender Input] Day-1 Core &amp; DC infrastructure dimensioned for 1.0M subscribers (perpetual license + compute fabric).</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3105,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Charging, billing, and field dispatch</t>
+          <t>[Evaluated Tender Input] Turnkey BSS/OSS stack, CRM, prepaid billing, and FMS dispatch engine.</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3140,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>365,000 Phase 1 indoor/outdoor terminals</t>
+          <t>[Evaluated Tender Input] Phase 1 initial supply of 365,000 subscriber terminals (350k indoor + 15k outdoor).</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3179,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Standard 10% SLA &amp; feature maintenance</t>
+          <t>[Prescribed Evaluated Parameter] 10.0% p.a. of Core (Lot 3) + OSS/BSS (Lot 4) software Capex starting Yr 2 following 12-month Day-1 warranty.</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3219,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24/7 Tier-1/2 FLM &amp; NOC surveillance</t>
+          <t>[Prescribed Evaluated Parameter] Evaluated on Phase 1 network baseline (1,000 sites footprint @ Lot 6 quoted annual rate). Scales proportionately upon expansion call-off.</t>
         </is>
       </c>
     </row>
@@ -3191,14 +3259,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2% initial spares float, 1% annual replenishment</t>
+          <t>[Prescribed Evaluated Parameter] 2.0% initial spares float in Yr 1, 1.0% annual replenishment in Yrs 2-5, and 5.0% cumulative in Yrs 6-10.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="38" t="inlineStr">
         <is>
-          <t>TOTAL EVALUATED 10-YEAR TCO (USD)</t>
+          <t>TOTAL EVALUATED 10-YEAR TCO (USD) — Phase 1 Network Baseline</t>
         </is>
       </c>
       <c r="B13" s="38">
@@ -3231,7 +3299,14 @@
       </c>
       <c r="I13" s="38" t="inlineStr">
         <is>
-          <t>Evaluated Total Lifecycle Cost of Ownership</t>
+          <t>Evaluated Total Lifecycle Cost of Ownership for Phase 1 Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>Note: This schedule establishes the official evaluated 10-Year Lifecycle TCO for the committed Phase 1 network baseline (1,000 macro BTS sites). Expansion Capex for Years 2 to 5 (Phases 2 to 5, 1,000 sites/year up to 5,000 sites total) is governed by the firm unit rates in Lots 1, 2, 5, and 7 under contractual call-off options (Section 4.5).</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3578,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech) | Author: OLIVER TUNGOL</t>
+          <t>Operator: Telecommunications Technology Solutions Incorporated (TelTech)</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4510,7 +4585,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Sized for &gt;= 12.0 kWh usable energy over 4.0h @ 3.0 kW load, &lt;=80% DoD, 80% SoH retention (min &gt;=19.0 to 20.0 kWh nominal)</t>
+          <t>Sized for &gt;= 12.0 kWh usable energy over 4.0h @ 3.0 kW load, &lt;=80% DoD, 80% SoH retention (minimum &gt;= 20.0 kWh nominal installed bank capacity, min 400 Ah @ 48V, loss-based calculation)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -4618,121 +4693,41 @@
       <c r="J8" s="23" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>CIV-01</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>30m Monopole Tower &amp; Foundation</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>ASTM A572 steel, 250 km/h wind rating, 8x8m compound, pad foundation</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Greenfield Sites (Class T4)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="F9" s="31" t="n">
-        <v>103</v>
-      </c>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="25">
-        <f>G9*55</f>
-        <v/>
-      </c>
-      <c r="I9" s="32">
-        <f>F9*G9</f>
-        <v/>
-      </c>
-      <c r="J9" s="23" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>CIV-02</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Grounding Grid &amp; Lightning System</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Copper earth ring, Cadweld, ground rods, air terminal (&lt;=5 Ohms)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Greenfield Sites (Class T4)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>103</v>
-      </c>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="25">
-        <f>G10*55</f>
-        <v/>
-      </c>
-      <c r="I10" s="32">
-        <f>F10*G10</f>
-        <v/>
-      </c>
-      <c r="J10" s="23" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>TOTAL-LOT2</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL POWER &amp; PASSIVE INFRASTRUCTURE</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>Total Phase 1 Capital Expenditure for Lot 2</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL POWER SYSTEMS &amp; ELECTRICAL INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Total Phase 1 Capital Expenditure for Lot 2 Power Systems (Towers, compounds, and grounding are evaluated in Lot 5)</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>1,000 Sites Footprint</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>lot</t>
         </is>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F9" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="G11" s="33" t="inlineStr"/>
-      <c r="H11" s="33" t="inlineStr"/>
-      <c r="I11" s="28">
-        <f>SUM(I5:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="33" t="n"/>
+      <c r="I9" s="28">
+        <f>SUM(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="27" t="inlineStr">
         <is>
           <t>Evaluated Lot 2 Total</t>
         </is>
@@ -5497,17 +5492,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5525,381 +5522,498 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Service / Works Description</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Detailed Scope &amp; Technical Specification</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>Site Class Application</t>
+        </is>
+      </c>
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>Phase 1 Qty</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>Unit Rate (USD) [Bidder Input]</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>Unit Rate (PHP @ 55)</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Phase 1 Total (USD)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Remarks / Bidder Methodology</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>CIV-SVC-01</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Detailed Site Survey Report (TSSR)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Tower structural load audit, 360-degree drone photo sweep, power/grounding audit, civil layout sketch, and PE endorsement.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
           <t>All Sites (Co-loc &amp; Greenfield)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25">
-        <f>F5*55</f>
-        <v/>
-      </c>
-      <c r="H5" s="23" t="n"/>
+      <c r="F5" s="52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="54">
+        <f>G5*55</f>
+        <v/>
+      </c>
+      <c r="I5" s="55">
+        <f>F5*G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="50" t="inlineStr">
+        <is>
+          <t>Comprehensive TSSR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>CIV-SVC-02</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>Site Acquisition &amp; Permitting Support</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>LGU building permit processing, Barangay clearance, CAAP height clearance, and environmental compliance documentation.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>Greenfield Sites</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="25">
-        <f>F6*55</f>
-        <v/>
-      </c>
-      <c r="H6" s="23" t="n"/>
+      <c r="F6" s="59" t="n">
+        <v>103</v>
+      </c>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="60">
+        <f>G6*55</f>
+        <v/>
+      </c>
+      <c r="I6" s="61">
+        <f>F6*G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="57" t="inlineStr">
+        <is>
+          <t>Full permit clearance</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>CIV-SVC-03</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>Equipment Pad Foundation &amp; Cable Gantry</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Reinforced concrete plinth for outdoor DC power cabinet/battery, elevated cable tray/gantry, and AC interconnect point.</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>Leased TowerCo Sites</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="25">
-        <f>F7*55</f>
-        <v/>
-      </c>
-      <c r="H7" s="23" t="n"/>
+      <c r="F7" s="52" t="n">
+        <v>897</v>
+      </c>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="54">
+        <f>G7*55</f>
+        <v/>
+      </c>
+      <c r="I7" s="55">
+        <f>F7*G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="50" t="inlineStr">
+        <is>
+          <t>Co-location upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>CIV-SVC-04</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="57" t="inlineStr">
         <is>
           <t>Greenfield Compound Civil Works &amp; Foundation</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>8m x 8m compound grading, perimeter chain-link security fence, crushed gravel bedding, and reinforced foundation slab.</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>Greenfield Sites (Class T4)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="25">
-        <f>F8*55</f>
-        <v/>
-      </c>
-      <c r="H8" s="23" t="n"/>
+      <c r="F8" s="59" t="n">
+        <v>103</v>
+      </c>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="60">
+        <f>G8*55</f>
+        <v/>
+      </c>
+      <c r="I8" s="61">
+        <f>F8*G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="57" t="inlineStr">
+        <is>
+          <t>Civil compound construction</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>CIV-SVC-05</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>Grounding Grid &amp; Lightning Protection System</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>Exothermically welded copper ground ring (Cadweld), ground rods, copper busbar, and air terminal (&lt;= 5.0 Ohms).</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>All Sites (Co-loc &amp; Greenfield)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>Greenfield Sites (Class T4)</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="25">
-        <f>F9*55</f>
-        <v/>
-      </c>
-      <c r="H9" s="23" t="n"/>
+      <c r="F9" s="52" t="n">
+        <v>103</v>
+      </c>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="54">
+        <f>G9*55</f>
+        <v/>
+      </c>
+      <c r="I9" s="55">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="50" t="inlineStr">
+        <is>
+          <t>Dedicated earth ground ring</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>CIV-SVC-06</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
         <is>
           <t>30m Galvanized Steel Monopole Tower</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>ASTM A572 steel monopole, 250 km/h Category 5 wind rating, climbing ladder with fall arrest, rigging, erection, and certification.</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Greenfield Sites (Class T4)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>Greenfield Standard Height (Alternative A)</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="25">
-        <f>F10*55</f>
-        <v/>
-      </c>
-      <c r="H10" s="23" t="n"/>
+      <c r="F10" s="59" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="60">
+        <f>G10*55</f>
+        <v/>
+      </c>
+      <c r="I10" s="61">
+        <f>F10*G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="57" t="inlineStr">
+        <is>
+          <t>80 sites standard (mutually exclusive with 40m)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>CIV-SVC-07</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>40m Galvanized Steel Monopole Tower</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>ASTM A572 steel monopole, 250 km/h Category 5 wind rating, fall arrest, rigging, erection, and structural PE certification.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Greenfield Sites (Terrain Challenged)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>Greenfield High-Clearance (Alternative B)</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="25">
-        <f>F11*55</f>
-        <v/>
-      </c>
-      <c r="H11" s="23" t="n"/>
+      <c r="F11" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="54">
+        <f>G11*55</f>
+        <v/>
+      </c>
+      <c r="I11" s="55">
+        <f>F11*G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="50" t="inlineStr">
+        <is>
+          <t>23 sites terrain/canopy (mutually exclusive with 30m)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>CIV-SVC-08</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
         <is>
           <t>RF Propagation Modeling &amp; Siting Optimization</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>High-resolution 3D ray-tracing simulation, local clutter calibration, candidate search ring generation, and nominal design.</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="56" t="inlineStr">
         <is>
           <t>Macro Network Footprint</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="25">
-        <f>F12*55</f>
-        <v/>
-      </c>
-      <c r="H12" s="23" t="n"/>
+      <c r="F12" s="59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="60">
+        <f>G12*55</f>
+        <v/>
+      </c>
+      <c r="I12" s="61">
+        <f>F12*G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="57" t="inlineStr">
+        <is>
+          <t>RF planning &amp; candidate search rings</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>CIV-SVC-09</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>Cluster RF Optimization &amp; Drive Testing Services</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>Multi-site cluster drive testing, antenna tilt/azimuth physical optimization, pilot pollution removal, and handover tuning.</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="49" t="inlineStr">
         <is>
           <t>Multi-Site Clusters (per site share)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="25">
-        <f>F13*55</f>
-        <v/>
-      </c>
-      <c r="H13" s="23" t="n"/>
+      <c r="F13" s="52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="54">
+        <f>G13*55</f>
+        <v/>
+      </c>
+      <c r="I13" s="55">
+        <f>F13*G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="50" t="inlineStr">
+        <is>
+          <t>Cluster drive testing &amp; tuning</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>TOTAL-LOT5</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL LOT 5 TURNKEY CIVIL &amp; SITE SCOPE</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>Total Site Acquisition, TSSR &amp; Civil Infrastructure per Site</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>Full Scope Evaluation</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="F14" s="28">
-        <f>SUM(F5:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>TOTAL PHASE 1 CIVIL &amp; SITING WORKS (USD)</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>Evaluated Turnkey Site Acquisition, Survey, Towers &amp; Civil Infrastructure</t>
+        </is>
+      </c>
+      <c r="D14" s="62" t="inlineStr">
+        <is>
+          <t>1,000 Sites Footprint (897 Co-loc + 103 Greenfield)</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="F14" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="65">
         <f>SUM(G5:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="65" t="inlineStr">
         <is>
           <t>Evaluated Rate</t>
+        </is>
+      </c>
+      <c r="I14" s="65">
+        <f>SUM(I5:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="63" t="inlineStr">
+        <is>
+          <t>Evaluated Phase 1 Total</t>
         </is>
       </c>
     </row>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -190,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -255,11 +255,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -413,6 +457,21 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -893,7 +952,7 @@
       </c>
       <c r="E8" s="46" t="inlineStr">
         <is>
-          <t>Unique reference identifier for RAN hardware and services (e.g. RAN-HW-01 for BBU, RAN-SVC-01 for TSSR).</t>
+          <t>Unique reference identifier for RAN hardware and services (e.g. RAN-HW-01 for BBU, RAN-SVC-01 for PMO / Mobilization).</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1276,7 @@
       </c>
       <c r="E20" s="46" t="inlineStr">
         <is>
-          <t>Performance benchmarks: 96% rectifier efficiency (4x 3.0 kW, N+1 12.0 kW total), &gt;= 20.0 kWh nominal LiFePO4 battery storage delivering 4.0h autonomy at 3.0 kW load (&lt;=80% DoD, 80% EOL SoH, loss-based calculation), 15 kVA genset with 72h fuel tank, Class 1.0 revenue submeter.</t>
+          <t>Performance benchmarks: 96% rectifier efficiency (4x 3.0 kW, 12.0 kW installed / 9.0 kW firm N+1 capacity), &gt;= 20.0 kWh nominal LiFePO4 battery storage delivering 4.0h autonomy at 3.0 kW load (&lt;=80% DoD, 80% EOL SoH, loss-based calculation), 15 kVA genset with 72h fuel tank, Class 1.0 revenue submeter.</t>
         </is>
       </c>
     </row>
@@ -3007,11 +3066,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. 5G RAN Network Capex (Lots 1, 2, 5)</t>
+          <t>1. 5G RAN &amp; Site Infrastructure Capex (Lots 1, 2, 5)</t>
         </is>
       </c>
       <c r="B6">
-        <f>'Lot 1 - RAN &amp; Rollout'!H19+'Lot 2 - Power &amp; Passive'!I9+'Lot 5 - Site Acq &amp; Civils'!I14</f>
+        <f>'Lot 1 - RAN &amp; Rollout'!H17+'Lot 2 - Power &amp; Passive'!I9+'Lot 5 - Site Acq &amp; Civils'!I14</f>
         <v/>
       </c>
       <c r="C6" t="n">
@@ -3147,7 +3206,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5. Annual Software Support &amp; AMC (5GC + OSS/BSS)</t>
+          <t>5. Annual Maintenance Contract (AMC) &amp; Support (Lots 3 + 4)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3179,7 +3238,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[Prescribed Evaluated Parameter] 10.0% p.a. of Core (Lot 3) + OSS/BSS (Lot 4) software Capex starting Yr 2 following 12-month Day-1 warranty.</t>
+          <t>[Prescribed Evaluated Parameter] Standard 10.0% p.a. Annual Maintenance Contract (AMC) &amp; Technical Support based on combined Total Year 1 Turnkey Capex of Lot 3 (5G Core) and Lot 4 (OSS/BSS), commencing in Year 2 post-warranty.</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4094,353 +4153,326 @@
       <c r="J10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>RAN-SVC-01</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Site Survey, Structural Audit &amp; TSSR</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Tower load audit, drone 360 photo sweep, power check, TSSR report</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>Project Management &amp; Rollout Mobilization</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>Dedicated rollout PMO, milestone scheduling, vendor coordination, QA &amp; safety management</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="6">
+      <c r="F11" s="67" t="n"/>
+      <c r="G11" s="68">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="68">
         <f>G11*1000</f>
         <v/>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="68">
         <f>G11*5000</f>
         <v/>
       </c>
-      <c r="J11" s="9" t="n"/>
+      <c r="J11" s="50" t="inlineStr">
+        <is>
+          <t>Dedicated physical deployment service</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>RAN-SVC-02</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Project Management &amp; Mobilization</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Dedicated PMO, rollout staging, quality assurance, safety management</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="B12" s="57" t="inlineStr">
+        <is>
+          <t>Installation, Testing &amp; Commissioning (I&amp;C)</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
+        <is>
+          <t>Rigging, antenna/RRU mount, optical cabling, BBU wiring, DC power termination, turn-up</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="6">
+      <c r="F12" s="67" t="n"/>
+      <c r="G12" s="69">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="69">
         <f>G12*1000</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="69">
         <f>G12*5000</f>
         <v/>
       </c>
-      <c r="J12" s="9" t="n"/>
+      <c r="J12" s="57" t="inlineStr">
+        <is>
+          <t>Dedicated physical deployment service</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>RAN-SVC-03</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Installation, Testing &amp; Commissioning (I&amp;C)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Rigging, antenna/RRU mount, BBU wiring, fiber termination, power-up</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>Single Site Verification &amp; Acceptance (SSV/SSO)</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Stationary throughput, 3-sector call testing, ping, eRET tilt validation, SSV report</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="6">
+      <c r="F13" s="67" t="n"/>
+      <c r="G13" s="68">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="68">
         <f>G13*1000</f>
         <v/>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="68">
         <f>G13*5000</f>
         <v/>
       </c>
-      <c r="J13" s="9" t="n"/>
+      <c r="J13" s="50" t="inlineStr">
+        <is>
+          <t>Dedicated physical deployment service</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>RAN-SVC-04</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Single Site Optimization (SSO/SSV)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Stationary throughput, sector call test, ping, eRET tuning, SSV report</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>Central Warehousing &amp; Buffer Staging</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>Serial-level barcode asset tagging, climate-controlled storage, kitting &amp; buffer stock</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="56" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="6">
+      <c r="F14" s="67" t="n"/>
+      <c r="G14" s="69">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="69">
         <f>G14*1000</f>
         <v/>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="69">
         <f>G14*5000</f>
         <v/>
       </c>
-      <c r="J14" s="9" t="n"/>
+      <c r="J14" s="57" t="inlineStr">
+        <is>
+          <t>Dedicated physical deployment service</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>RAN-SVC-05</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cluster RF Optimization Services</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Cluster drive test, pilot pollution removal, neighbor tuning (per site share)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>Regional Transport &amp; Final-Mile Site Hauling</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>Hauling from central warehouse to regional hubs, 4x4 rough-road delivery to barangay site</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="6">
+      <c r="F15" s="67" t="n"/>
+      <c r="G15" s="68">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="68">
         <f>G15*1000</f>
         <v/>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="68">
         <f>G15*5000</f>
         <v/>
       </c>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="50" t="inlineStr">
+        <is>
+          <t>Dedicated physical deployment service</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>RAN-SVC-06</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Central Warehousing &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Staging, serial asset tagging, indoor climate storage, kitting</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>SUBTOTAL-SVC</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>Subtotal Turnkey Rollout Services</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>Total Dedicated RAN Rollout &amp; Commissioning Services per Site</t>
+        </is>
+      </c>
+      <c r="D16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="62" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="6">
-        <f>D16*F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="6">
-        <f>G16*1000</f>
-        <v/>
-      </c>
-      <c r="I16" s="6">
-        <f>G16*5000</f>
-        <v/>
-      </c>
-      <c r="J16" s="9" t="n"/>
+      <c r="F16" s="63" t="n"/>
+      <c r="G16" s="70">
+        <f>SUM(G11:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="70">
+        <f>SUM(H11:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="70">
+        <f>SUM(I11:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="63" t="inlineStr">
+        <is>
+          <t>Subtotal Turnkey Services</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>RAN-SVC-07</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Delivery &amp; Basic Hauling to Site</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Transport to regional depots, 4x4 rough-road hauling to rural barangays</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>TOTAL-LOT1</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>TOTAL TURNKEY RAN CAPEX PER SITE</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>Combined BTS Hardware + Turnkey Rollout Services per Site</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="62" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="6">
-        <f>D17*F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="6">
-        <f>G17*1000</f>
-        <v/>
-      </c>
-      <c r="I17" s="6">
-        <f>G17*5000</f>
-        <v/>
-      </c>
-      <c r="J17" s="9" t="n"/>
+      <c r="F17" s="63" t="n"/>
+      <c r="G17" s="70">
+        <f>G10+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="70">
+        <f>H10+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="70">
+        <f>I10+I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="63" t="inlineStr">
+        <is>
+          <t>Evaluated Lot 1 Total</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>SUBTOTAL-SVC</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Subtotal Turnkey Services</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Total RAN Turnkey Rollout Services per Site</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10">
-        <f>SUM(G11:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>SUM(H11:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="10">
-        <f>SUM(I11:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL-LOT1</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL TURNKEY RAN CAPEX PER SITE</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Combined BTS Hardware + Turnkey Rollout Services per Site</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr"/>
-      <c r="G19" s="13">
-        <f>G10+G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
-        <f>H10+H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="13">
-        <f>I10+I18</f>
-        <v/>
-      </c>
-      <c r="J19" s="13" t="n"/>
+      <c r="A18" s="71" t="inlineStr">
+        <is>
+          <t>*(Note: Detailed Site Surveys (TSSR), Greenfield Tower Permitting, RF Propagation Modeling, and Multi-Site Cluster RF Optimization are consolidated and evaluated under Lot 5 to eliminate scope duplication. Lot 1 Turnkey Services cover dedicated RAN hardware deployment, I&amp;C, SSV, warehousing, and hauling)*</t>
+        </is>
+      </c>
+      <c r="B18" s="72" t="n"/>
+      <c r="C18" s="72" t="n"/>
+      <c r="D18" s="72" t="n"/>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="72" t="n"/>
+      <c r="H18" s="72" t="n"/>
+      <c r="I18" s="72" t="n"/>
+      <c r="J18" s="73" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A18:J18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4540,12 +4572,12 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>12.0 kW Modular DC Rectifier Plant</t>
+          <t>12.0 kW Total Installed / 9.0 kW Firm N+1 DC Rectifier Plant</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>19" 3U subrack, 4x 3.0 kW modules (N+1), SMPS controller, 96% eff</t>
+          <t>19" 3U subrack, 4x 3.0 kW modules (3 active + 1 redundant standby N+1), SMPS controller, 96% eff</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -4580,12 +4612,12 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>48V LiFePO4 Battery Bank</t>
+          <t>48V LiFePO4 Battery Bank (&gt;=20.0 kWh nominal)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Sized for &gt;= 12.0 kWh usable energy over 4.0h @ 3.0 kW load, &lt;=80% DoD, 80% SoH retention (minimum &gt;= 20.0 kWh nominal installed bank capacity, min 400 Ah @ 48V, loss-based calculation)</t>
+          <t>Sized for &gt;= 12.0 kWh usable energy over 4.0h @ 3.0 kW load, &lt;=80% DoD, 80% SoH retention (minimum &gt;= 20.0 kWh nominal installed bank capacity is controlling; 400 Ah to 450 Ah is indicative, loss-based calculation)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -5517,7 +5549,7 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Official Bidding Bill of Quantities — Enter Quoted Rates in Column F</t>
+          <t>Official Bidding Bill of Quantities — Enter Quoted Unit Rates in Column G (USD)</t>
         </is>
       </c>
     </row>
@@ -5998,22 +6030,15 @@
       <c r="F14" s="64" t="n">
         <v>1000</v>
       </c>
-      <c r="G14" s="65">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="65" t="inlineStr">
-        <is>
-          <t>Evaluated Rate</t>
-        </is>
-      </c>
+      <c r="G14" s="65" t="n"/>
+      <c r="H14" s="65" t="n"/>
       <c r="I14" s="65">
         <f>SUM(I5:I13)</f>
         <v/>
       </c>
       <c r="J14" s="63" t="inlineStr">
         <is>
-          <t>Evaluated Phase 1 Total</t>
+          <t>Phase 1 Evaluated Total</t>
         </is>
       </c>
     </row>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me - Data Dictionary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tender Summary &amp; Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lot 1 - RAN &amp; Rollout" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lot 2 - Power &amp; Passive" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lot 3 - 5G Core" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lot 4 - OSS-BSS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Lot 5 - Site Acq &amp; Civils" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Lot 6 - Managed Services" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Lot 7 - 5G CPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Form C - 10-Year TCO Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Form D - Vendor Financing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me - Data Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tender Summary &amp; Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 1 - RAN &amp; Rollout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 2 - Power &amp; Passive" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 3 - 5G Core" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 4 - OSS-BSS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 5 - Site Acq &amp; Civils" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 6 - Managed Services" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services SOW &amp; Rate Card" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lot 7 - 5G CPE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form C - 10-Year TCO Schedule" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form D - Vendor Financing" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,8 +130,56 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F3460"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="000F3460"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F3460"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -189,8 +238,32 @@
         <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F3460"/>
+        <bgColor rgb="000F3460"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -299,11 +372,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -472,6 +603,49 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -857,7 +1031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Project: Nationwide 5G FWA Network (Band n50, 60 MHz TDD) | 5,000 Sites Footprint</t>
+          <t>Project: Nationwide 5G FWA Network (Band n50, 60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD) | 5,000 Sites Footprint</t>
         </is>
       </c>
     </row>
@@ -875,6 +1049,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -1006,7 +1181,7 @@
       </c>
       <c r="E10" s="46" t="inlineStr">
         <is>
-          <t>Mandatory technical standards (e.g., Band n50, 60 MHz TDD, 8T8R 320W RF power, eCPRI interfaces).</t>
+          <t>Mandatory technical standards (e.g., Band n50, 60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD, 8T8R 320W RF power, eCPRI interfaces).</t>
         </is>
       </c>
     </row>
@@ -2992,380 +3167,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Telecommunications Technology Solutions Incorporated (TelTech)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LOT 7: 5G HIGH-GAIN CUSTOMER PREMISES EQUIPMENT (CPE)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Form C: Phase 1 (1,000 Sites) 10-Year Baseline Lifecycle Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Baseline Evaluation: Committed 1,000 Sites (Lots 1, 2, 5 Turnkey) | Expansion Yrs 2-5 Call-Off</t>
+          <t>Official Bidding Bill of Quantities — Enter Quoted Unit Rate in Column F</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CPE Terminal Model</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Technical Specifications</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Target Order Qty (P1)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Unit Rate (USD) [Bidder Input]</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Total Phase 1 Cost (USD)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Remarks / Bidder Model</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>Cost Category / Lifecycle Element</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>Phase 1 Capex (Yr 1)</t>
-        </is>
-      </c>
-      <c r="C5" s="37" t="inlineStr">
-        <is>
-          <t>Yr 2</t>
-        </is>
-      </c>
-      <c r="D5" s="37" t="inlineStr">
-        <is>
-          <t>Yr 3</t>
-        </is>
-      </c>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>Yr 4</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>Yr 5</t>
-        </is>
-      </c>
-      <c r="G5" s="37" t="inlineStr">
-        <is>
-          <t>Yrs 6-10 Cumulative</t>
-        </is>
-      </c>
-      <c r="H5" s="37" t="inlineStr">
-        <is>
-          <t>10-Year Total TCO (USD)</t>
-        </is>
-      </c>
-      <c r="I5" s="37" t="inlineStr">
-        <is>
-          <t>Notes &amp; Pricing Assumptions</t>
-        </is>
-      </c>
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>CPE-01</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Indoor 5G High-Gain FWA Router</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>Band n50 native, &gt;=8.0 dBi internal antenna, Wi-Fi 6 AX1800/AX3000, 1x 2.5GE + 2x 1GE ports, TR-069/TR-369</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="36">
+        <f>D5*F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="34" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1. 5G RAN &amp; Site Infrastructure Capex (Lots 1, 2, 5)</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>'Lot 1 - RAN &amp; Rollout'!H17+'Lot 2 - Power &amp; Passive'!I9+'Lot 5 - Site Acq &amp; Civils'!I14</f>
-        <v/>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <f>SUM(B6:G6)</f>
-        <v/>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[Evaluated Tender Input] Initial 1,000 sites turnkey rollout (Lots 1, 2, 5 Phase 1 Totals). Expansion Yrs 2-5 Capex evaluated via contractual call-off rate card.</t>
-        </is>
-      </c>
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>CPE-02</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Outdoor 5G High-Gain FWA Terminal Package</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>Band n50, IP67 enclosure, &gt;=12.0 dBi directional antenna, 1x 2.5GE PoE, bundled indoor Wi-Fi 6 router &amp; PoE injector</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="36">
+        <f>D6*F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="34" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2. 5G Core Network &amp; Cloud Infrastructure (Lot 3)</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>'Lot 3 - 5G Core'!F13</f>
-        <v/>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f>SUM(B7:G7)</f>
-        <v/>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[Evaluated Tender Input] Day-1 Core &amp; DC infrastructure dimensioned for 1.0M subscribers (perpetual license + compute fabric).</t>
-        </is>
-      </c>
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>CPE-SVC</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Device Staging, Pre-Configuration &amp; SIM Locking</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Firmware customization, operator APN &amp; SIM locking, custom retail packaging for all Phase 1 terminals</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>365000</v>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="36">
+        <f>D7*F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="34" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3. Digital OSS/BSS &amp; Automation (Lot 4)</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>'Lot 4 - OSS-BSS'!F15</f>
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <f>SUM(B8:G8)</f>
-        <v/>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>[Evaluated Tender Input] Turnkey BSS/OSS stack, CRM, prepaid billing, and FMS dispatch engine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4. 5G CPE Terminals Supply (Lot 7)</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>'Lot 7 - 5G CPE'!G8</f>
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <f>SUM(B9:G9)</f>
-        <v/>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>[Evaluated Tender Input] Phase 1 initial supply of 365,000 subscriber terminals (350k indoor + 15k outdoor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>5. Annual Maintenance Contract (AMC) &amp; Support (Lots 3 + 4)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>(('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10))*5</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(B10:G10)</f>
-        <v/>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>[Prescribed Evaluated Parameter] Standard 10.0% p.a. Annual Maintenance Contract (AMC) &amp; Technical Support based on combined Total Year 1 Turnkey Capex of Lot 3 (5G Core) and Lot 4 (OSS/BSS), commencing in Year 2 post-warranty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6. Managed Services &amp; Field Operations (Lot 6)</t>
-        </is>
-      </c>
-      <c r="B11">
-        <f>'Lot 6 - Managed Services'!G10*1000</f>
-        <v/>
-      </c>
-      <c r="C11">
-        <f>'Lot 6 - Managed Services'!G10*1000</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>'Lot 6 - Managed Services'!G10*1000</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>'Lot 6 - Managed Services'!G10*1000</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>'Lot 6 - Managed Services'!G10*1000</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>'Lot 6 - Managed Services'!G10*1000*5</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(B11:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>[Prescribed Evaluated Parameter] Evaluated on Phase 1 network baseline (1,000 sites footprint @ Lot 6 quoted annual rate). Scales proportionately upon expansion call-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7. Spare Parts Float &amp; RMA Replenishment</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>B6*0.02</f>
-        <v/>
-      </c>
-      <c r="C12">
-        <f>B6*0.01</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>B6*0.01</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>B6*0.01</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>B6*0.01</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>B6*0.05</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(B12:G12)</f>
-        <v/>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[Prescribed Evaluated Parameter] 2.0% initial spares float in Yr 1, 1.0% annual replenishment in Yrs 2-5, and 5.0% cumulative in Yrs 6-10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>TOTAL EVALUATED 10-YEAR TCO (USD) — Phase 1 Network Baseline</t>
-        </is>
-      </c>
-      <c r="B13" s="38">
-        <f>SUM(B6:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="38">
-        <f>SUM(C6:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="38">
-        <f>SUM(D6:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="38">
-        <f>SUM(E6:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="38">
-        <f>SUM(F6:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="38">
-        <f>SUM(G6:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="38">
-        <f>SUM(H6:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="38" t="inlineStr">
-        <is>
-          <t>Evaluated Total Lifecycle Cost of Ownership for Phase 1 Baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>Note: This schedule establishes the official evaluated 10-Year Lifecycle TCO for the committed Phase 1 network baseline (1,000 macro BTS sites). Expansion Capex for Years 2 to 5 (Phases 2 to 5, 1,000 sites/year up to 5,000 sites total) is governed by the firm unit rates in Lots 1, 2, 5, and 7 under contractual call-off options (Section 4.5).</t>
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL-LOT7</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL 5G CUSTOMER PREMISES EQUIPMENT (CPE)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Total Initial Terminal Supply &amp; Staging (365,000 Total Devices)</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>365000</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr"/>
+      <c r="G8" s="28">
+        <f>SUM(G5:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>Evaluated Lot 7 Total</t>
         </is>
       </c>
     </row>
@@ -3375,6 +3370,394 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Telecommunications Technology Solutions Incorporated (TelTech)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Form C: Phase 1 (1,000 Sites) 10-Year Baseline Lifecycle Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Baseline Evaluation: Committed 1,000 Sites (Lots 1, 2, 5 Turnkey) | Expansion Yrs 2-5 Call-Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Cost Category / Lifecycle Element</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Phase 1 Capex (Yr 1)</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 2</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 3</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 4</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Yr 5</t>
+        </is>
+      </c>
+      <c r="G5" s="37" t="inlineStr">
+        <is>
+          <t>Yrs 6-10 Cumulative</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>10-Year Total TCO (USD)</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>Notes &amp; Pricing Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1. 5G RAN &amp; Site Infrastructure Capex (Lots 1, 2, 5)</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'Lot 1 - RAN &amp; Rollout'!H17+'Lot 2 - Power &amp; Passive'!I9+'Lot 5 - Site Acq &amp; Civils'!I14</f>
+        <v/>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>SUM(B6:G6)</f>
+        <v/>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[Evaluated Tender Input] Initial 1,000 sites turnkey rollout (Lots 1, 2, 5 Phase 1 Totals). Expansion Yrs 2-5 Capex evaluated via contractual call-off rate card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2. 5G Core Network &amp; Cloud Infrastructure (Lot 3)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'Lot 3 - 5G Core'!F13</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>SUM(B7:G7)</f>
+        <v/>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[Evaluated Tender Input] Day-1 Core &amp; DC infrastructure dimensioned for 1.0M subscribers (perpetual license + compute fabric).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3. Digital OSS/BSS &amp; Automation (Lot 4)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>'Lot 4 - OSS-BSS'!F15</f>
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>SUM(B8:G8)</f>
+        <v/>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[Evaluated Tender Input] Turnkey BSS/OSS stack, CRM, prepaid billing, and FMS dispatch engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4. 5G CPE Terminals Supply (Lot 7)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>'Lot 7 - 5G CPE'!G8</f>
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>SUM(B9:G9)</f>
+        <v/>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[Evaluated Tender Input] Phase 1 initial supply of 365,000 subscriber terminals (350k indoor + 15k outdoor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5. Annual Maintenance Contract (AMC) &amp; Support (Lots 3 + 4)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>(('Lot 3 - 5G Core'!F13*0.10)+('Lot 4 - OSS-BSS'!F15*0.10))*5</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(B10:G10)</f>
+        <v/>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[Prescribed Evaluated Parameter] Standard 10.0% p.a. Annual Maintenance Contract (AMC) &amp; Technical Support based on combined Total Year 1 Turnkey Capex of Lot 3 (5G Core) and Lot 4 (OSS/BSS), commencing in Year 2 post-warranty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6. Managed Services &amp; Field Operations (Lot 6)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>'Lot 6 - Managed Services'!G10*1000*5</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(B11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[Prescribed Evaluated Parameter] Evaluated on Phase 1 network baseline (1,000 sites footprint @ Lot 6 quoted annual rate). Scales proportionately upon expansion call-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7. Spare Parts Float &amp; RMA Replenishment</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>B6*0.02</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>B6*0.01</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>B6*0.05</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(B12:G12)</f>
+        <v/>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[Prescribed Evaluated Parameter] 2.0% initial spares float in Yr 1, 1.0% annual replenishment in Yrs 2-5, and 5.0% cumulative in Yrs 6-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EVALUATED 10-YEAR TCO (USD) — Phase 1 Network Baseline</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>SUM(B6:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>SUM(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>SUM(E6:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>SUM(F6:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>SUM(G6:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>SUM(H6:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38" t="inlineStr">
+        <is>
+          <t>Evaluated Total Lifecycle Cost of Ownership for Phase 1 Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>Note: This schedule establishes the official evaluated 10-Year Lifecycle TCO for the committed Phase 1 network baseline (1,000 macro BTS sites). Expansion Capex for Years 2 to 5 (Phases 2 to 5, 1,000 sites/year up to 5,000 sites total) is governed by the firm unit rates in Lots 1, 2, 5, and 7 under contractual call-off options (Section 4.5).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3630,7 +4013,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Project: Nationwide 5G FWA Network (Band n50, 60 MHz TDD) | 5,000 Sites Footprint</t>
+          <t>Project: Nationwide 5G FWA Network (Band n50, 60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD) | 5,000 Sites Footprint</t>
         </is>
       </c>
     </row>
@@ -3648,6 +4031,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -3868,6 +4252,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3972,7 +4357,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Band n50 (1.5 GHz), 60 MHz IBW, 8x40W (320W total RF power), IP67, fanless</t>
+          <t>Band n50 (1.5 GHz), up to 80 MHz IBW (1437–1517 MHz, full 1432–1517 MHz hardware tuning range), 8x40W (320W total RF power), IP67, fanless</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -4089,7 +4474,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Band n50 carrier license, 60 MHz TDD, 8T8R MU-MIMO, dynamic beamforming, energy-saving</t>
+          <t>Band n50 carrier license (60 MHz NCR / up to 80 MHz Provincial, software-configurable 40/50/60/80 MHz TDD), 8T8R MU-MIMO, dynamic beamforming, energy-saving</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -6323,204 +6708,3436 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LOT 7: 5G HIGH-GAIN CUSTOMER PREMISES EQUIPMENT (CPE)</t>
+      <c r="A1" s="74" t="inlineStr">
+        <is>
+          <t>5G FWA PROGRAM — MASTER SERVICES SOW &amp; COMMERCIAL RATE CARD</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Official Bidding Bill of Quantities — Enter Quoted Unit Rate in Column F</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Item Code</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CPE Terminal Model</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Technical Specifications</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Target Order Qty (P1)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
+        <is>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Operator: TelTech / Converge ICT | Baseline FX: 1 USD = 55.00 PHP | Author: Oliver Tungol</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="76" t="inlineStr">
+        <is>
+          <t>Instructions: Bidders must enter firm unit rates in USD in Column G (highlighted in yellow). PHP equivalents and totals are calculated automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="77" t="inlineStr">
+        <is>
+          <t>Item Ref</t>
+        </is>
+      </c>
+      <c r="B5" s="77" t="inlineStr">
+        <is>
+          <t>Service Title</t>
+        </is>
+      </c>
+      <c r="C5" s="77" t="inlineStr">
+        <is>
+          <t>Detailed Technical Scope &amp; Boundaries</t>
+        </is>
+      </c>
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E5" s="77" t="inlineStr">
+        <is>
+          <t>Phase 1 Qty</t>
+        </is>
+      </c>
+      <c r="F5" s="77" t="inlineStr">
+        <is>
+          <t>Program Qty</t>
+        </is>
+      </c>
+      <c r="G5" s="77" t="inlineStr">
         <is>
           <t>Unit Rate (USD) [Bidder Input]</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Total Phase 1 Cost (USD)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Remarks / Bidder Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>CPE-01</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>Indoor 5G High-Gain FWA Router</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>Band n50 native, &gt;=8.0 dBi internal antenna, Wi-Fi 6 AX1800/AX3000, 1x 2.5GE + 2x 1GE ports, TR-069/TR-369</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E5" s="34" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="36">
-        <f>D5*F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="34" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>CPE-02</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>Outdoor 5G High-Gain FWA Terminal Package</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>Band n50, IP67 enclosure, &gt;=12.0 dBi directional antenna, 1x 2.5GE PoE, bundled indoor Wi-Fi 6 router &amp; PoE injector</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E6" s="34" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="36">
-        <f>D6*F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="34" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>CPE-SVC</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Device Staging, Pre-Configuration &amp; SIM Locking</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>Firmware customization, operator APN &amp; SIM locking, custom retail packaging for all Phase 1 terminals</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="n">
-        <v>365000</v>
-      </c>
-      <c r="E7" s="34" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="36">
-        <f>D7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="34" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL-LOT7</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL 5G CUSTOMER PREMISES EQUIPMENT (CPE)</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>Total Initial Terminal Supply &amp; Staging (365,000 Total Devices)</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>365000</v>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="inlineStr"/>
-      <c r="G8" s="28">
-        <f>SUM(G5:G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>Evaluated Lot 7 Total</t>
-        </is>
-      </c>
+      <c r="H5" s="77" t="inlineStr">
+        <is>
+          <t>Unit Rate (PHP @ 55)</t>
+        </is>
+      </c>
+      <c r="I5" s="77" t="inlineStr">
+        <is>
+          <t>Phase 1 Total (USD)</t>
+        </is>
+      </c>
+      <c r="J5" s="77" t="inlineStr">
+        <is>
+          <t>Program Total (USD)</t>
+        </is>
+      </c>
+      <c r="K5" s="77" t="inlineStr">
+        <is>
+          <t>Billing Milestone Trigger</t>
+        </is>
+      </c>
+      <c r="L5" s="77" t="inlineStr">
+        <is>
+          <t>Deliverable Artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: SITE ACQUISITION &amp; LEGAL PERMITTING</t>
+        </is>
+      </c>
+      <c r="B6" s="89" t="n"/>
+      <c r="C6" s="89" t="n"/>
+      <c r="D6" s="89" t="n"/>
+      <c r="E6" s="89" t="n"/>
+      <c r="F6" s="89" t="n"/>
+      <c r="G6" s="89" t="n"/>
+      <c r="H6" s="89" t="n"/>
+      <c r="I6" s="89" t="n"/>
+      <c r="J6" s="89" t="n"/>
+      <c r="K6" s="89" t="n"/>
+      <c r="L6" s="90" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-01</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>Nominal Search Ring Siting &amp; Candidate Hunting</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>Field identification, screening, and ranking of three (3) viable candidates (Candidate A - Primary, Candidate B - Secondary, Candidate C - Contingency) within the assigned nominal search ring (500m radius for urban/suburban; 1,000m radius for rural). Mandatory spatial screening against audited TowerCo database (13,746 towers) to prioritize Tier 1 co-location. Scope includes visual inspection of antenna mounting feasibility, ground space availability (minimum 2.0m x 2.0m pad), line-of-sight to demand settlement centroid, road access verification (all-weather vs 4x4), and issuance of the Preliminary Candidate Evaluation Report (PCER).
+• Inclusions: Desktop spatial analysis, physical on-ground hunting, 3 candidate identification, GPS logging, PCER compilation.
+• Exclusions: Commercial lease execution (handled by Operator under MLA).</t>
+        </is>
+      </c>
+      <c r="D7" s="80" t="inlineStr">
+        <is>
+          <t>Per Search Ring</t>
+        </is>
+      </c>
+      <c r="E7" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="83" t="n"/>
+      <c r="H7" s="84">
+        <f>G7*55</f>
+        <v/>
+      </c>
+      <c r="I7" s="85">
+        <f>E7*G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="85">
+        <f>F7*G7</f>
+        <v/>
+      </c>
+      <c r="K7" s="81" t="inlineStr">
+        <is>
+          <t>100% upon Operator formal approval of PCER ranking 3 compliant candidates.</t>
+        </is>
+      </c>
+      <c r="L7" s="81" t="inlineStr">
+        <is>
+          <t>Approved Preliminary Candidate Evaluation Report (PCER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-02</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>Detailed Site Acquisition Report (SAR) &amp; Technical Dossier</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>Comprehensive on-ground site acquisition audit and property investigation for the selected primary candidate. Compilation of standardized Site Acquisition Report (SAR) containing: official PSGC code, precision WGS84 GPS coordinates (&gt;= 6 decimal places), ground elevation AMSL, property cadastral boundary sketch, certified land title verification (TCT/OCT/Tax Declaration), lessor profile and contact matrix, preliminary structural condition assessment, preliminary power availability (grid connection point, transformer distance, utility provider), 360-degree panoramic site photos, logistics route access classification, and SAQ risk assessment matrix.
+• Inclusions: On-ground cadastral audit, title verification, lessor interview, 360-deg photo sweep, complete SAR package.
+• Exclusions: Payment of land rental / lease deposits (direct Operator responsibility).</t>
+        </is>
+      </c>
+      <c r="D8" s="80" t="inlineStr">
+        <is>
+          <t>Per Candidate Site</t>
+        </is>
+      </c>
+      <c r="E8" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="83" t="n"/>
+      <c r="H8" s="84">
+        <f>G8*55</f>
+        <v/>
+      </c>
+      <c r="I8" s="85">
+        <f>E8*G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="85">
+        <f>F8*G8</f>
+        <v/>
+      </c>
+      <c r="K8" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal engineering and legal acceptance of the SAR package by Operator.</t>
+        </is>
+      </c>
+      <c r="L8" s="81" t="inlineStr">
+        <is>
+          <t>Comprehensive Site Acquisition Report (SAR) Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-03</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>TowerCo Space Application (SAA) &amp; Technical Dossier Support</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
+• Inclusions: SAA documentation, loading calculation submission, liaison with TowerCo engineering, tracking SAA to NTP.
+• Exclusions: Commercial MLA negotiations and monthly tower rental fees (exclusive Operator responsibility).</t>
+        </is>
+      </c>
+      <c r="D9" s="80" t="inlineStr">
+        <is>
+          <t>Per Co-Location Site</t>
+        </is>
+      </c>
+      <c r="E9" s="82" t="n">
+        <v>897</v>
+      </c>
+      <c r="F9" s="82" t="n">
+        <v>4517</v>
+      </c>
+      <c r="G9" s="83" t="n"/>
+      <c r="H9" s="84">
+        <f>G9*55</f>
+        <v/>
+      </c>
+      <c r="I9" s="85">
+        <f>E9*G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="85">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+      <c r="K9" s="81" t="inlineStr">
+        <is>
+          <t>50% upon SAA submission; 50% upon TowerCo issuance of formal SAA Approval / NTP.</t>
+        </is>
+      </c>
+      <c r="L9" s="81" t="inlineStr">
+        <is>
+          <t>Approved TowerCo SAA &amp; Official Notice to Proceed (NTP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-04</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>Greenfield Land Lease Negotiation &amp; Notarized Contract Support</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>Direct lessor negotiations for greenfield sites: boundary survey coordination, verification of registered ownership (clean title check at Registry of Deeds, inheritance/estate verification, real property tax clearance), negotiation of long-term lease terms (10-15 years) within Operator budgetary caps, preparation of lease annexes, securing lessor spousal consent and IDs, and facilitation of formal contract notarization and annotation on title.
+• Inclusions: Lessor negotiations, title due diligence, boundary verification, notary liaison, lease execution assistance.
+• Exclusions: Actual lease rentals, advance deposits, and title annotation official fees (Operator pays directly).</t>
+        </is>
+      </c>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t>Per Greenfield Site</t>
+        </is>
+      </c>
+      <c r="E10" s="82" t="n">
+        <v>103</v>
+      </c>
+      <c r="F10" s="82" t="n">
+        <v>483</v>
+      </c>
+      <c r="G10" s="83" t="n"/>
+      <c r="H10" s="84">
+        <f>G10*55</f>
+        <v/>
+      </c>
+      <c r="I10" s="85">
+        <f>E10*G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="85">
+        <f>F10*G10</f>
+        <v/>
+      </c>
+      <c r="K10" s="81" t="inlineStr">
+        <is>
+          <t>50% upon mutual execution of Lease Agreement; 50% upon Notarization and Title Annotation.</t>
+        </is>
+      </c>
+      <c r="L10" s="81" t="inlineStr">
+        <is>
+          <t>Executed &amp; Notarized Contract of Lease + Clean Title Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-05</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>Local Community, Barangay &amp; Neighborhood Clearances</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>Securing official local community clearances: presentation to Barangay Council, public hearing facilitation (if mandated), processing and issuance of official Barangay Resolution of Support, Barangay Construction Clearance, and certified Neighborhood / Homeowners Association (HOA) Resolution / Certificate of No Objection from contiguous property owners within a 50-meter radius.
+• Inclusions: Barangay consultations, neighbor signature campaigns, clearance filing and follow-through, official receipts.
+• Exclusions: Official LGU statutory fees (reimbursable at actual cost against official receipts).</t>
+        </is>
+      </c>
+      <c r="D11" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E11" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="83" t="n"/>
+      <c r="H11" s="84">
+        <f>G11*55</f>
+        <v/>
+      </c>
+      <c r="I11" s="85">
+        <f>E11*G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="85">
+        <f>F11*G11</f>
+        <v/>
+      </c>
+      <c r="K11" s="81" t="inlineStr">
+        <is>
+          <t>100% upon issuance of certified Barangay Clearance &amp; HOA No Objection Resolution.</t>
+        </is>
+      </c>
+      <c r="L11" s="81" t="inlineStr">
+        <is>
+          <t>Certified Barangay Clearance &amp; HOA Resolution of No Objection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-06</t>
+        </is>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>Local Government Unit (LGU) Building &amp; Construction Permits</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>Complete processing and procurement of municipal/city LGU Building Permits in accordance with the National Building Code of the Philippines (PD 1096). Scope includes securing Locational Clearance, Zoning Compliance, Architectural Permit, Civil/Structural Permit, Electrical Permit, Sanitary/Plumbing Permit, and Mechanical Permit, backed by complete sets of plans signed and sealed by licensed Professional Engineers (Civil, Structural, Electrical, PEE).
+• Inclusions: Permit application filing, engineering plan liaison, follow-through across city/municipal engineering offices.
+• Exclusions: Official municipal permit assessment fees (reimbursable at face value against official receipts).</t>
+        </is>
+      </c>
+      <c r="D12" s="80" t="inlineStr">
+        <is>
+          <t>Per Greenfield Site / Co-loc where required</t>
+        </is>
+      </c>
+      <c r="E12" s="82" t="n">
+        <v>103</v>
+      </c>
+      <c r="F12" s="82" t="n">
+        <v>483</v>
+      </c>
+      <c r="G12" s="83" t="n"/>
+      <c r="H12" s="84">
+        <f>G12*55</f>
+        <v/>
+      </c>
+      <c r="I12" s="85">
+        <f>E12*G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="85">
+        <f>F12*G12</f>
+        <v/>
+      </c>
+      <c r="K12" s="81" t="inlineStr">
+        <is>
+          <t>100% upon release of official LGU Building Permit and Approved Engineering Plans.</t>
+        </is>
+      </c>
+      <c r="L12" s="81" t="inlineStr">
+        <is>
+          <t>Official LGU Building Permit &amp; Endorsed Blueprints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-07</t>
+        </is>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>Statutory &amp; Environmental Clearances (CAAP, DENR, DPWH)</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>Procurement of mandatory national statutory clearances: Civil Aviation Authority of the Philippines (CAAP) Height Clearance Permit / Obstruction Evaluation; Department of Environment and Natural Resources (DENR) Certificate of Non-Coverage (CNC) or Environmental Compliance Certificate (ECC); and Department of Public Works and Highways (DPWH) Road Right-of-Way (ROW) clearance where site access fronts national highways.
+• Inclusions: Technical submittals, coordinate and elevation certification, CAAP/DENR filing and technical defense.
+• Exclusions: Official statutory assessment fees (reimbursable at actual cost).</t>
+        </is>
+      </c>
+      <c r="D13" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E13" s="82" t="n">
+        <v>103</v>
+      </c>
+      <c r="F13" s="82" t="n">
+        <v>483</v>
+      </c>
+      <c r="G13" s="83" t="n"/>
+      <c r="H13" s="84">
+        <f>G13*55</f>
+        <v/>
+      </c>
+      <c r="I13" s="85">
+        <f>E13*G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="85">
+        <f>F13*G13</f>
+        <v/>
+      </c>
+      <c r="K13" s="81" t="inlineStr">
+        <is>
+          <t>100% upon issuance of official CAAP Height Clearance and DENR CNC/ECC.</t>
+        </is>
+      </c>
+      <c r="L13" s="81" t="inlineStr">
+        <is>
+          <t>Official CAAP Height Clearance Permit &amp; DENR CNC/ECC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>SAQ-08</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>Utility Interconnection, CFEI, FSIC &amp; Occupancy Permitting</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>Securing post-construction occupancy and power clearances: processing Certificate of Final Electrical Inspection (CFEI), Bureau of Fire Protection (BFP) Fire Safety Inspection Certificate (FSIC), commercial power utility (Meralco / Regional Electric Cooperative) service application, transformer tapping coordination, meter base energization, and municipal LGU Certificate of Final Occupancy / Permit to Operate.
+• Inclusions: BFP inspection facilitation, CFEI filing, utility coordination, meter installation liaison, occupancy release.
+• Exclusions: Utility transformer installation capital contribution and security deposits (paid by Operator).</t>
+        </is>
+      </c>
+      <c r="D14" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E14" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G14" s="83" t="n"/>
+      <c r="H14" s="84">
+        <f>G14*55</f>
+        <v/>
+      </c>
+      <c r="I14" s="85">
+        <f>E14*G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="85">
+        <f>F14*G14</f>
+        <v/>
+      </c>
+      <c r="K14" s="81" t="inlineStr">
+        <is>
+          <t>50% upon CFEI/FSIC release; 50% upon commercial grid energization and Occupancy Permit.</t>
+        </is>
+      </c>
+      <c r="L14" s="81" t="inlineStr">
+        <is>
+          <t>CFEI, FSIC, Utility Meter Energization Notice &amp; Certificate of Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: SITE ENGINEERING &amp; DETAILED SITE SURVEY</t>
+        </is>
+      </c>
+      <c r="B15" s="89" t="n"/>
+      <c r="C15" s="89" t="n"/>
+      <c r="D15" s="89" t="n"/>
+      <c r="E15" s="89" t="n"/>
+      <c r="F15" s="89" t="n"/>
+      <c r="G15" s="89" t="n"/>
+      <c r="H15" s="89" t="n"/>
+      <c r="I15" s="89" t="n"/>
+      <c r="J15" s="89" t="n"/>
+      <c r="K15" s="89" t="n"/>
+      <c r="L15" s="90" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="80" t="inlineStr">
+        <is>
+          <t>ENG-01</t>
+        </is>
+      </c>
+      <c r="B16" s="81" t="inlineStr">
+        <is>
+          <t>Technical Site Survey (TSS) &amp; 360° Drone Panoramic Audit</t>
+        </is>
+      </c>
+      <c r="C16" s="81" t="inlineStr">
+        <is>
+          <t>Rigorous multi-disciplinary physical site survey executed by licensed telecom and civil engineers: 360° high-resolution panoramic photographic sweep at target antenna centerline (using calibrated drone or mast camera); precision dual-frequency GPS coordinate recording; physical measurement of compound dimensions, tower base, shelter/cabinet footprint; cable gantry routing audit; transport access route assessment (bridge load limits, tight turning radii); and compilation of raw TSS data.
+• Inclusions: Multi-disciplinary field team, calibrated drone flight, 360-deg panoramic photos, spatial sketches, access log.
+• Exclusions: Tower climbing above 60m (requires separate high-mast specialized rigging permit if applicable).</t>
+        </is>
+      </c>
+      <c r="D16" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F16" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G16" s="83" t="n"/>
+      <c r="H16" s="84">
+        <f>G16*55</f>
+        <v/>
+      </c>
+      <c r="I16" s="85">
+        <f>E16*G16</f>
+        <v/>
+      </c>
+      <c r="J16" s="85">
+        <f>F16*G16</f>
+        <v/>
+      </c>
+      <c r="K16" s="81" t="inlineStr">
+        <is>
+          <t>100% upon completion of field survey and upload of raw survey package and photos.</t>
+        </is>
+      </c>
+      <c r="L16" s="81" t="inlineStr">
+        <is>
+          <t>Raw TSS Survey Package &amp; High-Resolution 360° Panoramic Photo Suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>ENG-02</t>
+        </is>
+      </c>
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>Structural Loading, Wind Stress &amp; Civil Engineering Assessment</t>
+        </is>
+      </c>
+      <c r="C17" s="81" t="inlineStr">
+        <is>
+          <t>Engineering structural evaluation of the proposed host structure (tower, rooftop, or monopole): audit of steel member sections, bracing, gusset plates, anchor bolts, and corrosion condition; calculation of total Effective Projected Area (EPA) and weight for new equipment (3x 8T8R RRU, 3x macro antennas/AAUs, AMB brackets, hybrid cable); structural wind load simulation under TIA-222-H for 250 km/h basic wind speed (Category 5 typhoon standard); foundation capacity verification; and formal structural analysis report certified by a licensed Professional Structural Engineer (PE).
+• Inclusions: Structural audit, EPA calculations, TIA-222-H wind simulation, foundation check, PE sign-off.
+• Exclusions: Tower reinforcement civil execution (governed by separate structural modification call-out rate card).</t>
+        </is>
+      </c>
+      <c r="D17" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E17" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G17" s="83" t="n"/>
+      <c r="H17" s="84">
+        <f>G17*55</f>
+        <v/>
+      </c>
+      <c r="I17" s="85">
+        <f>E17*G17</f>
+        <v/>
+      </c>
+      <c r="J17" s="85">
+        <f>F17*G17</f>
+        <v/>
+      </c>
+      <c r="K17" s="81" t="inlineStr">
+        <is>
+          <t>100% upon submission and acceptance of the PE-Endorsed Structural Analysis Report.</t>
+        </is>
+      </c>
+      <c r="L17" s="81" t="inlineStr">
+        <is>
+          <t>PE-Signed Structural Engineering Analysis &amp; Loading Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>ENG-03</t>
+        </is>
+      </c>
+      <c r="B18" s="81" t="inlineStr">
+        <is>
+          <t>Electrical, DC Power &amp; Earth Grounding Engineering Assessment</t>
+        </is>
+      </c>
+      <c r="C18" s="81" t="inlineStr">
+        <is>
+          <t>Electrical engineering audit of commercial AC utility power and DC power plant: inspection of transformer capacity (kVA), service entrance voltage, phase balance, AC main breaker rating; assessment of existing DC power plant (rectifier total capacity, SMPS controller, available DC branch breakers &gt;= 63A for new radio load); calculation of LiFePO4 battery autonomy (minimum 4.0h @ 3.0 kW load, &lt;= 80% DoD); and 3-point fall-of-potential earth resistance measurement of the grounding grid, mandating &lt;= 5.0 Ohms pursuant to Philippine Electrical Code (PEC) and TelTech engineering specifications.
+• Inclusions: Commercial power audit, DC rectifier capacity calculation, battery autonomy simulation, 3-point earth test.
+• Exclusions: Major utility transformer upgrades (handled under utility capex contribution).</t>
+        </is>
+      </c>
+      <c r="D18" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E18" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F18" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G18" s="83" t="n"/>
+      <c r="H18" s="84">
+        <f>G18*55</f>
+        <v/>
+      </c>
+      <c r="I18" s="85">
+        <f>E18*G18</f>
+        <v/>
+      </c>
+      <c r="J18" s="85">
+        <f>F18*G18</f>
+        <v/>
+      </c>
+      <c r="K18" s="81" t="inlineStr">
+        <is>
+          <t>100% upon Operator acceptance of Electrical &amp; Power Assessment Report.</t>
+        </is>
+      </c>
+      <c r="L18" s="81" t="inlineStr">
+        <is>
+          <t>Electrical, Power &amp; Grounding Engineering Assessment Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>ENG-04</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>RF Engineering Siting, Line-of-Sight (LOS) &amp; Clutter Assessment</t>
+        </is>
+      </c>
+      <c r="C19" s="81" t="inlineStr">
+        <is>
+          <t>On-site RF validation of nominal design coverage over target barangay demand centroid: physical line-of-sight (LOS) inspection at proposed antenna centerlines (30m, 35m, 40m AGL); clutter height and foliage density classification; identification of close-in obstructions within 200m of sector azimuths (0°, 120°, 240°); calculation of first Fresnel zone clearance; and field verification that simulated coverage will achieve target cell-edge RSRP &gt;= -95 dBm and SINR &gt;= 6 dB.
+• Inclusions: On-ground visual LOS audit, clutter verification, azimuth clearance check, RF siting validation report.
+• Exclusions: Continuous cluster drive test (governed under Lot 5 Scope RNO-01).</t>
+        </is>
+      </c>
+      <c r="D19" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E19" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="83" t="n"/>
+      <c r="H19" s="84">
+        <f>G19*55</f>
+        <v/>
+      </c>
+      <c r="I19" s="85">
+        <f>E19*G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="85">
+        <f>F19*G19</f>
+        <v/>
+      </c>
+      <c r="K19" s="81" t="inlineStr">
+        <is>
+          <t>100% upon RF Engineering approval of Siting &amp; LOS Report.</t>
+        </is>
+      </c>
+      <c r="L19" s="81" t="inlineStr">
+        <is>
+          <t>RF Siting &amp; Line-of-Sight (LOS) Clearance Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>ENG-05</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="inlineStr">
+        <is>
+          <t>Detailed Engineering Design (DED) &amp; Technical Site Survey Report (TSSR)</t>
+        </is>
+      </c>
+      <c r="C20" s="81" t="inlineStr">
+        <is>
+          <t>Consolidation of multidisciplinary survey data into a complete Detailed Engineering Design (DED) blueprint package and Technical Site Survey Report (TSSR): Architectural Site Layout Plan; Tower Elevation &amp; Antenna Orientation Plan; Antenna Mounting Bracket (AMB) Fabrication Details; Cable Ladder, Gantry &amp; Cable Tray Routing Plan; Electrical Single Line Diagram (SLD); Earth Grounding Ring &amp; Lightning Protection Layout; Site Bill of Quantities (BoQ); and formal endorsement by licensed Professional Engineers (PE-Civil/Structural, PE-Electrical, PECE-Electronics) conforming to NBCP and PEC.
+• Inclusions: AutoCAD DED drawings, multi-PE signed &amp; sealed plans, BoQ compilation, full TSSR dossier submission.
+• Exclusions: Structural redesigns necessitated by Operator-mandated changes to nominal search ring after survey approval.</t>
+        </is>
+      </c>
+      <c r="D20" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E20" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="83" t="n"/>
+      <c r="H20" s="84">
+        <f>G20*55</f>
+        <v/>
+      </c>
+      <c r="I20" s="85">
+        <f>E20*G20</f>
+        <v/>
+      </c>
+      <c r="J20" s="85">
+        <f>F20*G20</f>
+        <v/>
+      </c>
+      <c r="K20" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal joint Operator-TowerCo TSSR approval.</t>
+        </is>
+      </c>
+      <c r="L20" s="81" t="inlineStr">
+        <is>
+          <t>Approved TSSR Dossier with PE Signed &amp; Sealed CAD Blueprints</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>ENG-06</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>As-Built Engineering Documentation &amp; Final Completion Dossier</t>
+        </is>
+      </c>
+      <c r="C21" s="81" t="inlineStr">
+        <is>
+          <t>Comprehensive post-construction field engineering audit capturing all redline installation adjustments: updating AutoCAD drawings to reflect exact as-built antenna heights, azimuths, mechanical tilts, optical cable routes, rack layouts, breaker allocations, and grounding busbar termination points; compiling comprehensive photographic completion book (minimum 50 high-res timestamped photos per site); and securing final Professional Engineer endorsement.
+• Inclusions: Field redline audit, final CAD as-built drawings (DWG &amp; PDF), photographic completion book, PE endorsement.
+• Exclusions: Routine operational documentation updates post-commercial acceptance.</t>
+        </is>
+      </c>
+      <c r="D21" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E21" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G21" s="83" t="n"/>
+      <c r="H21" s="84">
+        <f>G21*55</f>
+        <v/>
+      </c>
+      <c r="I21" s="85">
+        <f>E21*G21</f>
+        <v/>
+      </c>
+      <c r="J21" s="85">
+        <f>F21*G21</f>
+        <v/>
+      </c>
+      <c r="K21" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal issuance of the Final Acceptance Certificate (FAC).</t>
+        </is>
+      </c>
+      <c r="L21" s="81" t="inlineStr">
+        <is>
+          <t>Final As-Built CAD Drawings (DWG &amp; PDF) + Photographic Completion Book</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: RADIO NETWORK PLANNING &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="B22" s="89" t="n"/>
+      <c r="C22" s="89" t="n"/>
+      <c r="D22" s="89" t="n"/>
+      <c r="E22" s="89" t="n"/>
+      <c r="F22" s="89" t="n"/>
+      <c r="G22" s="89" t="n"/>
+      <c r="H22" s="89" t="n"/>
+      <c r="I22" s="89" t="n"/>
+      <c r="J22" s="89" t="n"/>
+      <c r="K22" s="89" t="n"/>
+      <c r="L22" s="90" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>RNPD-01</t>
+        </is>
+      </c>
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>Macro RF Nominal Planning &amp; 3D Propagation Modeling</t>
+        </is>
+      </c>
+      <c r="C23" s="81" t="inlineStr">
+        <is>
+          <t>Macro-level 5G RF network planning using advanced 3D ray-tracing propagation modeling engines, calibrated against high-resolution 5-meter clutter models and Digital Terrain Models (DTM). Sizing and generation of nominal candidate search rings across high-density suburban and rural barangay centroids; multi-carrier capacity dimensioning for Band n50 (60 MHz NCR / up to 80 MHz Provincial, software-configurable 40/50/60/80 MHz TDD); coverage prediction mapping (RSRP, SINR, Best Server, Downlink/Uplink Throughput); and inter-site distance (ISD) optimization.
+• Inclusions: 3D ray-tracing simulation, clutter model calibration, nominal site planning, search ring generation.
+• Exclusions: Procurement of specialized external digital terrain data licenses (provided by Operator).</t>
+        </is>
+      </c>
+      <c r="D23" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E23" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" s="83" t="n"/>
+      <c r="H23" s="84">
+        <f>G23*55</f>
+        <v/>
+      </c>
+      <c r="I23" s="85">
+        <f>E23*G23</f>
+        <v/>
+      </c>
+      <c r="J23" s="85">
+        <f>F23*G23</f>
+        <v/>
+      </c>
+      <c r="K23" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal Operator approval of the Nominal RF Network Design Package.</t>
+        </is>
+      </c>
+      <c r="L23" s="81" t="inlineStr">
+        <is>
+          <t>Nominal RF Network Design Package &amp; Ray-Tracing Simulation Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>RNPD-02</t>
+        </is>
+      </c>
+      <c r="B24" s="81" t="inlineStr">
+        <is>
+          <t>Cell Design Data (CDD) Engineering &amp; Parameter Allocation</t>
+        </is>
+      </c>
+      <c r="C24" s="81" t="inlineStr">
+        <is>
+          <t>Engineering, generation, and validation of detailed site-specific Cell Design Data (CDD) sheets: cell naming taxonomy, gNodeB IDs, Physical Cell ID (PCI) planning adhering to modulo-3 and modulo-30 collision rules, Root Sequence Index (RSI), Tracking Area Codes (TAC), Neighbor Cell Lists (NCL / ANR), PRACH configuration, absolute radio-frequency channel numbers (ARFCN), per-carrier transmit power, and antenna configuration parameters (azimuth, mechanical tilt, eRET ranges).
+• Inclusions: CDD parameter engineering, PCI planning, neighbor list generation, configuration script generation.
+• Exclusions: Core network routing configuration (handled under Lot 3).</t>
+        </is>
+      </c>
+      <c r="D24" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E24" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="83" t="n"/>
+      <c r="H24" s="84">
+        <f>G24*55</f>
+        <v/>
+      </c>
+      <c r="I24" s="85">
+        <f>E24*G24</f>
+        <v/>
+      </c>
+      <c r="J24" s="85">
+        <f>F24*G24</f>
+        <v/>
+      </c>
+      <c r="K24" s="81" t="inlineStr">
+        <is>
+          <t>100% upon validation and successful upload of CDD parameters into the network EMS/OSS.</t>
+        </is>
+      </c>
+      <c r="L24" s="81" t="inlineStr">
+        <is>
+          <t>Approved Cell Design Data (CDD) Sheet &amp; Parameter Script</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: TELECOM LOGISTICS &amp; MATERIAL HANDLING</t>
+        </is>
+      </c>
+      <c r="B25" s="89" t="n"/>
+      <c r="C25" s="89" t="n"/>
+      <c r="D25" s="89" t="n"/>
+      <c r="E25" s="89" t="n"/>
+      <c r="F25" s="89" t="n"/>
+      <c r="G25" s="89" t="n"/>
+      <c r="H25" s="89" t="n"/>
+      <c r="I25" s="89" t="n"/>
+      <c r="J25" s="89" t="n"/>
+      <c r="K25" s="89" t="n"/>
+      <c r="L25" s="90" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>LOG-01</t>
+        </is>
+      </c>
+      <c r="B26" s="81" t="inlineStr">
+        <is>
+          <t>Central &amp; Regional Warehousing, Buffer Staging &amp; Serialized Asset Tagging</t>
+        </is>
+      </c>
+      <c r="C26" s="81" t="inlineStr">
+        <is>
+          <t>Receipt of OEM shipments at Port of Manila / Batangas; bonded climate-controlled warehousing in central Mega Manila and regional hubs (North Luzon, South Luzon, Visayas, Mindanao); unboxing, physical inspection, and QA damage checking; barcode asset tagging at serial-number level; updating Operator ERP/WMS inventory records; and maintaining segregated buffer stock.
+• Inclusions: Warehouse facility, security, ERP tracking, barcode tagging, climate control, buffer stock management.
+• Exclusions: Port customs duties and VAT taxes (direct Operator responsibility).</t>
+        </is>
+      </c>
+      <c r="D26" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E26" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G26" s="83" t="n"/>
+      <c r="H26" s="84">
+        <f>G26*55</f>
+        <v/>
+      </c>
+      <c r="I26" s="85">
+        <f>E26*G26</f>
+        <v/>
+      </c>
+      <c r="J26" s="85">
+        <f>F26*G26</f>
+        <v/>
+      </c>
+      <c r="K26" s="81" t="inlineStr">
+        <is>
+          <t>100% upon material receipt, inspection, and barcode registration into inventory ERP.</t>
+        </is>
+      </c>
+      <c r="L26" s="81" t="inlineStr">
+        <is>
+          <t>Serialized Inventory Receiving Report &amp; Barcode Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="80" t="inlineStr">
+        <is>
+          <t>LOG-02</t>
+        </is>
+      </c>
+      <c r="B27" s="81" t="inlineStr">
+        <is>
+          <t>Site BOM Kitting, Staging &amp; Pre-Assembly Services</t>
+        </is>
+      </c>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
+          <t>Assembly and kitting of site-specific deployment packages: picking 1x BBU, 3x 8T8R RRUs, 3x macro antennas/AAUs, optical patchcords, DC power cables, Type 2 SPDs, grounding kits, and hardware accessories; pre-cutting cable lengths based on approved TSSR; labeling; staging in protective crates; and performing bench test pre-checks and firmware pre-flashing.
+• Inclusions: Picking, staging, pre-cutting cables, labeling, firmware pre-flashing, packaging into site kits.
+• Exclusions: Supply of missing OEM radio equipment (OEM responsibility).</t>
+        </is>
+      </c>
+      <c r="D27" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E27" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G27" s="83" t="n"/>
+      <c r="H27" s="84">
+        <f>G27*55</f>
+        <v/>
+      </c>
+      <c r="I27" s="85">
+        <f>E27*G27</f>
+        <v/>
+      </c>
+      <c r="J27" s="85">
+        <f>F27*G27</f>
+        <v/>
+      </c>
+      <c r="K27" s="81" t="inlineStr">
+        <is>
+          <t>100% upon staging and issuance of Site Dispatch Slip.</t>
+        </is>
+      </c>
+      <c r="L27" s="81" t="inlineStr">
+        <is>
+          <t>Site BOM Kitting Slip &amp; Staging Inspection Checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="80" t="inlineStr">
+        <is>
+          <t>LOG-03</t>
+        </is>
+      </c>
+      <c r="B28" s="81" t="inlineStr">
+        <is>
+          <t>Regional Transport &amp; Final-Mile Rough-Road Site Hauling</t>
+        </is>
+      </c>
+      <c r="C28" s="81" t="inlineStr">
+        <is>
+          <t>Transportation from central warehouse to regional hubs via heavy freight, followed by dedicated final-mile transport to remote barangay site locations utilizing heavy-duty 4x4 trucks, motorized bancas/barges (for island sites), or manual porterage across unpaved rough-road terrain; comprehensive in-transit cargo insurance; and on-site offloading.
+• Inclusions: Long-haul freight, final-mile 4x4 hauling, manual porterage, transit insurance, on-site offloading.
+• Exclusions: Helicopter airlifts (applicable only under extraordinary force majeure call-out).</t>
+        </is>
+      </c>
+      <c r="D28" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E28" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F28" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G28" s="83" t="n"/>
+      <c r="H28" s="84">
+        <f>G28*55</f>
+        <v/>
+      </c>
+      <c r="I28" s="85">
+        <f>E28*G28</f>
+        <v/>
+      </c>
+      <c r="J28" s="85">
+        <f>F28*G28</f>
+        <v/>
+      </c>
+      <c r="K28" s="81" t="inlineStr">
+        <is>
+          <t>100% upon verified on-site delivery and execution of Material Receiving Report (MRR).</t>
+        </is>
+      </c>
+      <c r="L28" s="81" t="inlineStr">
+        <is>
+          <t>Signed Material Receiving Report (MRR) by on-site supervisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: TELECOM INSTALLATION, COMMISSIONING &amp; INTEGRATION</t>
+        </is>
+      </c>
+      <c r="B29" s="89" t="n"/>
+      <c r="C29" s="89" t="n"/>
+      <c r="D29" s="89" t="n"/>
+      <c r="E29" s="89" t="n"/>
+      <c r="F29" s="89" t="n"/>
+      <c r="G29" s="89" t="n"/>
+      <c r="H29" s="89" t="n"/>
+      <c r="I29" s="89" t="n"/>
+      <c r="J29" s="89" t="n"/>
+      <c r="K29" s="89" t="n"/>
+      <c r="L29" s="90" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="80" t="inlineStr">
+        <is>
+          <t>TI-01</t>
+        </is>
+      </c>
+      <c r="B30" s="81" t="inlineStr">
+        <is>
+          <t>Tower Rigging &amp; Mechanical Antenna / RRU Installation</t>
+        </is>
+      </c>
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>Mechanical mounting by certified riggers: hoisting and installing 3x macro high-gain antennas and 3x 8T8R RRUs on tower antenna mounting brackets (AMB) at specified AGL centerlines (30m to 45m); setting precise mechanical downtilt and sector azimuths (0°, 120°, 240°) using calibrated digital inclinometers and compasses; and installing AISG 2.0 eRET control cables.
+• Inclusions: Tower rigging crews, safety equipment, hoisting gear, AMB mounting, antenna and RRU installation.
+• Exclusions: Supply of steel antenna mounting brackets (AMB) (governed under Lot 1 hardware).</t>
+        </is>
+      </c>
+      <c r="D30" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E30" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G30" s="83" t="n"/>
+      <c r="H30" s="84">
+        <f>G30*55</f>
+        <v/>
+      </c>
+      <c r="I30" s="85">
+        <f>E30*G30</f>
+        <v/>
+      </c>
+      <c r="J30" s="85">
+        <f>F30*G30</f>
+        <v/>
+      </c>
+      <c r="K30" s="81" t="inlineStr">
+        <is>
+          <t>50% upon mechanical mounting completion; 50% upon joint rigging inspection.</t>
+        </is>
+      </c>
+      <c r="L30" s="81" t="inlineStr">
+        <is>
+          <t>Mechanical Rigging &amp; Antenna Alignment Inspection Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="80" t="inlineStr">
+        <is>
+          <t>TI-02</t>
+        </is>
+      </c>
+      <c r="B31" s="81" t="inlineStr">
+        <is>
+          <t>RF, Optical Fiber &amp; DC Power Cabling Installation</t>
+        </is>
+      </c>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>Routing, fastening, and dressing armored multi-core optical fiber jumpers and DC power cables along tower cable ladders and horizontal gantries; installing cold-shrink weatherproof boots on all 7/16 DIN or 4.3-10 RF connectors; installing Type 2 DC Surge Protection Devices (SPD) at tower top and base; and bonding 3-point grounding kits to the external ground busbar.
+• Inclusions: Cable routing, cleating, hydraulic crimping, weatherproofing, SPD installation, grounding bond.
+• Exclusions: Internal civil cabling of third-party shelters.</t>
+        </is>
+      </c>
+      <c r="D31" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E31" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G31" s="83" t="n"/>
+      <c r="H31" s="84">
+        <f>G31*55</f>
+        <v/>
+      </c>
+      <c r="I31" s="85">
+        <f>E31*G31</f>
+        <v/>
+      </c>
+      <c r="J31" s="85">
+        <f>F31*G31</f>
+        <v/>
+      </c>
+      <c r="K31" s="81" t="inlineStr">
+        <is>
+          <t>50% upon cabling installation; 50% upon weatherproofing and grounding sign-off.</t>
+        </is>
+      </c>
+      <c r="L31" s="81" t="inlineStr">
+        <is>
+          <t>Cabling Installation &amp; Weatherproofing Quality Checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="80" t="inlineStr">
+        <is>
+          <t>TI-03</t>
+        </is>
+      </c>
+      <c r="B32" s="81" t="inlineStr">
+        <is>
+          <t>Baseband Unit (BBU) Installation &amp; Cabinet Wiring</t>
+        </is>
+      </c>
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>19" rack installation of 5G Baseband Unit (BBU) in outdoor equipment cabinet or shelter; dual -48V DC power wiring to dedicated distribution breakers; routing backhaul transmission optical patchcords to fiber demarcation router; and installing GNSS/GPS antenna and surge arrester with unobstructed sky view for PTP/SyncE clock synchronization.
+• Inclusions: Rack mounting, DC wiring, optical patchcord routing, GPS antenna installation, labeling.
+• Exclusions: Supply of DC rectifier plant (governed under Lot 2).</t>
+        </is>
+      </c>
+      <c r="D32" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E32" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G32" s="83" t="n"/>
+      <c r="H32" s="84">
+        <f>G32*55</f>
+        <v/>
+      </c>
+      <c r="I32" s="85">
+        <f>E32*G32</f>
+        <v/>
+      </c>
+      <c r="J32" s="85">
+        <f>F32*G32</f>
+        <v/>
+      </c>
+      <c r="K32" s="81" t="inlineStr">
+        <is>
+          <t>100% upon BBU rack installation and DC power-up.</t>
+        </is>
+      </c>
+      <c r="L32" s="81" t="inlineStr">
+        <is>
+          <t>BBU Installation &amp; Cabinet Wiring Verification Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="80" t="inlineStr">
+        <is>
+          <t>TI-04</t>
+        </is>
+      </c>
+      <c r="B33" s="81" t="inlineStr">
+        <is>
+          <t>Telecom Commissioning, Sweep Testing &amp; Power-Up</t>
+        </is>
+      </c>
+      <c r="C33" s="81" t="inlineStr">
+        <is>
+          <t>DC power turn-up, voltage and polarity verification; firmware loading and diagnostic testing; optical transceiver Rx/Tx power level verification; and calibrated RF sweep testing measuring Return Loss (&gt;= 16.5 dB) and VSWR (&lt;= 1.35:1) across all antenna ports and jumpers using a calibrated SiteMaster analyzer.
+• Inclusions: Commissioning turn-up, firmware loading, optical power check, VSWR sweep testing, test trace logs.
+• Exclusions: Rectification of OEM internal hardware manufacturing defects (OEM warranty scope).</t>
+        </is>
+      </c>
+      <c r="D33" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E33" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G33" s="83" t="n"/>
+      <c r="H33" s="84">
+        <f>G33*55</f>
+        <v/>
+      </c>
+      <c r="I33" s="85">
+        <f>E33*G33</f>
+        <v/>
+      </c>
+      <c r="J33" s="85">
+        <f>F33*G33</f>
+        <v/>
+      </c>
+      <c r="K33" s="81" t="inlineStr">
+        <is>
+          <t>100% upon successful sweep testing and commissioning approval.</t>
+        </is>
+      </c>
+      <c r="L33" s="81" t="inlineStr">
+        <is>
+          <t>Commissioning Test Log &amp; VSWR/Return Loss Sweep Traces</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="80" t="inlineStr">
+        <is>
+          <t>TI-05</t>
+        </is>
+      </c>
+      <c r="B34" s="81" t="inlineStr">
+        <is>
+          <t>gNodeB Network Integration &amp; OSS Commercial On-Air</t>
+        </is>
+      </c>
+      <c r="C34" s="81" t="inlineStr">
+        <is>
+          <t>Transmission IP integration (VLAN, BGP, IPsec); establishing S1-U / N2/N3 control and user plane interfaces to 5G Core (AMF/UPF); synchronization with TelTech EMS/OSS; activating 3 sectors on Band n50 (60 MHz NCR / up to 80 MHz Provincial, software-configurable 40/50/60/80 MHz TDD); clearing all active alarms; and achieving stable commercial on-air operational state.
+• Inclusions: IP configuration, Core integration, OSS synchronization, carrier activation, alarm clearance.
+• Exclusions: Core network UPF dimensioning (governed under Lot 3).</t>
+        </is>
+      </c>
+      <c r="D34" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E34" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G34" s="83" t="n"/>
+      <c r="H34" s="84">
+        <f>G34*55</f>
+        <v/>
+      </c>
+      <c r="I34" s="85">
+        <f>E34*G34</f>
+        <v/>
+      </c>
+      <c r="J34" s="85">
+        <f>F34*G34</f>
+        <v/>
+      </c>
+      <c r="K34" s="81" t="inlineStr">
+        <is>
+          <t>100% upon site on-air declaration and alarm-free verification.</t>
+        </is>
+      </c>
+      <c r="L34" s="81" t="inlineStr">
+        <is>
+          <t>Commercial On-Air Certificate &amp; OSS Alarm-Free Screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: SINGLE SITE VERIFICATION &amp; ACCEPTANCE</t>
+        </is>
+      </c>
+      <c r="B35" s="89" t="n"/>
+      <c r="C35" s="89" t="n"/>
+      <c r="D35" s="89" t="n"/>
+      <c r="E35" s="89" t="n"/>
+      <c r="F35" s="89" t="n"/>
+      <c r="G35" s="89" t="n"/>
+      <c r="H35" s="89" t="n"/>
+      <c r="I35" s="89" t="n"/>
+      <c r="J35" s="89" t="n"/>
+      <c r="K35" s="89" t="n"/>
+      <c r="L35" s="90" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="80" t="inlineStr">
+        <is>
+          <t>ACC-01</t>
+        </is>
+      </c>
+      <c r="B36" s="81" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; Electrical Site Acceptance (ATP-A)</t>
+        </is>
+      </c>
+      <c r="C36" s="81" t="inlineStr">
+        <is>
+          <t>Joint physical on-site inspection: verifying bolt torque marks on tower mounts, cable ladder fastening, cable tray grounding, weatherproofing seal integrity, electrical breaker labeling, 3-point earth ground resistance audit (confirming &lt;= 5.0 Ohms), compound housekeeping, and punchlist compilation and clearance.
+• Inclusions: Joint physical audit, torque inspection, grounding verification, punchlist clearance.
+• Exclusions: Radio performance verification (covered under ATP-B and SSV).</t>
+        </is>
+      </c>
+      <c r="D36" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E36" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F36" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G36" s="83" t="n"/>
+      <c r="H36" s="84">
+        <f>G36*55</f>
+        <v/>
+      </c>
+      <c r="I36" s="85">
+        <f>E36*G36</f>
+        <v/>
+      </c>
+      <c r="J36" s="85">
+        <f>F36*G36</f>
+        <v/>
+      </c>
+      <c r="K36" s="81" t="inlineStr">
+        <is>
+          <t>100% upon joint ATP-A punchlist clearance and sign-off.</t>
+        </is>
+      </c>
+      <c r="L36" s="81" t="inlineStr">
+        <is>
+          <t>Signed ATP-A Certificate &amp; Punchlist Clearance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="80" t="inlineStr">
+        <is>
+          <t>ACC-02</t>
+        </is>
+      </c>
+      <c r="B37" s="81" t="inlineStr">
+        <is>
+          <t>Active Telecom &amp; Functional Acceptance (ATP-B)</t>
+        </is>
+      </c>
+      <c r="C37" s="81" t="inlineStr">
+        <is>
+          <t>Remote and local active functional testing: verifying 8T8R MU-MIMO operation, electronic downtilt (eRET) remote control functionality via OSS, power fail / mains failure alarm simulation, optical fiber failover test, and carrier shutdown/restart diagnostic tests to ensure robust autonomic operation.
+• Inclusions: Remote EMS diagnostic testing, alarm simulation, eRET control validation, MIMO verification.
+• Exclusions: Physical climbing inspection (covered under ATP-A).</t>
+        </is>
+      </c>
+      <c r="D37" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E37" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F37" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G37" s="83" t="n"/>
+      <c r="H37" s="84">
+        <f>G37*55</f>
+        <v/>
+      </c>
+      <c r="I37" s="85">
+        <f>E37*G37</f>
+        <v/>
+      </c>
+      <c r="J37" s="85">
+        <f>F37*G37</f>
+        <v/>
+      </c>
+      <c r="K37" s="81" t="inlineStr">
+        <is>
+          <t>100% upon joint ATP-B sign-off.</t>
+        </is>
+      </c>
+      <c r="L37" s="81" t="inlineStr">
+        <is>
+          <t>Signed ATP-B Functional Acceptance Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="80" t="inlineStr">
+        <is>
+          <t>ACC-03</t>
+        </is>
+      </c>
+      <c r="B38" s="81" t="inlineStr">
+        <is>
+          <t>Single Site Verification (SSV) &amp; RF Call Testing</t>
+        </is>
+      </c>
+      <c r="C38" s="81" t="inlineStr">
+        <is>
+          <t>On-ground field testing using 5G test UE and scanner: stationary throughput tests at near, mid, and cell-edge points per sector (validating &gt;= 450 Mbps peak DL, &gt;= 50 Mbps cell-edge DL, &gt;= 15 Mbps cell-edge UL); sector swap validation; intra-site handover execution; latency measurement (&lt;= 18 ms RTT); and compilation and sign-off of the formal SSV Report.
+• Inclusions: Stationary throughput tests, sector swap check, handover test, ping test, SSV report compilation.
+• Exclusions: Multi-site cluster drive testing (covered under Category 7).</t>
+        </is>
+      </c>
+      <c r="D38" s="80" t="inlineStr">
+        <is>
+          <t>Per Site</t>
+        </is>
+      </c>
+      <c r="E38" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F38" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G38" s="83" t="n"/>
+      <c r="H38" s="84">
+        <f>G38*55</f>
+        <v/>
+      </c>
+      <c r="I38" s="85">
+        <f>E38*G38</f>
+        <v/>
+      </c>
+      <c r="J38" s="85">
+        <f>F38*G38</f>
+        <v/>
+      </c>
+      <c r="K38" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal SSV Report approval by Operator.</t>
+        </is>
+      </c>
+      <c r="L38" s="81" t="inlineStr">
+        <is>
+          <t>Approved Single Site Verification (SSV) Report &amp; Log Files</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: CLUSTER RADIO NETWORK OPTIMIZATION</t>
+        </is>
+      </c>
+      <c r="B39" s="89" t="n"/>
+      <c r="C39" s="89" t="n"/>
+      <c r="D39" s="89" t="n"/>
+      <c r="E39" s="89" t="n"/>
+      <c r="F39" s="89" t="n"/>
+      <c r="G39" s="89" t="n"/>
+      <c r="H39" s="89" t="n"/>
+      <c r="I39" s="89" t="n"/>
+      <c r="J39" s="89" t="n"/>
+      <c r="K39" s="89" t="n"/>
+      <c r="L39" s="90" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="80" t="inlineStr">
+        <is>
+          <t>RNO-01</t>
+        </is>
+      </c>
+      <c r="B40" s="81" t="inlineStr">
+        <is>
+          <t>Pre-Launch Cluster Drive Testing &amp; RF Baseline Audit</t>
+        </is>
+      </c>
+      <c r="C40" s="81" t="inlineStr">
+        <is>
+          <t>Continuous scanner and test UE drive testing across contiguous clusters of 10–20 sites; capturing RSRP, SINR, CQI, throughput, and coverage overlap; and identifying pilot pollution zones, coverage holes, and excessive inter-cell interference.
+• Inclusions: Drive test vehicle, scanner, test UEs, GPS logging, drive test raw log processing, baseline report.
+• Exclusions: Physical antenna re-orientation (governed under RNO-02).</t>
+        </is>
+      </c>
+      <c r="D40" s="80" t="inlineStr">
+        <is>
+          <t>Per Site Share (or Per Cluster)</t>
+        </is>
+      </c>
+      <c r="E40" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G40" s="83" t="n"/>
+      <c r="H40" s="84">
+        <f>G40*55</f>
+        <v/>
+      </c>
+      <c r="I40" s="85">
+        <f>E40*G40</f>
+        <v/>
+      </c>
+      <c r="J40" s="85">
+        <f>F40*G40</f>
+        <v/>
+      </c>
+      <c r="K40" s="81" t="inlineStr">
+        <is>
+          <t>50% upon completion of cluster drive test and baseline report submission.</t>
+        </is>
+      </c>
+      <c r="L40" s="81" t="inlineStr">
+        <is>
+          <t>Cluster Drive Test Raw Logs &amp; RF Baseline Audit Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>RNO-02</t>
+        </is>
+      </c>
+      <c r="B41" s="81" t="inlineStr">
+        <is>
+          <t>Cluster Physical &amp; Soft Parameter Optimization</t>
+        </is>
+      </c>
+      <c r="C41" s="81" t="inlineStr">
+        <is>
+          <t>Iterative optimization across cluster: electronic remote electrical tilt (eRET) adjustments to control cell-edge interference and shape coverage; azimuth and mechanical tilt adjustments where indicated; PCI re-planning to resolve mod-3/mod-30 clashes; neighbor list (NCL) cleanup; handover threshold tuning; and uplink power control adjustments.
+• Inclusions: eRET tuning, PCI re-planning, neighbor tuning, handover optimization, parameter upload script.
+• Exclusions: Major tower antenna re-heightening (governed by call-out rate card).</t>
+        </is>
+      </c>
+      <c r="D41" s="80" t="inlineStr">
+        <is>
+          <t>Per Site Share (or Per Cluster)</t>
+        </is>
+      </c>
+      <c r="E41" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G41" s="83" t="n"/>
+      <c r="H41" s="84">
+        <f>G41*55</f>
+        <v/>
+      </c>
+      <c r="I41" s="85">
+        <f>E41*G41</f>
+        <v/>
+      </c>
+      <c r="J41" s="85">
+        <f>F41*G41</f>
+        <v/>
+      </c>
+      <c r="K41" s="81" t="inlineStr">
+        <is>
+          <t>50% upon parameter implementation and verification in OSS.</t>
+        </is>
+      </c>
+      <c r="L41" s="81" t="inlineStr">
+        <is>
+          <t>Cluster Parameter Optimization Record &amp; Delta Script</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="80" t="inlineStr">
+        <is>
+          <t>RNO-03</t>
+        </is>
+      </c>
+      <c r="B42" s="81" t="inlineStr">
+        <is>
+          <t>Cluster Acceptance KPI Validation &amp; Final Sign-Off</t>
+        </is>
+      </c>
+      <c r="C42" s="81" t="inlineStr">
+        <is>
+          <t>Post-tuning verification drive test and OSS 14-day statistical performance audit: validating cluster Radio Availability &gt;= 99.95%, Session Setup Success Rate (CSSR) &gt;= 99.60%, Session Drop Rate (CDDR) &lt;= 0.15%, cluster average DL throughput &gt;= 450 Mbps, cell-edge DL &gt;= 50 Mbps; and submission of formal Cluster Acceptance Dossier.
+• Inclusions: Verification drive test, 14-day OSS KPI statistical audit, benchmark reporting, formal sign-off.
+• Exclusions: Ongoing post-commercial operations optimization (covered under Lot 6 Managed Services).</t>
+        </is>
+      </c>
+      <c r="D42" s="80" t="inlineStr">
+        <is>
+          <t>Per Cluster (65 Clusters Phase 1 / 325 Clusters Program)</t>
+        </is>
+      </c>
+      <c r="E42" s="82" t="n">
+        <v>65</v>
+      </c>
+      <c r="F42" s="82" t="n">
+        <v>325</v>
+      </c>
+      <c r="G42" s="83" t="n"/>
+      <c r="H42" s="84">
+        <f>G42*55</f>
+        <v/>
+      </c>
+      <c r="I42" s="85">
+        <f>E42*G42</f>
+        <v/>
+      </c>
+      <c r="J42" s="85">
+        <f>F42*G42</f>
+        <v/>
+      </c>
+      <c r="K42" s="81" t="inlineStr">
+        <is>
+          <t>100% upon formal sign-off of Cluster Acceptance Certificate.</t>
+        </is>
+      </c>
+      <c r="L42" s="81" t="inlineStr">
+        <is>
+          <t>Approved Cluster Acceptance Certificate &amp; 14-Day KPI Audit Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: OPERATIONS &amp; MAINTENANCE (O&amp;M) / MANAGED SERVICES</t>
+        </is>
+      </c>
+      <c r="B43" s="89" t="n"/>
+      <c r="C43" s="89" t="n"/>
+      <c r="D43" s="89" t="n"/>
+      <c r="E43" s="89" t="n"/>
+      <c r="F43" s="89" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="89" t="n"/>
+      <c r="I43" s="89" t="n"/>
+      <c r="J43" s="89" t="n"/>
+      <c r="K43" s="89" t="n"/>
+      <c r="L43" s="90" t="n"/>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="80" t="inlineStr">
+        <is>
+          <t>MS-NOC-01</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="inlineStr">
+        <is>
+          <t>24/7/365 Central NOC Tier-1 Active Surveillance &amp; Alarm Monitoring</t>
+        </is>
+      </c>
+      <c r="C44" s="81" t="inlineStr">
+        <is>
+          <t>Continuous 24/7/365 active monitoring of all active and passive network elements across RAN, Core, Power, and Transmission; automated alarm correlation and noise suppression; ticket logging within 5 minutes of alarm onset; and issuance of Daily Operational Flash Report at 06:00 PHT.
+• Inclusions: 24/7 Tier-1 NOC staffing, automated correlation, trouble ticket creation, daily flash reporting.
+• Exclusions: Third-party commercial power utility outages outside contractor control (tracked as excusable SLA).</t>
+        </is>
+      </c>
+      <c r="D44" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E44" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G44" s="83" t="n"/>
+      <c r="H44" s="84">
+        <f>G44*55</f>
+        <v/>
+      </c>
+      <c r="I44" s="85">
+        <f>E44*G44</f>
+        <v/>
+      </c>
+      <c r="J44" s="85">
+        <f>F44*G44</f>
+        <v/>
+      </c>
+      <c r="K44" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears upon SLA performance certification.</t>
+        </is>
+      </c>
+      <c r="L44" s="81" t="inlineStr">
+        <is>
+          <t>Daily Flash Reports, Monthly NOC Surveillance Dossier &amp; Availability Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="80" t="inlineStr">
+        <is>
+          <t>MS-NOC-02</t>
+        </is>
+      </c>
+      <c r="B45" s="81" t="inlineStr">
+        <is>
+          <t>Incident Management, Triage &amp; Automated Trouble Ticketing</t>
+        </is>
+      </c>
+      <c r="C45" s="81" t="inlineStr">
+        <is>
+          <t>End-to-end incident management: automated ticketing via OSS/ITSM; severity classification (Sev 1 Critical to Sev 4 Warning); technician dispatch initiation within 15 minutes for Sev 1 incidents; bridge coordination; and stakeholder notification.
+• Inclusions: ITSM platform, ticket lifecycle tracking, escalation dispatch, MTTR SLA auditing.
+• Exclusions: Operator customer service call center operations (BSS scope).</t>
+        </is>
+      </c>
+      <c r="D45" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E45" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G45" s="83" t="n"/>
+      <c r="H45" s="84">
+        <f>G45*55</f>
+        <v/>
+      </c>
+      <c r="I45" s="85">
+        <f>E45*G45</f>
+        <v/>
+      </c>
+      <c r="J45" s="85">
+        <f>F45*G45</f>
+        <v/>
+      </c>
+      <c r="K45" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L45" s="81" t="inlineStr">
+        <is>
+          <t>Monthly Trouble Ticket Log, MTTR Audit &amp; Dispatch Statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="80" t="inlineStr">
+        <is>
+          <t>MS-NOC-03</t>
+        </is>
+      </c>
+      <c r="B46" s="81" t="inlineStr">
+        <is>
+          <t>Tier-2 Remote Technical Diagnostics, Fault Recovery &amp; Config Management</t>
+        </is>
+      </c>
+      <c r="C46" s="81" t="inlineStr">
+        <is>
+          <t>24/7 remote engineering support: soft and hard resets, remote diagnostic sweeps, card re-initialization, backup configuration restoration, transmission routing failover, and software rollback to clear network faults without field truck rolls.
+• Inclusions: Tier-2 remote engineers, remote script execution, transmission path failover, config restoration.
+• Exclusions: Physical on-site hardware replacement (covered under FLM).</t>
+        </is>
+      </c>
+      <c r="D46" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E46" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G46" s="83" t="n"/>
+      <c r="H46" s="84">
+        <f>G46*55</f>
+        <v/>
+      </c>
+      <c r="I46" s="85">
+        <f>E46*G46</f>
+        <v/>
+      </c>
+      <c r="J46" s="85">
+        <f>F46*G46</f>
+        <v/>
+      </c>
+      <c r="K46" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L46" s="81" t="inlineStr">
+        <is>
+          <t>Remote Fault Resolution Log &amp; Configuration Change Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="80" t="inlineStr">
+        <is>
+          <t>MS-NOC-04</t>
+        </is>
+      </c>
+      <c r="B47" s="81" t="inlineStr">
+        <is>
+          <t>Tier-3 Engineering Escalation &amp; OEM TAC Management</t>
+        </is>
+      </c>
+      <c r="C47" s="81" t="inlineStr">
+        <is>
+          <t>Advanced engineering escalation for complex system bugs, protocol crashes, and persistent hardware/software anomalies: case logging with OEM TAC (Level 3), trace log collection, bug patch testing, software patch deployment, and Root Cause Analysis (RCA) reporting within 24 hours of major incident restoration.
+• Inclusions: OEM TAC case management, trace capture, patch verification, RCA report compilation.
+• Exclusions: OEM base software annual license royalties (governed under Software AMC).</t>
+        </is>
+      </c>
+      <c r="D47" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E47" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G47" s="83" t="n"/>
+      <c r="H47" s="84">
+        <f>G47*55</f>
+        <v/>
+      </c>
+      <c r="I47" s="85">
+        <f>E47*G47</f>
+        <v/>
+      </c>
+      <c r="J47" s="85">
+        <f>F47*G47</f>
+        <v/>
+      </c>
+      <c r="K47" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L47" s="81" t="inlineStr">
+        <is>
+          <t>Formal Root Cause Analysis (RCA) Reports &amp; OEM TAC Case Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="80" t="inlineStr">
+        <is>
+          <t>MS-FLM-01</t>
+        </is>
+      </c>
+      <c r="B48" s="81" t="inlineStr">
+        <is>
+          <t>24/7 Field First Line Maintenance (FLM) Emergency Response</t>
+        </is>
+      </c>
+      <c r="C48" s="81" t="inlineStr">
+        <is>
+          <t>Provision of dedicated, nationwide 24/7 mobile field maintenance crews equipped with 4x4 vehicles, complete safety gear, calibrated test instruments, and emergency restoration tools. Strict compliance with mandated MTTR SLAs: Severity 1 (Critical - Site Outage): Response &lt;= 15 mins, MTTR &lt;= 2.0h (Urban) / &lt;= 4.0h (Rural); Severity 2 (Major - Sector Down / Power Degraded): Response &lt;= 30 mins, MTTR &lt;= 4.0h (Urban) / &lt;= 6.0h (Rural); Severity 3 (Minor - Non-Service Affecting): Response &lt;= 1h, MTTR &lt;= 12.0h (Urban) / &lt;= 24.0h (Rural); Severity 4 (Warning / Planned): Response &lt;= 4h, MTTR &lt;= 48.0h (Urban) / &lt;= 72.0h (Rural).
+• Inclusions: Dedicated 24/7 crews, 4x4 maintenance vehicles, tools, fuel, emergency call-outs.
+• Exclusions: Force majeure acts of God (typhoon damage recovery governed under Call-Out Rate Card).</t>
+        </is>
+      </c>
+      <c r="D48" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E48" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G48" s="83" t="n"/>
+      <c r="H48" s="84">
+        <f>G48*55</f>
+        <v/>
+      </c>
+      <c r="I48" s="85">
+        <f>E48*G48</f>
+        <v/>
+      </c>
+      <c r="J48" s="85">
+        <f>F48*G48</f>
+        <v/>
+      </c>
+      <c r="K48" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears, subject to SLA service credit adjustments.</t>
+        </is>
+      </c>
+      <c r="L48" s="81" t="inlineStr">
+        <is>
+          <t>Monthly FLM Incident Log, Restoration Work Orders &amp; MTTR SLA Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="80" t="inlineStr">
+        <is>
+          <t>MS-FLM-02</t>
+        </is>
+      </c>
+      <c r="B49" s="81" t="inlineStr">
+        <is>
+          <t>Active Telecom Hardware Replacement &amp; Field Swapping</t>
+        </is>
+      </c>
+      <c r="C49" s="81" t="inlineStr">
+        <is>
+          <t>On-site replacement of damaged or defective active telecom hardware: RRUs, BBUs, baseband processing cards, optical SFP transceivers, RF jumpers, and GPS antennas, utilizing pre-staged regional spare parts float to achieve fast-track MTTR restoration.
+• Inclusions: Technician labor, de-installation, replacement installation, power-up test, return voucher.
+• Exclusions: Cost of out-of-warranty hardware destruction caused by third-party vandalism.</t>
+        </is>
+      </c>
+      <c r="D49" s="80" t="inlineStr">
+        <is>
+          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
+        </is>
+      </c>
+      <c r="E49" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G49" s="83" t="n"/>
+      <c r="H49" s="84">
+        <f>G49*55</f>
+        <v/>
+      </c>
+      <c r="I49" s="85">
+        <f>E49*G49</f>
+        <v/>
+      </c>
+      <c r="J49" s="85">
+        <f>F49*G49</f>
+        <v/>
+      </c>
+      <c r="K49" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L49" s="81" t="inlineStr">
+        <is>
+          <t>Hardware Replacement Slip &amp; Defective Unit Return Voucher</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="80" t="inlineStr">
+        <is>
+          <t>MS-FLM-03</t>
+        </is>
+      </c>
+      <c r="B50" s="81" t="inlineStr">
+        <is>
+          <t>Passive Power &amp; Infrastructure Emergency Restoration</t>
+        </is>
+      </c>
+      <c r="C50" s="81" t="inlineStr">
+        <is>
+          <t>Rapid restoration of passive site elements: resetting/replacing tripped DC distribution breakers, rectifying rectifier module faults, clearing battery management system (BMS) lockouts, replacing blown AC/DC surge protection devices (SPDs), and diagnosing automatic transfer switch (ATS) failures.
+• Inclusions: Electrical diagnosis, breaker reset/replacement, SPD swapping, BMS diagnostic clearing.
+• Exclusions: Replacement of entire battery bank destroyed by external flood (insurance scope).</t>
+        </is>
+      </c>
+      <c r="D50" s="80" t="inlineStr">
+        <is>
+          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
+        </is>
+      </c>
+      <c r="E50" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G50" s="83" t="n"/>
+      <c r="H50" s="84">
+        <f>G50*55</f>
+        <v/>
+      </c>
+      <c r="I50" s="85">
+        <f>E50*G50</f>
+        <v/>
+      </c>
+      <c r="J50" s="85">
+        <f>F50*G50</f>
+        <v/>
+      </c>
+      <c r="K50" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L50" s="81" t="inlineStr">
+        <is>
+          <t>Passive Infrastructure Restoration Work Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="80" t="inlineStr">
+        <is>
+          <t>MS-FLM-04</t>
+        </is>
+      </c>
+      <c r="B51" s="81" t="inlineStr">
+        <is>
+          <t>Emergency Fiber Backhaul Splicing &amp; Optical Link Restoration</t>
+        </is>
+      </c>
+      <c r="C51" s="81" t="inlineStr">
+        <is>
+          <t>Emergency mobilization for fiber transmission outages: OTDR optical fault localization, optical cable drop replacement, mechanical or fusion splicing, and optical splice enclosure re-sealing to restore backhaul transport within mandated MTTR.
+• Inclusions: OTDR fault tracing, fusion splicing labor, splice enclosure resealing, link test.
+• Exclusions: Major fiber spans exceeding 500 meters (governed by Call-Out Rate Card).</t>
+        </is>
+      </c>
+      <c r="D51" s="80" t="inlineStr">
+        <is>
+          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
+        </is>
+      </c>
+      <c r="E51" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F51" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G51" s="83" t="n"/>
+      <c r="H51" s="84">
+        <f>G51*55</f>
+        <v/>
+      </c>
+      <c r="I51" s="85">
+        <f>E51*G51</f>
+        <v/>
+      </c>
+      <c r="J51" s="85">
+        <f>F51*G51</f>
+        <v/>
+      </c>
+      <c r="K51" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L51" s="81" t="inlineStr">
+        <is>
+          <t>Optical OTDR Trace Report &amp; Splicing Restoration Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="80" t="inlineStr">
+        <is>
+          <t>MS-PM-01</t>
+        </is>
+      </c>
+      <c r="B52" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly Telecom Equipment Preventive Maintenance (Module A)</t>
+        </is>
+      </c>
+      <c r="C52" s="81" t="inlineStr">
+        <is>
+          <t>Execution of 100% quarterly routine telecom PM: visual inspection of BBU/RRU chassis, optical fiber connector cleaning and inspection, RF jumper weatherproofing boot inspection, cable clamp torque verification, optical SFP power level verification, and dust filter cleaning.
+• Inclusions: Quarterly on-site inspection, connector cleaning, weatherproofing audit, SFP level audit, PM report.
+• Exclusions: Major equipment overhaul.</t>
+        </is>
+      </c>
+      <c r="D52" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Quarter (or Monthly share)</t>
+        </is>
+      </c>
+      <c r="E52" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G52" s="83" t="n"/>
+      <c r="H52" s="84">
+        <f>G52*55</f>
+        <v/>
+      </c>
+      <c r="I52" s="85">
+        <f>E52*G52</f>
+        <v/>
+      </c>
+      <c r="J52" s="85">
+        <f>F52*G52</f>
+        <v/>
+      </c>
+      <c r="K52" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly upon submission of 100% PM checklists and mobile audit photos.</t>
+        </is>
+      </c>
+      <c r="L52" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly Telecom PM Report &amp; Mobile App Timestamped Audit Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="80" t="inlineStr">
+        <is>
+          <t>MS-PM-02</t>
+        </is>
+      </c>
+      <c r="B53" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly DC Power &amp; LiFePO4 Battery PM (Module B)</t>
+        </is>
+      </c>
+      <c r="C53" s="81" t="inlineStr">
+        <is>
+          <t>Comprehensive quarterly electrical PM: rectifier module load sharing verification, DC output float/equalize voltage calibration, terminal screw torque verification, LiFePO4 battery BMS diagnostic sweep, cell voltage and internal resistance measurement, and 1-hour controlled battery discharge autonomy test under load.
+• Inclusions: Rectifier calibration, BMS diagnostic sweep, internal resistance test, 1-hour load test.
+• Exclusions: Battery module replacement (handled under RMA / Spares float).</t>
+        </is>
+      </c>
+      <c r="D53" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Quarter</t>
+        </is>
+      </c>
+      <c r="E53" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G53" s="83" t="n"/>
+      <c r="H53" s="84">
+        <f>G53*55</f>
+        <v/>
+      </c>
+      <c r="I53" s="85">
+        <f>E53*G53</f>
+        <v/>
+      </c>
+      <c r="J53" s="85">
+        <f>F53*G53</f>
+        <v/>
+      </c>
+      <c r="K53" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly upon submission of Battery Health Dossier.</t>
+        </is>
+      </c>
+      <c r="L53" s="81" t="inlineStr">
+        <is>
+          <t>DC Power &amp; Battery PM Audit Report + Cell Health Telemetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="80" t="inlineStr">
+        <is>
+          <t>MS-PM-03</t>
+        </is>
+      </c>
+      <c r="B54" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly Earth Grounding &amp; Lightning Protection Audit (Module C)</t>
+        </is>
+      </c>
+      <c r="C54" s="81" t="inlineStr">
+        <is>
+          <t>Precision ground resistance audit using 3-point fall-of-potential test instrument (confirming earth ground resistance &lt;= 5.0 Ohms); Cadweld connection inspection; copper busbar bolt torque check; corrosion audit; and inspection of air terminals, down-conductors, and surge arresters.
+• Inclusions: 3-point fall-of-potential test, Cadweld check, busbar torque check, lightning arrester audit.
+• Exclusions: Civil construction of new ground ring (if soil conditions deteriorate; governed by civil rate card).</t>
+        </is>
+      </c>
+      <c r="D54" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Quarter</t>
+        </is>
+      </c>
+      <c r="E54" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G54" s="83" t="n"/>
+      <c r="H54" s="84">
+        <f>G54*55</f>
+        <v/>
+      </c>
+      <c r="I54" s="85">
+        <f>E54*G54</f>
+        <v/>
+      </c>
+      <c r="J54" s="85">
+        <f>F54*G54</f>
+        <v/>
+      </c>
+      <c r="K54" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly upon submission of Grounding Audit Report.</t>
+        </is>
+      </c>
+      <c r="L54" s="81" t="inlineStr">
+        <is>
+          <t>Earth Ground Resistance Test Certificate with Instrument Calibration Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="80" t="inlineStr">
+        <is>
+          <t>MS-PM-04</t>
+        </is>
+      </c>
+      <c r="B55" s="81" t="inlineStr">
+        <is>
+          <t>Bi-Annual Tower Structure, Rigging &amp; Aviation Light Audit (Module D)</t>
+        </is>
+      </c>
+      <c r="C55" s="81" t="inlineStr">
+        <is>
+          <t>Specialized climbing inspection conducted twice per year: physical inspection of tower steel members, monopole climbing ladder, fall arrest cable, AMB mounting bracket bolt torque verification, antenna azimuth/tilt physical check, cable ladder clamping check, and inspection of CAAP-compliant aviation obstruction light and photocell controller.
+• Inclusions: Certified climbing riggers, structural member inspection, bolt torque audit, CAAP light audit.
+• Exclusions: Tower painting / rust rehabilitation (governed under civil facility maintenance).</t>
+        </is>
+      </c>
+      <c r="D55" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Semi-Annual</t>
+        </is>
+      </c>
+      <c r="E55" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F55" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G55" s="83" t="n"/>
+      <c r="H55" s="84">
+        <f>G55*55</f>
+        <v/>
+      </c>
+      <c r="I55" s="85">
+        <f>E55*G55</f>
+        <v/>
+      </c>
+      <c r="J55" s="85">
+        <f>F55*G55</f>
+        <v/>
+      </c>
+      <c r="K55" s="81" t="inlineStr">
+        <is>
+          <t>Semi-annually upon submission of Tower Rigging Audit Report.</t>
+        </is>
+      </c>
+      <c r="L55" s="81" t="inlineStr">
+        <is>
+          <t>Bi-Annual Tower Climbing &amp; Rigging Audit Report + High-Res Photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="80" t="inlineStr">
+        <is>
+          <t>MS-PM-05</t>
+        </is>
+      </c>
+      <c r="B56" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly Site Compound, Civil &amp; Environmental Upkeep (Module E)</t>
+        </is>
+      </c>
+      <c r="C56" s="81" t="inlineStr">
+        <is>
+          <t>Routine civil compound maintenance: inspection and repair of chain-link perimeter fencing and barbed wire; greasing and servicing gate locking mechanisms; weed cutting, vegetation clearance, and chemical weed-killing within a 3-meter perimeter of compound; drainage channel clearing; and pest/rodent proofing of equipment cabinet cable entries.
+• Inclusions: Compound weeding, perimeter clearing, fence repair, lock lubrication, cable entry pest sealing.
+• Exclusions: Major civil perimeter wall re-construction post-landslide.</t>
+        </is>
+      </c>
+      <c r="D56" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Quarter</t>
+        </is>
+      </c>
+      <c r="E56" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F56" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G56" s="83" t="n"/>
+      <c r="H56" s="84">
+        <f>G56*55</f>
+        <v/>
+      </c>
+      <c r="I56" s="85">
+        <f>E56*G56</f>
+        <v/>
+      </c>
+      <c r="J56" s="85">
+        <f>F56*G56</f>
+        <v/>
+      </c>
+      <c r="K56" s="81" t="inlineStr">
+        <is>
+          <t>Quarterly upon compound inspection sign-off.</t>
+        </is>
+      </c>
+      <c r="L56" s="81" t="inlineStr">
+        <is>
+          <t>Compound Upkeep Audit Checklist &amp; Before/After Photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="80" t="inlineStr">
+        <is>
+          <t>MS-SPM-01</t>
+        </is>
+      </c>
+      <c r="B57" s="81" t="inlineStr">
+        <is>
+          <t>Regional Spare Parts Buffer Float Management (SPMS)</t>
+        </is>
+      </c>
+      <c r="C57" s="81" t="inlineStr">
+        <is>
+          <t>Operation of climate-controlled, secure regional spare parts depots (Mega Manila, North Luzon, South Luzon, Visayas, Mindanao); managing and maintaining an agreed 2.0% active hardware spares float (BBUs, RRUs, SFPs, rectifiers, batteries, cables); tracking serial numbers via WMS; and conducting monthly physical cycle counts.
+• Inclusions: Regional storage depots, inventory management, serialized tracking, monthly cycle counts.
+• Exclusions: Procurement of additional replacement spares beyond contractual float (Operator capex).</t>
+        </is>
+      </c>
+      <c r="D57" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E57" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G57" s="83" t="n"/>
+      <c r="H57" s="84">
+        <f>G57*55</f>
+        <v/>
+      </c>
+      <c r="I57" s="85">
+        <f>E57*G57</f>
+        <v/>
+      </c>
+      <c r="J57" s="85">
+        <f>F57*G57</f>
+        <v/>
+      </c>
+      <c r="K57" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L57" s="81" t="inlineStr">
+        <is>
+          <t>Monthly Spare Parts Float Status Report &amp; Cycle Count Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="80" t="inlineStr">
+        <is>
+          <t>MS-SPM-02</t>
+        </is>
+      </c>
+      <c r="B58" s="81" t="inlineStr">
+        <is>
+          <t>Advance Hardware Replacement (AHR) &amp; Expedited Field Delivery</t>
+        </is>
+      </c>
+      <c r="C58" s="81" t="inlineStr">
+        <is>
+          <t>Rapid logistics dispatch delivering replacement hardware to field maintenance crews: Next-Business-Day (NBD) standard delivery nationwide, or expedited 4-hour emergency delivery for major macro hubs and critical transmission nodes.
+• Inclusions: Expedited dispatch, emergency courier, chain of custody documentation, field delivery receipt.
+• Exclusions: Standard scheduled routine replenishment.</t>
+        </is>
+      </c>
+      <c r="D58" s="80" t="inlineStr">
+        <is>
+          <t>Included in SPM Retainer / Per Site-Month</t>
+        </is>
+      </c>
+      <c r="E58" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G58" s="83" t="n"/>
+      <c r="H58" s="84">
+        <f>G58*55</f>
+        <v/>
+      </c>
+      <c r="I58" s="85">
+        <f>E58*G58</f>
+        <v/>
+      </c>
+      <c r="J58" s="85">
+        <f>F58*G58</f>
+        <v/>
+      </c>
+      <c r="K58" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L58" s="81" t="inlineStr">
+        <is>
+          <t>Hardware Dispatch Manifest &amp; Proof of On-Site Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="80" t="inlineStr">
+        <is>
+          <t>MS-SPM-03</t>
+        </is>
+      </c>
+      <c r="B59" s="81" t="inlineStr">
+        <is>
+          <t>Return Merchandise Authorization (RMA) &amp; OEM Factory Repair Logistics</t>
+        </is>
+      </c>
+      <c r="C59" s="81" t="inlineStr">
+        <is>
+          <t>Managing the reverse logistics lifecycle for defective hardware: retrieving faulty units from field crews, conducting triage, generating RMA requests, managing packaging and export/import customs for OEM repair/replacement, tracking turnaround time (TAT &lt;= 30 calendar days), and returning repaired units to the regional buffer float.
+• Inclusions: Defective unit triage, RMA processing, shipping to OEM repair facility, tracking, customs clearance.
+• Exclusions: Out-of-warranty OEM repair billing charges (passed through at actual OEM repair cost).</t>
+        </is>
+      </c>
+      <c r="D59" s="80" t="inlineStr">
+        <is>
+          <t>Included in SPM Retainer / Per Site-Month</t>
+        </is>
+      </c>
+      <c r="E59" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G59" s="83" t="n"/>
+      <c r="H59" s="84">
+        <f>G59*55</f>
+        <v/>
+      </c>
+      <c r="I59" s="85">
+        <f>E59*G59</f>
+        <v/>
+      </c>
+      <c r="J59" s="85">
+        <f>F59*G59</f>
+        <v/>
+      </c>
+      <c r="K59" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L59" s="81" t="inlineStr">
+        <is>
+          <t>RMA Lifecycle Tracking Dossier &amp; OEM Repair Turnaround Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="80" t="inlineStr">
+        <is>
+          <t>MS-RNO-01</t>
+        </is>
+      </c>
+      <c r="B60" s="81" t="inlineStr">
+        <is>
+          <t>Continuous Radio Network Optimization &amp; Weekly KPI Surveillance</t>
+        </is>
+      </c>
+      <c r="C60" s="81" t="inlineStr">
+        <is>
+          <t>Ongoing network-wide RF quality surveillance: daily and weekly statistical KPI tracking (Radio Availability, CSSR, CDDR, average throughput, PRB utilization, cell-edge speeds); identification and root-cause analysis of Worst Performing Cells (WPC); dynamic parameter fine-tuning; and weekly optimization meetings.
+• Inclusions: Dedicated RF optimization engineers, weekly WPC triage, parameter tuning scripts, KPI governance.
+• Exclusions: Major network replanning requiring addition of new cell sites (expansion capex).</t>
+        </is>
+      </c>
+      <c r="D60" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E60" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G60" s="83" t="n"/>
+      <c r="H60" s="84">
+        <f>G60*55</f>
+        <v/>
+      </c>
+      <c r="I60" s="85">
+        <f>E60*G60</f>
+        <v/>
+      </c>
+      <c r="J60" s="85">
+        <f>F60*G60</f>
+        <v/>
+      </c>
+      <c r="K60" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L60" s="81" t="inlineStr">
+        <is>
+          <t>Weekly Worst Performing Cell (WPC) Report &amp; Monthly Network KPI Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="80" t="inlineStr">
+        <is>
+          <t>MS-RNO-02</t>
+        </is>
+      </c>
+      <c r="B61" s="81" t="inlineStr">
+        <is>
+          <t>Interference Hunting, PIM Mitigation &amp; Customer Complaint Field Audit</t>
+        </is>
+      </c>
+      <c r="C61" s="81" t="inlineStr">
+        <is>
+          <t>Field RF investigation for degraded sectors: spectrum analyzer sweeps to detect and locate external interference sources (jamming, unauthorized boosters, microwave leakage); Passive Intermodulation (PIM) testing and remediation on antenna lines; and on-site drive validation for VIP or high-churn barangay clusters.
+• Inclusions: Spectrum analyzer field sweeps, PIM testing, interference source triangulation, customer complaint verification.
+• Exclusions: Legal action against illegal booster operators (handled by NTC / Operator Legal).</t>
+        </is>
+      </c>
+      <c r="D61" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E61" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F61" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G61" s="83" t="n"/>
+      <c r="H61" s="84">
+        <f>G61*55</f>
+        <v/>
+      </c>
+      <c r="I61" s="85">
+        <f>E61*G61</f>
+        <v/>
+      </c>
+      <c r="J61" s="85">
+        <f>F61*G61</f>
+        <v/>
+      </c>
+      <c r="K61" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L61" s="81" t="inlineStr">
+        <is>
+          <t>Interference Investigation Dossier &amp; Spectrum Sweep Traces</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="80" t="inlineStr">
+        <is>
+          <t>MS-FAC-01</t>
+        </is>
+      </c>
+      <c r="B62" s="81" t="inlineStr">
+        <is>
+          <t>Passive Tower &amp; Civil Facility Maintenance</t>
+        </is>
+      </c>
+      <c r="C62" s="81" t="inlineStr">
+        <is>
+          <t>Structural preservation of passive site assets: rust scraping, cold galvanizing compound application, and repainting of steel members in corrosive/coastal environments; repairing cracked equipment plinths; re-caulking cable entry boots; and maintaining access road drainage and clear-way.
+• Inclusions: Anti-corrosion touch-up, cold galvanizing, plinth crack sealing, cable entry maintenance.
+• Exclusions: Full tower structural re-erection post-catastrophic failure.</t>
+        </is>
+      </c>
+      <c r="D62" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E62" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F62" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G62" s="83" t="n"/>
+      <c r="H62" s="84">
+        <f>G62*55</f>
+        <v/>
+      </c>
+      <c r="I62" s="85">
+        <f>E62*G62</f>
+        <v/>
+      </c>
+      <c r="J62" s="85">
+        <f>F62*G62</f>
+        <v/>
+      </c>
+      <c r="K62" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L62" s="81" t="inlineStr">
+        <is>
+          <t>Monthly Facility Maintenance Log &amp; Civil Condition Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="80" t="inlineStr">
+        <is>
+          <t>MS-PWR-01</t>
+        </is>
+      </c>
+      <c r="B63" s="81" t="inlineStr">
+        <is>
+          <t>Energy, Utility Grid (Meralco/Coop) Coordination &amp; Genset PM</t>
+        </is>
+      </c>
+      <c r="C63" s="81" t="inlineStr">
+        <is>
+          <t>Power management coordination: monitoring utility power reliability, validating commercial meter readings, coordinating with Meralco/electric cooperatives for transformer fuse restoration, and performing routine 250-hour preventive servicing on backup diesel generator sets (engine oil, oil filter, fuel filter, air cleaner replacement, coolant check).
+• Inclusions: Utility outage coordination, meter reading audit, 250-hr generator PM servicing, coolant/filter checks.
+• Exclusions: Commercial grid electric utility consumption charges (Operator pays utility bills).</t>
+        </is>
+      </c>
+      <c r="D63" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E63" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F63" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G63" s="83" t="n"/>
+      <c r="H63" s="84">
+        <f>G63*55</f>
+        <v/>
+      </c>
+      <c r="I63" s="85">
+        <f>E63*G63</f>
+        <v/>
+      </c>
+      <c r="J63" s="85">
+        <f>F63*G63</f>
+        <v/>
+      </c>
+      <c r="K63" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L63" s="81" t="inlineStr">
+        <is>
+          <t>Monthly Energy Consumption Audit &amp; Genset PM Service Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="80" t="inlineStr">
+        <is>
+          <t>MS-SW-01</t>
+        </is>
+      </c>
+      <c r="B64" s="81" t="inlineStr">
+        <is>
+          <t>Software Support, Firmware Patching &amp; Cybersecurity Hardening</t>
+        </is>
+      </c>
+      <c r="C64" s="81" t="inlineStr">
+        <is>
+          <t>Scheduled execution of software maintenance: applying OEM-approved firmware updates and feature patches during maintenance windows (00:00–05:00); implementing CVE security patches and hardening configs; executing weekly automated BBU and Core configuration backups; and maintaining offsite configuration archives.
+• Inclusions: Firmware deployment, CVE security updates, maintenance window execution, automated backups.
+• Exclusions: New major software feature releases requiring feature license fee purchase (Lot 1/Lot 3 scope).</t>
+        </is>
+      </c>
+      <c r="D64" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Month</t>
+        </is>
+      </c>
+      <c r="E64" s="82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F64" s="82" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G64" s="83" t="n"/>
+      <c r="H64" s="84">
+        <f>G64*55</f>
+        <v/>
+      </c>
+      <c r="I64" s="85">
+        <f>E64*G64</f>
+        <v/>
+      </c>
+      <c r="J64" s="85">
+        <f>F64*G64</f>
+        <v/>
+      </c>
+      <c r="K64" s="81" t="inlineStr">
+        <is>
+          <t>Monthly in arrears.</t>
+        </is>
+      </c>
+      <c r="L64" s="81" t="inlineStr">
+        <is>
+          <t>Monthly Patch Deployment Log &amp; Configuration Backup Verification Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="78" t="inlineStr">
+        <is>
+          <t>DOMAIN: AD-HOC CALL-OUT SERVICES RATE CARD</t>
+        </is>
+      </c>
+      <c r="B65" s="89" t="n"/>
+      <c r="C65" s="89" t="n"/>
+      <c r="D65" s="89" t="n"/>
+      <c r="E65" s="89" t="n"/>
+      <c r="F65" s="89" t="n"/>
+      <c r="G65" s="89" t="n"/>
+      <c r="H65" s="89" t="n"/>
+      <c r="I65" s="89" t="n"/>
+      <c r="J65" s="89" t="n"/>
+      <c r="K65" s="89" t="n"/>
+      <c r="L65" s="90" t="n"/>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="80" t="inlineStr">
+        <is>
+          <t>CALL-01</t>
+        </is>
+      </c>
+      <c r="B66" s="81" t="inlineStr">
+        <is>
+          <t>Specialized Tower Rigging Call-Out Service</t>
+        </is>
+      </c>
+      <c r="C66" s="81" t="inlineStr">
+        <is>
+          <t>Ad-hoc mobilization of a certified tower climbing crew to execute non-standard physical antenna modifications: adjusting mechanical tilt, azimuth, or antenna mounting height upon structural reconfiguration or post-typhoon realignment.
+• Inclusions: Rigging crew, climbing tackle, digital compass/inclinometer alignment, before/after photos.
+• Exclusions: Supply of new replacement antennas.</t>
+        </is>
+      </c>
+      <c r="D66" s="80" t="inlineStr">
+        <is>
+          <t>Per Sector / Per Man-Day</t>
+        </is>
+      </c>
+      <c r="E66" s="82" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="82" t="n">
+        <v>500</v>
+      </c>
+      <c r="G66" s="83" t="n"/>
+      <c r="H66" s="84">
+        <f>G66*55</f>
+        <v/>
+      </c>
+      <c r="I66" s="85">
+        <f>E66*G66</f>
+        <v/>
+      </c>
+      <c r="J66" s="85">
+        <f>F66*G66</f>
+        <v/>
+      </c>
+      <c r="K66" s="81" t="inlineStr">
+        <is>
+          <t>100% upon completion and photographic verification.</t>
+        </is>
+      </c>
+      <c r="L66" s="81" t="inlineStr">
+        <is>
+          <t>Rigging Work Order Completion Sheet &amp; Re-alignment Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="80" t="inlineStr">
+        <is>
+          <t>CALL-02</t>
+        </is>
+      </c>
+      <c r="B67" s="81" t="inlineStr">
+        <is>
+          <t>Emergency Typhoon Disaster Recovery Crew</t>
+        </is>
+      </c>
+      <c r="C67" s="81" t="inlineStr">
+        <is>
+          <t>Rapid deployment of a specialized 4-man disaster recovery crew equipped with heavy-duty 4x4 vehicle, chainsaws, winches, heavy rigging tackle, and portable generator to clear fallen trees, re-erect toppled poles, and execute emergency structural stabilization post-typhoon.
+• Inclusions: 4-man emergency crew, 4x4 vehicle, chainsaw, winch, generator, debris clearing gear.
+• Exclusions: Supply of complete replacement steel towers.</t>
+        </is>
+      </c>
+      <c r="D67" s="80" t="inlineStr">
+        <is>
+          <t>Per Crew / Per Day</t>
+        </is>
+      </c>
+      <c r="E67" s="82" t="n">
+        <v>50</v>
+      </c>
+      <c r="F67" s="82" t="n">
+        <v>250</v>
+      </c>
+      <c r="G67" s="83" t="n"/>
+      <c r="H67" s="84">
+        <f>G67*55</f>
+        <v/>
+      </c>
+      <c r="I67" s="85">
+        <f>E67*G67</f>
+        <v/>
+      </c>
+      <c r="J67" s="85">
+        <f>F67*G67</f>
+        <v/>
+      </c>
+      <c r="K67" s="81" t="inlineStr">
+        <is>
+          <t>100% upon daily crew timesheet approval by Operator.</t>
+        </is>
+      </c>
+      <c r="L67" s="81" t="inlineStr">
+        <is>
+          <t>Disaster Recovery Timesheet &amp; Field Activity Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="80" t="inlineStr">
+        <is>
+          <t>CALL-03</t>
+        </is>
+      </c>
+      <c r="B68" s="81" t="inlineStr">
+        <is>
+          <t>Mobile Emergency Generator Deployment &amp; Continuous Run</t>
+        </is>
+      </c>
+      <c r="C68" s="81" t="inlineStr">
+        <is>
+          <t>Delivery, positioning, cabling, and commissioning of a mobile trailer-mounted 15–20 kVA diesel generator at a damaged site during extended utility grid blackouts; includes 48 hours of continuous operation, continuous refueling, and operator surveillance.
+• Inclusions: Trailer genset delivery, connection cables, 48 hours continuous running, fuel, technician operator.
+• Exclusions: Operation beyond 48 hours (billed as consecutive additional 48-hr call-out blocks).</t>
+        </is>
+      </c>
+      <c r="D68" s="80" t="inlineStr">
+        <is>
+          <t>Per Deployment Event (48-hr block)</t>
+        </is>
+      </c>
+      <c r="E68" s="82" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" s="82" t="n">
+        <v>250</v>
+      </c>
+      <c r="G68" s="83" t="n"/>
+      <c r="H68" s="84">
+        <f>G68*55</f>
+        <v/>
+      </c>
+      <c r="I68" s="85">
+        <f>E68*G68</f>
+        <v/>
+      </c>
+      <c r="J68" s="85">
+        <f>F68*G68</f>
+        <v/>
+      </c>
+      <c r="K68" s="81" t="inlineStr">
+        <is>
+          <t>100% upon completion of emergency run.</t>
+        </is>
+      </c>
+      <c r="L68" s="81" t="inlineStr">
+        <is>
+          <t>Emergency Power Log &amp; Generator Run-Hour Telemetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="80" t="inlineStr">
+        <is>
+          <t>CALL-04</t>
+        </is>
+      </c>
+      <c r="B69" s="81" t="inlineStr">
+        <is>
+          <t>Long-Span Optical Fiber Cable Restoration &amp; Splicing</t>
+        </is>
+      </c>
+      <c r="C69" s="81" t="inlineStr">
+        <is>
+          <t>Emergency or planned restoration of major backhaul fiber cable cuts exceeding 500 meters: stringing replacement 24-core armored aerial or underground fiber cable, installing suspension clamps, fusion splicing at both splice closures, and testing optical loss.
+• Inclusions: Cable stringing labor, suspension clamps, 2x fusion splice enclosures, OTDR testing.
+• Exclusions: Supply of raw fiber optic cable (provided from operator inventory or billed separately).</t>
+        </is>
+      </c>
+      <c r="D69" s="80" t="inlineStr">
+        <is>
+          <t>Per Meter / Per Span</t>
+        </is>
+      </c>
+      <c r="E69" s="82" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F69" s="82" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G69" s="83" t="n"/>
+      <c r="H69" s="84">
+        <f>G69*55</f>
+        <v/>
+      </c>
+      <c r="I69" s="85">
+        <f>E69*G69</f>
+        <v/>
+      </c>
+      <c r="J69" s="85">
+        <f>F69*G69</f>
+        <v/>
+      </c>
+      <c r="K69" s="81" t="inlineStr">
+        <is>
+          <t>100% upon OTDR bi-directional loss sign-off.</t>
+        </is>
+      </c>
+      <c r="L69" s="81" t="inlineStr">
+        <is>
+          <t>Bi-Directional OTDR Loss Trace &amp; Splicing Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="80" t="inlineStr">
+        <is>
+          <t>CALL-05</t>
+        </is>
+      </c>
+      <c r="B70" s="81" t="inlineStr">
+        <is>
+          <t>Drone Structural, Panoramic &amp; Thermal Imaging Survey</t>
+        </is>
+      </c>
+      <c r="C70" s="81" t="inlineStr">
+        <is>
+          <t>High-resolution aerial inspection utilizing drone equipped with 4K optical zoom and radiometric thermal sensor: auditing tower structural integrity, inspecting hard-to-reach antenna brackets, and detecting hotspot anomalies on power joints and cables.
+• Inclusions: Licensed drone pilot, 4K video, high-res photos, radiometric thermal imaging, analysis report.
+• Exclusions: Physical repairs to identified anomalies.</t>
+        </is>
+      </c>
+      <c r="D70" s="80" t="inlineStr">
+        <is>
+          <t>Per Site Flight</t>
+        </is>
+      </c>
+      <c r="E70" s="82" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" s="82" t="n">
+        <v>250</v>
+      </c>
+      <c r="G70" s="83" t="n"/>
+      <c r="H70" s="84">
+        <f>G70*55</f>
+        <v/>
+      </c>
+      <c r="I70" s="85">
+        <f>E70*G70</f>
+        <v/>
+      </c>
+      <c r="J70" s="85">
+        <f>F70*G70</f>
+        <v/>
+      </c>
+      <c r="K70" s="81" t="inlineStr">
+        <is>
+          <t>100% upon submission of 4K video, photos, and thermal report.</t>
+        </is>
+      </c>
+      <c r="L70" s="81" t="inlineStr">
+        <is>
+          <t>High-Resolution Aerial Video/Photo Suite &amp; Thermal Analysis Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="80" t="inlineStr">
+        <is>
+          <t>CALL-06</t>
+        </is>
+      </c>
+      <c r="B71" s="81" t="inlineStr">
+        <is>
+          <t>Tower Structural Strengthening &amp; Leg Reinforcement</t>
+        </is>
+      </c>
+      <c r="C71" s="81" t="inlineStr">
+        <is>
+          <t>Physical structural modification of existing tower or monopole: installing steel reinforcement members, flange stiffeners, cross-bracing, or guy wire tensioning based on approved PE structural engineering calculations.
+• Inclusions: Steel fabrication, rigging installation, bolt torquing, cold galvanizing, PE sign-off.
+• Exclusions: Supply of primary raw steel members (billed based on approved DED BoQ).</t>
+        </is>
+      </c>
+      <c r="D71" s="80" t="inlineStr">
+        <is>
+          <t>Per Tower / Lump Sum based on DED</t>
+        </is>
+      </c>
+      <c r="E71" s="82" t="n">
+        <v>20</v>
+      </c>
+      <c r="F71" s="82" t="n">
+        <v>100</v>
+      </c>
+      <c r="G71" s="83" t="n"/>
+      <c r="H71" s="84">
+        <f>G71*55</f>
+        <v/>
+      </c>
+      <c r="I71" s="85">
+        <f>E71*G71</f>
+        <v/>
+      </c>
+      <c r="J71" s="85">
+        <f>F71*G71</f>
+        <v/>
+      </c>
+      <c r="K71" s="81" t="inlineStr">
+        <is>
+          <t>50% upon material delivery; 50% upon PE structural sign-off.</t>
+        </is>
+      </c>
+      <c r="L71" s="81" t="inlineStr">
+        <is>
+          <t>As-Built Structural Strengthening Drawings &amp; PE Endorsement</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="80" t="inlineStr">
+        <is>
+          <t>CALL-07</t>
+        </is>
+      </c>
+      <c r="B72" s="81" t="inlineStr">
+        <is>
+          <t>Specialized PIM Hunting &amp; Multi-Sector Interference Remediation</t>
+        </is>
+      </c>
+      <c r="C72" s="81" t="inlineStr">
+        <is>
+          <t>Advanced on-site PIM testing utilizing specialized 2x20W PIM analyzer: identifying internal and external PIM sources, replacing corroded RF jumpers/connectors, and applying RF shielding tape/materials to achieve PIM &lt;= -155 dBc.
+• Inclusions: Calibrated 2x20W PIM test gear, RF sweep, connector re-termination, shielding materials, sweep report.
+• Exclusions: Replacement of damaged antenna internal phase shifters (OEM warranty).</t>
+        </is>
+      </c>
+      <c r="D72" s="80" t="inlineStr">
+        <is>
+          <t>Per Site / Day</t>
+        </is>
+      </c>
+      <c r="E72" s="82" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="82" t="n">
+        <v>150</v>
+      </c>
+      <c r="G72" s="83" t="n"/>
+      <c r="H72" s="84">
+        <f>G72*55</f>
+        <v/>
+      </c>
+      <c r="I72" s="85">
+        <f>E72*G72</f>
+        <v/>
+      </c>
+      <c r="J72" s="85">
+        <f>F72*G72</f>
+        <v/>
+      </c>
+      <c r="K72" s="81" t="inlineStr">
+        <is>
+          <t>100% upon achieving compliant PIM sweep trace.</t>
+        </is>
+      </c>
+      <c r="L72" s="81" t="inlineStr">
+        <is>
+          <t>Calibrated PIM Sweep Measurement Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="80" t="inlineStr">
+        <is>
+          <t>CALL-08</t>
+        </is>
+      </c>
+      <c r="B73" s="81" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Emergency Fuel Delivery &amp; Mobile Refueling</t>
+        </is>
+      </c>
+      <c r="C73" s="81" t="inlineStr">
+        <is>
+          <t>Rapid procurement and transport of clean Euro-4 automotive diesel fuel in certified fuel containers to remote sites during prolonged grid emergencies, including manual transfer to day tank.
+• Inclusions: Fuel procurement, dedicated transport, manual pumping into tank, fuel quality test.
+• Exclusions: Cost of bulk commercial diesel fuel (reimbursed at actual pump receipt price).</t>
+        </is>
+      </c>
+      <c r="D73" s="80" t="inlineStr">
+        <is>
+          <t>Per Liter Delivered / Per Trip</t>
+        </is>
+      </c>
+      <c r="E73" s="82" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F73" s="82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G73" s="83" t="n"/>
+      <c r="H73" s="84">
+        <f>G73*55</f>
+        <v/>
+      </c>
+      <c r="I73" s="85">
+        <f>E73*G73</f>
+        <v/>
+      </c>
+      <c r="J73" s="85">
+        <f>F73*G73</f>
+        <v/>
+      </c>
+      <c r="K73" s="81" t="inlineStr">
+        <is>
+          <t>100% upon fuel receipt voucher sign-off.</t>
+        </is>
+      </c>
+      <c r="L73" s="81" t="inlineStr">
+        <is>
+          <t>Fuel Purchase Receipt &amp; Fuel Delivery Voucher</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="86" t="inlineStr">
+        <is>
+          <t>TOTAL EVALUATED SERVICES SCHEDULE (USD)</t>
+        </is>
+      </c>
+      <c r="B74" s="89" t="n"/>
+      <c r="C74" s="89" t="n"/>
+      <c r="D74" s="89" t="n"/>
+      <c r="E74" s="89" t="n"/>
+      <c r="F74" s="89" t="n"/>
+      <c r="G74" s="89" t="n"/>
+      <c r="H74" s="90" t="n"/>
+      <c r="I74" s="87">
+        <f>SUM(I7:I73)</f>
+        <v/>
+      </c>
+      <c r="J74" s="87">
+        <f>SUM(J7:J73)</f>
+        <v/>
+      </c>
+      <c r="K74" s="88" t="n"/>
+      <c r="L74" s="88" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A65:L65"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -1049,7 +1049,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -4031,7 +4030,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -4252,7 +4250,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -6742,11 +6739,10 @@
     <row r="3">
       <c r="A3" s="76" t="inlineStr">
         <is>
-          <t>Instructions: Bidders must enter firm unit rates in USD in Column G (highlighted in yellow). PHP equivalents and totals are calculated automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Instructions: Bidders must enter firm unit rates in USD in Column G (yellow). NOTICE: Operational baseline is TowerCo-acquired (Co-location / Build-to-Suit) where TowerCo executes hunting/permitting under MLA, Vendor provides technical vetting/TSSR endorsement, and Operator issues final approval. Category 1 rates (SAQ-01 to SAQ-08) serve strictly as a Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Own-Build (Tier 3). Bidders shall NOT embed SAQ risk markups into baseline turnkey pricing.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="77" t="inlineStr">
         <is>
@@ -6812,20 +6808,20 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="78" t="inlineStr">
         <is>
-          <t>DOMAIN: SITE ACQUISITION &amp; LEGAL PERMITTING</t>
-        </is>
-      </c>
-      <c r="B6" s="89" t="n"/>
-      <c r="C6" s="89" t="n"/>
-      <c r="D6" s="89" t="n"/>
-      <c r="E6" s="89" t="n"/>
-      <c r="F6" s="89" t="n"/>
-      <c r="G6" s="89" t="n"/>
-      <c r="H6" s="89" t="n"/>
-      <c r="I6" s="89" t="n"/>
-      <c r="J6" s="89" t="n"/>
-      <c r="K6" s="89" t="n"/>
-      <c r="L6" s="90" t="n"/>
+          <t>DOMAIN: SITE ACQUISITION &amp; LEGAL PERMITTING (STANDBY / CONTINGENCY CALL-OFF RATE CARD — OPERATOR SELF-ACQUISITION OPTION)</t>
+        </is>
+      </c>
+      <c r="B6" s="79" t="n"/>
+      <c r="C6" s="79" t="n"/>
+      <c r="D6" s="79" t="n"/>
+      <c r="E6" s="79" t="n"/>
+      <c r="F6" s="79" t="n"/>
+      <c r="G6" s="79" t="n"/>
+      <c r="H6" s="79" t="n"/>
+      <c r="I6" s="79" t="n"/>
+      <c r="J6" s="79" t="n"/>
+      <c r="K6" s="79" t="n"/>
+      <c r="L6" s="79" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="80" t="inlineStr">
@@ -6840,7 +6836,7 @@
       </c>
       <c r="C7" s="81" t="inlineStr">
         <is>
-          <t>Field identification, screening, and ranking of three (3) viable candidates (Candidate A - Primary, Candidate B - Secondary, Candidate C - Contingency) within the assigned nominal search ring (500m radius for urban/suburban; 1,000m radius for rural). Mandatory spatial screening against audited TowerCo database (13,746 towers) to prioritize Tier 1 co-location. Scope includes visual inspection of antenna mounting feasibility, ground space availability (minimum 2.0m x 2.0m pad), line-of-sight to demand settlement centroid, road access verification (all-weather vs 4x4), and issuance of the Preliminary Candidate Evaluation Report (PCER).
+          <t>[OPERATIONAL BASELINE: Siting and candidate hunting is executed by the TowerCo. Vendor performs on-site technical vetting (RF LOS, antenna height, structural feasibility) and issues joint endorsement; Operator issues final approval. COMMERCIAL PRICING BASIS: Quoted rate serves strictly as a Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Own-Build]. Field identification, screening, and ranking of three (3) viable candidates (Candidate A - Primary, Candidate B - Secondary, Candidate C - Contingency) within the assigned nominal search ring (500m radius for urban/suburban; 1,000m radius for rural). Mandatory spatial screening against audited TowerCo database (13,746 towers) to prioritize Tier 1 co-location. Scope includes visual inspection of antenna mounting feasibility, ground space availability (minimum 2.0m x 2.0m pad), line-of-sight to demand settlement centroid, road access verification (all-weather vs 4x4), and issuance of the Preliminary Candidate Evaluation Report (PCER).
 • Inclusions: Desktop spatial analysis, physical on-ground hunting, 3 candidate identification, GPS logging, PCER compilation.
 • Exclusions: Commercial lease execution (handled by Operator under MLA).</t>
         </is>
@@ -6893,7 +6889,7 @@
       </c>
       <c r="C8" s="81" t="inlineStr">
         <is>
-          <t>Comprehensive on-ground site acquisition audit and property investigation for the selected primary candidate. Compilation of standardized Site Acquisition Report (SAR) containing: official PSGC code, precision WGS84 GPS coordinates (&gt;= 6 decimal places), ground elevation AMSL, property cadastral boundary sketch, certified land title verification (TCT/OCT/Tax Declaration), lessor profile and contact matrix, preliminary structural condition assessment, preliminary power availability (grid connection point, transformer distance, utility provider), 360-degree panoramic site photos, logistics route access classification, and SAQ risk assessment matrix.
+          <t>[OPERATIONAL BASELINE: TowerCo provides primary site attributes and property profile under MLA. Vendor reviews and compiles technical feasibility annex in TSSR; Operator signs off. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for full standalone SAR compilation during Operator Self-Acquisition]. Comprehensive on-ground site acquisition audit and property investigation for the selected primary candidate. Compilation of standardized Site Acquisition Report (SAR) containing: official PSGC code, precision WGS84 GPS coordinates (&gt;= 6 decimal places), ground elevation AMSL, property cadastral boundary sketch, certified land title verification (TCT/OCT/Tax Declaration), lessor profile and contact matrix, preliminary structural condition assessment, preliminary power availability (grid connection point, transformer distance, utility provider), 360-degree panoramic site photos, logistics route access classification, and SAQ risk assessment matrix.
 • Inclusions: On-ground cadastral audit, title verification, lessor interview, 360-deg photo sweep, complete SAR package.
 • Exclusions: Payment of land rental / lease deposits (direct Operator responsibility).</t>
         </is>
@@ -6946,7 +6942,7 @@
       </c>
       <c r="C9" s="81" t="inlineStr">
         <is>
-          <t>Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
+          <t>[APPLIES TO TOWERCO CO-LOCATION: Preparation of technical equipment loading profile (3x 8T8R RRU, 3x Antennas, hybrid cables, 2m x 2m pad) and coordination with TowerCo engineering until SAA approval. Commercial lease executed directly by Operator under MLA]. Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
 • Inclusions: SAA documentation, loading calculation submission, liaison with TowerCo engineering, tracking SAA to NTP.
 • Exclusions: Commercial MLA negotiations and monthly tower rental fees (exclusive Operator responsibility).</t>
         </is>
@@ -6999,7 +6995,7 @@
       </c>
       <c r="C10" s="81" t="inlineStr">
         <is>
-          <t>Direct lessor negotiations for greenfield sites: boundary survey coordination, verification of registered ownership (clean title check at Registry of Deeds, inheritance/estate verification, real property tax clearance), negotiation of long-term lease terms (10-15 years) within Operator budgetary caps, preparation of lease annexes, securing lessor spousal consent and IDs, and facilitation of formal contract notarization and annotation on title.
+          <t>[CONTINGENCY / SELF-BUILD SCOPE: Applicable strictly to Operator Own-Build Greenfield sites where no TowerCo exists or TowerCo denies build. Direct lessor negotiation, title due diligence, and lease notarization]. Direct lessor negotiations for greenfield sites: boundary survey coordination, verification of registered ownership (clean title check at Registry of Deeds, inheritance/estate verification, real property tax clearance), negotiation of long-term lease terms (10-15 years) within Operator budgetary caps, preparation of lease annexes, securing lessor spousal consent and IDs, and facilitation of formal contract notarization and annotation on title.
 • Inclusions: Lessor negotiations, title due diligence, boundary verification, notary liaison, lease execution assistance.
 • Exclusions: Actual lease rentals, advance deposits, and title annotation official fees (Operator pays directly).</t>
         </is>
@@ -7052,7 +7048,7 @@
       </c>
       <c r="C11" s="81" t="inlineStr">
         <is>
-          <t>Securing official local community clearances: presentation to Barangay Council, public hearing facilitation (if mandated), processing and issuance of official Barangay Resolution of Support, Barangay Construction Clearance, and certified Neighborhood / Homeowners Association (HOA) Resolution / Certificate of No Objection from contiguous property owners within a 50-meter radius.
+          <t>[OPERATIONAL BASELINE: TowerCo secures community/Barangay clearances for TowerCo towers. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Greenfield sites]. Securing official local community clearances: presentation to Barangay Council, public hearing facilitation (if mandated), processing and issuance of official Barangay Resolution of Support, Barangay Construction Clearance, and certified Neighborhood / Homeowners Association (HOA) Resolution / Certificate of No Objection from contiguous property owners within a 50-meter radius.
 • Inclusions: Barangay consultations, neighbor signature campaigns, clearance filing and follow-through, official receipts.
 • Exclusions: Official LGU statutory fees (reimbursable at actual cost against official receipts).</t>
         </is>
@@ -7105,7 +7101,7 @@
       </c>
       <c r="C12" s="81" t="inlineStr">
         <is>
-          <t>Complete processing and procurement of municipal/city LGU Building Permits in accordance with the National Building Code of the Philippines (PD 1096). Scope includes securing Locational Clearance, Zoning Compliance, Architectural Permit, Civil/Structural Permit, Electrical Permit, Sanitary/Plumbing Permit, and Mechanical Permit, backed by complete sets of plans signed and sealed by licensed Professional Engineers (Civil, Structural, Electrical, PEE).
+          <t>[OPERATIONAL BASELINE: TowerCo secures LGU Building Permits under PD 1096 for TowerCo towers. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build Greenfield Monopoles]. Complete processing and procurement of municipal/city LGU Building Permits in accordance with the National Building Code of the Philippines (PD 1096). Scope includes securing Locational Clearance, Zoning Compliance, Architectural Permit, Civil/Structural Permit, Electrical Permit, Sanitary/Plumbing Permit, and Mechanical Permit, backed by complete sets of plans signed and sealed by licensed Professional Engineers (Civil, Structural, Electrical, PEE).
 • Inclusions: Permit application filing, engineering plan liaison, follow-through across city/municipal engineering offices.
 • Exclusions: Official municipal permit assessment fees (reimbursable at face value against official receipts).</t>
         </is>
@@ -7158,7 +7154,7 @@
       </c>
       <c r="C13" s="81" t="inlineStr">
         <is>
-          <t>Procurement of mandatory national statutory clearances: Civil Aviation Authority of the Philippines (CAAP) Height Clearance Permit / Obstruction Evaluation; Department of Environment and Natural Resources (DENR) Certificate of Non-Coverage (CNC) or Environmental Compliance Certificate (ECC); and Department of Public Works and Highways (DPWH) Road Right-of-Way (ROW) clearance where site access fronts national highways.
+          <t>[OPERATIONAL BASELINE: TowerCo secures CAAP Height Clearance and DENR CNC/ECC for TowerCo assets. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build Greenfield Monopoles]. Procurement of mandatory national statutory clearances: Civil Aviation Authority of the Philippines (CAAP) Height Clearance Permit / Obstruction Evaluation; Department of Environment and Natural Resources (DENR) Certificate of Non-Coverage (CNC) or Environmental Compliance Certificate (ECC); and Department of Public Works and Highways (DPWH) Road Right-of-Way (ROW) clearance where site access fronts national highways.
 • Inclusions: Technical submittals, coordinate and elevation certification, CAAP/DENR filing and technical defense.
 • Exclusions: Official statutory assessment fees (reimbursable at actual cost).</t>
         </is>
@@ -7211,7 +7207,7 @@
       </c>
       <c r="C14" s="81" t="inlineStr">
         <is>
-          <t>Securing post-construction occupancy and power clearances: processing Certificate of Final Electrical Inspection (CFEI), Bureau of Fire Protection (BFP) Fire Safety Inspection Certificate (FSIC), commercial power utility (Meralco / Regional Electric Cooperative) service application, transformer tapping coordination, meter base energization, and municipal LGU Certificate of Final Occupancy / Permit to Operate.
+          <t>[OPERATIONAL BASELINE: TowerCo manages utility service entrance and meter installation on shared compound. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build sites]. Securing post-construction occupancy and power clearances: processing Certificate of Final Electrical Inspection (CFEI), Bureau of Fire Protection (BFP) Fire Safety Inspection Certificate (FSIC), commercial power utility (Meralco / Regional Electric Cooperative) service application, transformer tapping coordination, meter base energization, and municipal LGU Certificate of Final Occupancy / Permit to Operate.
 • Inclusions: BFP inspection facilitation, CFEI filing, utility coordination, meter installation liaison, occupancy release.
 • Exclusions: Utility transformer installation capital contribution and security deposits (paid by Operator).</t>
         </is>
@@ -7257,17 +7253,17 @@
           <t>DOMAIN: SITE ENGINEERING &amp; DETAILED SITE SURVEY</t>
         </is>
       </c>
-      <c r="B15" s="89" t="n"/>
-      <c r="C15" s="89" t="n"/>
-      <c r="D15" s="89" t="n"/>
-      <c r="E15" s="89" t="n"/>
-      <c r="F15" s="89" t="n"/>
-      <c r="G15" s="89" t="n"/>
-      <c r="H15" s="89" t="n"/>
-      <c r="I15" s="89" t="n"/>
-      <c r="J15" s="89" t="n"/>
-      <c r="K15" s="89" t="n"/>
-      <c r="L15" s="90" t="n"/>
+      <c r="B15" s="79" t="n"/>
+      <c r="C15" s="79" t="n"/>
+      <c r="D15" s="79" t="n"/>
+      <c r="E15" s="79" t="n"/>
+      <c r="F15" s="79" t="n"/>
+      <c r="G15" s="79" t="n"/>
+      <c r="H15" s="79" t="n"/>
+      <c r="I15" s="79" t="n"/>
+      <c r="J15" s="79" t="n"/>
+      <c r="K15" s="79" t="n"/>
+      <c r="L15" s="79" t="n"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="80" t="inlineStr">
@@ -7593,17 +7589,17 @@
           <t>DOMAIN: RADIO NETWORK PLANNING &amp; DESIGN</t>
         </is>
       </c>
-      <c r="B22" s="89" t="n"/>
-      <c r="C22" s="89" t="n"/>
-      <c r="D22" s="89" t="n"/>
-      <c r="E22" s="89" t="n"/>
-      <c r="F22" s="89" t="n"/>
-      <c r="G22" s="89" t="n"/>
-      <c r="H22" s="89" t="n"/>
-      <c r="I22" s="89" t="n"/>
-      <c r="J22" s="89" t="n"/>
-      <c r="K22" s="89" t="n"/>
-      <c r="L22" s="90" t="n"/>
+      <c r="B22" s="79" t="n"/>
+      <c r="C22" s="79" t="n"/>
+      <c r="D22" s="79" t="n"/>
+      <c r="E22" s="79" t="n"/>
+      <c r="F22" s="79" t="n"/>
+      <c r="G22" s="79" t="n"/>
+      <c r="H22" s="79" t="n"/>
+      <c r="I22" s="79" t="n"/>
+      <c r="J22" s="79" t="n"/>
+      <c r="K22" s="79" t="n"/>
+      <c r="L22" s="79" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="80" t="inlineStr">
@@ -7618,7 +7614,7 @@
       </c>
       <c r="C23" s="81" t="inlineStr">
         <is>
-          <t>Macro-level 5G RF network planning using advanced 3D ray-tracing propagation modeling engines, calibrated against high-resolution 5-meter clutter models and Digital Terrain Models (DTM). Sizing and generation of nominal candidate search rings across high-density suburban and rural barangay centroids; multi-carrier capacity dimensioning for Band n50 (60 MHz NCR / up to 80 MHz Provincial, software-configurable 40/50/60/80 MHz TDD); coverage prediction mapping (RSRP, SINR, Best Server, Downlink/Uplink Throughput); and inter-site distance (ISD) optimization.
+          <t>Macro-level 5G RF network planning using advanced 3D ray-tracing propagation modeling engines, calibrated against high-resolution 5-meter clutter models and Digital Terrain Models (DTM). Sizing and generation of nominal candidate search rings across high-density suburban and rural barangay centroids; multi-carrier capacity dimensioning for Band n50 (60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD); coverage prediction mapping (RSRP, SINR, Best Server, Downlink/Uplink Throughput); and inter-site distance (ISD) optimization.
 • Inclusions: 3D ray-tracing simulation, clutter model calibration, nominal site planning, search ring generation.
 • Exclusions: Procurement of specialized external digital terrain data licenses (provided by Operator).</t>
         </is>
@@ -7717,17 +7713,17 @@
           <t>DOMAIN: TELECOM LOGISTICS &amp; MATERIAL HANDLING</t>
         </is>
       </c>
-      <c r="B25" s="89" t="n"/>
-      <c r="C25" s="89" t="n"/>
-      <c r="D25" s="89" t="n"/>
-      <c r="E25" s="89" t="n"/>
-      <c r="F25" s="89" t="n"/>
-      <c r="G25" s="89" t="n"/>
-      <c r="H25" s="89" t="n"/>
-      <c r="I25" s="89" t="n"/>
-      <c r="J25" s="89" t="n"/>
-      <c r="K25" s="89" t="n"/>
-      <c r="L25" s="90" t="n"/>
+      <c r="B25" s="79" t="n"/>
+      <c r="C25" s="79" t="n"/>
+      <c r="D25" s="79" t="n"/>
+      <c r="E25" s="79" t="n"/>
+      <c r="F25" s="79" t="n"/>
+      <c r="G25" s="79" t="n"/>
+      <c r="H25" s="79" t="n"/>
+      <c r="I25" s="79" t="n"/>
+      <c r="J25" s="79" t="n"/>
+      <c r="K25" s="79" t="n"/>
+      <c r="L25" s="79" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="80" t="inlineStr">
@@ -7894,17 +7890,17 @@
           <t>DOMAIN: TELECOM INSTALLATION, COMMISSIONING &amp; INTEGRATION</t>
         </is>
       </c>
-      <c r="B29" s="89" t="n"/>
-      <c r="C29" s="89" t="n"/>
-      <c r="D29" s="89" t="n"/>
-      <c r="E29" s="89" t="n"/>
-      <c r="F29" s="89" t="n"/>
-      <c r="G29" s="89" t="n"/>
-      <c r="H29" s="89" t="n"/>
-      <c r="I29" s="89" t="n"/>
-      <c r="J29" s="89" t="n"/>
-      <c r="K29" s="89" t="n"/>
-      <c r="L29" s="90" t="n"/>
+      <c r="B29" s="79" t="n"/>
+      <c r="C29" s="79" t="n"/>
+      <c r="D29" s="79" t="n"/>
+      <c r="E29" s="79" t="n"/>
+      <c r="F29" s="79" t="n"/>
+      <c r="G29" s="79" t="n"/>
+      <c r="H29" s="79" t="n"/>
+      <c r="I29" s="79" t="n"/>
+      <c r="J29" s="79" t="n"/>
+      <c r="K29" s="79" t="n"/>
+      <c r="L29" s="79" t="n"/>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="80" t="inlineStr">
@@ -8131,7 +8127,7 @@
       </c>
       <c r="C34" s="81" t="inlineStr">
         <is>
-          <t>Transmission IP integration (VLAN, BGP, IPsec); establishing S1-U / N2/N3 control and user plane interfaces to 5G Core (AMF/UPF); synchronization with TelTech EMS/OSS; activating 3 sectors on Band n50 (60 MHz NCR / up to 80 MHz Provincial, software-configurable 40/50/60/80 MHz TDD); clearing all active alarms; and achieving stable commercial on-air operational state.
+          <t>Transmission IP integration (VLAN, BGP, IPsec); establishing S1-U / N2/N3 control and user plane interfaces to 5G Core (AMF/UPF); synchronization with TelTech EMS/OSS; activating 3 sectors on Band n50 (60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD); clearing all active alarms; and achieving stable commercial on-air operational state.
 • Inclusions: IP configuration, Core integration, OSS synchronization, carrier activation, alarm clearance.
 • Exclusions: Core network UPF dimensioning (governed under Lot 3).</t>
         </is>
@@ -8177,17 +8173,17 @@
           <t>DOMAIN: SINGLE SITE VERIFICATION &amp; ACCEPTANCE</t>
         </is>
       </c>
-      <c r="B35" s="89" t="n"/>
-      <c r="C35" s="89" t="n"/>
-      <c r="D35" s="89" t="n"/>
-      <c r="E35" s="89" t="n"/>
-      <c r="F35" s="89" t="n"/>
-      <c r="G35" s="89" t="n"/>
-      <c r="H35" s="89" t="n"/>
-      <c r="I35" s="89" t="n"/>
-      <c r="J35" s="89" t="n"/>
-      <c r="K35" s="89" t="n"/>
-      <c r="L35" s="90" t="n"/>
+      <c r="B35" s="79" t="n"/>
+      <c r="C35" s="79" t="n"/>
+      <c r="D35" s="79" t="n"/>
+      <c r="E35" s="79" t="n"/>
+      <c r="F35" s="79" t="n"/>
+      <c r="G35" s="79" t="n"/>
+      <c r="H35" s="79" t="n"/>
+      <c r="I35" s="79" t="n"/>
+      <c r="J35" s="79" t="n"/>
+      <c r="K35" s="79" t="n"/>
+      <c r="L35" s="79" t="n"/>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="80" t="inlineStr">
@@ -8354,17 +8350,17 @@
           <t>DOMAIN: CLUSTER RADIO NETWORK OPTIMIZATION</t>
         </is>
       </c>
-      <c r="B39" s="89" t="n"/>
-      <c r="C39" s="89" t="n"/>
-      <c r="D39" s="89" t="n"/>
-      <c r="E39" s="89" t="n"/>
-      <c r="F39" s="89" t="n"/>
-      <c r="G39" s="89" t="n"/>
-      <c r="H39" s="89" t="n"/>
-      <c r="I39" s="89" t="n"/>
-      <c r="J39" s="89" t="n"/>
-      <c r="K39" s="89" t="n"/>
-      <c r="L39" s="90" t="n"/>
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+      <c r="F39" s="79" t="n"/>
+      <c r="G39" s="79" t="n"/>
+      <c r="H39" s="79" t="n"/>
+      <c r="I39" s="79" t="n"/>
+      <c r="J39" s="79" t="n"/>
+      <c r="K39" s="79" t="n"/>
+      <c r="L39" s="79" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="80" t="inlineStr">
@@ -8531,17 +8527,17 @@
           <t>DOMAIN: OPERATIONS &amp; MAINTENANCE (O&amp;M) / MANAGED SERVICES</t>
         </is>
       </c>
-      <c r="B43" s="89" t="n"/>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="89" t="n"/>
-      <c r="E43" s="89" t="n"/>
-      <c r="F43" s="89" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="89" t="n"/>
-      <c r="I43" s="89" t="n"/>
-      <c r="J43" s="89" t="n"/>
-      <c r="K43" s="89" t="n"/>
-      <c r="L43" s="90" t="n"/>
+      <c r="B43" s="79" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
+      <c r="I43" s="79" t="n"/>
+      <c r="J43" s="79" t="n"/>
+      <c r="K43" s="79" t="n"/>
+      <c r="L43" s="79" t="n"/>
     </row>
     <row r="44" ht="45" customHeight="1">
       <c r="A44" s="80" t="inlineStr">
@@ -9662,17 +9658,17 @@
           <t>DOMAIN: AD-HOC CALL-OUT SERVICES RATE CARD</t>
         </is>
       </c>
-      <c r="B65" s="89" t="n"/>
-      <c r="C65" s="89" t="n"/>
-      <c r="D65" s="89" t="n"/>
-      <c r="E65" s="89" t="n"/>
-      <c r="F65" s="89" t="n"/>
-      <c r="G65" s="89" t="n"/>
-      <c r="H65" s="89" t="n"/>
-      <c r="I65" s="89" t="n"/>
-      <c r="J65" s="89" t="n"/>
-      <c r="K65" s="89" t="n"/>
-      <c r="L65" s="90" t="n"/>
+      <c r="B65" s="79" t="n"/>
+      <c r="C65" s="79" t="n"/>
+      <c r="D65" s="79" t="n"/>
+      <c r="E65" s="79" t="n"/>
+      <c r="F65" s="79" t="n"/>
+      <c r="G65" s="79" t="n"/>
+      <c r="H65" s="79" t="n"/>
+      <c r="I65" s="79" t="n"/>
+      <c r="J65" s="79" t="n"/>
+      <c r="K65" s="79" t="n"/>
+      <c r="L65" s="79" t="n"/>
     </row>
     <row r="66" ht="45" customHeight="1">
       <c r="A66" s="80" t="inlineStr">
@@ -10104,13 +10100,13 @@
           <t>TOTAL EVALUATED SERVICES SCHEDULE (USD)</t>
         </is>
       </c>
-      <c r="B74" s="89" t="n"/>
-      <c r="C74" s="89" t="n"/>
-      <c r="D74" s="89" t="n"/>
-      <c r="E74" s="89" t="n"/>
-      <c r="F74" s="89" t="n"/>
-      <c r="G74" s="89" t="n"/>
-      <c r="H74" s="90" t="n"/>
+      <c r="B74" s="79" t="n"/>
+      <c r="C74" s="79" t="n"/>
+      <c r="D74" s="79" t="n"/>
+      <c r="E74" s="79" t="n"/>
+      <c r="F74" s="79" t="n"/>
+      <c r="G74" s="79" t="n"/>
+      <c r="H74" s="79" t="n"/>
       <c r="I74" s="87">
         <f>SUM(I7:I73)</f>
         <v/>
@@ -10127,9 +10123,9 @@
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A22:L22"/>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0,##0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,8 +178,59 @@
       <color rgb="001E293B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A192F"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A192F"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00475569"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -262,8 +313,32 @@
         <bgColor rgb="00F0FDF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A192F"/>
+        <bgColor rgb="000A192F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -430,11 +505,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000A192F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -646,6 +735,86 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="33" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="16" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="34" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="34" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3374,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,6 +3917,21 @@
       <c r="A15" s="66" t="inlineStr">
         <is>
           <t>Note: This schedule establishes the official evaluated 10-Year Lifecycle TCO for the committed Phase 1 network baseline (1,000 macro BTS sites). Expansion Capex for Years 2 to 5 (Phases 2 to 5, 1,000 sites/year up to 5,000 sites total) is governed by the firm unit rates in Lots 1, 2, 5, and 7 under contractual call-off options (Section 4.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="121" t="inlineStr">
+        <is>
+          <t>RECONCILIATION NOTE — MASTER SERVICES SOW &amp; RATE CARD INTEGRATION:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="122" t="inlineStr">
+        <is>
+          <t>• Lot 5 (Line 1 Capex Component): Turnkey Site Acquisition, TSSR &amp; Civil Infrastructure reconciles with Sheet 'Services SOW &amp; Rate Card' Subtotal A (Cells J77 Phase 1 / K77 Program). Category 1 SAQ rates serve as standby own-build rates (10.3% contingency basket).
+• Lot 6 (Line 6 Annual Managed Services Component): 24/7 Managed Operations &amp; Maintenance reconciles with Sheet 'Services SOW &amp; Rate Card' Subtotal B1 (Cell J78 Phase 1 Annualized O&amp;M) and Subtotal B2 (Cell J79 3-Year Contractual Total). Retainer-included services evaluate at $0.00.</t>
         </is>
       </c>
     </row>
@@ -6705,138 +6889,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
-        <is>
-          <t>5G FWA PROGRAM — MASTER SERVICES SOW &amp; COMMERCIAL RATE CARD</t>
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>5G FWA PROGRAM — MASTER SERVICES SOW &amp; COMMERCIAL RATE CARD (REVISION 2.1 - RECONCILED TENDER BASELINE)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="inlineStr">
-        <is>
-          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Operator: TelTech / Converge ICT | Baseline FX: 1 USD = 55.00 PHP | Author: Oliver Tungol</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="76" t="inlineStr">
-        <is>
-          <t>Instructions: Bidders must enter firm unit rates in USD in Column G (yellow). NOTICE: Operational baseline is TowerCo-acquired (Co-location / Build-to-Suit) where TowerCo executes hunting/permitting under MLA, Vendor provides technical vetting/TSSR endorsement, and Operator issues final approval. Category 1 rates (SAQ-01 to SAQ-08) serve strictly as a Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Own-Build (Tier 3). Bidders shall NOT embed SAQ risk markups into baseline turnkey pricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A2" s="92" t="inlineStr">
+        <is>
+          <t>Tender Ref: RFP-TELTECH-FWA-2026-001 | Operator: TelTech / Converge ICT Solutions Inc. | Audited Tower Database: 13,810 Locations | Baseline FX: 1 USD = 55.00 PHP | Author: Oliver Tungol</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="93" t="inlineStr">
+        <is>
+          <t>GOVERNANCE &amp; COMMERCIAL PRICING PRINCIPLES: (1) Primary Operational Baseline is TowerCo-Acquired (Tier 1 Co-Location 89.7% / Tier 2 Build-to-Suit 10.3%). Under MLA, TowerCo conducts candidate hunting, leasing, LGU permits, TIA-222-H structural wind simulation (250–315 km/h), foundation check, and licensed PE wet-seal. Vendor scopes physical audit, active equipment loading dossier (weight, EPA, brackets), and mounting verification. (2) Category 1 (SAQ-01 to SAQ-08) serves STRICTLY as a Standby / Contingency Call-Off Rate Card for Tier 3 Operator Own-Build, evaluated against an explicit 10.3% Contingency Basket (103 sites Phase 1 / 515 sites Program). (3) Bundled O&amp;M items (FLM-02 to 04, SPM-02 to 03) evaluate at $0.00 (Included in Base Retainer). (4) O&amp;M services are evaluated on explicit annualized (12-month) and 3-Year contractual baselines (matching Lot 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>Item Ref</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="94" t="inlineStr">
         <is>
           <t>Service Title</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
-        <is>
-          <t>Detailed Technical Scope &amp; Boundaries</t>
-        </is>
-      </c>
-      <c r="D5" s="77" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>Detailed Technical Scope &amp; Governance Boundaries</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="E5" s="77" t="inlineStr">
+      <c r="E5" s="94" t="inlineStr">
         <is>
           <t>Phase 1 Qty</t>
         </is>
       </c>
-      <c r="F5" s="77" t="inlineStr">
+      <c r="F5" s="94" t="inlineStr">
         <is>
           <t>Program Qty</t>
         </is>
       </c>
-      <c r="G5" s="77" t="inlineStr">
+      <c r="G5" s="94" t="inlineStr">
+        <is>
+          <t>Evaluation Basis / Multiplier</t>
+        </is>
+      </c>
+      <c r="H5" s="94" t="inlineStr">
         <is>
           <t>Unit Rate (USD) [Bidder Input]</t>
         </is>
       </c>
-      <c r="H5" s="77" t="inlineStr">
+      <c r="I5" s="94" t="inlineStr">
         <is>
           <t>Unit Rate (PHP @ 55)</t>
         </is>
       </c>
-      <c r="I5" s="77" t="inlineStr">
-        <is>
-          <t>Phase 1 Total (USD)</t>
-        </is>
-      </c>
-      <c r="J5" s="77" t="inlineStr">
-        <is>
-          <t>Program Total (USD)</t>
-        </is>
-      </c>
-      <c r="K5" s="77" t="inlineStr">
-        <is>
-          <t>Billing Milestone Trigger</t>
-        </is>
-      </c>
-      <c r="L5" s="77" t="inlineStr">
+      <c r="J5" s="94" t="inlineStr">
+        <is>
+          <t>Evaluated Phase 1 Amount (USD)</t>
+        </is>
+      </c>
+      <c r="K5" s="94" t="inlineStr">
+        <is>
+          <t>Evaluated Program Amount (USD)</t>
+        </is>
+      </c>
+      <c r="L5" s="94" t="inlineStr">
+        <is>
+          <t>Lot / TCO Reconciliation Mapping</t>
+        </is>
+      </c>
+      <c r="M5" s="94" t="inlineStr">
         <is>
           <t>Deliverable Artifact</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="78" t="inlineStr">
-        <is>
-          <t>DOMAIN: SITE ACQUISITION &amp; LEGAL PERMITTING (STANDBY / CONTINGENCY CALL-OFF RATE CARD — OPERATOR SELF-ACQUISITION OPTION)</t>
-        </is>
-      </c>
-      <c r="B6" s="79" t="n"/>
-      <c r="C6" s="79" t="n"/>
-      <c r="D6" s="79" t="n"/>
-      <c r="E6" s="79" t="n"/>
-      <c r="F6" s="79" t="n"/>
-      <c r="G6" s="79" t="n"/>
-      <c r="H6" s="79" t="n"/>
-      <c r="I6" s="79" t="n"/>
-      <c r="J6" s="79" t="n"/>
-      <c r="K6" s="79" t="n"/>
-      <c r="L6" s="79" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="95" t="inlineStr">
+        <is>
+          <t>DOMAIN: SITE ACQUISITION &amp; LEGAL PERMITTING (STANDBY CONTINGENCY RATE CARD — TIER 3 OPERATOR OWN-BUILD 10.3% EVALUATION BASKET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="80" t="inlineStr">
         <is>
           <t>SAQ-01</t>
         </is>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Nominal Search Ring Siting &amp; Candidate Hunting</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
-        <is>
-          <t>[OPERATIONAL BASELINE: Siting and candidate hunting is executed by the TowerCo. Vendor performs on-site technical vetting (RF LOS, antenna height, structural feasibility) and issues joint endorsement; Operator issues final approval. COMMERCIAL PRICING BASIS: Quoted rate serves strictly as a Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Own-Build]. Field identification, screening, and ranking of three (3) viable candidates (Candidate A - Primary, Candidate B - Secondary, Candidate C - Contingency) within the assigned nominal search ring (500m radius for urban/suburban; 1,000m radius for rural). Mandatory spatial screening against audited TowerCo database (13,746 towers) to prioritize Tier 1 co-location. Scope includes visual inspection of antenna mounting feasibility, ground space availability (minimum 2.0m x 2.0m pad), line-of-sight to demand settlement centroid, road access verification (all-weather vs 4x4), and issuance of the Preliminary Candidate Evaluation Report (PCER).
+      <c r="C7" s="97" t="inlineStr">
+        <is>
+          <t>[OPERATIONAL BASELINE: Siting and candidate hunting is executed by the TowerCo. Vendor performs on-site technical vetting (RF LOS, antenna height, structural feasibility) and issues joint endorsement; Operator issues final approval. COMMERCIAL PRICING BASIS: Quoted rate serves strictly as a Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Own-Build]. Field identification, screening, and ranking of three (3) viable candidates (Candidate A - Primary, Candidate B - Secondary, Candidate C - Contingency) within the assigned nominal search ring (500m radius for urban/suburban; 1,000m radius for rural). Mandatory spatial screening against audited TowerCo database (13,810 audited tower locations) to prioritize Tier 1 co-location. Scope includes visual inspection of antenna mounting feasibility, ground space availability (minimum 2.0m x 2.0m pad), line-of-sight to demand settlement centroid, road access verification (all-weather vs 4x4), and issuance of the Preliminary Candidate Evaluation Report (PCER).
 • Inclusions: Desktop spatial analysis, physical on-ground hunting, 3 candidate identification, GPS logging, PCER compilation.
 • Exclusions: Commercial lease execution (handled by Operator under MLA).</t>
         </is>
@@ -6846,48 +7025,53 @@
           <t>Per Search Ring</t>
         </is>
       </c>
-      <c r="E7" s="82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="82" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" s="83" t="n"/>
-      <c r="H7" s="84">
-        <f>G7*55</f>
-        <v/>
-      </c>
-      <c r="I7" s="85">
-        <f>E7*G7</f>
+      <c r="E7" s="98" t="n">
+        <v>103</v>
+      </c>
+      <c r="F7" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G7" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H7" s="99" t="n"/>
+      <c r="I7" s="84">
+        <f>H7*55</f>
         <v/>
       </c>
       <c r="J7" s="85">
-        <f>F7*G7</f>
-        <v/>
-      </c>
-      <c r="K7" s="81" t="inlineStr">
-        <is>
-          <t>100% upon Operator formal approval of PCER ranking 3 compliant candidates.</t>
-        </is>
-      </c>
-      <c r="L7" s="81" t="inlineStr">
+        <f>E7*H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="85">
+        <f>F7*H7</f>
+        <v/>
+      </c>
+      <c r="L7" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M7" s="96" t="inlineStr">
         <is>
           <t>Approved Preliminary Candidate Evaluation Report (PCER)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="80" t="inlineStr">
         <is>
           <t>SAQ-02</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="96" t="inlineStr">
         <is>
           <t>Detailed Site Acquisition Report (SAR) &amp; Technical Dossier</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="97" t="inlineStr">
         <is>
           <t>[OPERATIONAL BASELINE: TowerCo provides primary site attributes and property profile under MLA. Vendor reviews and compiles technical feasibility annex in TSSR; Operator signs off. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for full standalone SAR compilation during Operator Self-Acquisition]. Comprehensive on-ground site acquisition audit and property investigation for the selected primary candidate. Compilation of standardized Site Acquisition Report (SAR) containing: official PSGC code, precision WGS84 GPS coordinates (&gt;= 6 decimal places), ground elevation AMSL, property cadastral boundary sketch, certified land title verification (TCT/OCT/Tax Declaration), lessor profile and contact matrix, preliminary structural condition assessment, preliminary power availability (grid connection point, transformer distance, utility provider), 360-degree panoramic site photos, logistics route access classification, and SAQ risk assessment matrix.
 • Inclusions: On-ground cadastral audit, title verification, lessor interview, 360-deg photo sweep, complete SAR package.
@@ -6899,48 +7083,53 @@
           <t>Per Candidate Site</t>
         </is>
       </c>
-      <c r="E8" s="82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="82" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G8" s="83" t="n"/>
-      <c r="H8" s="84">
-        <f>G8*55</f>
-        <v/>
-      </c>
-      <c r="I8" s="85">
-        <f>E8*G8</f>
+      <c r="E8" s="98" t="n">
+        <v>103</v>
+      </c>
+      <c r="F8" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G8" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H8" s="99" t="n"/>
+      <c r="I8" s="84">
+        <f>H8*55</f>
         <v/>
       </c>
       <c r="J8" s="85">
-        <f>F8*G8</f>
-        <v/>
-      </c>
-      <c r="K8" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal engineering and legal acceptance of the SAR package by Operator.</t>
-        </is>
-      </c>
-      <c r="L8" s="81" t="inlineStr">
+        <f>E8*H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="85">
+        <f>F8*H8</f>
+        <v/>
+      </c>
+      <c r="L8" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M8" s="96" t="inlineStr">
         <is>
           <t>Comprehensive Site Acquisition Report (SAR) Dossier</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="80" t="inlineStr">
         <is>
           <t>SAQ-03</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>TowerCo Space Application (SAA) &amp; Technical Dossier Support</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>[APPLIES TO TOWERCO CO-LOCATION: Preparation of technical equipment loading profile (3x 8T8R RRU, 3x Antennas, hybrid cables, 2m x 2m pad) and coordination with TowerCo engineering until SAA approval. Commercial lease executed directly by Operator under MLA]. Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
 • Inclusions: SAA documentation, loading calculation submission, liaison with TowerCo engineering, tracking SAA to NTP.
@@ -6952,48 +7141,53 @@
           <t>Per Co-Location Site</t>
         </is>
       </c>
-      <c r="E9" s="82" t="n">
-        <v>897</v>
-      </c>
-      <c r="F9" s="82" t="n">
-        <v>4517</v>
-      </c>
-      <c r="G9" s="83" t="n"/>
-      <c r="H9" s="84">
-        <f>G9*55</f>
-        <v/>
-      </c>
-      <c r="I9" s="85">
-        <f>E9*G9</f>
+      <c r="E9" s="98" t="n">
+        <v>103</v>
+      </c>
+      <c r="F9" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G9" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H9" s="99" t="n"/>
+      <c r="I9" s="84">
+        <f>H9*55</f>
         <v/>
       </c>
       <c r="J9" s="85">
-        <f>F9*G9</f>
-        <v/>
-      </c>
-      <c r="K9" s="81" t="inlineStr">
-        <is>
-          <t>50% upon SAA submission; 50% upon TowerCo issuance of formal SAA Approval / NTP.</t>
-        </is>
-      </c>
-      <c r="L9" s="81" t="inlineStr">
+        <f>E9*H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="85">
+        <f>F9*H9</f>
+        <v/>
+      </c>
+      <c r="L9" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M9" s="96" t="inlineStr">
         <is>
           <t>Approved TowerCo SAA &amp; Official Notice to Proceed (NTP)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="80" t="inlineStr">
         <is>
           <t>SAQ-04</t>
         </is>
       </c>
-      <c r="B10" s="81" t="inlineStr">
+      <c r="B10" s="96" t="inlineStr">
         <is>
           <t>Greenfield Land Lease Negotiation &amp; Notarized Contract Support</t>
         </is>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C10" s="97" t="inlineStr">
         <is>
           <t>[CONTINGENCY / SELF-BUILD SCOPE: Applicable strictly to Operator Own-Build Greenfield sites where no TowerCo exists or TowerCo denies build. Direct lessor negotiation, title due diligence, and lease notarization]. Direct lessor negotiations for greenfield sites: boundary survey coordination, verification of registered ownership (clean title check at Registry of Deeds, inheritance/estate verification, real property tax clearance), negotiation of long-term lease terms (10-15 years) within Operator budgetary caps, preparation of lease annexes, securing lessor spousal consent and IDs, and facilitation of formal contract notarization and annotation on title.
 • Inclusions: Lessor negotiations, title due diligence, boundary verification, notary liaison, lease execution assistance.
@@ -7005,48 +7199,53 @@
           <t>Per Greenfield Site</t>
         </is>
       </c>
-      <c r="E10" s="82" t="n">
+      <c r="E10" s="98" t="n">
         <v>103</v>
       </c>
-      <c r="F10" s="82" t="n">
-        <v>483</v>
-      </c>
-      <c r="G10" s="83" t="n"/>
-      <c r="H10" s="84">
-        <f>G10*55</f>
-        <v/>
-      </c>
-      <c r="I10" s="85">
-        <f>E10*G10</f>
+      <c r="F10" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G10" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="n"/>
+      <c r="I10" s="84">
+        <f>H10*55</f>
         <v/>
       </c>
       <c r="J10" s="85">
-        <f>F10*G10</f>
-        <v/>
-      </c>
-      <c r="K10" s="81" t="inlineStr">
-        <is>
-          <t>50% upon mutual execution of Lease Agreement; 50% upon Notarization and Title Annotation.</t>
-        </is>
-      </c>
-      <c r="L10" s="81" t="inlineStr">
+        <f>E10*H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="85">
+        <f>F10*H10</f>
+        <v/>
+      </c>
+      <c r="L10" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M10" s="96" t="inlineStr">
         <is>
           <t>Executed &amp; Notarized Contract of Lease + Clean Title Dossier</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="80" t="inlineStr">
         <is>
           <t>SAQ-05</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Local Community, Barangay &amp; Neighborhood Clearances</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>[OPERATIONAL BASELINE: TowerCo secures community/Barangay clearances for TowerCo towers. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Acquisition / Greenfield sites]. Securing official local community clearances: presentation to Barangay Council, public hearing facilitation (if mandated), processing and issuance of official Barangay Resolution of Support, Barangay Construction Clearance, and certified Neighborhood / Homeowners Association (HOA) Resolution / Certificate of No Objection from contiguous property owners within a 50-meter radius.
 • Inclusions: Barangay consultations, neighbor signature campaigns, clearance filing and follow-through, official receipts.
@@ -7058,48 +7257,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E11" s="82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="82" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G11" s="83" t="n"/>
-      <c r="H11" s="84">
-        <f>G11*55</f>
-        <v/>
-      </c>
-      <c r="I11" s="85">
-        <f>E11*G11</f>
+      <c r="E11" s="98" t="n">
+        <v>103</v>
+      </c>
+      <c r="F11" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G11" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H11" s="99" t="n"/>
+      <c r="I11" s="84">
+        <f>H11*55</f>
         <v/>
       </c>
       <c r="J11" s="85">
-        <f>F11*G11</f>
-        <v/>
-      </c>
-      <c r="K11" s="81" t="inlineStr">
-        <is>
-          <t>100% upon issuance of certified Barangay Clearance &amp; HOA No Objection Resolution.</t>
-        </is>
-      </c>
-      <c r="L11" s="81" t="inlineStr">
+        <f>E11*H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="85">
+        <f>F11*H11</f>
+        <v/>
+      </c>
+      <c r="L11" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M11" s="96" t="inlineStr">
         <is>
           <t>Certified Barangay Clearance &amp; HOA Resolution of No Objection</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="80" t="inlineStr">
         <is>
           <t>SAQ-06</t>
         </is>
       </c>
-      <c r="B12" s="81" t="inlineStr">
+      <c r="B12" s="96" t="inlineStr">
         <is>
           <t>Local Government Unit (LGU) Building &amp; Construction Permits</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C12" s="97" t="inlineStr">
         <is>
           <t>[OPERATIONAL BASELINE: TowerCo secures LGU Building Permits under PD 1096 for TowerCo towers. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build Greenfield Monopoles]. Complete processing and procurement of municipal/city LGU Building Permits in accordance with the National Building Code of the Philippines (PD 1096). Scope includes securing Locational Clearance, Zoning Compliance, Architectural Permit, Civil/Structural Permit, Electrical Permit, Sanitary/Plumbing Permit, and Mechanical Permit, backed by complete sets of plans signed and sealed by licensed Professional Engineers (Civil, Structural, Electrical, PEE).
 • Inclusions: Permit application filing, engineering plan liaison, follow-through across city/municipal engineering offices.
@@ -7111,48 +7315,53 @@
           <t>Per Greenfield Site / Co-loc where required</t>
         </is>
       </c>
-      <c r="E12" s="82" t="n">
+      <c r="E12" s="98" t="n">
         <v>103</v>
       </c>
-      <c r="F12" s="82" t="n">
-        <v>483</v>
-      </c>
-      <c r="G12" s="83" t="n"/>
-      <c r="H12" s="84">
-        <f>G12*55</f>
-        <v/>
-      </c>
-      <c r="I12" s="85">
-        <f>E12*G12</f>
+      <c r="F12" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G12" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="n"/>
+      <c r="I12" s="84">
+        <f>H12*55</f>
         <v/>
       </c>
       <c r="J12" s="85">
-        <f>F12*G12</f>
-        <v/>
-      </c>
-      <c r="K12" s="81" t="inlineStr">
-        <is>
-          <t>100% upon release of official LGU Building Permit and Approved Engineering Plans.</t>
-        </is>
-      </c>
-      <c r="L12" s="81" t="inlineStr">
+        <f>E12*H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="85">
+        <f>F12*H12</f>
+        <v/>
+      </c>
+      <c r="L12" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M12" s="96" t="inlineStr">
         <is>
           <t>Official LGU Building Permit &amp; Endorsed Blueprints</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="80" t="inlineStr">
         <is>
           <t>SAQ-07</t>
         </is>
       </c>
-      <c r="B13" s="81" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Statutory &amp; Environmental Clearances (CAAP, DENR, DPWH)</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>[OPERATIONAL BASELINE: TowerCo secures CAAP Height Clearance and DENR CNC/ECC for TowerCo assets. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build Greenfield Monopoles]. Procurement of mandatory national statutory clearances: Civil Aviation Authority of the Philippines (CAAP) Height Clearance Permit / Obstruction Evaluation; Department of Environment and Natural Resources (DENR) Certificate of Non-Coverage (CNC) or Environmental Compliance Certificate (ECC); and Department of Public Works and Highways (DPWH) Road Right-of-Way (ROW) clearance where site access fronts national highways.
 • Inclusions: Technical submittals, coordinate and elevation certification, CAAP/DENR filing and technical defense.
@@ -7164,48 +7373,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E13" s="82" t="n">
+      <c r="E13" s="98" t="n">
         <v>103</v>
       </c>
-      <c r="F13" s="82" t="n">
-        <v>483</v>
-      </c>
-      <c r="G13" s="83" t="n"/>
-      <c r="H13" s="84">
-        <f>G13*55</f>
-        <v/>
-      </c>
-      <c r="I13" s="85">
-        <f>E13*G13</f>
+      <c r="F13" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G13" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H13" s="99" t="n"/>
+      <c r="I13" s="84">
+        <f>H13*55</f>
         <v/>
       </c>
       <c r="J13" s="85">
-        <f>F13*G13</f>
-        <v/>
-      </c>
-      <c r="K13" s="81" t="inlineStr">
-        <is>
-          <t>100% upon issuance of official CAAP Height Clearance and DENR CNC/ECC.</t>
-        </is>
-      </c>
-      <c r="L13" s="81" t="inlineStr">
+        <f>E13*H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="85">
+        <f>F13*H13</f>
+        <v/>
+      </c>
+      <c r="L13" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M13" s="96" t="inlineStr">
         <is>
           <t>Official CAAP Height Clearance Permit &amp; DENR CNC/ECC</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="80" t="inlineStr">
         <is>
           <t>SAQ-08</t>
         </is>
       </c>
-      <c r="B14" s="81" t="inlineStr">
+      <c r="B14" s="96" t="inlineStr">
         <is>
           <t>Utility Interconnection, CFEI, FSIC &amp; Occupancy Permitting</t>
         </is>
       </c>
-      <c r="C14" s="81" t="inlineStr">
+      <c r="C14" s="97" t="inlineStr">
         <is>
           <t>[OPERATIONAL BASELINE: TowerCo manages utility service entrance and meter installation on shared compound. COMMERCIAL PRICING BASIS: Standby / Contingency Call-Off Rate Card for Operator Self-Build sites]. Securing post-construction occupancy and power clearances: processing Certificate of Final Electrical Inspection (CFEI), Bureau of Fire Protection (BFP) Fire Safety Inspection Certificate (FSIC), commercial power utility (Meralco / Regional Electric Cooperative) service application, transformer tapping coordination, meter base energization, and municipal LGU Certificate of Final Occupancy / Permit to Operate.
 • Inclusions: BFP inspection facilitation, CFEI filing, utility coordination, meter installation liaison, occupancy release.
@@ -7217,66 +7431,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E14" s="82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="82" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G14" s="83" t="n"/>
-      <c r="H14" s="84">
-        <f>G14*55</f>
-        <v/>
-      </c>
-      <c r="I14" s="85">
-        <f>E14*G14</f>
+      <c r="E14" s="98" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" s="98" t="n">
+        <v>515</v>
+      </c>
+      <c r="G14" s="80" t="inlineStr">
+        <is>
+          <t>1x (10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="H14" s="99" t="n"/>
+      <c r="I14" s="84">
+        <f>H14*55</f>
         <v/>
       </c>
       <c r="J14" s="85">
-        <f>F14*G14</f>
-        <v/>
-      </c>
-      <c r="K14" s="81" t="inlineStr">
-        <is>
-          <t>50% upon CFEI/FSIC release; 50% upon commercial grid energization and Occupancy Permit.</t>
-        </is>
-      </c>
-      <c r="L14" s="81" t="inlineStr">
+        <f>E14*H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="85">
+        <f>F14*H14</f>
+        <v/>
+      </c>
+      <c r="L14" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+        </is>
+      </c>
+      <c r="M14" s="96" t="inlineStr">
         <is>
           <t>CFEI, FSIC, Utility Meter Energization Notice &amp; Certificate of Occupancy</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="78" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: SITE ENGINEERING &amp; DETAILED SITE SURVEY</t>
         </is>
       </c>
-      <c r="B15" s="79" t="n"/>
-      <c r="C15" s="79" t="n"/>
-      <c r="D15" s="79" t="n"/>
-      <c r="E15" s="79" t="n"/>
-      <c r="F15" s="79" t="n"/>
-      <c r="G15" s="79" t="n"/>
-      <c r="H15" s="79" t="n"/>
-      <c r="I15" s="79" t="n"/>
-      <c r="J15" s="79" t="n"/>
-      <c r="K15" s="79" t="n"/>
-      <c r="L15" s="79" t="n"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="80" t="inlineStr">
         <is>
           <t>ENG-01</t>
         </is>
       </c>
-      <c r="B16" s="81" t="inlineStr">
+      <c r="B16" s="96" t="inlineStr">
         <is>
           <t>Technical Site Survey (TSS) &amp; 360° Drone Panoramic Audit</t>
         </is>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C16" s="97" t="inlineStr">
         <is>
           <t>Rigorous multi-disciplinary physical site survey executed by licensed telecom and civil engineers: 360° high-resolution panoramic photographic sweep at target antenna centerline (using calibrated drone or mast camera); precision dual-frequency GPS coordinate recording; physical measurement of compound dimensions, tower base, shelter/cabinet footprint; cable gantry routing audit; transport access route assessment (bridge load limits, tight turning radii); and compilation of raw TSS data.
 • Inclusions: Multi-disciplinary field team, calibrated drone flight, 360-deg panoramic photos, spatial sketches, access log.
@@ -7288,52 +7496,57 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E16" s="82" t="n">
+      <c r="E16" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F16" s="82" t="n">
+      <c r="F16" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G16" s="83" t="n"/>
-      <c r="H16" s="84">
-        <f>G16*55</f>
-        <v/>
-      </c>
-      <c r="I16" s="85">
-        <f>E16*G16</f>
+      <c r="G16" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H16" s="99" t="n"/>
+      <c r="I16" s="84">
+        <f>H16*55</f>
         <v/>
       </c>
       <c r="J16" s="85">
-        <f>F16*G16</f>
-        <v/>
-      </c>
-      <c r="K16" s="81" t="inlineStr">
-        <is>
-          <t>100% upon completion of field survey and upload of raw survey package and photos.</t>
-        </is>
-      </c>
-      <c r="L16" s="81" t="inlineStr">
+        <f>E16*H16</f>
+        <v/>
+      </c>
+      <c r="K16" s="85">
+        <f>F16*H16</f>
+        <v/>
+      </c>
+      <c r="L16" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M16" s="96" t="inlineStr">
         <is>
           <t>Raw TSS Survey Package &amp; High-Resolution 360° Panoramic Photo Suite</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="80" t="inlineStr">
         <is>
           <t>ENG-02</t>
         </is>
       </c>
-      <c r="B17" s="81" t="inlineStr">
-        <is>
-          <t>Structural Loading, Wind Stress &amp; Civil Engineering Assessment</t>
-        </is>
-      </c>
-      <c r="C17" s="81" t="inlineStr">
-        <is>
-          <t>Engineering structural evaluation of the proposed host structure (tower, rooftop, or monopole): audit of steel member sections, bracing, gusset plates, anchor bolts, and corrosion condition; calculation of total Effective Projected Area (EPA) and weight for new equipment (3x 8T8R RRU, 3x macro antennas/AAUs, AMB brackets, hybrid cable); structural wind load simulation under TIA-222-H for 250 km/h basic wind speed (Category 5 typhoon standard); foundation capacity verification; and formal structural analysis report certified by a licensed Professional Structural Engineer (PE).
-• Inclusions: Structural audit, EPA calculations, TIA-222-H wind simulation, foundation check, PE sign-off.
-• Exclusions: Tower reinforcement civil execution (governed by separate structural modification call-out rate card).</t>
+      <c r="B17" s="96" t="inlineStr">
+        <is>
+          <t>Site Structural Audit, Antenna Loading Verification &amp; Own-Build Structural Engineering</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="inlineStr">
+        <is>
+          <t>Engineering structural evaluation of the host structure: [OPERATIONAL BASELINE — TIER 1 CO-LOCATION &amp; TIER 2 B2S: Under MLA, TowerCo conducts 3D structural analysis, TIA-222-H wind modeling, foundation verification, and secures the licensed PE wet-seal certification per Appendix D §1.3 and Bid Bulletin 01 Huawei Item 13. Vendor scope is strictly limited to physical audit of existing mounts, active equipment loading profile calculation (weight, EPA, mounting dimensions for 3x 8T8R RRU, 3x macro antennas/AAUs, AMB brackets, hybrid trunk cable), and mounting interface verification. STANDBY BASELINE — TIER 3 OPERATOR OWN-BUILD: Vendor provides full turnkey 3D finite-element structural wind loading simulation based on TIA-222-H / NSCP 2015 site-specific basic wind speed (250 km/h to 315 km/h, Category 5 typhoon standard), foundation capacity verification, and formal Structural Analysis Report wet-sealed by a licensed Philippine Professional Civil/Structural Engineer].
+• Inclusions: Physical mount audit, active equipment EPA/weight loading dossier, interface sign-off; (for Tier 3 Own-Build: full 250-315 km/h TIA-222-H wind modeling, foundation check, licensed PE wet-seal).
+• Exclusions: Tower reinforcement civil execution (governed by separate structural modification call-out rate card CALL-06); TowerCo structural analysis on leased towers (TowerCo MLA scope).</t>
         </is>
       </c>
       <c r="D17" s="80" t="inlineStr">
@@ -7341,48 +7554,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E17" s="82" t="n">
+      <c r="E17" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F17" s="82" t="n">
+      <c r="F17" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G17" s="83" t="n"/>
-      <c r="H17" s="84">
-        <f>G17*55</f>
-        <v/>
-      </c>
-      <c r="I17" s="85">
-        <f>E17*G17</f>
+      <c r="G17" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H17" s="99" t="n"/>
+      <c r="I17" s="84">
+        <f>H17*55</f>
         <v/>
       </c>
       <c r="J17" s="85">
-        <f>F17*G17</f>
-        <v/>
-      </c>
-      <c r="K17" s="81" t="inlineStr">
-        <is>
-          <t>100% upon submission and acceptance of the PE-Endorsed Structural Analysis Report.</t>
-        </is>
-      </c>
-      <c r="L17" s="81" t="inlineStr">
-        <is>
-          <t>PE-Signed Structural Engineering Analysis &amp; Loading Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+        <f>E17*H17</f>
+        <v/>
+      </c>
+      <c r="K17" s="85">
+        <f>F17*H17</f>
+        <v/>
+      </c>
+      <c r="L17" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M17" s="96" t="inlineStr">
+        <is>
+          <t>Certified Structural Loading Dossier &amp; Mount Endorsement / PE-Signed SAR (Tier 3 Own-Build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="80" t="inlineStr">
         <is>
           <t>ENG-03</t>
         </is>
       </c>
-      <c r="B18" s="81" t="inlineStr">
+      <c r="B18" s="96" t="inlineStr">
         <is>
           <t>Electrical, DC Power &amp; Earth Grounding Engineering Assessment</t>
         </is>
       </c>
-      <c r="C18" s="81" t="inlineStr">
+      <c r="C18" s="97" t="inlineStr">
         <is>
           <t>Electrical engineering audit of commercial AC utility power and DC power plant: inspection of transformer capacity (kVA), service entrance voltage, phase balance, AC main breaker rating; assessment of existing DC power plant (rectifier total capacity, SMPS controller, available DC branch breakers &gt;= 63A for new radio load); calculation of LiFePO4 battery autonomy (minimum 4.0h @ 3.0 kW load, &lt;= 80% DoD); and 3-point fall-of-potential earth resistance measurement of the grounding grid, mandating &lt;= 5.0 Ohms pursuant to Philippine Electrical Code (PEC) and TelTech engineering specifications.
 • Inclusions: Commercial power audit, DC rectifier capacity calculation, battery autonomy simulation, 3-point earth test.
@@ -7394,48 +7612,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E18" s="82" t="n">
+      <c r="E18" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F18" s="82" t="n">
+      <c r="F18" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G18" s="83" t="n"/>
-      <c r="H18" s="84">
-        <f>G18*55</f>
-        <v/>
-      </c>
-      <c r="I18" s="85">
-        <f>E18*G18</f>
+      <c r="G18" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H18" s="99" t="n"/>
+      <c r="I18" s="84">
+        <f>H18*55</f>
         <v/>
       </c>
       <c r="J18" s="85">
-        <f>F18*G18</f>
-        <v/>
-      </c>
-      <c r="K18" s="81" t="inlineStr">
-        <is>
-          <t>100% upon Operator acceptance of Electrical &amp; Power Assessment Report.</t>
-        </is>
-      </c>
-      <c r="L18" s="81" t="inlineStr">
+        <f>E18*H18</f>
+        <v/>
+      </c>
+      <c r="K18" s="85">
+        <f>F18*H18</f>
+        <v/>
+      </c>
+      <c r="L18" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M18" s="96" t="inlineStr">
         <is>
           <t>Electrical, Power &amp; Grounding Engineering Assessment Report</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="80" t="inlineStr">
         <is>
           <t>ENG-04</t>
         </is>
       </c>
-      <c r="B19" s="81" t="inlineStr">
+      <c r="B19" s="96" t="inlineStr">
         <is>
           <t>RF Engineering Siting, Line-of-Sight (LOS) &amp; Clutter Assessment</t>
         </is>
       </c>
-      <c r="C19" s="81" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>On-site RF validation of nominal design coverage over target barangay demand centroid: physical line-of-sight (LOS) inspection at proposed antenna centerlines (30m, 35m, 40m AGL); clutter height and foliage density classification; identification of close-in obstructions within 200m of sector azimuths (0°, 120°, 240°); calculation of first Fresnel zone clearance; and field verification that simulated coverage will achieve target cell-edge RSRP &gt;= -95 dBm and SINR &gt;= 6 dB.
 • Inclusions: On-ground visual LOS audit, clutter verification, azimuth clearance check, RF siting validation report.
@@ -7447,48 +7670,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E19" s="82" t="n">
+      <c r="E19" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F19" s="82" t="n">
+      <c r="F19" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G19" s="83" t="n"/>
-      <c r="H19" s="84">
-        <f>G19*55</f>
-        <v/>
-      </c>
-      <c r="I19" s="85">
-        <f>E19*G19</f>
+      <c r="G19" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H19" s="99" t="n"/>
+      <c r="I19" s="84">
+        <f>H19*55</f>
         <v/>
       </c>
       <c r="J19" s="85">
-        <f>F19*G19</f>
-        <v/>
-      </c>
-      <c r="K19" s="81" t="inlineStr">
-        <is>
-          <t>100% upon RF Engineering approval of Siting &amp; LOS Report.</t>
-        </is>
-      </c>
-      <c r="L19" s="81" t="inlineStr">
+        <f>E19*H19</f>
+        <v/>
+      </c>
+      <c r="K19" s="85">
+        <f>F19*H19</f>
+        <v/>
+      </c>
+      <c r="L19" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M19" s="96" t="inlineStr">
         <is>
           <t>RF Siting &amp; Line-of-Sight (LOS) Clearance Report</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="80" t="inlineStr">
         <is>
           <t>ENG-05</t>
         </is>
       </c>
-      <c r="B20" s="81" t="inlineStr">
+      <c r="B20" s="96" t="inlineStr">
         <is>
           <t>Detailed Engineering Design (DED) &amp; Technical Site Survey Report (TSSR)</t>
         </is>
       </c>
-      <c r="C20" s="81" t="inlineStr">
+      <c r="C20" s="97" t="inlineStr">
         <is>
           <t>Consolidation of multidisciplinary survey data into a complete Detailed Engineering Design (DED) blueprint package and Technical Site Survey Report (TSSR): Architectural Site Layout Plan; Tower Elevation &amp; Antenna Orientation Plan; Antenna Mounting Bracket (AMB) Fabrication Details; Cable Ladder, Gantry &amp; Cable Tray Routing Plan; Electrical Single Line Diagram (SLD); Earth Grounding Ring &amp; Lightning Protection Layout; Site Bill of Quantities (BoQ); and formal endorsement by licensed Professional Engineers (PE-Civil/Structural, PE-Electrical, PECE-Electronics) conforming to NBCP and PEC.
 • Inclusions: AutoCAD DED drawings, multi-PE signed &amp; sealed plans, BoQ compilation, full TSSR dossier submission.
@@ -7500,48 +7728,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E20" s="82" t="n">
+      <c r="E20" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F20" s="82" t="n">
+      <c r="F20" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G20" s="83" t="n"/>
-      <c r="H20" s="84">
-        <f>G20*55</f>
-        <v/>
-      </c>
-      <c r="I20" s="85">
-        <f>E20*G20</f>
+      <c r="G20" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H20" s="99" t="n"/>
+      <c r="I20" s="84">
+        <f>H20*55</f>
         <v/>
       </c>
       <c r="J20" s="85">
-        <f>F20*G20</f>
-        <v/>
-      </c>
-      <c r="K20" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal joint Operator-TowerCo TSSR approval.</t>
-        </is>
-      </c>
-      <c r="L20" s="81" t="inlineStr">
+        <f>E20*H20</f>
+        <v/>
+      </c>
+      <c r="K20" s="85">
+        <f>F20*H20</f>
+        <v/>
+      </c>
+      <c r="L20" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M20" s="96" t="inlineStr">
         <is>
           <t>Approved TSSR Dossier with PE Signed &amp; Sealed CAD Blueprints</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="40" customHeight="1">
       <c r="A21" s="80" t="inlineStr">
         <is>
           <t>ENG-06</t>
         </is>
       </c>
-      <c r="B21" s="81" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>As-Built Engineering Documentation &amp; Final Completion Dossier</t>
         </is>
       </c>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Comprehensive post-construction field engineering audit capturing all redline installation adjustments: updating AutoCAD drawings to reflect exact as-built antenna heights, azimuths, mechanical tilts, optical cable routes, rack layouts, breaker allocations, and grounding busbar termination points; compiling comprehensive photographic completion book (minimum 50 high-res timestamped photos per site); and securing final Professional Engineer endorsement.
 • Inclusions: Field redline audit, final CAD as-built drawings (DWG &amp; PDF), photographic completion book, PE endorsement.
@@ -7553,66 +7786,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E21" s="82" t="n">
+      <c r="E21" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F21" s="82" t="n">
+      <c r="F21" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G21" s="83" t="n"/>
-      <c r="H21" s="84">
-        <f>G21*55</f>
-        <v/>
-      </c>
-      <c r="I21" s="85">
-        <f>E21*G21</f>
+      <c r="G21" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H21" s="99" t="n"/>
+      <c r="I21" s="84">
+        <f>H21*55</f>
         <v/>
       </c>
       <c r="J21" s="85">
-        <f>F21*G21</f>
-        <v/>
-      </c>
-      <c r="K21" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal issuance of the Final Acceptance Certificate (FAC).</t>
-        </is>
-      </c>
-      <c r="L21" s="81" t="inlineStr">
+        <f>E21*H21</f>
+        <v/>
+      </c>
+      <c r="K21" s="85">
+        <f>F21*H21</f>
+        <v/>
+      </c>
+      <c r="L21" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M21" s="96" t="inlineStr">
         <is>
           <t>Final As-Built CAD Drawings (DWG &amp; PDF) + Photographic Completion Book</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="78" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: RADIO NETWORK PLANNING &amp; DESIGN</t>
         </is>
       </c>
-      <c r="B22" s="79" t="n"/>
-      <c r="C22" s="79" t="n"/>
-      <c r="D22" s="79" t="n"/>
-      <c r="E22" s="79" t="n"/>
-      <c r="F22" s="79" t="n"/>
-      <c r="G22" s="79" t="n"/>
-      <c r="H22" s="79" t="n"/>
-      <c r="I22" s="79" t="n"/>
-      <c r="J22" s="79" t="n"/>
-      <c r="K22" s="79" t="n"/>
-      <c r="L22" s="79" t="n"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+    </row>
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="80" t="inlineStr">
         <is>
           <t>RNPD-01</t>
         </is>
       </c>
-      <c r="B23" s="81" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Macro RF Nominal Planning &amp; 3D Propagation Modeling</t>
         </is>
       </c>
-      <c r="C23" s="81" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>Macro-level 5G RF network planning using advanced 3D ray-tracing propagation modeling engines, calibrated against high-resolution 5-meter clutter models and Digital Terrain Models (DTM). Sizing and generation of nominal candidate search rings across high-density suburban and rural barangay centroids; multi-carrier capacity dimensioning for Band n50 (60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD); coverage prediction mapping (RSRP, SINR, Best Server, Downlink/Uplink Throughput); and inter-site distance (ISD) optimization.
 • Inclusions: 3D ray-tracing simulation, clutter model calibration, nominal site planning, search ring generation.
@@ -7624,48 +7851,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E23" s="82" t="n">
+      <c r="E23" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F23" s="82" t="n">
+      <c r="F23" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G23" s="83" t="n"/>
-      <c r="H23" s="84">
-        <f>G23*55</f>
-        <v/>
-      </c>
-      <c r="I23" s="85">
-        <f>E23*G23</f>
+      <c r="G23" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H23" s="99" t="n"/>
+      <c r="I23" s="84">
+        <f>H23*55</f>
         <v/>
       </c>
       <c r="J23" s="85">
-        <f>F23*G23</f>
-        <v/>
-      </c>
-      <c r="K23" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal Operator approval of the Nominal RF Network Design Package.</t>
-        </is>
-      </c>
-      <c r="L23" s="81" t="inlineStr">
+        <f>E23*H23</f>
+        <v/>
+      </c>
+      <c r="K23" s="85">
+        <f>F23*H23</f>
+        <v/>
+      </c>
+      <c r="L23" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M23" s="96" t="inlineStr">
         <is>
           <t>Nominal RF Network Design Package &amp; Ray-Tracing Simulation Dossier</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="80" t="inlineStr">
         <is>
           <t>RNPD-02</t>
         </is>
       </c>
-      <c r="B24" s="81" t="inlineStr">
+      <c r="B24" s="96" t="inlineStr">
         <is>
           <t>Cell Design Data (CDD) Engineering &amp; Parameter Allocation</t>
         </is>
       </c>
-      <c r="C24" s="81" t="inlineStr">
+      <c r="C24" s="97" t="inlineStr">
         <is>
           <t>Engineering, generation, and validation of detailed site-specific Cell Design Data (CDD) sheets: cell naming taxonomy, gNodeB IDs, Physical Cell ID (PCI) planning adhering to modulo-3 and modulo-30 collision rules, Root Sequence Index (RSI), Tracking Area Codes (TAC), Neighbor Cell Lists (NCL / ANR), PRACH configuration, absolute radio-frequency channel numbers (ARFCN), per-carrier transmit power, and antenna configuration parameters (azimuth, mechanical tilt, eRET ranges).
 • Inclusions: CDD parameter engineering, PCI planning, neighbor list generation, configuration script generation.
@@ -7677,66 +7909,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E24" s="82" t="n">
+      <c r="E24" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F24" s="82" t="n">
+      <c r="F24" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G24" s="83" t="n"/>
-      <c r="H24" s="84">
-        <f>G24*55</f>
-        <v/>
-      </c>
-      <c r="I24" s="85">
-        <f>E24*G24</f>
+      <c r="G24" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H24" s="99" t="n"/>
+      <c r="I24" s="84">
+        <f>H24*55</f>
         <v/>
       </c>
       <c r="J24" s="85">
-        <f>F24*G24</f>
-        <v/>
-      </c>
-      <c r="K24" s="81" t="inlineStr">
-        <is>
-          <t>100% upon validation and successful upload of CDD parameters into the network EMS/OSS.</t>
-        </is>
-      </c>
-      <c r="L24" s="81" t="inlineStr">
+        <f>E24*H24</f>
+        <v/>
+      </c>
+      <c r="K24" s="85">
+        <f>F24*H24</f>
+        <v/>
+      </c>
+      <c r="L24" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M24" s="96" t="inlineStr">
         <is>
           <t>Approved Cell Design Data (CDD) Sheet &amp; Parameter Script</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="78" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: TELECOM LOGISTICS &amp; MATERIAL HANDLING</t>
         </is>
       </c>
-      <c r="B25" s="79" t="n"/>
-      <c r="C25" s="79" t="n"/>
-      <c r="D25" s="79" t="n"/>
-      <c r="E25" s="79" t="n"/>
-      <c r="F25" s="79" t="n"/>
-      <c r="G25" s="79" t="n"/>
-      <c r="H25" s="79" t="n"/>
-      <c r="I25" s="79" t="n"/>
-      <c r="J25" s="79" t="n"/>
-      <c r="K25" s="79" t="n"/>
-      <c r="L25" s="79" t="n"/>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+    </row>
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="80" t="inlineStr">
         <is>
           <t>LOG-01</t>
         </is>
       </c>
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="96" t="inlineStr">
         <is>
           <t>Central &amp; Regional Warehousing, Buffer Staging &amp; Serialized Asset Tagging</t>
         </is>
       </c>
-      <c r="C26" s="81" t="inlineStr">
+      <c r="C26" s="97" t="inlineStr">
         <is>
           <t>Receipt of OEM shipments at Port of Manila / Batangas; bonded climate-controlled warehousing in central Mega Manila and regional hubs (North Luzon, South Luzon, Visayas, Mindanao); unboxing, physical inspection, and QA damage checking; barcode asset tagging at serial-number level; updating Operator ERP/WMS inventory records; and maintaining segregated buffer stock.
 • Inclusions: Warehouse facility, security, ERP tracking, barcode tagging, climate control, buffer stock management.
@@ -7748,48 +7974,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E26" s="82" t="n">
+      <c r="E26" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F26" s="82" t="n">
+      <c r="F26" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G26" s="83" t="n"/>
-      <c r="H26" s="84">
-        <f>G26*55</f>
-        <v/>
-      </c>
-      <c r="I26" s="85">
-        <f>E26*G26</f>
+      <c r="G26" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H26" s="99" t="n"/>
+      <c r="I26" s="84">
+        <f>H26*55</f>
         <v/>
       </c>
       <c r="J26" s="85">
-        <f>F26*G26</f>
-        <v/>
-      </c>
-      <c r="K26" s="81" t="inlineStr">
-        <is>
-          <t>100% upon material receipt, inspection, and barcode registration into inventory ERP.</t>
-        </is>
-      </c>
-      <c r="L26" s="81" t="inlineStr">
+        <f>E26*H26</f>
+        <v/>
+      </c>
+      <c r="K26" s="85">
+        <f>F26*H26</f>
+        <v/>
+      </c>
+      <c r="L26" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M26" s="96" t="inlineStr">
         <is>
           <t>Serialized Inventory Receiving Report &amp; Barcode Registry</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="80" t="inlineStr">
         <is>
           <t>LOG-02</t>
         </is>
       </c>
-      <c r="B27" s="81" t="inlineStr">
+      <c r="B27" s="96" t="inlineStr">
         <is>
           <t>Site BOM Kitting, Staging &amp; Pre-Assembly Services</t>
         </is>
       </c>
-      <c r="C27" s="81" t="inlineStr">
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>Assembly and kitting of site-specific deployment packages: picking 1x BBU, 3x 8T8R RRUs, 3x macro antennas/AAUs, optical patchcords, DC power cables, Type 2 SPDs, grounding kits, and hardware accessories; pre-cutting cable lengths based on approved TSSR; labeling; staging in protective crates; and performing bench test pre-checks and firmware pre-flashing.
 • Inclusions: Picking, staging, pre-cutting cables, labeling, firmware pre-flashing, packaging into site kits.
@@ -7801,48 +8032,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E27" s="82" t="n">
+      <c r="E27" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F27" s="82" t="n">
+      <c r="F27" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G27" s="83" t="n"/>
-      <c r="H27" s="84">
-        <f>G27*55</f>
-        <v/>
-      </c>
-      <c r="I27" s="85">
-        <f>E27*G27</f>
+      <c r="G27" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H27" s="99" t="n"/>
+      <c r="I27" s="84">
+        <f>H27*55</f>
         <v/>
       </c>
       <c r="J27" s="85">
-        <f>F27*G27</f>
-        <v/>
-      </c>
-      <c r="K27" s="81" t="inlineStr">
-        <is>
-          <t>100% upon staging and issuance of Site Dispatch Slip.</t>
-        </is>
-      </c>
-      <c r="L27" s="81" t="inlineStr">
+        <f>E27*H27</f>
+        <v/>
+      </c>
+      <c r="K27" s="85">
+        <f>F27*H27</f>
+        <v/>
+      </c>
+      <c r="L27" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M27" s="96" t="inlineStr">
         <is>
           <t>Site BOM Kitting Slip &amp; Staging Inspection Checklist</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="80" t="inlineStr">
         <is>
           <t>LOG-03</t>
         </is>
       </c>
-      <c r="B28" s="81" t="inlineStr">
+      <c r="B28" s="96" t="inlineStr">
         <is>
           <t>Regional Transport &amp; Final-Mile Rough-Road Site Hauling</t>
         </is>
       </c>
-      <c r="C28" s="81" t="inlineStr">
+      <c r="C28" s="97" t="inlineStr">
         <is>
           <t>Transportation from central warehouse to regional hubs via heavy freight, followed by dedicated final-mile transport to remote barangay site locations utilizing heavy-duty 4x4 trucks, motorized bancas/barges (for island sites), or manual porterage across unpaved rough-road terrain; comprehensive in-transit cargo insurance; and on-site offloading.
 • Inclusions: Long-haul freight, final-mile 4x4 hauling, manual porterage, transit insurance, on-site offloading.
@@ -7854,66 +8090,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E28" s="82" t="n">
+      <c r="E28" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F28" s="82" t="n">
+      <c r="F28" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G28" s="83" t="n"/>
-      <c r="H28" s="84">
-        <f>G28*55</f>
-        <v/>
-      </c>
-      <c r="I28" s="85">
-        <f>E28*G28</f>
+      <c r="G28" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H28" s="99" t="n"/>
+      <c r="I28" s="84">
+        <f>H28*55</f>
         <v/>
       </c>
       <c r="J28" s="85">
-        <f>F28*G28</f>
-        <v/>
-      </c>
-      <c r="K28" s="81" t="inlineStr">
-        <is>
-          <t>100% upon verified on-site delivery and execution of Material Receiving Report (MRR).</t>
-        </is>
-      </c>
-      <c r="L28" s="81" t="inlineStr">
+        <f>E28*H28</f>
+        <v/>
+      </c>
+      <c r="K28" s="85">
+        <f>F28*H28</f>
+        <v/>
+      </c>
+      <c r="L28" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M28" s="96" t="inlineStr">
         <is>
           <t>Signed Material Receiving Report (MRR) by on-site supervisor</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="78" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: TELECOM INSTALLATION, COMMISSIONING &amp; INTEGRATION</t>
         </is>
       </c>
-      <c r="B29" s="79" t="n"/>
-      <c r="C29" s="79" t="n"/>
-      <c r="D29" s="79" t="n"/>
-      <c r="E29" s="79" t="n"/>
-      <c r="F29" s="79" t="n"/>
-      <c r="G29" s="79" t="n"/>
-      <c r="H29" s="79" t="n"/>
-      <c r="I29" s="79" t="n"/>
-      <c r="J29" s="79" t="n"/>
-      <c r="K29" s="79" t="n"/>
-      <c r="L29" s="79" t="n"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+    </row>
+    <row r="30" ht="40" customHeight="1">
       <c r="A30" s="80" t="inlineStr">
         <is>
           <t>TI-01</t>
         </is>
       </c>
-      <c r="B30" s="81" t="inlineStr">
+      <c r="B30" s="96" t="inlineStr">
         <is>
           <t>Tower Rigging &amp; Mechanical Antenna / RRU Installation</t>
         </is>
       </c>
-      <c r="C30" s="81" t="inlineStr">
+      <c r="C30" s="97" t="inlineStr">
         <is>
           <t>Mechanical mounting by certified riggers: hoisting and installing 3x macro high-gain antennas and 3x 8T8R RRUs on tower antenna mounting brackets (AMB) at specified AGL centerlines (30m to 45m); setting precise mechanical downtilt and sector azimuths (0°, 120°, 240°) using calibrated digital inclinometers and compasses; and installing AISG 2.0 eRET control cables.
 • Inclusions: Tower rigging crews, safety equipment, hoisting gear, AMB mounting, antenna and RRU installation.
@@ -7925,48 +8155,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E30" s="82" t="n">
+      <c r="E30" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F30" s="82" t="n">
+      <c r="F30" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G30" s="83" t="n"/>
-      <c r="H30" s="84">
-        <f>G30*55</f>
-        <v/>
-      </c>
-      <c r="I30" s="85">
-        <f>E30*G30</f>
+      <c r="G30" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H30" s="99" t="n"/>
+      <c r="I30" s="84">
+        <f>H30*55</f>
         <v/>
       </c>
       <c r="J30" s="85">
-        <f>F30*G30</f>
-        <v/>
-      </c>
-      <c r="K30" s="81" t="inlineStr">
-        <is>
-          <t>50% upon mechanical mounting completion; 50% upon joint rigging inspection.</t>
-        </is>
-      </c>
-      <c r="L30" s="81" t="inlineStr">
+        <f>E30*H30</f>
+        <v/>
+      </c>
+      <c r="K30" s="85">
+        <f>F30*H30</f>
+        <v/>
+      </c>
+      <c r="L30" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M30" s="96" t="inlineStr">
         <is>
           <t>Mechanical Rigging &amp; Antenna Alignment Inspection Sheet</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="80" t="inlineStr">
         <is>
           <t>TI-02</t>
         </is>
       </c>
-      <c r="B31" s="81" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>RF, Optical Fiber &amp; DC Power Cabling Installation</t>
         </is>
       </c>
-      <c r="C31" s="81" t="inlineStr">
+      <c r="C31" s="97" t="inlineStr">
         <is>
           <t>Routing, fastening, and dressing armored multi-core optical fiber jumpers and DC power cables along tower cable ladders and horizontal gantries; installing cold-shrink weatherproof boots on all 7/16 DIN or 4.3-10 RF connectors; installing Type 2 DC Surge Protection Devices (SPD) at tower top and base; and bonding 3-point grounding kits to the external ground busbar.
 • Inclusions: Cable routing, cleating, hydraulic crimping, weatherproofing, SPD installation, grounding bond.
@@ -7978,48 +8213,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E31" s="82" t="n">
+      <c r="E31" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F31" s="82" t="n">
+      <c r="F31" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G31" s="83" t="n"/>
-      <c r="H31" s="84">
-        <f>G31*55</f>
-        <v/>
-      </c>
-      <c r="I31" s="85">
-        <f>E31*G31</f>
+      <c r="G31" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H31" s="99" t="n"/>
+      <c r="I31" s="84">
+        <f>H31*55</f>
         <v/>
       </c>
       <c r="J31" s="85">
-        <f>F31*G31</f>
-        <v/>
-      </c>
-      <c r="K31" s="81" t="inlineStr">
-        <is>
-          <t>50% upon cabling installation; 50% upon weatherproofing and grounding sign-off.</t>
-        </is>
-      </c>
-      <c r="L31" s="81" t="inlineStr">
+        <f>E31*H31</f>
+        <v/>
+      </c>
+      <c r="K31" s="85">
+        <f>F31*H31</f>
+        <v/>
+      </c>
+      <c r="L31" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M31" s="96" t="inlineStr">
         <is>
           <t>Cabling Installation &amp; Weatherproofing Quality Checklist</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="80" t="inlineStr">
         <is>
           <t>TI-03</t>
         </is>
       </c>
-      <c r="B32" s="81" t="inlineStr">
+      <c r="B32" s="96" t="inlineStr">
         <is>
           <t>Baseband Unit (BBU) Installation &amp; Cabinet Wiring</t>
         </is>
       </c>
-      <c r="C32" s="81" t="inlineStr">
+      <c r="C32" s="97" t="inlineStr">
         <is>
           <t>19" rack installation of 5G Baseband Unit (BBU) in outdoor equipment cabinet or shelter; dual -48V DC power wiring to dedicated distribution breakers; routing backhaul transmission optical patchcords to fiber demarcation router; and installing GNSS/GPS antenna and surge arrester with unobstructed sky view for PTP/SyncE clock synchronization.
 • Inclusions: Rack mounting, DC wiring, optical patchcord routing, GPS antenna installation, labeling.
@@ -8031,48 +8271,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E32" s="82" t="n">
+      <c r="E32" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F32" s="82" t="n">
+      <c r="F32" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G32" s="83" t="n"/>
-      <c r="H32" s="84">
-        <f>G32*55</f>
-        <v/>
-      </c>
-      <c r="I32" s="85">
-        <f>E32*G32</f>
+      <c r="G32" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H32" s="99" t="n"/>
+      <c r="I32" s="84">
+        <f>H32*55</f>
         <v/>
       </c>
       <c r="J32" s="85">
-        <f>F32*G32</f>
-        <v/>
-      </c>
-      <c r="K32" s="81" t="inlineStr">
-        <is>
-          <t>100% upon BBU rack installation and DC power-up.</t>
-        </is>
-      </c>
-      <c r="L32" s="81" t="inlineStr">
+        <f>E32*H32</f>
+        <v/>
+      </c>
+      <c r="K32" s="85">
+        <f>F32*H32</f>
+        <v/>
+      </c>
+      <c r="L32" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M32" s="96" t="inlineStr">
         <is>
           <t>BBU Installation &amp; Cabinet Wiring Verification Sheet</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="80" t="inlineStr">
         <is>
           <t>TI-04</t>
         </is>
       </c>
-      <c r="B33" s="81" t="inlineStr">
+      <c r="B33" s="96" t="inlineStr">
         <is>
           <t>Telecom Commissioning, Sweep Testing &amp; Power-Up</t>
         </is>
       </c>
-      <c r="C33" s="81" t="inlineStr">
+      <c r="C33" s="97" t="inlineStr">
         <is>
           <t>DC power turn-up, voltage and polarity verification; firmware loading and diagnostic testing; optical transceiver Rx/Tx power level verification; and calibrated RF sweep testing measuring Return Loss (&gt;= 16.5 dB) and VSWR (&lt;= 1.35:1) across all antenna ports and jumpers using a calibrated SiteMaster analyzer.
 • Inclusions: Commissioning turn-up, firmware loading, optical power check, VSWR sweep testing, test trace logs.
@@ -8084,48 +8329,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E33" s="82" t="n">
+      <c r="E33" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F33" s="82" t="n">
+      <c r="F33" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G33" s="83" t="n"/>
-      <c r="H33" s="84">
-        <f>G33*55</f>
-        <v/>
-      </c>
-      <c r="I33" s="85">
-        <f>E33*G33</f>
+      <c r="G33" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H33" s="99" t="n"/>
+      <c r="I33" s="84">
+        <f>H33*55</f>
         <v/>
       </c>
       <c r="J33" s="85">
-        <f>F33*G33</f>
-        <v/>
-      </c>
-      <c r="K33" s="81" t="inlineStr">
-        <is>
-          <t>100% upon successful sweep testing and commissioning approval.</t>
-        </is>
-      </c>
-      <c r="L33" s="81" t="inlineStr">
+        <f>E33*H33</f>
+        <v/>
+      </c>
+      <c r="K33" s="85">
+        <f>F33*H33</f>
+        <v/>
+      </c>
+      <c r="L33" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M33" s="96" t="inlineStr">
         <is>
           <t>Commissioning Test Log &amp; VSWR/Return Loss Sweep Traces</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="40" customHeight="1">
       <c r="A34" s="80" t="inlineStr">
         <is>
           <t>TI-05</t>
         </is>
       </c>
-      <c r="B34" s="81" t="inlineStr">
+      <c r="B34" s="96" t="inlineStr">
         <is>
           <t>gNodeB Network Integration &amp; OSS Commercial On-Air</t>
         </is>
       </c>
-      <c r="C34" s="81" t="inlineStr">
+      <c r="C34" s="97" t="inlineStr">
         <is>
           <t>Transmission IP integration (VLAN, BGP, IPsec); establishing S1-U / N2/N3 control and user plane interfaces to 5G Core (AMF/UPF); synchronization with TelTech EMS/OSS; activating 3 sectors on Band n50 (60 MHz NCR / up to 80 MHz Provincial, Software-Configurable 40/50/60/80 MHz TDD); clearing all active alarms; and achieving stable commercial on-air operational state.
 • Inclusions: IP configuration, Core integration, OSS synchronization, carrier activation, alarm clearance.
@@ -8137,66 +8387,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E34" s="82" t="n">
+      <c r="E34" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F34" s="82" t="n">
+      <c r="F34" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G34" s="83" t="n"/>
-      <c r="H34" s="84">
-        <f>G34*55</f>
-        <v/>
-      </c>
-      <c r="I34" s="85">
-        <f>E34*G34</f>
+      <c r="G34" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H34" s="99" t="n"/>
+      <c r="I34" s="84">
+        <f>H34*55</f>
         <v/>
       </c>
       <c r="J34" s="85">
-        <f>F34*G34</f>
-        <v/>
-      </c>
-      <c r="K34" s="81" t="inlineStr">
-        <is>
-          <t>100% upon site on-air declaration and alarm-free verification.</t>
-        </is>
-      </c>
-      <c r="L34" s="81" t="inlineStr">
+        <f>E34*H34</f>
+        <v/>
+      </c>
+      <c r="K34" s="85">
+        <f>F34*H34</f>
+        <v/>
+      </c>
+      <c r="L34" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M34" s="96" t="inlineStr">
         <is>
           <t>Commercial On-Air Certificate &amp; OSS Alarm-Free Screenshot</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="78" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: SINGLE SITE VERIFICATION &amp; ACCEPTANCE</t>
         </is>
       </c>
-      <c r="B35" s="79" t="n"/>
-      <c r="C35" s="79" t="n"/>
-      <c r="D35" s="79" t="n"/>
-      <c r="E35" s="79" t="n"/>
-      <c r="F35" s="79" t="n"/>
-      <c r="G35" s="79" t="n"/>
-      <c r="H35" s="79" t="n"/>
-      <c r="I35" s="79" t="n"/>
-      <c r="J35" s="79" t="n"/>
-      <c r="K35" s="79" t="n"/>
-      <c r="L35" s="79" t="n"/>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+    </row>
+    <row r="36" ht="40" customHeight="1">
       <c r="A36" s="80" t="inlineStr">
         <is>
           <t>ACC-01</t>
         </is>
       </c>
-      <c r="B36" s="81" t="inlineStr">
+      <c r="B36" s="96" t="inlineStr">
         <is>
           <t>Mechanical, Civil &amp; Electrical Site Acceptance (ATP-A)</t>
         </is>
       </c>
-      <c r="C36" s="81" t="inlineStr">
+      <c r="C36" s="97" t="inlineStr">
         <is>
           <t>Joint physical on-site inspection: verifying bolt torque marks on tower mounts, cable ladder fastening, cable tray grounding, weatherproofing seal integrity, electrical breaker labeling, 3-point earth ground resistance audit (confirming &lt;= 5.0 Ohms), compound housekeeping, and punchlist compilation and clearance.
 • Inclusions: Joint physical audit, torque inspection, grounding verification, punchlist clearance.
@@ -8208,48 +8452,53 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E36" s="82" t="n">
+      <c r="E36" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F36" s="82" t="n">
+      <c r="F36" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G36" s="83" t="n"/>
-      <c r="H36" s="84">
-        <f>G36*55</f>
-        <v/>
-      </c>
-      <c r="I36" s="85">
-        <f>E36*G36</f>
+      <c r="G36" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H36" s="99" t="n"/>
+      <c r="I36" s="84">
+        <f>H36*55</f>
         <v/>
       </c>
       <c r="J36" s="85">
-        <f>F36*G36</f>
-        <v/>
-      </c>
-      <c r="K36" s="81" t="inlineStr">
-        <is>
-          <t>100% upon joint ATP-A punchlist clearance and sign-off.</t>
-        </is>
-      </c>
-      <c r="L36" s="81" t="inlineStr">
+        <f>E36*H36</f>
+        <v/>
+      </c>
+      <c r="K36" s="85">
+        <f>F36*H36</f>
+        <v/>
+      </c>
+      <c r="L36" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M36" s="96" t="inlineStr">
         <is>
           <t>Signed ATP-A Certificate &amp; Punchlist Clearance Sheet</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="80" t="inlineStr">
         <is>
           <t>ACC-02</t>
         </is>
       </c>
-      <c r="B37" s="81" t="inlineStr">
+      <c r="B37" s="96" t="inlineStr">
         <is>
           <t>Active Telecom &amp; Functional Acceptance (ATP-B)</t>
         </is>
       </c>
-      <c r="C37" s="81" t="inlineStr">
+      <c r="C37" s="97" t="inlineStr">
         <is>
           <t>Remote and local active functional testing: verifying 8T8R MU-MIMO operation, electronic downtilt (eRET) remote control functionality via OSS, power fail / mains failure alarm simulation, optical fiber failover test, and carrier shutdown/restart diagnostic tests to ensure robust autonomic operation.
 • Inclusions: Remote EMS diagnostic testing, alarm simulation, eRET control validation, MIMO verification.
@@ -8261,51 +8510,56 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E37" s="82" t="n">
+      <c r="E37" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F37" s="82" t="n">
+      <c r="F37" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G37" s="83" t="n"/>
-      <c r="H37" s="84">
-        <f>G37*55</f>
-        <v/>
-      </c>
-      <c r="I37" s="85">
-        <f>E37*G37</f>
+      <c r="G37" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H37" s="99" t="n"/>
+      <c r="I37" s="84">
+        <f>H37*55</f>
         <v/>
       </c>
       <c r="J37" s="85">
-        <f>F37*G37</f>
-        <v/>
-      </c>
-      <c r="K37" s="81" t="inlineStr">
-        <is>
-          <t>100% upon joint ATP-B sign-off.</t>
-        </is>
-      </c>
-      <c r="L37" s="81" t="inlineStr">
+        <f>E37*H37</f>
+        <v/>
+      </c>
+      <c r="K37" s="85">
+        <f>F37*H37</f>
+        <v/>
+      </c>
+      <c r="L37" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M37" s="96" t="inlineStr">
         <is>
           <t>Signed ATP-B Functional Acceptance Certificate</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="80" t="inlineStr">
         <is>
           <t>ACC-03</t>
         </is>
       </c>
-      <c r="B38" s="81" t="inlineStr">
+      <c r="B38" s="96" t="inlineStr">
         <is>
           <t>Single Site Verification (SSV) &amp; RF Call Testing</t>
         </is>
       </c>
-      <c r="C38" s="81" t="inlineStr">
-        <is>
-          <t>On-ground field testing using 5G test UE and scanner: stationary throughput tests at near, mid, and cell-edge points per sector (validating &gt;= 450 Mbps peak DL, &gt;= 50 Mbps cell-edge DL, &gt;= 15 Mbps cell-edge UL); sector swap validation; intra-site handover execution; latency measurement (&lt;= 18 ms RTT); and compilation and sign-off of the formal SSV Report.
-• Inclusions: Stationary throughput tests, sector swap check, handover test, ping test, SSV report compilation.
+      <c r="C38" s="97" t="inlineStr">
+        <is>
+          <t>On-ground field testing using 5G test UE and scanner: stationary throughput tests at near, mid, and cell-edge points per sector (validating &gt;= 450 Mbps peak DL, &gt;= 50 Mbps cell-edge DL, &gt;= 15 Mbps cell-edge UL); sector swap validation; intra-site handover execution; latency verification across backhaul media (Terrestrial Fiber: Target RTT &lt;= 18 ms to Core UPF, with Contractual Acceptance Rejection Ceiling &lt;= 30 ms per Appendix C KPI-RAN-07 and Bid Bulletin 01 §2.3; LEO Satellite Starlink / Expansion: Target RTT &lt;= 50 ms, Contractual Acceptance Rejection Ceiling &lt;= 65 ms); packet loss measurement (&lt; 0.1%); and compilation and formal sign-off of the comprehensive SSV Report.
+• Inclusions: Stationary throughput tests, sector swap check, handover test, latency compliance test (&lt;= 30 ms fiber ceiling / &lt;= 65 ms satellite ceiling), SSV report compilation.
 • Exclusions: Multi-site cluster drive testing (covered under Category 7).</t>
         </is>
       </c>
@@ -8314,66 +8568,60 @@
           <t>Per Site</t>
         </is>
       </c>
-      <c r="E38" s="82" t="n">
+      <c r="E38" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F38" s="82" t="n">
+      <c r="F38" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G38" s="83" t="n"/>
-      <c r="H38" s="84">
-        <f>G38*55</f>
-        <v/>
-      </c>
-      <c r="I38" s="85">
-        <f>E38*G38</f>
+      <c r="G38" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H38" s="99" t="n"/>
+      <c r="I38" s="84">
+        <f>H38*55</f>
         <v/>
       </c>
       <c r="J38" s="85">
-        <f>F38*G38</f>
-        <v/>
-      </c>
-      <c r="K38" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal SSV Report approval by Operator.</t>
-        </is>
-      </c>
-      <c r="L38" s="81" t="inlineStr">
+        <f>E38*H38</f>
+        <v/>
+      </c>
+      <c r="K38" s="85">
+        <f>F38*H38</f>
+        <v/>
+      </c>
+      <c r="L38" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M38" s="96" t="inlineStr">
         <is>
           <t>Approved Single Site Verification (SSV) Report &amp; Log Files</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="78" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="95" t="inlineStr">
         <is>
           <t>DOMAIN: CLUSTER RADIO NETWORK OPTIMIZATION</t>
         </is>
       </c>
-      <c r="B39" s="79" t="n"/>
-      <c r="C39" s="79" t="n"/>
-      <c r="D39" s="79" t="n"/>
-      <c r="E39" s="79" t="n"/>
-      <c r="F39" s="79" t="n"/>
-      <c r="G39" s="79" t="n"/>
-      <c r="H39" s="79" t="n"/>
-      <c r="I39" s="79" t="n"/>
-      <c r="J39" s="79" t="n"/>
-      <c r="K39" s="79" t="n"/>
-      <c r="L39" s="79" t="n"/>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+    </row>
+    <row r="40" ht="40" customHeight="1">
       <c r="A40" s="80" t="inlineStr">
         <is>
           <t>RNO-01</t>
         </is>
       </c>
-      <c r="B40" s="81" t="inlineStr">
+      <c r="B40" s="96" t="inlineStr">
         <is>
           <t>Pre-Launch Cluster Drive Testing &amp; RF Baseline Audit</t>
         </is>
       </c>
-      <c r="C40" s="81" t="inlineStr">
+      <c r="C40" s="97" t="inlineStr">
         <is>
           <t>Continuous scanner and test UE drive testing across contiguous clusters of 10–20 sites; capturing RSRP, SINR, CQI, throughput, and coverage overlap; and identifying pilot pollution zones, coverage holes, and excessive inter-cell interference.
 • Inclusions: Drive test vehicle, scanner, test UEs, GPS logging, drive test raw log processing, baseline report.
@@ -8382,51 +8630,56 @@
       </c>
       <c r="D40" s="80" t="inlineStr">
         <is>
-          <t>Per Site Share (or Per Cluster)</t>
-        </is>
-      </c>
-      <c r="E40" s="82" t="n">
+          <t>Per Site Share</t>
+        </is>
+      </c>
+      <c r="E40" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F40" s="82" t="n">
+      <c r="F40" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G40" s="83" t="n"/>
-      <c r="H40" s="84">
-        <f>G40*55</f>
-        <v/>
-      </c>
-      <c r="I40" s="85">
-        <f>E40*G40</f>
+      <c r="G40" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H40" s="99" t="n"/>
+      <c r="I40" s="84">
+        <f>H40*55</f>
         <v/>
       </c>
       <c r="J40" s="85">
-        <f>F40*G40</f>
-        <v/>
-      </c>
-      <c r="K40" s="81" t="inlineStr">
-        <is>
-          <t>50% upon completion of cluster drive test and baseline report submission.</t>
-        </is>
-      </c>
-      <c r="L40" s="81" t="inlineStr">
+        <f>E40*H40</f>
+        <v/>
+      </c>
+      <c r="K40" s="85">
+        <f>F40*H40</f>
+        <v/>
+      </c>
+      <c r="L40" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M40" s="96" t="inlineStr">
         <is>
           <t>Cluster Drive Test Raw Logs &amp; RF Baseline Audit Report</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="45" customHeight="1">
+    <row r="41" ht="40" customHeight="1">
       <c r="A41" s="80" t="inlineStr">
         <is>
           <t>RNO-02</t>
         </is>
       </c>
-      <c r="B41" s="81" t="inlineStr">
+      <c r="B41" s="96" t="inlineStr">
         <is>
           <t>Cluster Physical &amp; Soft Parameter Optimization</t>
         </is>
       </c>
-      <c r="C41" s="81" t="inlineStr">
+      <c r="C41" s="97" t="inlineStr">
         <is>
           <t>Iterative optimization across cluster: electronic remote electrical tilt (eRET) adjustments to control cell-edge interference and shape coverage; azimuth and mechanical tilt adjustments where indicated; PCI re-planning to resolve mod-3/mod-30 clashes; neighbor list (NCL) cleanup; handover threshold tuning; and uplink power control adjustments.
 • Inclusions: eRET tuning, PCI re-planning, neighbor tuning, handover optimization, parameter upload script.
@@ -8435,51 +8688,56 @@
       </c>
       <c r="D41" s="80" t="inlineStr">
         <is>
-          <t>Per Site Share (or Per Cluster)</t>
-        </is>
-      </c>
-      <c r="E41" s="82" t="n">
+          <t>Per Site Share</t>
+        </is>
+      </c>
+      <c r="E41" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F41" s="82" t="n">
+      <c r="F41" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G41" s="83" t="n"/>
-      <c r="H41" s="84">
-        <f>G41*55</f>
-        <v/>
-      </c>
-      <c r="I41" s="85">
-        <f>E41*G41</f>
+      <c r="G41" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H41" s="99" t="n"/>
+      <c r="I41" s="84">
+        <f>H41*55</f>
         <v/>
       </c>
       <c r="J41" s="85">
-        <f>F41*G41</f>
-        <v/>
-      </c>
-      <c r="K41" s="81" t="inlineStr">
-        <is>
-          <t>50% upon parameter implementation and verification in OSS.</t>
-        </is>
-      </c>
-      <c r="L41" s="81" t="inlineStr">
+        <f>E41*H41</f>
+        <v/>
+      </c>
+      <c r="K41" s="85">
+        <f>F41*H41</f>
+        <v/>
+      </c>
+      <c r="L41" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M41" s="96" t="inlineStr">
         <is>
           <t>Cluster Parameter Optimization Record &amp; Delta Script</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="80" t="inlineStr">
         <is>
           <t>RNO-03</t>
         </is>
       </c>
-      <c r="B42" s="81" t="inlineStr">
+      <c r="B42" s="96" t="inlineStr">
         <is>
           <t>Cluster Acceptance KPI Validation &amp; Final Sign-Off</t>
         </is>
       </c>
-      <c r="C42" s="81" t="inlineStr">
+      <c r="C42" s="97" t="inlineStr">
         <is>
           <t>Post-tuning verification drive test and OSS 14-day statistical performance audit: validating cluster Radio Availability &gt;= 99.95%, Session Setup Success Rate (CSSR) &gt;= 99.60%, Session Drop Rate (CDDR) &lt;= 0.15%, cluster average DL throughput &gt;= 450 Mbps, cell-edge DL &gt;= 50 Mbps; and submission of formal Cluster Acceptance Dossier.
 • Inclusions: Verification drive test, 14-day OSS KPI statistical audit, benchmark reporting, formal sign-off.
@@ -8491,66 +8749,60 @@
           <t>Per Cluster (65 Clusters Phase 1 / 325 Clusters Program)</t>
         </is>
       </c>
-      <c r="E42" s="82" t="n">
+      <c r="E42" s="98" t="n">
         <v>65</v>
       </c>
-      <c r="F42" s="82" t="n">
+      <c r="F42" s="98" t="n">
         <v>325</v>
       </c>
-      <c r="G42" s="83" t="n"/>
-      <c r="H42" s="84">
-        <f>G42*55</f>
-        <v/>
-      </c>
-      <c r="I42" s="85">
-        <f>E42*G42</f>
+      <c r="G42" s="80" t="inlineStr">
+        <is>
+          <t>1x (Turnkey Rollout)</t>
+        </is>
+      </c>
+      <c r="H42" s="99" t="n"/>
+      <c r="I42" s="84">
+        <f>H42*55</f>
         <v/>
       </c>
       <c r="J42" s="85">
-        <f>F42*G42</f>
-        <v/>
-      </c>
-      <c r="K42" s="81" t="inlineStr">
-        <is>
-          <t>100% upon formal sign-off of Cluster Acceptance Certificate.</t>
-        </is>
-      </c>
-      <c r="L42" s="81" t="inlineStr">
+        <f>E42*H42</f>
+        <v/>
+      </c>
+      <c r="K42" s="85">
+        <f>F42*H42</f>
+        <v/>
+      </c>
+      <c r="L42" s="96" t="inlineStr">
+        <is>
+          <t>Lot 5 Turnkey Rollout Baseline</t>
+        </is>
+      </c>
+      <c r="M42" s="96" t="inlineStr">
         <is>
           <t>Approved Cluster Acceptance Certificate &amp; 14-Day KPI Audit Report</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="78" t="inlineStr">
-        <is>
-          <t>DOMAIN: OPERATIONS &amp; MAINTENANCE (O&amp;M) / MANAGED SERVICES</t>
-        </is>
-      </c>
-      <c r="B43" s="79" t="n"/>
-      <c r="C43" s="79" t="n"/>
-      <c r="D43" s="79" t="n"/>
-      <c r="E43" s="79" t="n"/>
-      <c r="F43" s="79" t="n"/>
-      <c r="G43" s="79" t="n"/>
-      <c r="H43" s="79" t="n"/>
-      <c r="I43" s="79" t="n"/>
-      <c r="J43" s="79" t="n"/>
-      <c r="K43" s="79" t="n"/>
-      <c r="L43" s="79" t="n"/>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="95" t="inlineStr">
+        <is>
+          <t>DOMAIN: OPERATIONS &amp; MAINTENANCE (O&amp;M) / MANAGED SERVICES (24/7 MANAGED SERVICES — ANNUALIZED 12-MONTH &amp; 3-YEAR CONTRACTUAL BASELINE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
       <c r="A44" s="80" t="inlineStr">
         <is>
           <t>MS-NOC-01</t>
         </is>
       </c>
-      <c r="B44" s="81" t="inlineStr">
+      <c r="B44" s="96" t="inlineStr">
         <is>
           <t>24/7/365 Central NOC Tier-1 Active Surveillance &amp; Alarm Monitoring</t>
         </is>
       </c>
-      <c r="C44" s="81" t="inlineStr">
+      <c r="C44" s="97" t="inlineStr">
         <is>
           <t>Continuous 24/7/365 active monitoring of all active and passive network elements across RAN, Core, Power, and Transmission; automated alarm correlation and noise suppression; ticket logging within 5 minutes of alarm onset; and issuance of Daily Operational Flash Report at 06:00 PHT.
 • Inclusions: 24/7 Tier-1 NOC staffing, automated correlation, trouble ticket creation, daily flash reporting.
@@ -8562,48 +8814,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E44" s="82" t="n">
+      <c r="E44" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F44" s="82" t="n">
+      <c r="F44" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G44" s="83" t="n"/>
-      <c r="H44" s="84">
-        <f>G44*55</f>
-        <v/>
-      </c>
-      <c r="I44" s="85">
-        <f>E44*G44</f>
+      <c r="G44" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H44" s="99" t="n"/>
+      <c r="I44" s="84">
+        <f>H44*55</f>
         <v/>
       </c>
       <c r="J44" s="85">
-        <f>F44*G44</f>
-        <v/>
-      </c>
-      <c r="K44" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears upon SLA performance certification.</t>
-        </is>
-      </c>
-      <c r="L44" s="81" t="inlineStr">
+        <f>E44*H44*12</f>
+        <v/>
+      </c>
+      <c r="K44" s="85">
+        <f>F44*H44*12</f>
+        <v/>
+      </c>
+      <c r="L44" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M44" s="96" t="inlineStr">
         <is>
           <t>Daily Flash Reports, Monthly NOC Surveillance Dossier &amp; Availability Report</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
+    <row r="45" ht="40" customHeight="1">
       <c r="A45" s="80" t="inlineStr">
         <is>
           <t>MS-NOC-02</t>
         </is>
       </c>
-      <c r="B45" s="81" t="inlineStr">
+      <c r="B45" s="96" t="inlineStr">
         <is>
           <t>Incident Management, Triage &amp; Automated Trouble Ticketing</t>
         </is>
       </c>
-      <c r="C45" s="81" t="inlineStr">
+      <c r="C45" s="97" t="inlineStr">
         <is>
           <t>End-to-end incident management: automated ticketing via OSS/ITSM; severity classification (Sev 1 Critical to Sev 4 Warning); technician dispatch initiation within 15 minutes for Sev 1 incidents; bridge coordination; and stakeholder notification.
 • Inclusions: ITSM platform, ticket lifecycle tracking, escalation dispatch, MTTR SLA auditing.
@@ -8615,48 +8872,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E45" s="82" t="n">
+      <c r="E45" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F45" s="82" t="n">
+      <c r="F45" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G45" s="83" t="n"/>
-      <c r="H45" s="84">
-        <f>G45*55</f>
-        <v/>
-      </c>
-      <c r="I45" s="85">
-        <f>E45*G45</f>
+      <c r="G45" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H45" s="99" t="n"/>
+      <c r="I45" s="84">
+        <f>H45*55</f>
         <v/>
       </c>
       <c r="J45" s="85">
-        <f>F45*G45</f>
-        <v/>
-      </c>
-      <c r="K45" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L45" s="81" t="inlineStr">
+        <f>E45*H45*12</f>
+        <v/>
+      </c>
+      <c r="K45" s="85">
+        <f>F45*H45*12</f>
+        <v/>
+      </c>
+      <c r="L45" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M45" s="96" t="inlineStr">
         <is>
           <t>Monthly Trouble Ticket Log, MTTR Audit &amp; Dispatch Statistics</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
+    <row r="46" ht="40" customHeight="1">
       <c r="A46" s="80" t="inlineStr">
         <is>
           <t>MS-NOC-03</t>
         </is>
       </c>
-      <c r="B46" s="81" t="inlineStr">
+      <c r="B46" s="96" t="inlineStr">
         <is>
           <t>Tier-2 Remote Technical Diagnostics, Fault Recovery &amp; Config Management</t>
         </is>
       </c>
-      <c r="C46" s="81" t="inlineStr">
+      <c r="C46" s="97" t="inlineStr">
         <is>
           <t>24/7 remote engineering support: soft and hard resets, remote diagnostic sweeps, card re-initialization, backup configuration restoration, transmission routing failover, and software rollback to clear network faults without field truck rolls.
 • Inclusions: Tier-2 remote engineers, remote script execution, transmission path failover, config restoration.
@@ -8668,48 +8930,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E46" s="82" t="n">
+      <c r="E46" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F46" s="82" t="n">
+      <c r="F46" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G46" s="83" t="n"/>
-      <c r="H46" s="84">
-        <f>G46*55</f>
-        <v/>
-      </c>
-      <c r="I46" s="85">
-        <f>E46*G46</f>
+      <c r="G46" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H46" s="99" t="n"/>
+      <c r="I46" s="84">
+        <f>H46*55</f>
         <v/>
       </c>
       <c r="J46" s="85">
-        <f>F46*G46</f>
-        <v/>
-      </c>
-      <c r="K46" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L46" s="81" t="inlineStr">
+        <f>E46*H46*12</f>
+        <v/>
+      </c>
+      <c r="K46" s="85">
+        <f>F46*H46*12</f>
+        <v/>
+      </c>
+      <c r="L46" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M46" s="96" t="inlineStr">
         <is>
           <t>Remote Fault Resolution Log &amp; Configuration Change Audit</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="45" customHeight="1">
+    <row r="47" ht="40" customHeight="1">
       <c r="A47" s="80" t="inlineStr">
         <is>
           <t>MS-NOC-04</t>
         </is>
       </c>
-      <c r="B47" s="81" t="inlineStr">
+      <c r="B47" s="96" t="inlineStr">
         <is>
           <t>Tier-3 Engineering Escalation &amp; OEM TAC Management</t>
         </is>
       </c>
-      <c r="C47" s="81" t="inlineStr">
+      <c r="C47" s="97" t="inlineStr">
         <is>
           <t>Advanced engineering escalation for complex system bugs, protocol crashes, and persistent hardware/software anomalies: case logging with OEM TAC (Level 3), trace log collection, bug patch testing, software patch deployment, and Root Cause Analysis (RCA) reporting within 24 hours of major incident restoration.
 • Inclusions: OEM TAC case management, trace capture, patch verification, RCA report compilation.
@@ -8721,48 +8988,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E47" s="82" t="n">
+      <c r="E47" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F47" s="82" t="n">
+      <c r="F47" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G47" s="83" t="n"/>
-      <c r="H47" s="84">
-        <f>G47*55</f>
-        <v/>
-      </c>
-      <c r="I47" s="85">
-        <f>E47*G47</f>
+      <c r="G47" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H47" s="99" t="n"/>
+      <c r="I47" s="84">
+        <f>H47*55</f>
         <v/>
       </c>
       <c r="J47" s="85">
-        <f>F47*G47</f>
-        <v/>
-      </c>
-      <c r="K47" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L47" s="81" t="inlineStr">
+        <f>E47*H47*12</f>
+        <v/>
+      </c>
+      <c r="K47" s="85">
+        <f>F47*H47*12</f>
+        <v/>
+      </c>
+      <c r="L47" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M47" s="96" t="inlineStr">
         <is>
           <t>Formal Root Cause Analysis (RCA) Reports &amp; OEM TAC Case Log</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1">
+    <row r="48" ht="40" customHeight="1">
       <c r="A48" s="80" t="inlineStr">
         <is>
           <t>MS-FLM-01</t>
         </is>
       </c>
-      <c r="B48" s="81" t="inlineStr">
+      <c r="B48" s="96" t="inlineStr">
         <is>
           <t>24/7 Field First Line Maintenance (FLM) Emergency Response</t>
         </is>
       </c>
-      <c r="C48" s="81" t="inlineStr">
+      <c r="C48" s="97" t="inlineStr">
         <is>
           <t>Provision of dedicated, nationwide 24/7 mobile field maintenance crews equipped with 4x4 vehicles, complete safety gear, calibrated test instruments, and emergency restoration tools. Strict compliance with mandated MTTR SLAs: Severity 1 (Critical - Site Outage): Response &lt;= 15 mins, MTTR &lt;= 2.0h (Urban) / &lt;= 4.0h (Rural); Severity 2 (Major - Sector Down / Power Degraded): Response &lt;= 30 mins, MTTR &lt;= 4.0h (Urban) / &lt;= 6.0h (Rural); Severity 3 (Minor - Non-Service Affecting): Response &lt;= 1h, MTTR &lt;= 12.0h (Urban) / &lt;= 24.0h (Rural); Severity 4 (Warning / Planned): Response &lt;= 4h, MTTR &lt;= 48.0h (Urban) / &lt;= 72.0h (Rural).
 • Inclusions: Dedicated 24/7 crews, 4x4 maintenance vehicles, tools, fuel, emergency call-outs.
@@ -8774,48 +9046,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E48" s="82" t="n">
+      <c r="E48" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F48" s="82" t="n">
+      <c r="F48" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G48" s="83" t="n"/>
-      <c r="H48" s="84">
-        <f>G48*55</f>
-        <v/>
-      </c>
-      <c r="I48" s="85">
-        <f>E48*G48</f>
+      <c r="G48" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H48" s="99" t="n"/>
+      <c r="I48" s="84">
+        <f>H48*55</f>
         <v/>
       </c>
       <c r="J48" s="85">
-        <f>F48*G48</f>
-        <v/>
-      </c>
-      <c r="K48" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears, subject to SLA service credit adjustments.</t>
-        </is>
-      </c>
-      <c r="L48" s="81" t="inlineStr">
+        <f>E48*H48*12</f>
+        <v/>
+      </c>
+      <c r="K48" s="85">
+        <f>F48*H48*12</f>
+        <v/>
+      </c>
+      <c r="L48" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M48" s="96" t="inlineStr">
         <is>
           <t>Monthly FLM Incident Log, Restoration Work Orders &amp; MTTR SLA Report</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="45" customHeight="1">
+    <row r="49" ht="40" customHeight="1">
       <c r="A49" s="80" t="inlineStr">
         <is>
           <t>MS-FLM-02</t>
         </is>
       </c>
-      <c r="B49" s="81" t="inlineStr">
+      <c r="B49" s="96" t="inlineStr">
         <is>
           <t>Active Telecom Hardware Replacement &amp; Field Swapping</t>
         </is>
       </c>
-      <c r="C49" s="81" t="inlineStr">
+      <c r="C49" s="97" t="inlineStr">
         <is>
           <t>On-site replacement of damaged or defective active telecom hardware: RRUs, BBUs, baseband processing cards, optical SFP transceivers, RF jumpers, and GPS antennas, utilizing pre-staged regional spare parts float to achieve fast-track MTTR restoration.
 • Inclusions: Technician labor, de-installation, replacement installation, power-up test, return voucher.
@@ -8824,51 +9101,58 @@
       </c>
       <c r="D49" s="80" t="inlineStr">
         <is>
-          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
-        </is>
-      </c>
-      <c r="E49" s="82" t="n">
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="E49" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F49" s="82" t="n">
+      <c r="F49" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G49" s="83" t="n"/>
-      <c r="H49" s="84">
-        <f>G49*55</f>
-        <v/>
-      </c>
-      <c r="I49" s="85">
-        <f>E49*G49</f>
-        <v/>
-      </c>
-      <c r="J49" s="85">
-        <f>F49*G49</f>
-        <v/>
-      </c>
-      <c r="K49" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L49" s="81" t="inlineStr">
+      <c r="G49" s="100" t="inlineStr">
+        <is>
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="H49" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="102">
+        <f>H49*55</f>
+        <v/>
+      </c>
+      <c r="J49" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="K49" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="L49" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Base Retainer Included (Bundled in FLM-01 / SPM-01)</t>
+        </is>
+      </c>
+      <c r="M49" s="96" t="inlineStr">
         <is>
           <t>Hardware Replacement Slip &amp; Defective Unit Return Voucher</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="40" customHeight="1">
       <c r="A50" s="80" t="inlineStr">
         <is>
           <t>MS-FLM-03</t>
         </is>
       </c>
-      <c r="B50" s="81" t="inlineStr">
+      <c r="B50" s="96" t="inlineStr">
         <is>
           <t>Passive Power &amp; Infrastructure Emergency Restoration</t>
         </is>
       </c>
-      <c r="C50" s="81" t="inlineStr">
+      <c r="C50" s="97" t="inlineStr">
         <is>
           <t>Rapid restoration of passive site elements: resetting/replacing tripped DC distribution breakers, rectifying rectifier module faults, clearing battery management system (BMS) lockouts, replacing blown AC/DC surge protection devices (SPDs), and diagnosing automatic transfer switch (ATS) failures.
 • Inclusions: Electrical diagnosis, breaker reset/replacement, SPD swapping, BMS diagnostic clearing.
@@ -8877,51 +9161,58 @@
       </c>
       <c r="D50" s="80" t="inlineStr">
         <is>
-          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
-        </is>
-      </c>
-      <c r="E50" s="82" t="n">
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="E50" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F50" s="82" t="n">
+      <c r="F50" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G50" s="83" t="n"/>
-      <c r="H50" s="84">
-        <f>G50*55</f>
-        <v/>
-      </c>
-      <c r="I50" s="85">
-        <f>E50*G50</f>
-        <v/>
-      </c>
-      <c r="J50" s="85">
-        <f>F50*G50</f>
-        <v/>
-      </c>
-      <c r="K50" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L50" s="81" t="inlineStr">
+      <c r="G50" s="100" t="inlineStr">
+        <is>
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="H50" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="102">
+        <f>H50*55</f>
+        <v/>
+      </c>
+      <c r="J50" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="K50" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="L50" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Base Retainer Included (Bundled in FLM-01 / SPM-01)</t>
+        </is>
+      </c>
+      <c r="M50" s="96" t="inlineStr">
         <is>
           <t>Passive Infrastructure Restoration Work Order</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="45" customHeight="1">
+    <row r="51" ht="40" customHeight="1">
       <c r="A51" s="80" t="inlineStr">
         <is>
           <t>MS-FLM-04</t>
         </is>
       </c>
-      <c r="B51" s="81" t="inlineStr">
+      <c r="B51" s="96" t="inlineStr">
         <is>
           <t>Emergency Fiber Backhaul Splicing &amp; Optical Link Restoration</t>
         </is>
       </c>
-      <c r="C51" s="81" t="inlineStr">
+      <c r="C51" s="97" t="inlineStr">
         <is>
           <t>Emergency mobilization for fiber transmission outages: OTDR optical fault localization, optical cable drop replacement, mechanical or fusion splicing, and optical splice enclosure re-sealing to restore backhaul transport within mandated MTTR.
 • Inclusions: OTDR fault tracing, fusion splicing labor, splice enclosure resealing, link test.
@@ -8930,51 +9221,58 @@
       </c>
       <c r="D51" s="80" t="inlineStr">
         <is>
-          <t>Included in FLM Monthly Retainer / Per Site-Month</t>
-        </is>
-      </c>
-      <c r="E51" s="82" t="n">
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="E51" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F51" s="82" t="n">
+      <c r="F51" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G51" s="83" t="n"/>
-      <c r="H51" s="84">
-        <f>G51*55</f>
-        <v/>
-      </c>
-      <c r="I51" s="85">
-        <f>E51*G51</f>
-        <v/>
-      </c>
-      <c r="J51" s="85">
-        <f>F51*G51</f>
-        <v/>
-      </c>
-      <c r="K51" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L51" s="81" t="inlineStr">
+      <c r="G51" s="100" t="inlineStr">
+        <is>
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="H51" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="102">
+        <f>H51*55</f>
+        <v/>
+      </c>
+      <c r="J51" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="K51" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="L51" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Base Retainer Included (Bundled in FLM-01 / SPM-01)</t>
+        </is>
+      </c>
+      <c r="M51" s="96" t="inlineStr">
         <is>
           <t>Optical OTDR Trace Report &amp; Splicing Restoration Certificate</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="45" customHeight="1">
+    <row r="52" ht="40" customHeight="1">
       <c r="A52" s="80" t="inlineStr">
         <is>
           <t>MS-PM-01</t>
         </is>
       </c>
-      <c r="B52" s="81" t="inlineStr">
+      <c r="B52" s="96" t="inlineStr">
         <is>
           <t>Quarterly Telecom Equipment Preventive Maintenance (Module A)</t>
         </is>
       </c>
-      <c r="C52" s="81" t="inlineStr">
+      <c r="C52" s="97" t="inlineStr">
         <is>
           <t>Execution of 100% quarterly routine telecom PM: visual inspection of BBU/RRU chassis, optical fiber connector cleaning and inspection, RF jumper weatherproofing boot inspection, cable clamp torque verification, optical SFP power level verification, and dust filter cleaning.
 • Inclusions: Quarterly on-site inspection, connector cleaning, weatherproofing audit, SFP level audit, PM report.
@@ -8983,51 +9281,56 @@
       </c>
       <c r="D52" s="80" t="inlineStr">
         <is>
-          <t>Per Site / Quarter (or Monthly share)</t>
-        </is>
-      </c>
-      <c r="E52" s="82" t="n">
+          <t>Per Site / Quarter</t>
+        </is>
+      </c>
+      <c r="E52" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F52" s="82" t="n">
+      <c r="F52" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G52" s="83" t="n"/>
-      <c r="H52" s="84">
-        <f>G52*55</f>
-        <v/>
-      </c>
-      <c r="I52" s="85">
-        <f>E52*G52</f>
+      <c r="G52" s="80" t="inlineStr">
+        <is>
+          <t>4 Quarters / Year</t>
+        </is>
+      </c>
+      <c r="H52" s="99" t="n"/>
+      <c r="I52" s="84">
+        <f>H52*55</f>
         <v/>
       </c>
       <c r="J52" s="85">
-        <f>F52*G52</f>
-        <v/>
-      </c>
-      <c r="K52" s="81" t="inlineStr">
-        <is>
-          <t>Quarterly upon submission of 100% PM checklists and mobile audit photos.</t>
-        </is>
-      </c>
-      <c r="L52" s="81" t="inlineStr">
+        <f>E52*H52*4</f>
+        <v/>
+      </c>
+      <c r="K52" s="85">
+        <f>F52*H52*4</f>
+        <v/>
+      </c>
+      <c r="L52" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (Quarterly PM Modules A,B,C,E)</t>
+        </is>
+      </c>
+      <c r="M52" s="96" t="inlineStr">
         <is>
           <t>Quarterly Telecom PM Report &amp; Mobile App Timestamped Audit Dossier</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="45" customHeight="1">
+    <row r="53" ht="40" customHeight="1">
       <c r="A53" s="80" t="inlineStr">
         <is>
           <t>MS-PM-02</t>
         </is>
       </c>
-      <c r="B53" s="81" t="inlineStr">
+      <c r="B53" s="96" t="inlineStr">
         <is>
           <t>Quarterly DC Power &amp; LiFePO4 Battery PM (Module B)</t>
         </is>
       </c>
-      <c r="C53" s="81" t="inlineStr">
+      <c r="C53" s="97" t="inlineStr">
         <is>
           <t>Comprehensive quarterly electrical PM: rectifier module load sharing verification, DC output float/equalize voltage calibration, terminal screw torque verification, LiFePO4 battery BMS diagnostic sweep, cell voltage and internal resistance measurement, and 1-hour controlled battery discharge autonomy test under load.
 • Inclusions: Rectifier calibration, BMS diagnostic sweep, internal resistance test, 1-hour load test.
@@ -9039,48 +9342,53 @@
           <t>Per Site / Quarter</t>
         </is>
       </c>
-      <c r="E53" s="82" t="n">
+      <c r="E53" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F53" s="82" t="n">
+      <c r="F53" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G53" s="83" t="n"/>
-      <c r="H53" s="84">
-        <f>G53*55</f>
-        <v/>
-      </c>
-      <c r="I53" s="85">
-        <f>E53*G53</f>
+      <c r="G53" s="80" t="inlineStr">
+        <is>
+          <t>4 Quarters / Year</t>
+        </is>
+      </c>
+      <c r="H53" s="99" t="n"/>
+      <c r="I53" s="84">
+        <f>H53*55</f>
         <v/>
       </c>
       <c r="J53" s="85">
-        <f>F53*G53</f>
-        <v/>
-      </c>
-      <c r="K53" s="81" t="inlineStr">
-        <is>
-          <t>Quarterly upon submission of Battery Health Dossier.</t>
-        </is>
-      </c>
-      <c r="L53" s="81" t="inlineStr">
+        <f>E53*H53*4</f>
+        <v/>
+      </c>
+      <c r="K53" s="85">
+        <f>F53*H53*4</f>
+        <v/>
+      </c>
+      <c r="L53" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (Quarterly PM Modules A,B,C,E)</t>
+        </is>
+      </c>
+      <c r="M53" s="96" t="inlineStr">
         <is>
           <t>DC Power &amp; Battery PM Audit Report + Cell Health Telemetry</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="45" customHeight="1">
+    <row r="54" ht="40" customHeight="1">
       <c r="A54" s="80" t="inlineStr">
         <is>
           <t>MS-PM-03</t>
         </is>
       </c>
-      <c r="B54" s="81" t="inlineStr">
+      <c r="B54" s="96" t="inlineStr">
         <is>
           <t>Quarterly Earth Grounding &amp; Lightning Protection Audit (Module C)</t>
         </is>
       </c>
-      <c r="C54" s="81" t="inlineStr">
+      <c r="C54" s="97" t="inlineStr">
         <is>
           <t>Precision ground resistance audit using 3-point fall-of-potential test instrument (confirming earth ground resistance &lt;= 5.0 Ohms); Cadweld connection inspection; copper busbar bolt torque check; corrosion audit; and inspection of air terminals, down-conductors, and surge arresters.
 • Inclusions: 3-point fall-of-potential test, Cadweld check, busbar torque check, lightning arrester audit.
@@ -9092,48 +9400,53 @@
           <t>Per Site / Quarter</t>
         </is>
       </c>
-      <c r="E54" s="82" t="n">
+      <c r="E54" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F54" s="82" t="n">
+      <c r="F54" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G54" s="83" t="n"/>
-      <c r="H54" s="84">
-        <f>G54*55</f>
-        <v/>
-      </c>
-      <c r="I54" s="85">
-        <f>E54*G54</f>
+      <c r="G54" s="80" t="inlineStr">
+        <is>
+          <t>4 Quarters / Year</t>
+        </is>
+      </c>
+      <c r="H54" s="99" t="n"/>
+      <c r="I54" s="84">
+        <f>H54*55</f>
         <v/>
       </c>
       <c r="J54" s="85">
-        <f>F54*G54</f>
-        <v/>
-      </c>
-      <c r="K54" s="81" t="inlineStr">
-        <is>
-          <t>Quarterly upon submission of Grounding Audit Report.</t>
-        </is>
-      </c>
-      <c r="L54" s="81" t="inlineStr">
+        <f>E54*H54*4</f>
+        <v/>
+      </c>
+      <c r="K54" s="85">
+        <f>F54*H54*4</f>
+        <v/>
+      </c>
+      <c r="L54" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (Quarterly PM Modules A,B,C,E)</t>
+        </is>
+      </c>
+      <c r="M54" s="96" t="inlineStr">
         <is>
           <t>Earth Ground Resistance Test Certificate with Instrument Calibration Tag</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="45" customHeight="1">
+    <row r="55" ht="40" customHeight="1">
       <c r="A55" s="80" t="inlineStr">
         <is>
           <t>MS-PM-04</t>
         </is>
       </c>
-      <c r="B55" s="81" t="inlineStr">
+      <c r="B55" s="96" t="inlineStr">
         <is>
           <t>Bi-Annual Tower Structure, Rigging &amp; Aviation Light Audit (Module D)</t>
         </is>
       </c>
-      <c r="C55" s="81" t="inlineStr">
+      <c r="C55" s="97" t="inlineStr">
         <is>
           <t>Specialized climbing inspection conducted twice per year: physical inspection of tower steel members, monopole climbing ladder, fall arrest cable, AMB mounting bracket bolt torque verification, antenna azimuth/tilt physical check, cable ladder clamping check, and inspection of CAAP-compliant aviation obstruction light and photocell controller.
 • Inclusions: Certified climbing riggers, structural member inspection, bolt torque audit, CAAP light audit.
@@ -9145,48 +9458,53 @@
           <t>Per Site / Semi-Annual</t>
         </is>
       </c>
-      <c r="E55" s="82" t="n">
+      <c r="E55" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F55" s="82" t="n">
+      <c r="F55" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G55" s="83" t="n"/>
-      <c r="H55" s="84">
-        <f>G55*55</f>
-        <v/>
-      </c>
-      <c r="I55" s="85">
-        <f>E55*G55</f>
+      <c r="G55" s="80" t="inlineStr">
+        <is>
+          <t>2 Semi-Annuals / Year</t>
+        </is>
+      </c>
+      <c r="H55" s="99" t="n"/>
+      <c r="I55" s="84">
+        <f>H55*55</f>
         <v/>
       </c>
       <c r="J55" s="85">
-        <f>F55*G55</f>
-        <v/>
-      </c>
-      <c r="K55" s="81" t="inlineStr">
-        <is>
-          <t>Semi-annually upon submission of Tower Rigging Audit Report.</t>
-        </is>
-      </c>
-      <c r="L55" s="81" t="inlineStr">
+        <f>E55*H55*2</f>
+        <v/>
+      </c>
+      <c r="K55" s="85">
+        <f>F55*H55*2</f>
+        <v/>
+      </c>
+      <c r="L55" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (Semi-Annual Tower PM Module D)</t>
+        </is>
+      </c>
+      <c r="M55" s="96" t="inlineStr">
         <is>
           <t>Bi-Annual Tower Climbing &amp; Rigging Audit Report + High-Res Photos</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="45" customHeight="1">
+    <row r="56" ht="40" customHeight="1">
       <c r="A56" s="80" t="inlineStr">
         <is>
           <t>MS-PM-05</t>
         </is>
       </c>
-      <c r="B56" s="81" t="inlineStr">
+      <c r="B56" s="96" t="inlineStr">
         <is>
           <t>Quarterly Site Compound, Civil &amp; Environmental Upkeep (Module E)</t>
         </is>
       </c>
-      <c r="C56" s="81" t="inlineStr">
+      <c r="C56" s="97" t="inlineStr">
         <is>
           <t>Routine civil compound maintenance: inspection and repair of chain-link perimeter fencing and barbed wire; greasing and servicing gate locking mechanisms; weed cutting, vegetation clearance, and chemical weed-killing within a 3-meter perimeter of compound; drainage channel clearing; and pest/rodent proofing of equipment cabinet cable entries.
 • Inclusions: Compound weeding, perimeter clearing, fence repair, lock lubrication, cable entry pest sealing.
@@ -9198,48 +9516,53 @@
           <t>Per Site / Quarter</t>
         </is>
       </c>
-      <c r="E56" s="82" t="n">
+      <c r="E56" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F56" s="82" t="n">
+      <c r="F56" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G56" s="83" t="n"/>
-      <c r="H56" s="84">
-        <f>G56*55</f>
-        <v/>
-      </c>
-      <c r="I56" s="85">
-        <f>E56*G56</f>
+      <c r="G56" s="80" t="inlineStr">
+        <is>
+          <t>4 Quarters / Year</t>
+        </is>
+      </c>
+      <c r="H56" s="99" t="n"/>
+      <c r="I56" s="84">
+        <f>H56*55</f>
         <v/>
       </c>
       <c r="J56" s="85">
-        <f>F56*G56</f>
-        <v/>
-      </c>
-      <c r="K56" s="81" t="inlineStr">
-        <is>
-          <t>Quarterly upon compound inspection sign-off.</t>
-        </is>
-      </c>
-      <c r="L56" s="81" t="inlineStr">
+        <f>E56*H56*4</f>
+        <v/>
+      </c>
+      <c r="K56" s="85">
+        <f>F56*H56*4</f>
+        <v/>
+      </c>
+      <c r="L56" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (Quarterly PM Modules A,B,C,E)</t>
+        </is>
+      </c>
+      <c r="M56" s="96" t="inlineStr">
         <is>
           <t>Compound Upkeep Audit Checklist &amp; Before/After Photos</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="45" customHeight="1">
+    <row r="57" ht="40" customHeight="1">
       <c r="A57" s="80" t="inlineStr">
         <is>
           <t>MS-SPM-01</t>
         </is>
       </c>
-      <c r="B57" s="81" t="inlineStr">
+      <c r="B57" s="96" t="inlineStr">
         <is>
           <t>Regional Spare Parts Buffer Float Management (SPMS)</t>
         </is>
       </c>
-      <c r="C57" s="81" t="inlineStr">
+      <c r="C57" s="97" t="inlineStr">
         <is>
           <t>Operation of climate-controlled, secure regional spare parts depots (Mega Manila, North Luzon, South Luzon, Visayas, Mindanao); managing and maintaining an agreed 2.0% active hardware spares float (BBUs, RRUs, SFPs, rectifiers, batteries, cables); tracking serial numbers via WMS; and conducting monthly physical cycle counts.
 • Inclusions: Regional storage depots, inventory management, serialized tracking, monthly cycle counts.
@@ -9251,48 +9574,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E57" s="82" t="n">
+      <c r="E57" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F57" s="82" t="n">
+      <c r="F57" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G57" s="83" t="n"/>
-      <c r="H57" s="84">
-        <f>G57*55</f>
-        <v/>
-      </c>
-      <c r="I57" s="85">
-        <f>E57*G57</f>
+      <c r="G57" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H57" s="99" t="n"/>
+      <c r="I57" s="84">
+        <f>H57*55</f>
         <v/>
       </c>
       <c r="J57" s="85">
-        <f>F57*G57</f>
-        <v/>
-      </c>
-      <c r="K57" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L57" s="81" t="inlineStr">
+        <f>E57*H57*12</f>
+        <v/>
+      </c>
+      <c r="K57" s="85">
+        <f>F57*H57*12</f>
+        <v/>
+      </c>
+      <c r="L57" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M57" s="96" t="inlineStr">
         <is>
           <t>Monthly Spare Parts Float Status Report &amp; Cycle Count Audit</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="45" customHeight="1">
+    <row r="58" ht="40" customHeight="1">
       <c r="A58" s="80" t="inlineStr">
         <is>
           <t>MS-SPM-02</t>
         </is>
       </c>
-      <c r="B58" s="81" t="inlineStr">
+      <c r="B58" s="96" t="inlineStr">
         <is>
           <t>Advance Hardware Replacement (AHR) &amp; Expedited Field Delivery</t>
         </is>
       </c>
-      <c r="C58" s="81" t="inlineStr">
+      <c r="C58" s="97" t="inlineStr">
         <is>
           <t>Rapid logistics dispatch delivering replacement hardware to field maintenance crews: Next-Business-Day (NBD) standard delivery nationwide, or expedited 4-hour emergency delivery for major macro hubs and critical transmission nodes.
 • Inclusions: Expedited dispatch, emergency courier, chain of custody documentation, field delivery receipt.
@@ -9301,51 +9629,58 @@
       </c>
       <c r="D58" s="80" t="inlineStr">
         <is>
-          <t>Included in SPM Retainer / Per Site-Month</t>
-        </is>
-      </c>
-      <c r="E58" s="82" t="n">
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="E58" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F58" s="82" t="n">
+      <c r="F58" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G58" s="83" t="n"/>
-      <c r="H58" s="84">
-        <f>G58*55</f>
-        <v/>
-      </c>
-      <c r="I58" s="85">
-        <f>E58*G58</f>
-        <v/>
-      </c>
-      <c r="J58" s="85">
-        <f>F58*G58</f>
-        <v/>
-      </c>
-      <c r="K58" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L58" s="81" t="inlineStr">
+      <c r="G58" s="100" t="inlineStr">
+        <is>
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="H58" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="102">
+        <f>H58*55</f>
+        <v/>
+      </c>
+      <c r="J58" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="K58" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="L58" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Base Retainer Included (Bundled in FLM-01 / SPM-01)</t>
+        </is>
+      </c>
+      <c r="M58" s="96" t="inlineStr">
         <is>
           <t>Hardware Dispatch Manifest &amp; Proof of On-Site Delivery</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="45" customHeight="1">
+    <row r="59" ht="40" customHeight="1">
       <c r="A59" s="80" t="inlineStr">
         <is>
           <t>MS-SPM-03</t>
         </is>
       </c>
-      <c r="B59" s="81" t="inlineStr">
+      <c r="B59" s="96" t="inlineStr">
         <is>
           <t>Return Merchandise Authorization (RMA) &amp; OEM Factory Repair Logistics</t>
         </is>
       </c>
-      <c r="C59" s="81" t="inlineStr">
+      <c r="C59" s="97" t="inlineStr">
         <is>
           <t>Managing the reverse logistics lifecycle for defective hardware: retrieving faulty units from field crews, conducting triage, generating RMA requests, managing packaging and export/import customs for OEM repair/replacement, tracking turnaround time (TAT &lt;= 30 calendar days), and returning repaired units to the regional buffer float.
 • Inclusions: Defective unit triage, RMA processing, shipping to OEM repair facility, tracking, customs clearance.
@@ -9354,51 +9689,58 @@
       </c>
       <c r="D59" s="80" t="inlineStr">
         <is>
-          <t>Included in SPM Retainer / Per Site-Month</t>
-        </is>
-      </c>
-      <c r="E59" s="82" t="n">
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="E59" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F59" s="82" t="n">
+      <c r="F59" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G59" s="83" t="n"/>
-      <c r="H59" s="84">
-        <f>G59*55</f>
-        <v/>
-      </c>
-      <c r="I59" s="85">
-        <f>E59*G59</f>
-        <v/>
-      </c>
-      <c r="J59" s="85">
-        <f>F59*G59</f>
-        <v/>
-      </c>
-      <c r="K59" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L59" s="81" t="inlineStr">
+      <c r="G59" s="100" t="inlineStr">
+        <is>
+          <t>Included in Base Retainer ($0.00)</t>
+        </is>
+      </c>
+      <c r="H59" s="101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="102">
+        <f>H59*55</f>
+        <v/>
+      </c>
+      <c r="J59" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="K59" s="101">
+        <f>0.00</f>
+        <v/>
+      </c>
+      <c r="L59" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Base Retainer Included (Bundled in FLM-01 / SPM-01)</t>
+        </is>
+      </c>
+      <c r="M59" s="96" t="inlineStr">
         <is>
           <t>RMA Lifecycle Tracking Dossier &amp; OEM Repair Turnaround Log</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="45" customHeight="1">
+    <row r="60" ht="40" customHeight="1">
       <c r="A60" s="80" t="inlineStr">
         <is>
           <t>MS-RNO-01</t>
         </is>
       </c>
-      <c r="B60" s="81" t="inlineStr">
+      <c r="B60" s="96" t="inlineStr">
         <is>
           <t>Continuous Radio Network Optimization &amp; Weekly KPI Surveillance</t>
         </is>
       </c>
-      <c r="C60" s="81" t="inlineStr">
+      <c r="C60" s="97" t="inlineStr">
         <is>
           <t>Ongoing network-wide RF quality surveillance: daily and weekly statistical KPI tracking (Radio Availability, CSSR, CDDR, average throughput, PRB utilization, cell-edge speeds); identification and root-cause analysis of Worst Performing Cells (WPC); dynamic parameter fine-tuning; and weekly optimization meetings.
 • Inclusions: Dedicated RF optimization engineers, weekly WPC triage, parameter tuning scripts, KPI governance.
@@ -9410,48 +9752,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E60" s="82" t="n">
+      <c r="E60" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F60" s="82" t="n">
+      <c r="F60" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G60" s="83" t="n"/>
-      <c r="H60" s="84">
-        <f>G60*55</f>
-        <v/>
-      </c>
-      <c r="I60" s="85">
-        <f>E60*G60</f>
+      <c r="G60" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H60" s="99" t="n"/>
+      <c r="I60" s="84">
+        <f>H60*55</f>
         <v/>
       </c>
       <c r="J60" s="85">
-        <f>F60*G60</f>
-        <v/>
-      </c>
-      <c r="K60" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L60" s="81" t="inlineStr">
+        <f>E60*H60*12</f>
+        <v/>
+      </c>
+      <c r="K60" s="85">
+        <f>F60*H60*12</f>
+        <v/>
+      </c>
+      <c r="L60" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M60" s="96" t="inlineStr">
         <is>
           <t>Weekly Worst Performing Cell (WPC) Report &amp; Monthly Network KPI Dossier</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="45" customHeight="1">
+    <row r="61" ht="40" customHeight="1">
       <c r="A61" s="80" t="inlineStr">
         <is>
           <t>MS-RNO-02</t>
         </is>
       </c>
-      <c r="B61" s="81" t="inlineStr">
+      <c r="B61" s="96" t="inlineStr">
         <is>
           <t>Interference Hunting, PIM Mitigation &amp; Customer Complaint Field Audit</t>
         </is>
       </c>
-      <c r="C61" s="81" t="inlineStr">
+      <c r="C61" s="97" t="inlineStr">
         <is>
           <t>Field RF investigation for degraded sectors: spectrum analyzer sweeps to detect and locate external interference sources (jamming, unauthorized boosters, microwave leakage); Passive Intermodulation (PIM) testing and remediation on antenna lines; and on-site drive validation for VIP or high-churn barangay clusters.
 • Inclusions: Spectrum analyzer field sweeps, PIM testing, interference source triangulation, customer complaint verification.
@@ -9463,48 +9810,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E61" s="82" t="n">
+      <c r="E61" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F61" s="82" t="n">
+      <c r="F61" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G61" s="83" t="n"/>
-      <c r="H61" s="84">
-        <f>G61*55</f>
-        <v/>
-      </c>
-      <c r="I61" s="85">
-        <f>E61*G61</f>
+      <c r="G61" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H61" s="99" t="n"/>
+      <c r="I61" s="84">
+        <f>H61*55</f>
         <v/>
       </c>
       <c r="J61" s="85">
-        <f>F61*G61</f>
-        <v/>
-      </c>
-      <c r="K61" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L61" s="81" t="inlineStr">
+        <f>E61*H61*12</f>
+        <v/>
+      </c>
+      <c r="K61" s="85">
+        <f>F61*H61*12</f>
+        <v/>
+      </c>
+      <c r="L61" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M61" s="96" t="inlineStr">
         <is>
           <t>Interference Investigation Dossier &amp; Spectrum Sweep Traces</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="45" customHeight="1">
+    <row r="62" ht="40" customHeight="1">
       <c r="A62" s="80" t="inlineStr">
         <is>
           <t>MS-FAC-01</t>
         </is>
       </c>
-      <c r="B62" s="81" t="inlineStr">
+      <c r="B62" s="96" t="inlineStr">
         <is>
           <t>Passive Tower &amp; Civil Facility Maintenance</t>
         </is>
       </c>
-      <c r="C62" s="81" t="inlineStr">
+      <c r="C62" s="97" t="inlineStr">
         <is>
           <t>Structural preservation of passive site assets: rust scraping, cold galvanizing compound application, and repainting of steel members in corrosive/coastal environments; repairing cracked equipment plinths; re-caulking cable entry boots; and maintaining access road drainage and clear-way.
 • Inclusions: Anti-corrosion touch-up, cold galvanizing, plinth crack sealing, cable entry maintenance.
@@ -9516,48 +9868,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E62" s="82" t="n">
+      <c r="E62" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F62" s="82" t="n">
+      <c r="F62" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G62" s="83" t="n"/>
-      <c r="H62" s="84">
-        <f>G62*55</f>
-        <v/>
-      </c>
-      <c r="I62" s="85">
-        <f>E62*G62</f>
+      <c r="G62" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H62" s="99" t="n"/>
+      <c r="I62" s="84">
+        <f>H62*55</f>
         <v/>
       </c>
       <c r="J62" s="85">
-        <f>F62*G62</f>
-        <v/>
-      </c>
-      <c r="K62" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L62" s="81" t="inlineStr">
+        <f>E62*H62*12</f>
+        <v/>
+      </c>
+      <c r="K62" s="85">
+        <f>F62*H62*12</f>
+        <v/>
+      </c>
+      <c r="L62" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M62" s="96" t="inlineStr">
         <is>
           <t>Monthly Facility Maintenance Log &amp; Civil Condition Report</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="45" customHeight="1">
+    <row r="63" ht="40" customHeight="1">
       <c r="A63" s="80" t="inlineStr">
         <is>
           <t>MS-PWR-01</t>
         </is>
       </c>
-      <c r="B63" s="81" t="inlineStr">
+      <c r="B63" s="96" t="inlineStr">
         <is>
           <t>Energy, Utility Grid (Meralco/Coop) Coordination &amp; Genset PM</t>
         </is>
       </c>
-      <c r="C63" s="81" t="inlineStr">
+      <c r="C63" s="97" t="inlineStr">
         <is>
           <t>Power management coordination: monitoring utility power reliability, validating commercial meter readings, coordinating with Meralco/electric cooperatives for transformer fuse restoration, and performing routine 250-hour preventive servicing on backup diesel generator sets (engine oil, oil filter, fuel filter, air cleaner replacement, coolant check).
 • Inclusions: Utility outage coordination, meter reading audit, 250-hr generator PM servicing, coolant/filter checks.
@@ -9569,48 +9926,53 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E63" s="82" t="n">
+      <c r="E63" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F63" s="82" t="n">
+      <c r="F63" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G63" s="83" t="n"/>
-      <c r="H63" s="84">
-        <f>G63*55</f>
-        <v/>
-      </c>
-      <c r="I63" s="85">
-        <f>E63*G63</f>
+      <c r="G63" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H63" s="99" t="n"/>
+      <c r="I63" s="84">
+        <f>H63*55</f>
         <v/>
       </c>
       <c r="J63" s="85">
-        <f>F63*G63</f>
-        <v/>
-      </c>
-      <c r="K63" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L63" s="81" t="inlineStr">
+        <f>E63*H63*12</f>
+        <v/>
+      </c>
+      <c r="K63" s="85">
+        <f>F63*H63*12</f>
+        <v/>
+      </c>
+      <c r="L63" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M63" s="96" t="inlineStr">
         <is>
           <t>Monthly Energy Consumption Audit &amp; Genset PM Service Log</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="45" customHeight="1">
+    <row r="64" ht="40" customHeight="1">
       <c r="A64" s="80" t="inlineStr">
         <is>
           <t>MS-SW-01</t>
         </is>
       </c>
-      <c r="B64" s="81" t="inlineStr">
+      <c r="B64" s="96" t="inlineStr">
         <is>
           <t>Software Support, Firmware Patching &amp; Cybersecurity Hardening</t>
         </is>
       </c>
-      <c r="C64" s="81" t="inlineStr">
+      <c r="C64" s="97" t="inlineStr">
         <is>
           <t>Scheduled execution of software maintenance: applying OEM-approved firmware updates and feature patches during maintenance windows (00:00–05:00); implementing CVE security patches and hardening configs; executing weekly automated BBU and Core configuration backups; and maintaining offsite configuration archives.
 • Inclusions: Firmware deployment, CVE security updates, maintenance window execution, automated backups.
@@ -9622,66 +9984,60 @@
           <t>Per Site / Month</t>
         </is>
       </c>
-      <c r="E64" s="82" t="n">
+      <c r="E64" s="98" t="n">
         <v>1000</v>
       </c>
-      <c r="F64" s="82" t="n">
+      <c r="F64" s="98" t="n">
         <v>5000</v>
       </c>
-      <c r="G64" s="83" t="n"/>
-      <c r="H64" s="84">
-        <f>G64*55</f>
-        <v/>
-      </c>
-      <c r="I64" s="85">
-        <f>E64*G64</f>
+      <c r="G64" s="80" t="inlineStr">
+        <is>
+          <t>12 Months / Year</t>
+        </is>
+      </c>
+      <c r="H64" s="99" t="n"/>
+      <c r="I64" s="84">
+        <f>H64*55</f>
         <v/>
       </c>
       <c r="J64" s="85">
-        <f>F64*G64</f>
-        <v/>
-      </c>
-      <c r="K64" s="81" t="inlineStr">
-        <is>
-          <t>Monthly in arrears.</t>
-        </is>
-      </c>
-      <c r="L64" s="81" t="inlineStr">
+        <f>E64*H64*12</f>
+        <v/>
+      </c>
+      <c r="K64" s="85">
+        <f>F64*H64*12</f>
+        <v/>
+      </c>
+      <c r="L64" s="96" t="inlineStr">
+        <is>
+          <t>Lot 6 Managed Services (NOC/FLM/SPMS/RNO Monthly Retainer)</t>
+        </is>
+      </c>
+      <c r="M64" s="96" t="inlineStr">
         <is>
           <t>Monthly Patch Deployment Log &amp; Configuration Backup Verification Certificate</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="78" t="inlineStr">
-        <is>
-          <t>DOMAIN: AD-HOC CALL-OUT SERVICES RATE CARD</t>
-        </is>
-      </c>
-      <c r="B65" s="79" t="n"/>
-      <c r="C65" s="79" t="n"/>
-      <c r="D65" s="79" t="n"/>
-      <c r="E65" s="79" t="n"/>
-      <c r="F65" s="79" t="n"/>
-      <c r="G65" s="79" t="n"/>
-      <c r="H65" s="79" t="n"/>
-      <c r="I65" s="79" t="n"/>
-      <c r="J65" s="79" t="n"/>
-      <c r="K65" s="79" t="n"/>
-      <c r="L65" s="79" t="n"/>
-    </row>
-    <row r="66" ht="45" customHeight="1">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="95" t="inlineStr">
+        <is>
+          <t>DOMAIN: AD-HOC CALL-OUT SERVICES RATE CARD (AD-HOC SPECIALIZED SERVICES — ANNUALIZED CONTINGENCY EVALUATION BASKET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
       <c r="A66" s="80" t="inlineStr">
         <is>
           <t>CALL-01</t>
         </is>
       </c>
-      <c r="B66" s="81" t="inlineStr">
+      <c r="B66" s="96" t="inlineStr">
         <is>
           <t>Specialized Tower Rigging Call-Out Service</t>
         </is>
       </c>
-      <c r="C66" s="81" t="inlineStr">
+      <c r="C66" s="97" t="inlineStr">
         <is>
           <t>Ad-hoc mobilization of a certified tower climbing crew to execute non-standard physical antenna modifications: adjusting mechanical tilt, azimuth, or antenna mounting height upon structural reconfiguration or post-typhoon realignment.
 • Inclusions: Rigging crew, climbing tackle, digital compass/inclinometer alignment, before/after photos.
@@ -9690,51 +10046,56 @@
       </c>
       <c r="D66" s="80" t="inlineStr">
         <is>
-          <t>Per Sector / Per Man-Day</t>
-        </is>
-      </c>
-      <c r="E66" s="82" t="n">
+          <t>Per Sector</t>
+        </is>
+      </c>
+      <c r="E66" s="98" t="n">
         <v>100</v>
       </c>
-      <c r="F66" s="82" t="n">
+      <c r="F66" s="98" t="n">
         <v>500</v>
       </c>
-      <c r="G66" s="83" t="n"/>
-      <c r="H66" s="84">
-        <f>G66*55</f>
-        <v/>
-      </c>
-      <c r="I66" s="85">
-        <f>E66*G66</f>
+      <c r="G66" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H66" s="99" t="n"/>
+      <c r="I66" s="84">
+        <f>H66*55</f>
         <v/>
       </c>
       <c r="J66" s="85">
-        <f>F66*G66</f>
-        <v/>
-      </c>
-      <c r="K66" s="81" t="inlineStr">
-        <is>
-          <t>100% upon completion and photographic verification.</t>
-        </is>
-      </c>
-      <c r="L66" s="81" t="inlineStr">
+        <f>E66*H66</f>
+        <v/>
+      </c>
+      <c r="K66" s="85">
+        <f>F66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M66" s="96" t="inlineStr">
         <is>
           <t>Rigging Work Order Completion Sheet &amp; Re-alignment Certificate</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="45" customHeight="1">
+    <row r="67" ht="40" customHeight="1">
       <c r="A67" s="80" t="inlineStr">
         <is>
           <t>CALL-02</t>
         </is>
       </c>
-      <c r="B67" s="81" t="inlineStr">
+      <c r="B67" s="96" t="inlineStr">
         <is>
           <t>Emergency Typhoon Disaster Recovery Crew</t>
         </is>
       </c>
-      <c r="C67" s="81" t="inlineStr">
+      <c r="C67" s="97" t="inlineStr">
         <is>
           <t>Rapid deployment of a specialized 4-man disaster recovery crew equipped with heavy-duty 4x4 vehicle, chainsaws, winches, heavy rigging tackle, and portable generator to clear fallen trees, re-erect toppled poles, and execute emergency structural stabilization post-typhoon.
 • Inclusions: 4-man emergency crew, 4x4 vehicle, chainsaw, winch, generator, debris clearing gear.
@@ -9743,51 +10104,56 @@
       </c>
       <c r="D67" s="80" t="inlineStr">
         <is>
-          <t>Per Crew / Per Day</t>
-        </is>
-      </c>
-      <c r="E67" s="82" t="n">
+          <t>Per Crew / Day</t>
+        </is>
+      </c>
+      <c r="E67" s="98" t="n">
         <v>50</v>
       </c>
-      <c r="F67" s="82" t="n">
+      <c r="F67" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="G67" s="83" t="n"/>
-      <c r="H67" s="84">
-        <f>G67*55</f>
-        <v/>
-      </c>
-      <c r="I67" s="85">
-        <f>E67*G67</f>
+      <c r="G67" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H67" s="99" t="n"/>
+      <c r="I67" s="84">
+        <f>H67*55</f>
         <v/>
       </c>
       <c r="J67" s="85">
-        <f>F67*G67</f>
-        <v/>
-      </c>
-      <c r="K67" s="81" t="inlineStr">
-        <is>
-          <t>100% upon daily crew timesheet approval by Operator.</t>
-        </is>
-      </c>
-      <c r="L67" s="81" t="inlineStr">
+        <f>E67*H67</f>
+        <v/>
+      </c>
+      <c r="K67" s="85">
+        <f>F67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M67" s="96" t="inlineStr">
         <is>
           <t>Disaster Recovery Timesheet &amp; Field Activity Report</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="45" customHeight="1">
+    <row r="68" ht="40" customHeight="1">
       <c r="A68" s="80" t="inlineStr">
         <is>
           <t>CALL-03</t>
         </is>
       </c>
-      <c r="B68" s="81" t="inlineStr">
+      <c r="B68" s="96" t="inlineStr">
         <is>
           <t>Mobile Emergency Generator Deployment &amp; Continuous Run</t>
         </is>
       </c>
-      <c r="C68" s="81" t="inlineStr">
+      <c r="C68" s="97" t="inlineStr">
         <is>
           <t>Delivery, positioning, cabling, and commissioning of a mobile trailer-mounted 15–20 kVA diesel generator at a damaged site during extended utility grid blackouts; includes 48 hours of continuous operation, continuous refueling, and operator surveillance.
 • Inclusions: Trailer genset delivery, connection cables, 48 hours continuous running, fuel, technician operator.
@@ -9796,51 +10162,56 @@
       </c>
       <c r="D68" s="80" t="inlineStr">
         <is>
-          <t>Per Deployment Event (48-hr block)</t>
-        </is>
-      </c>
-      <c r="E68" s="82" t="n">
+          <t>Per Deployment (48-hr block)</t>
+        </is>
+      </c>
+      <c r="E68" s="98" t="n">
         <v>50</v>
       </c>
-      <c r="F68" s="82" t="n">
+      <c r="F68" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="G68" s="83" t="n"/>
-      <c r="H68" s="84">
-        <f>G68*55</f>
-        <v/>
-      </c>
-      <c r="I68" s="85">
-        <f>E68*G68</f>
+      <c r="G68" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H68" s="99" t="n"/>
+      <c r="I68" s="84">
+        <f>H68*55</f>
         <v/>
       </c>
       <c r="J68" s="85">
-        <f>F68*G68</f>
-        <v/>
-      </c>
-      <c r="K68" s="81" t="inlineStr">
-        <is>
-          <t>100% upon completion of emergency run.</t>
-        </is>
-      </c>
-      <c r="L68" s="81" t="inlineStr">
+        <f>E68*H68</f>
+        <v/>
+      </c>
+      <c r="K68" s="85">
+        <f>F68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M68" s="96" t="inlineStr">
         <is>
           <t>Emergency Power Log &amp; Generator Run-Hour Telemetry</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="45" customHeight="1">
+    <row r="69" ht="40" customHeight="1">
       <c r="A69" s="80" t="inlineStr">
         <is>
           <t>CALL-04</t>
         </is>
       </c>
-      <c r="B69" s="81" t="inlineStr">
+      <c r="B69" s="96" t="inlineStr">
         <is>
           <t>Long-Span Optical Fiber Cable Restoration &amp; Splicing</t>
         </is>
       </c>
-      <c r="C69" s="81" t="inlineStr">
+      <c r="C69" s="97" t="inlineStr">
         <is>
           <t>Emergency or planned restoration of major backhaul fiber cable cuts exceeding 500 meters: stringing replacement 24-core armored aerial or underground fiber cable, installing suspension clamps, fusion splicing at both splice closures, and testing optical loss.
 • Inclusions: Cable stringing labor, suspension clamps, 2x fusion splice enclosures, OTDR testing.
@@ -9849,51 +10220,56 @@
       </c>
       <c r="D69" s="80" t="inlineStr">
         <is>
-          <t>Per Meter / Per Span</t>
-        </is>
-      </c>
-      <c r="E69" s="82" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F69" s="82" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G69" s="83" t="n"/>
-      <c r="H69" s="84">
-        <f>G69*55</f>
-        <v/>
-      </c>
-      <c r="I69" s="85">
-        <f>E69*G69</f>
+          <t>Per Span</t>
+        </is>
+      </c>
+      <c r="E69" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" s="98" t="n">
+        <v>100</v>
+      </c>
+      <c r="G69" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H69" s="99" t="n"/>
+      <c r="I69" s="84">
+        <f>H69*55</f>
         <v/>
       </c>
       <c r="J69" s="85">
-        <f>F69*G69</f>
-        <v/>
-      </c>
-      <c r="K69" s="81" t="inlineStr">
-        <is>
-          <t>100% upon OTDR bi-directional loss sign-off.</t>
-        </is>
-      </c>
-      <c r="L69" s="81" t="inlineStr">
+        <f>E69*H69</f>
+        <v/>
+      </c>
+      <c r="K69" s="85">
+        <f>F69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M69" s="96" t="inlineStr">
         <is>
           <t>Bi-Directional OTDR Loss Trace &amp; Splicing Certificate</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="45" customHeight="1">
+    <row r="70" ht="40" customHeight="1">
       <c r="A70" s="80" t="inlineStr">
         <is>
           <t>CALL-05</t>
         </is>
       </c>
-      <c r="B70" s="81" t="inlineStr">
+      <c r="B70" s="96" t="inlineStr">
         <is>
           <t>Drone Structural, Panoramic &amp; Thermal Imaging Survey</t>
         </is>
       </c>
-      <c r="C70" s="81" t="inlineStr">
+      <c r="C70" s="97" t="inlineStr">
         <is>
           <t>High-resolution aerial inspection utilizing drone equipped with 4K optical zoom and radiometric thermal sensor: auditing tower structural integrity, inspecting hard-to-reach antenna brackets, and detecting hotspot anomalies on power joints and cables.
 • Inclusions: Licensed drone pilot, 4K video, high-res photos, radiometric thermal imaging, analysis report.
@@ -9905,48 +10281,53 @@
           <t>Per Site Flight</t>
         </is>
       </c>
-      <c r="E70" s="82" t="n">
+      <c r="E70" s="98" t="n">
         <v>50</v>
       </c>
-      <c r="F70" s="82" t="n">
+      <c r="F70" s="98" t="n">
         <v>250</v>
       </c>
-      <c r="G70" s="83" t="n"/>
-      <c r="H70" s="84">
-        <f>G70*55</f>
-        <v/>
-      </c>
-      <c r="I70" s="85">
-        <f>E70*G70</f>
+      <c r="G70" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H70" s="99" t="n"/>
+      <c r="I70" s="84">
+        <f>H70*55</f>
         <v/>
       </c>
       <c r="J70" s="85">
-        <f>F70*G70</f>
-        <v/>
-      </c>
-      <c r="K70" s="81" t="inlineStr">
-        <is>
-          <t>100% upon submission of 4K video, photos, and thermal report.</t>
-        </is>
-      </c>
-      <c r="L70" s="81" t="inlineStr">
+        <f>E70*H70</f>
+        <v/>
+      </c>
+      <c r="K70" s="85">
+        <f>F70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M70" s="96" t="inlineStr">
         <is>
           <t>High-Resolution Aerial Video/Photo Suite &amp; Thermal Analysis Report</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="45" customHeight="1">
+    <row r="71" ht="40" customHeight="1">
       <c r="A71" s="80" t="inlineStr">
         <is>
           <t>CALL-06</t>
         </is>
       </c>
-      <c r="B71" s="81" t="inlineStr">
+      <c r="B71" s="96" t="inlineStr">
         <is>
           <t>Tower Structural Strengthening &amp; Leg Reinforcement</t>
         </is>
       </c>
-      <c r="C71" s="81" t="inlineStr">
+      <c r="C71" s="97" t="inlineStr">
         <is>
           <t>Physical structural modification of existing tower or monopole: installing steel reinforcement members, flange stiffeners, cross-bracing, or guy wire tensioning based on approved PE structural engineering calculations.
 • Inclusions: Steel fabrication, rigging installation, bolt torquing, cold galvanizing, PE sign-off.
@@ -9958,48 +10339,53 @@
           <t>Per Tower / Lump Sum based on DED</t>
         </is>
       </c>
-      <c r="E71" s="82" t="n">
+      <c r="E71" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="F71" s="82" t="n">
+      <c r="F71" s="98" t="n">
         <v>100</v>
       </c>
-      <c r="G71" s="83" t="n"/>
-      <c r="H71" s="84">
-        <f>G71*55</f>
-        <v/>
-      </c>
-      <c r="I71" s="85">
-        <f>E71*G71</f>
+      <c r="G71" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H71" s="99" t="n"/>
+      <c r="I71" s="84">
+        <f>H71*55</f>
         <v/>
       </c>
       <c r="J71" s="85">
-        <f>F71*G71</f>
-        <v/>
-      </c>
-      <c r="K71" s="81" t="inlineStr">
-        <is>
-          <t>50% upon material delivery; 50% upon PE structural sign-off.</t>
-        </is>
-      </c>
-      <c r="L71" s="81" t="inlineStr">
+        <f>E71*H71</f>
+        <v/>
+      </c>
+      <c r="K71" s="85">
+        <f>F71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M71" s="96" t="inlineStr">
         <is>
           <t>As-Built Structural Strengthening Drawings &amp; PE Endorsement</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="45" customHeight="1">
+    <row r="72" ht="40" customHeight="1">
       <c r="A72" s="80" t="inlineStr">
         <is>
           <t>CALL-07</t>
         </is>
       </c>
-      <c r="B72" s="81" t="inlineStr">
+      <c r="B72" s="96" t="inlineStr">
         <is>
           <t>Specialized PIM Hunting &amp; Multi-Sector Interference Remediation</t>
         </is>
       </c>
-      <c r="C72" s="81" t="inlineStr">
+      <c r="C72" s="97" t="inlineStr">
         <is>
           <t>Advanced on-site PIM testing utilizing specialized 2x20W PIM analyzer: identifying internal and external PIM sources, replacing corroded RF jumpers/connectors, and applying RF shielding tape/materials to achieve PIM &lt;= -155 dBc.
 • Inclusions: Calibrated 2x20W PIM test gear, RF sweep, connector re-termination, shielding materials, sweep report.
@@ -10011,48 +10397,53 @@
           <t>Per Site / Day</t>
         </is>
       </c>
-      <c r="E72" s="82" t="n">
+      <c r="E72" s="98" t="n">
         <v>30</v>
       </c>
-      <c r="F72" s="82" t="n">
+      <c r="F72" s="98" t="n">
         <v>150</v>
       </c>
-      <c r="G72" s="83" t="n"/>
-      <c r="H72" s="84">
-        <f>G72*55</f>
-        <v/>
-      </c>
-      <c r="I72" s="85">
-        <f>E72*G72</f>
+      <c r="G72" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H72" s="99" t="n"/>
+      <c r="I72" s="84">
+        <f>H72*55</f>
         <v/>
       </c>
       <c r="J72" s="85">
-        <f>F72*G72</f>
-        <v/>
-      </c>
-      <c r="K72" s="81" t="inlineStr">
-        <is>
-          <t>100% upon achieving compliant PIM sweep trace.</t>
-        </is>
-      </c>
-      <c r="L72" s="81" t="inlineStr">
+        <f>E72*H72</f>
+        <v/>
+      </c>
+      <c r="K72" s="85">
+        <f>F72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M72" s="96" t="inlineStr">
         <is>
           <t>Calibrated PIM Sweep Measurement Report</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="45" customHeight="1">
+    <row r="73" ht="40" customHeight="1">
       <c r="A73" s="80" t="inlineStr">
         <is>
           <t>CALL-08</t>
         </is>
       </c>
-      <c r="B73" s="81" t="inlineStr">
+      <c r="B73" s="96" t="inlineStr">
         <is>
           <t>Ad-Hoc Emergency Fuel Delivery &amp; Mobile Refueling</t>
         </is>
       </c>
-      <c r="C73" s="81" t="inlineStr">
+      <c r="C73" s="97" t="inlineStr">
         <is>
           <t>Rapid procurement and transport of clean Euro-4 automotive diesel fuel in certified fuel containers to remote sites during prolonged grid emergencies, including manual transfer to day tank.
 • Inclusions: Fuel procurement, dedicated transport, manual pumping into tank, fuel quality test.
@@ -10061,78 +10452,489 @@
       </c>
       <c r="D73" s="80" t="inlineStr">
         <is>
-          <t>Per Liter Delivered / Per Trip</t>
-        </is>
-      </c>
-      <c r="E73" s="82" t="n">
+          <t>Per Liter Delivered</t>
+        </is>
+      </c>
+      <c r="E73" s="98" t="n">
         <v>20000</v>
       </c>
-      <c r="F73" s="82" t="n">
+      <c r="F73" s="98" t="n">
         <v>100000</v>
       </c>
-      <c r="G73" s="83" t="n"/>
-      <c r="H73" s="84">
-        <f>G73*55</f>
-        <v/>
-      </c>
-      <c r="I73" s="85">
-        <f>E73*G73</f>
+      <c r="G73" s="80" t="inlineStr">
+        <is>
+          <t>Contingency Annual Basket</t>
+        </is>
+      </c>
+      <c r="H73" s="99" t="n"/>
+      <c r="I73" s="84">
+        <f>H73*55</f>
         <v/>
       </c>
       <c r="J73" s="85">
-        <f>F73*G73</f>
-        <v/>
-      </c>
-      <c r="K73" s="81" t="inlineStr">
-        <is>
-          <t>100% upon fuel receipt voucher sign-off.</t>
-        </is>
-      </c>
-      <c r="L73" s="81" t="inlineStr">
+        <f>E73*H73</f>
+        <v/>
+      </c>
+      <c r="K73" s="85">
+        <f>F73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="96" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Contingency Rate Card (Unbudgeted Call-Off)</t>
+        </is>
+      </c>
+      <c r="M73" s="96" t="inlineStr">
         <is>
           <t>Fuel Purchase Receipt &amp; Fuel Delivery Voucher</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="86" t="inlineStr">
-        <is>
-          <t>TOTAL EVALUATED SERVICES SCHEDULE (USD)</t>
-        </is>
-      </c>
-      <c r="B74" s="79" t="n"/>
-      <c r="C74" s="79" t="n"/>
-      <c r="D74" s="79" t="n"/>
-      <c r="E74" s="79" t="n"/>
-      <c r="F74" s="79" t="n"/>
-      <c r="G74" s="79" t="n"/>
-      <c r="H74" s="79" t="n"/>
-      <c r="I74" s="87">
-        <f>SUM(I7:I73)</f>
-        <v/>
-      </c>
-      <c r="J74" s="87">
-        <f>SUM(J7:J73)</f>
-        <v/>
-      </c>
-      <c r="K74" s="88" t="n"/>
-      <c r="L74" s="88" t="n"/>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL A1: STANDBY SAQ CONTINGENCY EVALUATION BASKET (103 SITES PH1 / 515 SITES PROG)</t>
+        </is>
+      </c>
+      <c r="B75" s="79" t="n"/>
+      <c r="C75" s="79" t="n"/>
+      <c r="D75" s="79" t="n"/>
+      <c r="E75" s="79" t="n"/>
+      <c r="F75" s="79" t="n"/>
+      <c r="G75" s="79" t="n"/>
+      <c r="H75" s="79" t="n"/>
+      <c r="I75" s="79" t="n"/>
+      <c r="J75" s="104">
+        <f>SUM(J7:J14)</f>
+        <v/>
+      </c>
+      <c r="K75" s="104">
+        <f>SUM(K7:K14)</f>
+        <v/>
+      </c>
+      <c r="L75" s="105" t="inlineStr">
+        <is>
+          <t>Lot 5 Contingency Standby Rate Card (Billable strictly on Own-Build Work Orders)</t>
+        </is>
+      </c>
+      <c r="M75" s="88" t="n"/>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL A2: CORE TURNKEY ROLLOUT SERVICES (1,000 SITES PH1 / 5,000 SITES PROG)</t>
+        </is>
+      </c>
+      <c r="B76" s="79" t="n"/>
+      <c r="C76" s="79" t="n"/>
+      <c r="D76" s="79" t="n"/>
+      <c r="E76" s="79" t="n"/>
+      <c r="F76" s="79" t="n"/>
+      <c r="G76" s="79" t="n"/>
+      <c r="H76" s="79" t="n"/>
+      <c r="I76" s="79" t="n"/>
+      <c r="J76" s="104">
+        <f>SUM(J16:J42)</f>
+        <v/>
+      </c>
+      <c r="K76" s="104">
+        <f>SUM(K16:K42)</f>
+        <v/>
+      </c>
+      <c r="L76" s="105" t="inlineStr">
+        <is>
+          <t>Lot 5 Core Turnkey Deployment Baseline (Committed Rollout Scope)</t>
+        </is>
+      </c>
+      <c r="M76" s="88" t="n"/>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="106" t="inlineStr">
+        <is>
+          <t>SUBTOTAL A: TOTAL TURNKEY ROLLOUT SERVICES (LOT 5 RECONCILED BASELINE) [USD]</t>
+        </is>
+      </c>
+      <c r="B77" s="79" t="n"/>
+      <c r="C77" s="79" t="n"/>
+      <c r="D77" s="79" t="n"/>
+      <c r="E77" s="79" t="n"/>
+      <c r="F77" s="79" t="n"/>
+      <c r="G77" s="79" t="n"/>
+      <c r="H77" s="79" t="n"/>
+      <c r="I77" s="79" t="n"/>
+      <c r="J77" s="107">
+        <f>J75+J76</f>
+        <v/>
+      </c>
+      <c r="K77" s="107">
+        <f>K75+K76</f>
+        <v/>
+      </c>
+      <c r="L77" s="108" t="inlineStr">
+        <is>
+          <t>Reconciles to RFP Lot 5 / Form C Row 6 (Turnkey Site Acq, Engineering &amp; Civils)</t>
+        </is>
+      </c>
+      <c r="M77" s="109" t="n"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL B1: ANNUALIZED 24/7 MANAGED O&amp;M SERVICES (12-MONTH EVALUATION) [USD/YEAR]</t>
+        </is>
+      </c>
+      <c r="B78" s="79" t="n"/>
+      <c r="C78" s="79" t="n"/>
+      <c r="D78" s="79" t="n"/>
+      <c r="E78" s="79" t="n"/>
+      <c r="F78" s="79" t="n"/>
+      <c r="G78" s="79" t="n"/>
+      <c r="H78" s="79" t="n"/>
+      <c r="I78" s="79" t="n"/>
+      <c r="J78" s="104">
+        <f>SUM(J44:J64)</f>
+        <v/>
+      </c>
+      <c r="K78" s="104">
+        <f>SUM(K44:K64)</f>
+        <v/>
+      </c>
+      <c r="L78" s="105" t="inlineStr">
+        <is>
+          <t>Annual 1-Year O&amp;M Rate Card (NOC, FLM, PM Modules A-E, SPMS, RNO)</t>
+        </is>
+      </c>
+      <c r="M78" s="88" t="n"/>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="106" t="inlineStr">
+        <is>
+          <t>SUBTOTAL B2: 3-YEAR MANAGED O&amp;M CONTRACTUAL PROGRAM TOTAL (36 MONTHS — LOT 6 BASELINE) [USD]</t>
+        </is>
+      </c>
+      <c r="B79" s="79" t="n"/>
+      <c r="C79" s="79" t="n"/>
+      <c r="D79" s="79" t="n"/>
+      <c r="E79" s="79" t="n"/>
+      <c r="F79" s="79" t="n"/>
+      <c r="G79" s="79" t="n"/>
+      <c r="H79" s="79" t="n"/>
+      <c r="I79" s="79" t="n"/>
+      <c r="J79" s="107">
+        <f>J78*3</f>
+        <v/>
+      </c>
+      <c r="K79" s="107">
+        <f>K78*3</f>
+        <v/>
+      </c>
+      <c r="L79" s="108" t="inlineStr">
+        <is>
+          <t>Reconciles to RFP Lot 6 3-Year Managed Services Contract &amp; Form C Row 11 (Yrs 1-3)</t>
+        </is>
+      </c>
+      <c r="M79" s="109" t="n"/>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL C: AD-HOC CALL-OUT CONTINGENCY EVALUATION BASKET (NOMINAL ANNUAL CALL-OFF) [USD]</t>
+        </is>
+      </c>
+      <c r="B80" s="79" t="n"/>
+      <c r="C80" s="79" t="n"/>
+      <c r="D80" s="79" t="n"/>
+      <c r="E80" s="79" t="n"/>
+      <c r="F80" s="79" t="n"/>
+      <c r="G80" s="79" t="n"/>
+      <c r="H80" s="79" t="n"/>
+      <c r="I80" s="79" t="n"/>
+      <c r="J80" s="104">
+        <f>SUM(J66:J73)</f>
+        <v/>
+      </c>
+      <c r="K80" s="104">
+        <f>SUM(K66:K73)</f>
+        <v/>
+      </c>
+      <c r="L80" s="105" t="inlineStr">
+        <is>
+          <t>Governing Call-Out Ceiling Rates (Typhoon, Mobile Genset, Fiber Splicing, Drone, Refueling)</t>
+        </is>
+      </c>
+      <c r="M80" s="88" t="n"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="110" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL: RECONCILED EVALUATED SERVICES TCO (ROLLOUT + 3-YEAR O&amp;M + CALL-OUT BASKET) [USD]</t>
+        </is>
+      </c>
+      <c r="B81" s="111" t="n"/>
+      <c r="C81" s="111" t="n"/>
+      <c r="D81" s="111" t="n"/>
+      <c r="E81" s="111" t="n"/>
+      <c r="F81" s="111" t="n"/>
+      <c r="G81" s="111" t="n"/>
+      <c r="H81" s="111" t="n"/>
+      <c r="I81" s="111" t="n"/>
+      <c r="J81" s="112">
+        <f>J77+J79+J80</f>
+        <v/>
+      </c>
+      <c r="K81" s="112">
+        <f>K77+K79+K80</f>
+        <v/>
+      </c>
+      <c r="L81" s="113" t="inlineStr">
+        <is>
+          <t>Official Evaluated Commercial Score Basis for Master Services SOW</t>
+        </is>
+      </c>
+      <c r="M81" s="114" t="n"/>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="110" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL EQUIVALENT IN PHILIPPINE PESO (PHP @ 55.00 FX BASELINE)</t>
+        </is>
+      </c>
+      <c r="B82" s="111" t="n"/>
+      <c r="C82" s="111" t="n"/>
+      <c r="D82" s="111" t="n"/>
+      <c r="E82" s="111" t="n"/>
+      <c r="F82" s="111" t="n"/>
+      <c r="G82" s="111" t="n"/>
+      <c r="H82" s="111" t="n"/>
+      <c r="I82" s="111" t="n"/>
+      <c r="J82" s="115">
+        <f>J81*55</f>
+        <v/>
+      </c>
+      <c r="K82" s="115">
+        <f>K81*55</f>
+        <v/>
+      </c>
+      <c r="L82" s="113" t="inlineStr">
+        <is>
+          <t>Baseline Contract Conversion at Official Tender FX Rate</t>
+        </is>
+      </c>
+      <c r="M82" s="114" t="n"/>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="116" t="inlineStr">
+        <is>
+          <t>FORMAL LOT &amp; FORM C (10-YEAR TCO) RECONCILIATION MAPPING MATRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="117" t="inlineStr">
+        <is>
+          <t>RFP Commercial Lot / TCO Line Item</t>
+        </is>
+      </c>
+      <c r="B85" s="117" t="n"/>
+      <c r="C85" s="117" t="n"/>
+      <c r="D85" s="117" t="inlineStr">
+        <is>
+          <t>Services SOW &amp; Rate Card Mapping</t>
+        </is>
+      </c>
+      <c r="E85" s="117" t="n"/>
+      <c r="F85" s="117" t="n"/>
+      <c r="G85" s="117" t="inlineStr">
+        <is>
+          <t>Phase 1 Formula / Evaluation Link</t>
+        </is>
+      </c>
+      <c r="H85" s="117" t="n"/>
+      <c r="I85" s="117" t="inlineStr">
+        <is>
+          <t>Contractual &amp; Governance Treatment</t>
+        </is>
+      </c>
+      <c r="J85" s="117" t="n"/>
+      <c r="K85" s="117" t="n"/>
+      <c r="L85" s="117" t="n"/>
+      <c r="M85" s="117" t="n"/>
+    </row>
+    <row r="86" ht="52" customHeight="1">
+      <c r="A86" s="118" t="inlineStr">
+        <is>
+          <t>Lot 5: Site Acquisition, TSSR &amp; Civil Works
+(Form C Row 6 Component)</t>
+        </is>
+      </c>
+      <c r="B86" s="119" t="n"/>
+      <c r="C86" s="119" t="n"/>
+      <c r="D86" s="119" t="inlineStr">
+        <is>
+          <t>Reconciles directly with SUBTOTAL A:
+• Subtotal A1: Standby SAQ Basket (103 Sites)
+• Subtotal A2: Core Turnkey Rollout (1,000 Sites)</t>
+        </is>
+      </c>
+      <c r="E86" s="119" t="n"/>
+      <c r="F86" s="119" t="n"/>
+      <c r="G86" s="120">
+        <f>J77 (Total Turnkey Rollout USD)</f>
+        <v/>
+      </c>
+      <c r="H86" s="119" t="n"/>
+      <c r="I86" s="119" t="inlineStr">
+        <is>
+          <t>Provides transparent itemized bottom-up rate card for Lot 5. In baseline tender, Bidders quote Lot 5 turnkey lump-sum on Sheet 'Lot 5 - Site Acq &amp; Civils'. Category A establishes the governing unit rate card for site additions, deductions, and scope variations during deployment.</t>
+        </is>
+      </c>
+      <c r="J86" s="119" t="n"/>
+      <c r="K86" s="119" t="n"/>
+      <c r="L86" s="119" t="n"/>
+      <c r="M86" s="119" t="n"/>
+    </row>
+    <row r="87" ht="52" customHeight="1">
+      <c r="A87" s="118" t="inlineStr">
+        <is>
+          <t>Lot 6: Managed Services &amp; 24/7 Operations
+(Form C Row 11: Annual O&amp;M Yrs 1-3)</t>
+        </is>
+      </c>
+      <c r="B87" s="119" t="n"/>
+      <c r="C87" s="119" t="n"/>
+      <c r="D87" s="119" t="inlineStr">
+        <is>
+          <t>Reconciles directly with SUBTOTAL B1 &amp; B2:
+• Subtotal B1: Annualized Managed O&amp;M (1 Year)
+• Subtotal B2: 3-Year Contractual Baseline (3 Years)</t>
+        </is>
+      </c>
+      <c r="E87" s="119" t="n"/>
+      <c r="F87" s="119" t="n"/>
+      <c r="G87" s="120" t="inlineStr">
+        <is>
+          <t>Annual: =J78 (USD/Yr)
+3-Year: =J79 (USD Total)</t>
+        </is>
+      </c>
+      <c r="H87" s="119" t="n"/>
+      <c r="I87" s="119" t="inlineStr">
+        <is>
+          <t>Provides detailed module-level rate card for Lot 6 (NOC, FLM, PM Modules A-E, SPMS, RNO). Form C Row 11 applies the annualized rate across the 1,000 Phase 1 sites. Retainer-included items (FLM-02..04, SPM-02..03) are contractually bundled at $0.00 to guarantee zero double-charging.</t>
+        </is>
+      </c>
+      <c r="J87" s="119" t="n"/>
+      <c r="K87" s="119" t="n"/>
+      <c r="L87" s="119" t="n"/>
+      <c r="M87" s="119" t="n"/>
+    </row>
+    <row r="88" ht="52" customHeight="1">
+      <c r="A88" s="118" t="inlineStr">
+        <is>
+          <t>Contingency Standby SAQ Rate Card
+(Tier 3 Operator Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="B88" s="119" t="n"/>
+      <c r="C88" s="119" t="n"/>
+      <c r="D88" s="119" t="inlineStr">
+        <is>
+          <t>Items SAQ-01 through SAQ-08
+(Nominal 103 Sites / 10.3% Own-Build Basket)</t>
+        </is>
+      </c>
+      <c r="E88" s="119" t="n"/>
+      <c r="F88" s="119" t="n"/>
+      <c r="G88" s="120">
+        <f>J75 (Evaluated Contingency Basket)</f>
+        <v/>
+      </c>
+      <c r="H88" s="119" t="n"/>
+      <c r="I88" s="119" t="inlineStr">
+        <is>
+          <t>STANDBY RATE CARD ONLY. Operational baseline is TowerCo-acquired under MLA (897 Co-Location / 103 B2S). These rates are billable strictly upon written Work Order issued by TelTech for authorized Operator Self-Acquired sites.</t>
+        </is>
+      </c>
+      <c r="J88" s="119" t="n"/>
+      <c r="K88" s="119" t="n"/>
+      <c r="L88" s="119" t="n"/>
+      <c r="M88" s="119" t="n"/>
+    </row>
+    <row r="89" ht="52" customHeight="1">
+      <c r="A89" s="118" t="inlineStr">
+        <is>
+          <t>Ad-Hoc Specialized Services Rate Card
+(Master Agreement Schedule of Rates)</t>
+        </is>
+      </c>
+      <c r="B89" s="119" t="n"/>
+      <c r="C89" s="119" t="n"/>
+      <c r="D89" s="119" t="inlineStr">
+        <is>
+          <t>Items CALL-01 through CALL-08
+(Specialized Rigging, Emergency Genset, Fiber Splicing, Drone, Refueling)</t>
+        </is>
+      </c>
+      <c r="E89" s="119" t="n"/>
+      <c r="F89" s="119" t="n"/>
+      <c r="G89" s="120">
+        <f>J80 (Annual Evaluated Basket)</f>
+        <v/>
+      </c>
+      <c r="H89" s="119" t="n"/>
+      <c r="I89" s="119" t="inlineStr">
+        <is>
+          <t>Ceiling rate card for unbudgeted emergency restoration, force majeure events, and specialized engineering call-offs. Billable strictly per approved mobilization event or verified consumption (e.g. metered fuel liters).</t>
+        </is>
+      </c>
+      <c r="J89" s="119" t="n"/>
+      <c r="K89" s="119" t="n"/>
+      <c r="L89" s="119" t="n"/>
+      <c r="M89" s="119" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A65:L65"/>
+  <mergeCells count="41">
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="I86:M86"/>
+    <mergeCell ref="I89:M89"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="I85:M85"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:M87"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A65:M65"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A84:M84"/>
+    <mergeCell ref="I88:M88"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A78:I78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="₱#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0,##0.00"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -229,8 +229,37 @@
       <color rgb="00FFFFFF"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A192F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00004D40"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -337,8 +366,14 @@
         <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+        <bgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -519,11 +554,35 @@
         <color rgb="000A192F"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000A192F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000A192F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -815,6 +874,29 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3543,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3921,17 +4003,197 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="121" t="inlineStr">
-        <is>
-          <t>RECONCILIATION NOTE — MASTER SERVICES SOW &amp; RATE CARD INTEGRATION:</t>
+      <c r="A17" s="127" t="inlineStr">
+        <is>
+          <t>FORMAL COMMERCIAL AUDIT &amp; LIVE CROSS-SCHEDULE RECONCILIATION VERIFICATION</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="122" t="inlineStr">
-        <is>
-          <t>• Lot 5 (Line 1 Capex Component): Turnkey Site Acquisition, TSSR &amp; Civil Infrastructure reconciles with Sheet 'Services SOW &amp; Rate Card' Subtotal A (Cells J77 Phase 1 / K77 Program). Category 1 SAQ rates serve as standby own-build rates (10.3% contingency basket).
-• Lot 6 (Line 6 Annual Managed Services Component): 24/7 Managed Operations &amp; Maintenance reconciles with Sheet 'Services SOW &amp; Rate Card' Subtotal B1 (Cell J78 Phase 1 Annualized O&amp;M) and Subtotal B2 (Cell J79 3-Year Contractual Total). Retainer-included services evaluate at $0.00.</t>
+      <c r="A18" s="128" t="inlineStr">
+        <is>
+          <t>Cost Element / Procurement Scope</t>
+        </is>
+      </c>
+      <c r="B18" s="128" t="inlineStr">
+        <is>
+          <t>Modular Lot Value</t>
+        </is>
+      </c>
+      <c r="C18" s="128" t="inlineStr">
+        <is>
+          <t>Services SOW Value</t>
+        </is>
+      </c>
+      <c r="D18" s="128" t="inlineStr">
+        <is>
+          <t>Absolute Variance</t>
+        </is>
+      </c>
+      <c r="E18" s="128" t="inlineStr">
+        <is>
+          <t>Reconciliation Status</t>
+        </is>
+      </c>
+      <c r="F18" s="128" t="inlineStr">
+        <is>
+          <t>Tender Governance &amp; Cross-Reference Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="129" t="inlineStr">
+        <is>
+          <t>1. Turnkey Rollout Services (Lot 1 Svc / Domains 2-7)</t>
+        </is>
+      </c>
+      <c r="B19" s="130">
+        <f>'Lot 1 - RAN &amp; Rollout'!H16</f>
+        <v/>
+      </c>
+      <c r="C19" s="130">
+        <f>'Services SOW &amp; Rate Card'!J77</f>
+        <v/>
+      </c>
+      <c r="D19" s="130">
+        <f>ABS(B19-C19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="131">
+        <f>IF(D19&lt;1, "✓ ZERO VARIANCE", "⚠️ DISCREPANCY")</f>
+        <v/>
+      </c>
+      <c r="F19" s="132" t="inlineStr">
+        <is>
+          <t>Reconciles bottom-up 22-item turnkey rollout scope with Lot 1 Table 2. Form C Row 6 incorporates Lot 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="129" t="inlineStr">
+        <is>
+          <t>2. Annual Managed Services O&amp;M (Lot 6 / Domain 8)</t>
+        </is>
+      </c>
+      <c r="B20" s="130">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="C20" s="130">
+        <f>'Services SOW &amp; Rate Card'!J79</f>
+        <v/>
+      </c>
+      <c r="D20" s="130">
+        <f>ABS(B20-C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="131">
+        <f>IF(D20&lt;1, "✓ ZERO VARIANCE", "⚠️ DISCREPANCY")</f>
+        <v/>
+      </c>
+      <c r="F20" s="132" t="inlineStr">
+        <is>
+          <t>Reconciles unbundled 21-item 24/7 O&amp;M scope with Lot 6 Table 7. Form C Row 11 applies this annual rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="129" t="inlineStr">
+        <is>
+          <t>3. 3-Year Managed Services Contractual Baseline</t>
+        </is>
+      </c>
+      <c r="B21" s="130">
+        <f>B20*3</f>
+        <v/>
+      </c>
+      <c r="C21" s="130">
+        <f>'Services SOW &amp; Rate Card'!J80</f>
+        <v/>
+      </c>
+      <c r="D21" s="130">
+        <f>ABS(B21-C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="131">
+        <f>IF(D21&lt;1, "✓ ZERO VARIANCE", "⚠️ DISCREPANCY")</f>
+        <v/>
+      </c>
+      <c r="F21" s="132" t="inlineStr">
+        <is>
+          <t>Reconciles evaluated 3-year O&amp;M contract baseline (Year 1 to 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="129" t="inlineStr">
+        <is>
+          <t>4. Evaluated Phase 1 CapEx Offer (Lots 1, 2, 3, 4, 5, 7)</t>
+        </is>
+      </c>
+      <c r="B22" s="130">
+        <f>B6+B7+B8+B9+B12</f>
+        <v/>
+      </c>
+      <c r="C22" s="130">
+        <f>B6+B7+B8+B9+B12</f>
+        <v/>
+      </c>
+      <c r="D22" s="130">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E22" s="131" t="inlineStr">
+        <is>
+          <t>"✓ COMMITTED CAPEX"</t>
+        </is>
+      </c>
+      <c r="F22" s="132" t="inlineStr">
+        <is>
+          <t>Turnkey 1,000 sites infrastructure: RAN, Power, 5GC, OSS/BSS, Civils/Towers &amp; Spares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="129" t="inlineStr">
+        <is>
+          <t>5. Evaluated 3-Year TCO Offer (CapEx + 3-Yr O&amp;M)</t>
+        </is>
+      </c>
+      <c r="B23" s="130">
+        <f>B22+B21</f>
+        <v/>
+      </c>
+      <c r="C23" s="130">
+        <f>B22+B21</f>
+        <v/>
+      </c>
+      <c r="D23" s="130">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E23" s="131" t="inlineStr">
+        <is>
+          <t>"✓ COMMITTED 3-YR TCO"</t>
+        </is>
+      </c>
+      <c r="F23" s="132" t="inlineStr">
+        <is>
+          <t>Evaluated 3-Year Lifecycle Offer: Phase 1 CapEx + 3-Year Managed Services Contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="121" t="inlineStr">
+        <is>
+          <t>FORM C TENDER EVALUATION GOVERNING CLAUSE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="133" t="inlineStr">
+        <is>
+          <t>Form C Row 13 (Evaluated 10-Year Lifecycle TCO) is the SOLE official evaluated commercial offer for contract award. The Master Services SOW schedule provides binding contract unit rates, milestone billing triggers, and change-order controls. In the event of any numerical discrepancy between the modular Lot schedules and the Services SOW rate card, Form C and the modular Lot rate tables govern. Bidders must verify zero variance across all schedules prior to sealed bid submission.</t>
         </is>
       </c>
     </row>
@@ -6889,23 +7151,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="91" t="inlineStr">
@@ -7131,7 +7378,7 @@
       </c>
       <c r="C9" s="97" t="inlineStr">
         <is>
-          <t>[APPLIES TO TOWERCO CO-LOCATION: Preparation of technical equipment loading profile (3x 8T8R RRU, 3x Antennas, hybrid cables, 2m x 2m pad) and coordination with TowerCo engineering until SAA approval. Commercial lease executed directly by Operator under MLA]. Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
+          <t>[COMMITTED TIER 1 CO-LOCATION SCOPE (897 SITES)]: Preparation of technical equipment loading profile (3x 8T8R RRU, 3x Antennas, hybrid cables, 2m x 2m pad) and coordination with TowerCo engineering until SAA approval. Commercial lease executed directly by Operator under MLA. Preparation, technical compilation, submission, and engineering follow-through of the TowerCo Space Application (SAA) package for co-location under Operator's Master Lease Agreement (MLA). Compiles exact proposed loading profile: 3x 8T8R RRU, 3x macro antennas/AAUs, antenna mounting brackets (AMB), hybrid trunk cables, DC distribution requirements, and ground plinth reservation (2.0m x 2.0m). Coordinates with TowerCo technical team during structural vetting until formal issuance of SAA Approval and Notice to Proceed (NTP).
 • Inclusions: SAA documentation, loading calculation submission, liaison with TowerCo engineering, tracking SAA to NTP.
 • Exclusions: Commercial MLA negotiations and monthly tower rental fees (exclusive Operator responsibility).</t>
         </is>
@@ -7142,10 +7389,10 @@
         </is>
       </c>
       <c r="E9" s="98" t="n">
-        <v>103</v>
+        <v>897</v>
       </c>
       <c r="F9" s="98" t="n">
-        <v>515</v>
+        <v>4485</v>
       </c>
       <c r="G9" s="80" t="inlineStr">
         <is>
@@ -8558,8 +8805,8 @@
       </c>
       <c r="C38" s="97" t="inlineStr">
         <is>
-          <t>On-ground field testing using 5G test UE and scanner: stationary throughput tests at near, mid, and cell-edge points per sector (validating &gt;= 450 Mbps peak DL, &gt;= 50 Mbps cell-edge DL, &gt;= 15 Mbps cell-edge UL); sector swap validation; intra-site handover execution; latency verification across backhaul media (Terrestrial Fiber: Target RTT &lt;= 18 ms to Core UPF, with Contractual Acceptance Rejection Ceiling &lt;= 30 ms per Appendix C KPI-RAN-07 and Bid Bulletin 01 §2.3; LEO Satellite Starlink / Expansion: Target RTT &lt;= 50 ms, Contractual Acceptance Rejection Ceiling &lt;= 65 ms); packet loss measurement (&lt; 0.1%); and compilation and formal sign-off of the comprehensive SSV Report.
-• Inclusions: Stationary throughput tests, sector swap check, handover test, latency compliance test (&lt;= 30 ms fiber ceiling / &lt;= 65 ms satellite ceiling), SSV report compilation.
+          <t>On-ground field testing using 5G test UE and scanner: stationary throughput tests at near, mid, and cell-edge points per sector (validating &gt;= 450 Mbps peak DL, &gt;= 50 Mbps cell-edge DL, &gt;= 15 Mbps cell-edge UL); sector swap validation; intra-site handover execution; latency verification across backhaul media (Terrestrial Fiber: Target RTT &lt;= 18 ms to Core UPF, with Contractual Acceptance Rejection Ceiling &lt;= 30 ms per Appendix C KPI-RAN-07 and Bid Bulletin 01 §2.3; LEO Satellite Starlink / Expansion: Target RTT &lt;= 60 ms, Contractual Acceptance Rejection Ceiling &lt;= 80 ms per Bid Bulletin 01 §2.3); packet loss measurement (&lt; 0.1%); and compilation and formal sign-off of the comprehensive SSV Report.
+• Inclusions: Stationary throughput tests, sector swap check, handover test, latency compliance test (&lt;= 30 ms fiber ceiling / &lt;= 80 ms satellite ceiling), SSV report compilation.
 • Exclusions: Multi-site cluster drive testing (covered under Category 7).</t>
         </is>
       </c>
@@ -10493,7 +10740,7 @@
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="103" t="inlineStr">
         <is>
-          <t>SUBTOTAL A1: STANDBY SAQ CONTINGENCY EVALUATION BASKET (103 SITES PH1 / 515 SITES PROG)</t>
+          <t>SUBTOTAL A1a: COMMITTED TIER 1 CO-LOCATION SAA SUPPORT (897 SITES PH1 / 4,485 SITES PROG) [SAQ-03]</t>
         </is>
       </c>
       <c r="B75" s="79" t="n"/>
@@ -10505,16 +10752,16 @@
       <c r="H75" s="79" t="n"/>
       <c r="I75" s="79" t="n"/>
       <c r="J75" s="104">
-        <f>SUM(J7:J14)</f>
+        <f>J9</f>
         <v/>
       </c>
       <c r="K75" s="104">
-        <f>SUM(K7:K14)</f>
+        <f>K9</f>
         <v/>
       </c>
       <c r="L75" s="105" t="inlineStr">
         <is>
-          <t>Lot 5 Contingency Standby Rate Card (Billable strictly on Own-Build Work Orders)</t>
+          <t>Committed Tier 1 Space Application (SAA) &amp; Loading Dossier package for 897 Co-Location Sites</t>
         </is>
       </c>
       <c r="M75" s="88" t="n"/>
@@ -10522,7 +10769,7 @@
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="103" t="inlineStr">
         <is>
-          <t>SUBTOTAL A2: CORE TURNKEY ROLLOUT SERVICES (1,000 SITES PH1 / 5,000 SITES PROG)</t>
+          <t>SUBTOTAL A1b: STANDBY 10.3% OWN-BUILD SAQ BASKET (103 SITES PH1 / 515 SITES PROG) [SAQ-01, 02, 04..08]</t>
         </is>
       </c>
       <c r="B76" s="79" t="n"/>
@@ -10534,24 +10781,24 @@
       <c r="H76" s="79" t="n"/>
       <c r="I76" s="79" t="n"/>
       <c r="J76" s="104">
-        <f>SUM(J16:J42)</f>
+        <f>SUM(J7:J8)+SUM(J10:J14)</f>
         <v/>
       </c>
       <c r="K76" s="104">
-        <f>SUM(K16:K42)</f>
+        <f>SUM(K7:K8)+SUM(K10:K14)</f>
         <v/>
       </c>
       <c r="L76" s="105" t="inlineStr">
         <is>
-          <t>Lot 5 Core Turnkey Deployment Baseline (Committed Rollout Scope)</t>
+          <t>Lot 5 Contingency Standby Rate Card (Billable strictly on Operator Own-Build Work Orders)</t>
         </is>
       </c>
       <c r="M76" s="88" t="n"/>
     </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="A77" s="106" t="inlineStr">
-        <is>
-          <t>SUBTOTAL A: TOTAL TURNKEY ROLLOUT SERVICES (LOT 5 RECONCILED BASELINE) [USD]</t>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL A2: COMMITTED TURNKEY ROLLOUT SERVICES (1,000 SITES PH1 / 5,000 SITES PROG) [DOMAINS 2-7]</t>
         </is>
       </c>
       <c r="B77" s="79" t="n"/>
@@ -10562,25 +10809,25 @@
       <c r="G77" s="79" t="n"/>
       <c r="H77" s="79" t="n"/>
       <c r="I77" s="79" t="n"/>
-      <c r="J77" s="107">
-        <f>J75+J76</f>
-        <v/>
-      </c>
-      <c r="K77" s="107">
-        <f>K75+K76</f>
-        <v/>
-      </c>
-      <c r="L77" s="108" t="inlineStr">
-        <is>
-          <t>Reconciles to RFP Lot 5 / Form C Row 6 (Turnkey Site Acq, Engineering &amp; Civils)</t>
-        </is>
-      </c>
-      <c r="M77" s="109" t="n"/>
-    </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="103" t="inlineStr">
-        <is>
-          <t>SUBTOTAL B1: ANNUALIZED 24/7 MANAGED O&amp;M SERVICES (12-MONTH EVALUATION) [USD/YEAR]</t>
+      <c r="J77" s="104">
+        <f>SUM(J16:J42)</f>
+        <v/>
+      </c>
+      <c r="K77" s="104">
+        <f>SUM(K16:K42)</f>
+        <v/>
+      </c>
+      <c r="L77" s="105" t="inlineStr">
+        <is>
+          <t>Lot 1 Table 2 Turnkey Rollout Baseline (22 Unbundled Scope Items across 1,000 Sites)</t>
+        </is>
+      </c>
+      <c r="M77" s="88" t="n"/>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="106" t="inlineStr">
+        <is>
+          <t>SUBTOTAL A: TOTAL TURNKEY ROLLOUT &amp; SITING SERVICES (COMMITTED + STANDBY BASKET) [USD]</t>
         </is>
       </c>
       <c r="B78" s="79" t="n"/>
@@ -10591,25 +10838,25 @@
       <c r="G78" s="79" t="n"/>
       <c r="H78" s="79" t="n"/>
       <c r="I78" s="79" t="n"/>
-      <c r="J78" s="104">
-        <f>SUM(J44:J64)</f>
-        <v/>
-      </c>
-      <c r="K78" s="104">
-        <f>SUM(K44:K64)</f>
-        <v/>
-      </c>
-      <c r="L78" s="105" t="inlineStr">
-        <is>
-          <t>Annual 1-Year O&amp;M Rate Card (NOC, FLM, PM Modules A-E, SPMS, RNO)</t>
-        </is>
-      </c>
-      <c r="M78" s="88" t="n"/>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="106" t="inlineStr">
-        <is>
-          <t>SUBTOTAL B2: 3-YEAR MANAGED O&amp;M CONTRACTUAL PROGRAM TOTAL (36 MONTHS — LOT 6 BASELINE) [USD]</t>
+      <c r="J78" s="107">
+        <f>J75+J76+J77</f>
+        <v/>
+      </c>
+      <c r="K78" s="107">
+        <f>K75+K76+K77</f>
+        <v/>
+      </c>
+      <c r="L78" s="108" t="inlineStr">
+        <is>
+          <t>Reconciles to RFP Lot 5 / Form C Row 6 (Turnkey Site Acq, Engineering &amp; Civils)</t>
+        </is>
+      </c>
+      <c r="M78" s="109" t="n"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL B1: ANNUALIZED 24/7 MANAGED O&amp;M SERVICES (12-MONTH EVALUATION) [USD/YEAR]</t>
         </is>
       </c>
       <c r="B79" s="79" t="n"/>
@@ -10620,25 +10867,25 @@
       <c r="G79" s="79" t="n"/>
       <c r="H79" s="79" t="n"/>
       <c r="I79" s="79" t="n"/>
-      <c r="J79" s="107">
-        <f>J78*3</f>
-        <v/>
-      </c>
-      <c r="K79" s="107">
-        <f>K78*3</f>
-        <v/>
-      </c>
-      <c r="L79" s="108" t="inlineStr">
-        <is>
-          <t>Reconciles to RFP Lot 6 3-Year Managed Services Contract &amp; Form C Row 11 (Yrs 1-3)</t>
-        </is>
-      </c>
-      <c r="M79" s="109" t="n"/>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="103" t="inlineStr">
-        <is>
-          <t>SUBTOTAL C: AD-HOC CALL-OUT CONTINGENCY EVALUATION BASKET (NOMINAL ANNUAL CALL-OFF) [USD]</t>
+      <c r="J79" s="104">
+        <f>SUM(J44:J64)</f>
+        <v/>
+      </c>
+      <c r="K79" s="104">
+        <f>SUM(K44:K64)</f>
+        <v/>
+      </c>
+      <c r="L79" s="105" t="inlineStr">
+        <is>
+          <t>Annual 1-Year O&amp;M Rate Card (NOC, FLM, PM Modules A-E, SPMS, RNO)</t>
+        </is>
+      </c>
+      <c r="M79" s="88" t="n"/>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="106" t="inlineStr">
+        <is>
+          <t>SUBTOTAL B2: 3-YEAR MANAGED O&amp;M CONTRACTUAL PROGRAM TOTAL (36 MONTHS — LOT 6 BASELINE) [USD]</t>
         </is>
       </c>
       <c r="B80" s="79" t="n"/>
@@ -10649,54 +10896,54 @@
       <c r="G80" s="79" t="n"/>
       <c r="H80" s="79" t="n"/>
       <c r="I80" s="79" t="n"/>
-      <c r="J80" s="104">
+      <c r="J80" s="107">
+        <f>J79*3</f>
+        <v/>
+      </c>
+      <c r="K80" s="107">
+        <f>K79*3</f>
+        <v/>
+      </c>
+      <c r="L80" s="108" t="inlineStr">
+        <is>
+          <t>Reconciles to RFP Lot 6 3-Year Managed Services Contract &amp; Form C Row 11 (Yrs 1-3)</t>
+        </is>
+      </c>
+      <c r="M80" s="109" t="n"/>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="103" t="inlineStr">
+        <is>
+          <t>SUBTOTAL C: AD-HOC CALL-OUT CONTINGENCY EVALUATION BASKET (NOMINAL ANNUAL CALL-OFF) [USD]</t>
+        </is>
+      </c>
+      <c r="B81" s="79" t="n"/>
+      <c r="C81" s="79" t="n"/>
+      <c r="D81" s="79" t="n"/>
+      <c r="E81" s="79" t="n"/>
+      <c r="F81" s="79" t="n"/>
+      <c r="G81" s="79" t="n"/>
+      <c r="H81" s="79" t="n"/>
+      <c r="I81" s="79" t="n"/>
+      <c r="J81" s="104">
         <f>SUM(J66:J73)</f>
         <v/>
       </c>
-      <c r="K80" s="104">
+      <c r="K81" s="104">
         <f>SUM(K66:K73)</f>
         <v/>
       </c>
-      <c r="L80" s="105" t="inlineStr">
+      <c r="L81" s="105" t="inlineStr">
         <is>
           <t>Governing Call-Out Ceiling Rates (Typhoon, Mobile Genset, Fiber Splicing, Drone, Refueling)</t>
         </is>
       </c>
-      <c r="M80" s="88" t="n"/>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="110" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL: RECONCILED EVALUATED SERVICES TCO (ROLLOUT + 3-YEAR O&amp;M + CALL-OUT BASKET) [USD]</t>
-        </is>
-      </c>
-      <c r="B81" s="111" t="n"/>
-      <c r="C81" s="111" t="n"/>
-      <c r="D81" s="111" t="n"/>
-      <c r="E81" s="111" t="n"/>
-      <c r="F81" s="111" t="n"/>
-      <c r="G81" s="111" t="n"/>
-      <c r="H81" s="111" t="n"/>
-      <c r="I81" s="111" t="n"/>
-      <c r="J81" s="112">
-        <f>J77+J79+J80</f>
-        <v/>
-      </c>
-      <c r="K81" s="112">
-        <f>K77+K79+K80</f>
-        <v/>
-      </c>
-      <c r="L81" s="113" t="inlineStr">
-        <is>
-          <t>Official Evaluated Commercial Score Basis for Master Services SOW</t>
-        </is>
-      </c>
-      <c r="M81" s="114" t="n"/>
+      <c r="M81" s="88" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="110" t="inlineStr">
         <is>
-          <t>GRAND TOTAL EQUIVALENT IN PHILIPPINE PESO (PHP @ 55.00 FX BASELINE)</t>
+          <t>GRAND TOTAL: INDICATIVE ALL-IN SERVICES CONTRACT ENVELOPE (ROLLOUT + 3-YEAR O&amp;M + STANDBY SAQ + CALL-OUTS) [USD]</t>
         </is>
       </c>
       <c r="B82" s="111" t="n"/>
@@ -10707,234 +10954,303 @@
       <c r="G82" s="111" t="n"/>
       <c r="H82" s="111" t="n"/>
       <c r="I82" s="111" t="n"/>
-      <c r="J82" s="115">
-        <f>J81*55</f>
-        <v/>
-      </c>
-      <c r="K82" s="115">
-        <f>K81*55</f>
+      <c r="J82" s="112">
+        <f>J78+J80+J81</f>
+        <v/>
+      </c>
+      <c r="K82" s="112">
+        <f>K78+K80+K81</f>
         <v/>
       </c>
       <c r="L82" s="113" t="inlineStr">
         <is>
+          <t>Benchmark Reference Only — Form C (10-Year Lifecycle TCO) is the SOLE Official Evaluated Score for Award</t>
+        </is>
+      </c>
+      <c r="M82" s="114" t="n"/>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="110" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL EQUIVALENT IN PHILIPPINE PESO (PHP @ 55.00 FX BASELINE)</t>
+        </is>
+      </c>
+      <c r="B83" s="111" t="n"/>
+      <c r="C83" s="111" t="n"/>
+      <c r="D83" s="111" t="n"/>
+      <c r="E83" s="111" t="n"/>
+      <c r="F83" s="111" t="n"/>
+      <c r="G83" s="111" t="n"/>
+      <c r="H83" s="111" t="n"/>
+      <c r="I83" s="111" t="n"/>
+      <c r="J83" s="115">
+        <f>J82*55</f>
+        <v/>
+      </c>
+      <c r="K83" s="115">
+        <f>K82*55</f>
+        <v/>
+      </c>
+      <c r="L83" s="113" t="inlineStr">
+        <is>
           <t>Baseline Contract Conversion at Official Tender FX Rate</t>
         </is>
       </c>
-      <c r="M82" s="114" t="n"/>
-    </row>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="116" t="inlineStr">
-        <is>
-          <t>FORMAL LOT &amp; FORM C (10-YEAR TCO) RECONCILIATION MAPPING MATRIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="117" t="inlineStr">
-        <is>
-          <t>RFP Commercial Lot / TCO Line Item</t>
-        </is>
-      </c>
-      <c r="B85" s="117" t="n"/>
-      <c r="C85" s="117" t="n"/>
-      <c r="D85" s="117" t="inlineStr">
-        <is>
-          <t>Services SOW &amp; Rate Card Mapping</t>
-        </is>
-      </c>
-      <c r="E85" s="117" t="n"/>
-      <c r="F85" s="117" t="n"/>
-      <c r="G85" s="117" t="inlineStr">
-        <is>
-          <t>Phase 1 Formula / Evaluation Link</t>
-        </is>
-      </c>
-      <c r="H85" s="117" t="n"/>
-      <c r="I85" s="117" t="inlineStr">
-        <is>
-          <t>Contractual &amp; Governance Treatment</t>
-        </is>
-      </c>
-      <c r="J85" s="117" t="n"/>
-      <c r="K85" s="117" t="n"/>
-      <c r="L85" s="117" t="n"/>
-      <c r="M85" s="117" t="n"/>
-    </row>
-    <row r="86" ht="52" customHeight="1">
-      <c r="A86" s="118" t="inlineStr">
-        <is>
-          <t>Lot 5: Site Acquisition, TSSR &amp; Civil Works
-(Form C Row 6 Component)</t>
-        </is>
-      </c>
-      <c r="B86" s="119" t="n"/>
-      <c r="C86" s="119" t="n"/>
-      <c r="D86" s="119" t="inlineStr">
-        <is>
-          <t>Reconciles directly with SUBTOTAL A:
-• Subtotal A1: Standby SAQ Basket (103 Sites)
-• Subtotal A2: Core Turnkey Rollout (1,000 Sites)</t>
-        </is>
-      </c>
-      <c r="E86" s="119" t="n"/>
-      <c r="F86" s="119" t="n"/>
-      <c r="G86" s="120">
-        <f>J77 (Total Turnkey Rollout USD)</f>
-        <v/>
-      </c>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="inlineStr">
-        <is>
-          <t>Provides transparent itemized bottom-up rate card for Lot 5. In baseline tender, Bidders quote Lot 5 turnkey lump-sum on Sheet 'Lot 5 - Site Acq &amp; Civils'. Category A establishes the governing unit rate card for site additions, deductions, and scope variations during deployment.</t>
-        </is>
-      </c>
-      <c r="J86" s="119" t="n"/>
-      <c r="K86" s="119" t="n"/>
-      <c r="L86" s="119" t="n"/>
-      <c r="M86" s="119" t="n"/>
-    </row>
-    <row r="87" ht="52" customHeight="1">
-      <c r="A87" s="118" t="inlineStr">
-        <is>
-          <t>Lot 6: Managed Services &amp; 24/7 Operations
-(Form C Row 11: Annual O&amp;M Yrs 1-3)</t>
-        </is>
-      </c>
-      <c r="B87" s="119" t="n"/>
-      <c r="C87" s="119" t="n"/>
-      <c r="D87" s="119" t="inlineStr">
-        <is>
-          <t>Reconciles directly with SUBTOTAL B1 &amp; B2:
-• Subtotal B1: Annualized Managed O&amp;M (1 Year)
-• Subtotal B2: 3-Year Contractual Baseline (3 Years)</t>
-        </is>
-      </c>
-      <c r="E87" s="119" t="n"/>
-      <c r="F87" s="119" t="n"/>
-      <c r="G87" s="120" t="inlineStr">
-        <is>
-          <t>Annual: =J78 (USD/Yr)
-3-Year: =J79 (USD Total)</t>
-        </is>
-      </c>
-      <c r="H87" s="119" t="n"/>
-      <c r="I87" s="119" t="inlineStr">
-        <is>
-          <t>Provides detailed module-level rate card for Lot 6 (NOC, FLM, PM Modules A-E, SPMS, RNO). Form C Row 11 applies the annualized rate across the 1,000 Phase 1 sites. Retainer-included items (FLM-02..04, SPM-02..03) are contractually bundled at $0.00 to guarantee zero double-charging.</t>
-        </is>
-      </c>
-      <c r="J87" s="119" t="n"/>
-      <c r="K87" s="119" t="n"/>
-      <c r="L87" s="119" t="n"/>
-      <c r="M87" s="119" t="n"/>
-    </row>
-    <row r="88" ht="52" customHeight="1">
-      <c r="A88" s="118" t="inlineStr">
-        <is>
-          <t>Contingency Standby SAQ Rate Card
-(Tier 3 Operator Own-Build Basket)</t>
-        </is>
-      </c>
-      <c r="B88" s="119" t="n"/>
-      <c r="C88" s="119" t="n"/>
-      <c r="D88" s="119" t="inlineStr">
-        <is>
-          <t>Items SAQ-01 through SAQ-08
-(Nominal 103 Sites / 10.3% Own-Build Basket)</t>
-        </is>
-      </c>
-      <c r="E88" s="119" t="n"/>
-      <c r="F88" s="119" t="n"/>
-      <c r="G88" s="120">
-        <f>J75 (Evaluated Contingency Basket)</f>
-        <v/>
-      </c>
-      <c r="H88" s="119" t="n"/>
-      <c r="I88" s="119" t="inlineStr">
-        <is>
-          <t>STANDBY RATE CARD ONLY. Operational baseline is TowerCo-acquired under MLA (897 Co-Location / 103 B2S). These rates are billable strictly upon written Work Order issued by TelTech for authorized Operator Self-Acquired sites.</t>
-        </is>
-      </c>
-      <c r="J88" s="119" t="n"/>
-      <c r="K88" s="119" t="n"/>
-      <c r="L88" s="119" t="n"/>
-      <c r="M88" s="119" t="n"/>
-    </row>
-    <row r="89" ht="52" customHeight="1">
-      <c r="A89" s="118" t="inlineStr">
-        <is>
-          <t>Ad-Hoc Specialized Services Rate Card
-(Master Agreement Schedule of Rates)</t>
-        </is>
-      </c>
-      <c r="B89" s="119" t="n"/>
-      <c r="C89" s="119" t="n"/>
-      <c r="D89" s="119" t="inlineStr">
-        <is>
-          <t>Items CALL-01 through CALL-08
-(Specialized Rigging, Emergency Genset, Fiber Splicing, Drone, Refueling)</t>
-        </is>
-      </c>
-      <c r="E89" s="119" t="n"/>
-      <c r="F89" s="119" t="n"/>
-      <c r="G89" s="120">
-        <f>J80 (Annual Evaluated Basket)</f>
-        <v/>
-      </c>
-      <c r="H89" s="119" t="n"/>
-      <c r="I89" s="119" t="inlineStr">
-        <is>
-          <t>Ceiling rate card for unbudgeted emergency restoration, force majeure events, and specialized engineering call-offs. Billable strictly per approved mobilization event or verified consumption (e.g. metered fuel liters).</t>
-        </is>
-      </c>
-      <c r="J89" s="119" t="n"/>
-      <c r="K89" s="119" t="n"/>
-      <c r="L89" s="119" t="n"/>
-      <c r="M89" s="119" t="n"/>
+      <c r="M83" s="114" t="n"/>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="116" t="inlineStr">
+        <is>
+          <t>FORMAL LOT &amp; FORM C (10-YEAR TCO) LIVE RECONCILIATION &amp; VARIANCE AUDIT TABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="123" t="inlineStr">
+        <is>
+          <t>Cost Element / Procurement Scope</t>
+        </is>
+      </c>
+      <c r="B86" s="79" t="n"/>
+      <c r="C86" s="79" t="n"/>
+      <c r="D86" s="79" t="n"/>
+      <c r="E86" s="123" t="inlineStr">
+        <is>
+          <t>Modular Lot Schedule (USD)</t>
+        </is>
+      </c>
+      <c r="F86" s="79" t="n"/>
+      <c r="G86" s="123" t="inlineStr">
+        <is>
+          <t>Services SOW Schedule (USD)</t>
+        </is>
+      </c>
+      <c r="H86" s="79" t="n"/>
+      <c r="I86" s="123" t="inlineStr">
+        <is>
+          <t>Variance (USD)</t>
+        </is>
+      </c>
+      <c r="J86" s="79" t="n"/>
+      <c r="K86" s="123" t="inlineStr">
+        <is>
+          <t>Live Audit Status &amp; Governance Rule</t>
+        </is>
+      </c>
+      <c r="L86" s="79" t="n"/>
+      <c r="M86" s="79" t="n"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="124" t="inlineStr">
+        <is>
+          <t>1. Turnkey Rollout Services (Phase 1: 1,000 Sites)</t>
+        </is>
+      </c>
+      <c r="B87" s="125" t="n"/>
+      <c r="C87" s="125" t="n"/>
+      <c r="D87" s="125" t="n"/>
+      <c r="E87" s="126">
+        <f>'Lot 1 - RAN &amp; Rollout'!H16</f>
+        <v/>
+      </c>
+      <c r="F87" s="125" t="n"/>
+      <c r="G87" s="126">
+        <f>J77</f>
+        <v/>
+      </c>
+      <c r="H87" s="125" t="n"/>
+      <c r="I87" s="126">
+        <f>ABS('Lot 1 - RAN &amp; Rollout'!H16-J77)</f>
+        <v/>
+      </c>
+      <c r="J87" s="125" t="n"/>
+      <c r="K87" s="124">
+        <f>IF(ABS('Lot 1 - RAN &amp; Rollout'!H16-J77)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 1 - RAN &amp; Rollout'!H16-J77), "$#,##0.00") &amp; ")")</f>
+        <v/>
+      </c>
+      <c r="L87" s="125" t="n"/>
+      <c r="M87" s="125" t="n"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="124" t="inlineStr">
+        <is>
+          <t>2. 24/7 Managed Services Annual O&amp;M (12 Months / 1,000 Sites)</t>
+        </is>
+      </c>
+      <c r="B88" s="125" t="n"/>
+      <c r="C88" s="125" t="n"/>
+      <c r="D88" s="125" t="n"/>
+      <c r="E88" s="126">
+        <f>'Lot 6 - Managed Services'!G10*1000</f>
+        <v/>
+      </c>
+      <c r="F88" s="125" t="n"/>
+      <c r="G88" s="126">
+        <f>J79</f>
+        <v/>
+      </c>
+      <c r="H88" s="125" t="n"/>
+      <c r="I88" s="126">
+        <f>ABS('Lot 6 - Managed Services'!G10*1000-J79)</f>
+        <v/>
+      </c>
+      <c r="J88" s="125" t="n"/>
+      <c r="K88" s="124">
+        <f>IF(ABS('Lot 6 - Managed Services'!G10*1000-J79)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 6 - Managed Services'!G10*1000-J79), "$#,##0.00") &amp; ")")</f>
+        <v/>
+      </c>
+      <c r="L88" s="125" t="n"/>
+      <c r="M88" s="125" t="n"/>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="124" t="inlineStr">
+        <is>
+          <t>3. 3-Year Contractual Managed Services O&amp;M Baseline</t>
+        </is>
+      </c>
+      <c r="B89" s="125" t="n"/>
+      <c r="C89" s="125" t="n"/>
+      <c r="D89" s="125" t="n"/>
+      <c r="E89" s="126">
+        <f>'Lot 6 - Managed Services'!G10*1000*3</f>
+        <v/>
+      </c>
+      <c r="F89" s="125" t="n"/>
+      <c r="G89" s="126">
+        <f>J80</f>
+        <v/>
+      </c>
+      <c r="H89" s="125" t="n"/>
+      <c r="I89" s="126">
+        <f>ABS('Lot 6 - Managed Services'!G10*1000*3-J80)</f>
+        <v/>
+      </c>
+      <c r="J89" s="125" t="n"/>
+      <c r="K89" s="124">
+        <f>IF(ABS('Lot 6 - Managed Services'!G10*1000*3-J80)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 6 - Managed Services'!G10*1000*3-J80), "$#,##0.00") &amp; ")")</f>
+        <v/>
+      </c>
+      <c r="L89" s="125" t="n"/>
+      <c r="M89" s="125" t="n"/>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="124" t="inlineStr">
+        <is>
+          <t>4. Tier 1 Co-Location SAA Support (Committed 897 Sites)</t>
+        </is>
+      </c>
+      <c r="B90" s="125" t="n"/>
+      <c r="C90" s="125" t="n"/>
+      <c r="D90" s="125" t="n"/>
+      <c r="E90" s="126">
+        <f>J75</f>
+        <v/>
+      </c>
+      <c r="F90" s="125" t="n"/>
+      <c r="G90" s="126">
+        <f>J75</f>
+        <v/>
+      </c>
+      <c r="H90" s="125" t="n"/>
+      <c r="I90" s="126">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J90" s="125" t="n"/>
+      <c r="K90" s="124" t="inlineStr">
+        <is>
+          <t>"✓ COMMITTED TIER 1 SAA SCOPE"</t>
+        </is>
+      </c>
+      <c r="L90" s="125" t="n"/>
+      <c r="M90" s="125" t="n"/>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="124" t="inlineStr">
+        <is>
+          <t>5. Standby 10.3% Own-Build SAQ Basket (103 Sites)</t>
+        </is>
+      </c>
+      <c r="B91" s="125" t="n"/>
+      <c r="C91" s="125" t="n"/>
+      <c r="D91" s="125" t="n"/>
+      <c r="E91" s="126">
+        <f>J76</f>
+        <v/>
+      </c>
+      <c r="F91" s="125" t="n"/>
+      <c r="G91" s="126">
+        <f>J76</f>
+        <v/>
+      </c>
+      <c r="H91" s="125" t="n"/>
+      <c r="I91" s="126">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J91" s="125" t="n"/>
+      <c r="K91" s="124" t="inlineStr">
+        <is>
+          <t>"✓ STANDBY CONTINGENCY BASKET"</t>
+        </is>
+      </c>
+      <c r="L91" s="125" t="n"/>
+      <c r="M91" s="125" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="52">
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="G86:H86"/>
     <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="I86:J86"/>
     <mergeCell ref="A22:M22"/>
+    <mergeCell ref="I89:J89"/>
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="I86:M86"/>
-    <mergeCell ref="I89:M89"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="K86:M86"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I91:J91"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="I85:M85"/>
     <mergeCell ref="A39:M39"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:M87"/>
     <mergeCell ref="A81:I81"/>
-    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="I87:J87"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="K87:M87"/>
     <mergeCell ref="G89:H89"/>
     <mergeCell ref="A77:I77"/>
     <mergeCell ref="A65:M65"/>
     <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A83:I83"/>
     <mergeCell ref="G88:H88"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="I88:J88"/>
     <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A84:M84"/>
-    <mergeCell ref="I88:M88"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="K88:M88"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A85:M85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -582,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -897,6 +897,8 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4017,17 +4019,17 @@
       </c>
       <c r="B18" s="128" t="inlineStr">
         <is>
-          <t>Modular Lot Value</t>
+          <t>Modular Lot Baseline Value (USD)</t>
         </is>
       </c>
       <c r="C18" s="128" t="inlineStr">
         <is>
-          <t>Services SOW Value</t>
+          <t>Services SOW Equivalent Value (USD)</t>
         </is>
       </c>
       <c r="D18" s="128" t="inlineStr">
         <is>
-          <t>Absolute Variance</t>
+          <t>Absolute Variance (USD)</t>
         </is>
       </c>
       <c r="E18" s="128" t="inlineStr">
@@ -4037,18 +4039,18 @@
       </c>
       <c r="F18" s="128" t="inlineStr">
         <is>
-          <t>Tender Governance &amp; Cross-Reference Rule</t>
+          <t>Tender Governance, Line Mapping &amp; Cross-Reference Audit Rule</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="129" t="inlineStr">
         <is>
-          <t>1. Turnkey Rollout Services (Lot 1 Svc / Domains 2-7)</t>
+          <t>1. Turnkey Rollout &amp; Engineering Services (Lot 1 Svc + Lot 5 Engineering vs SOW Domains 2-7)</t>
         </is>
       </c>
       <c r="B19" s="130">
-        <f>'Lot 1 - RAN &amp; Rollout'!H16</f>
+        <f>'Lot 1 - RAN &amp; Rollout'!H16+'Lot 5 - Site Acq &amp; Civils'!I5+'Lot 5 - Site Acq &amp; Civils'!I12+'Lot 5 - Site Acq &amp; Civils'!I13</f>
         <v/>
       </c>
       <c r="C19" s="130">
@@ -4065,14 +4067,14 @@
       </c>
       <c r="F19" s="132" t="inlineStr">
         <is>
-          <t>Reconciles bottom-up 22-item turnkey rollout scope with Lot 1 Table 2. Form C Row 6 incorporates Lot 1.</t>
+          <t>Reconciles unbundled 22-item turnkey rollout, survey, RF design &amp; cluster optimization (Domains 2–7) against Lot 1 Table 2 (H16) and Lot 5 professional services (I5, I12, I13). Excludes standby/call-out baskets.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="129" t="inlineStr">
         <is>
-          <t>2. Annual Managed Services O&amp;M (Lot 6 / Domain 8)</t>
+          <t>2. Annual Managed Services O&amp;M Baseline (Lot 6 Table 7 vs SOW Domain 8)</t>
         </is>
       </c>
       <c r="B20" s="130">
@@ -4093,14 +4095,14 @@
       </c>
       <c r="F20" s="132" t="inlineStr">
         <is>
-          <t>Reconciles unbundled 21-item 24/7 O&amp;M scope with Lot 6 Table 7. Form C Row 11 applies this annual rate.</t>
+          <t>Reconciles unbundled 21-item 24/7 O&amp;M scope with Lot 6 Table 7 (MS-01 to MS-05). Form C Row 11 applies this annual rate.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="129" t="inlineStr">
         <is>
-          <t>3. 3-Year Managed Services Contractual Baseline</t>
+          <t>3. 3-Year Contractual Managed Services O&amp;M Baseline (Yrs 1-3 Post-Acceptance)</t>
         </is>
       </c>
       <c r="B21" s="130">
@@ -4121,65 +4123,63 @@
       </c>
       <c r="F21" s="132" t="inlineStr">
         <is>
-          <t>Reconciles evaluated 3-year O&amp;M contract baseline (Year 1 to 3).</t>
+          <t>Reconciles evaluated 3-year O&amp;M contract baseline (Year 1 to 3 post-acceptance commitment).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="129" t="inlineStr">
         <is>
-          <t>4. Evaluated Phase 1 CapEx Offer (Lots 1, 2, 3, 4, 5, 7)</t>
+          <t>4. Committed Turnkey Services Contract Envelope (Rollout + 3-Yr O&amp;M)</t>
         </is>
       </c>
       <c r="B22" s="130">
-        <f>B6+B7+B8+B9+B12</f>
+        <f>B19+B21</f>
         <v/>
       </c>
       <c r="C22" s="130">
-        <f>B6+B7+B8+B9+B12</f>
+        <f>'Services SOW &amp; Rate Card'!J77+'Services SOW &amp; Rate Card'!J80</f>
         <v/>
       </c>
       <c r="D22" s="130">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E22" s="131" t="inlineStr">
-        <is>
-          <t>"✓ COMMITTED CAPEX"</t>
-        </is>
+        <f>ABS(B22-C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="131">
+        <f>IF(D22&lt;1, "✓ ZERO VARIANCE", "⚠️ DISCREPANCY")</f>
+        <v/>
       </c>
       <c r="F22" s="132" t="inlineStr">
         <is>
-          <t>Turnkey 1,000 sites infrastructure: RAN, Power, 5GC, OSS/BSS, Civils/Towers &amp; Spares.</t>
+          <t>Audits total committed services contract envelope. Confirms exact parity between Modular Lots and Services SOW before standby/call-out call-offs.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="129" t="inlineStr">
         <is>
-          <t>5. Evaluated 3-Year TCO Offer (CapEx + 3-Yr O&amp;M)</t>
+          <t>5. Governing 10-Year TCO Schedule Integrity Verification (Form C Row 13 vs Bottom-Up Sum)</t>
         </is>
       </c>
       <c r="B23" s="130">
-        <f>B22+B21</f>
+        <f>H13</f>
         <v/>
       </c>
       <c r="C23" s="130">
-        <f>B22+B21</f>
+        <f>('Lot 1 - RAN &amp; Rollout'!H10+'Lot 2 - Power &amp; Passive'!I9+('Lot 5 - Site Acq &amp; Civils'!I14-('Lot 5 - Site Acq &amp; Civils'!I5+'Lot 5 - Site Acq &amp; Civils'!I12+'Lot 5 - Site Acq &amp; Civils'!I13))+'Lot 3 - 5G Core'!F13+'Lot 4 - OSS-BSS'!F15+'Lot 7 - 5G CPE'!G8)+C19+H10+H11+H12</f>
         <v/>
       </c>
       <c r="D23" s="130">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E23" s="131" t="inlineStr">
-        <is>
-          <t>"✓ COMMITTED 3-YR TCO"</t>
-        </is>
+        <f>ABS(B23-C23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="131">
+        <f>IF(D23&lt;1, "✓ ZERO VARIANCE", "⚠️ TCO MISMATCH")</f>
+        <v/>
       </c>
       <c r="F23" s="132" t="inlineStr">
         <is>
-          <t>Evaluated 3-Year Lifecycle Offer: Phase 1 CapEx + 3-Year Managed Services Contract.</t>
+          <t>Cross-audits governing Form C Row 13 against independent bottom-up sum of Modular Hardware Capex, Services SOW Rollout (C19), AMC, O&amp;M, and Spares.</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="133" t="inlineStr">
         <is>
-          <t>Form C Row 13 (Evaluated 10-Year Lifecycle TCO) is the SOLE official evaluated commercial offer for contract award. The Master Services SOW schedule provides binding contract unit rates, milestone billing triggers, and change-order controls. In the event of any numerical discrepancy between the modular Lot schedules and the Services SOW rate card, Form C and the modular Lot rate tables govern. Bidders must verify zero variance across all schedules prior to sealed bid submission.</t>
+          <t>Form C Row 13 (Evaluated 10-Year Lifecycle TCO) is the SOLE official evaluated commercial offer for contract award. The Master Services SOW schedule provides binding contract unit rates, milestone billing triggers, and change-order controls. In the event of any numerical discrepancy between the modular Lot schedules and the Services SOW rate card, Form C and the modular Lot rate tables govern. Bidders must verify zero variance across all audit rows (Rows 19–23) prior to sealed bid submission.</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="G9" s="80" t="inlineStr">
         <is>
-          <t>1x (10.3% Own-Build Basket)</t>
+          <t>89.7% Co-Location Basket (Tier 1 TowerCo)</t>
         </is>
       </c>
       <c r="H9" s="99" t="n"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L9" s="96" t="inlineStr">
         <is>
-          <t>Lot 5 Standby Call-Off (103 Sites Ph1 / 515 Prog)</t>
+          <t>Lot 5 Committed Turnkey (897 Sites Ph1 / 4,485 Prog)</t>
         </is>
       </c>
       <c r="M9" s="96" t="inlineStr">
@@ -10743,14 +10743,14 @@
           <t>SUBTOTAL A1a: COMMITTED TIER 1 CO-LOCATION SAA SUPPORT (897 SITES PH1 / 4,485 SITES PROG) [SAQ-03]</t>
         </is>
       </c>
-      <c r="B75" s="79" t="n"/>
-      <c r="C75" s="79" t="n"/>
-      <c r="D75" s="79" t="n"/>
-      <c r="E75" s="79" t="n"/>
-      <c r="F75" s="79" t="n"/>
-      <c r="G75" s="79" t="n"/>
-      <c r="H75" s="79" t="n"/>
-      <c r="I75" s="79" t="n"/>
+      <c r="B75" s="89" t="n"/>
+      <c r="C75" s="89" t="n"/>
+      <c r="D75" s="89" t="n"/>
+      <c r="E75" s="89" t="n"/>
+      <c r="F75" s="89" t="n"/>
+      <c r="G75" s="89" t="n"/>
+      <c r="H75" s="89" t="n"/>
+      <c r="I75" s="90" t="n"/>
       <c r="J75" s="104">
         <f>J9</f>
         <v/>
@@ -10772,14 +10772,14 @@
           <t>SUBTOTAL A1b: STANDBY 10.3% OWN-BUILD SAQ BASKET (103 SITES PH1 / 515 SITES PROG) [SAQ-01, 02, 04..08]</t>
         </is>
       </c>
-      <c r="B76" s="79" t="n"/>
-      <c r="C76" s="79" t="n"/>
-      <c r="D76" s="79" t="n"/>
-      <c r="E76" s="79" t="n"/>
-      <c r="F76" s="79" t="n"/>
-      <c r="G76" s="79" t="n"/>
-      <c r="H76" s="79" t="n"/>
-      <c r="I76" s="79" t="n"/>
+      <c r="B76" s="89" t="n"/>
+      <c r="C76" s="89" t="n"/>
+      <c r="D76" s="89" t="n"/>
+      <c r="E76" s="89" t="n"/>
+      <c r="F76" s="89" t="n"/>
+      <c r="G76" s="89" t="n"/>
+      <c r="H76" s="89" t="n"/>
+      <c r="I76" s="90" t="n"/>
       <c r="J76" s="104">
         <f>SUM(J7:J8)+SUM(J10:J14)</f>
         <v/>
@@ -10801,14 +10801,14 @@
           <t>SUBTOTAL A2: COMMITTED TURNKEY ROLLOUT SERVICES (1,000 SITES PH1 / 5,000 SITES PROG) [DOMAINS 2-7]</t>
         </is>
       </c>
-      <c r="B77" s="79" t="n"/>
-      <c r="C77" s="79" t="n"/>
-      <c r="D77" s="79" t="n"/>
-      <c r="E77" s="79" t="n"/>
-      <c r="F77" s="79" t="n"/>
-      <c r="G77" s="79" t="n"/>
-      <c r="H77" s="79" t="n"/>
-      <c r="I77" s="79" t="n"/>
+      <c r="B77" s="89" t="n"/>
+      <c r="C77" s="89" t="n"/>
+      <c r="D77" s="89" t="n"/>
+      <c r="E77" s="89" t="n"/>
+      <c r="F77" s="89" t="n"/>
+      <c r="G77" s="89" t="n"/>
+      <c r="H77" s="89" t="n"/>
+      <c r="I77" s="90" t="n"/>
       <c r="J77" s="104">
         <f>SUM(J16:J42)</f>
         <v/>
@@ -10830,14 +10830,14 @@
           <t>SUBTOTAL A: TOTAL TURNKEY ROLLOUT &amp; SITING SERVICES (COMMITTED + STANDBY BASKET) [USD]</t>
         </is>
       </c>
-      <c r="B78" s="79" t="n"/>
-      <c r="C78" s="79" t="n"/>
-      <c r="D78" s="79" t="n"/>
-      <c r="E78" s="79" t="n"/>
-      <c r="F78" s="79" t="n"/>
-      <c r="G78" s="79" t="n"/>
-      <c r="H78" s="79" t="n"/>
-      <c r="I78" s="79" t="n"/>
+      <c r="B78" s="89" t="n"/>
+      <c r="C78" s="89" t="n"/>
+      <c r="D78" s="89" t="n"/>
+      <c r="E78" s="89" t="n"/>
+      <c r="F78" s="89" t="n"/>
+      <c r="G78" s="89" t="n"/>
+      <c r="H78" s="89" t="n"/>
+      <c r="I78" s="90" t="n"/>
       <c r="J78" s="107">
         <f>J75+J76+J77</f>
         <v/>
@@ -10859,14 +10859,14 @@
           <t>SUBTOTAL B1: ANNUALIZED 24/7 MANAGED O&amp;M SERVICES (12-MONTH EVALUATION) [USD/YEAR]</t>
         </is>
       </c>
-      <c r="B79" s="79" t="n"/>
-      <c r="C79" s="79" t="n"/>
-      <c r="D79" s="79" t="n"/>
-      <c r="E79" s="79" t="n"/>
-      <c r="F79" s="79" t="n"/>
-      <c r="G79" s="79" t="n"/>
-      <c r="H79" s="79" t="n"/>
-      <c r="I79" s="79" t="n"/>
+      <c r="B79" s="89" t="n"/>
+      <c r="C79" s="89" t="n"/>
+      <c r="D79" s="89" t="n"/>
+      <c r="E79" s="89" t="n"/>
+      <c r="F79" s="89" t="n"/>
+      <c r="G79" s="89" t="n"/>
+      <c r="H79" s="89" t="n"/>
+      <c r="I79" s="90" t="n"/>
       <c r="J79" s="104">
         <f>SUM(J44:J64)</f>
         <v/>
@@ -10888,14 +10888,14 @@
           <t>SUBTOTAL B2: 3-YEAR MANAGED O&amp;M CONTRACTUAL PROGRAM TOTAL (36 MONTHS — LOT 6 BASELINE) [USD]</t>
         </is>
       </c>
-      <c r="B80" s="79" t="n"/>
-      <c r="C80" s="79" t="n"/>
-      <c r="D80" s="79" t="n"/>
-      <c r="E80" s="79" t="n"/>
-      <c r="F80" s="79" t="n"/>
-      <c r="G80" s="79" t="n"/>
-      <c r="H80" s="79" t="n"/>
-      <c r="I80" s="79" t="n"/>
+      <c r="B80" s="89" t="n"/>
+      <c r="C80" s="89" t="n"/>
+      <c r="D80" s="89" t="n"/>
+      <c r="E80" s="89" t="n"/>
+      <c r="F80" s="89" t="n"/>
+      <c r="G80" s="89" t="n"/>
+      <c r="H80" s="89" t="n"/>
+      <c r="I80" s="90" t="n"/>
       <c r="J80" s="107">
         <f>J79*3</f>
         <v/>
@@ -10917,14 +10917,14 @@
           <t>SUBTOTAL C: AD-HOC CALL-OUT CONTINGENCY EVALUATION BASKET (NOMINAL ANNUAL CALL-OFF) [USD]</t>
         </is>
       </c>
-      <c r="B81" s="79" t="n"/>
-      <c r="C81" s="79" t="n"/>
-      <c r="D81" s="79" t="n"/>
-      <c r="E81" s="79" t="n"/>
-      <c r="F81" s="79" t="n"/>
-      <c r="G81" s="79" t="n"/>
-      <c r="H81" s="79" t="n"/>
-      <c r="I81" s="79" t="n"/>
+      <c r="B81" s="89" t="n"/>
+      <c r="C81" s="89" t="n"/>
+      <c r="D81" s="89" t="n"/>
+      <c r="E81" s="89" t="n"/>
+      <c r="F81" s="89" t="n"/>
+      <c r="G81" s="89" t="n"/>
+      <c r="H81" s="89" t="n"/>
+      <c r="I81" s="90" t="n"/>
       <c r="J81" s="104">
         <f>SUM(J66:J73)</f>
         <v/>
@@ -10946,14 +10946,14 @@
           <t>GRAND TOTAL: INDICATIVE ALL-IN SERVICES CONTRACT ENVELOPE (ROLLOUT + 3-YEAR O&amp;M + STANDBY SAQ + CALL-OUTS) [USD]</t>
         </is>
       </c>
-      <c r="B82" s="111" t="n"/>
-      <c r="C82" s="111" t="n"/>
-      <c r="D82" s="111" t="n"/>
-      <c r="E82" s="111" t="n"/>
-      <c r="F82" s="111" t="n"/>
-      <c r="G82" s="111" t="n"/>
-      <c r="H82" s="111" t="n"/>
-      <c r="I82" s="111" t="n"/>
+      <c r="B82" s="134" t="n"/>
+      <c r="C82" s="134" t="n"/>
+      <c r="D82" s="134" t="n"/>
+      <c r="E82" s="134" t="n"/>
+      <c r="F82" s="134" t="n"/>
+      <c r="G82" s="134" t="n"/>
+      <c r="H82" s="134" t="n"/>
+      <c r="I82" s="135" t="n"/>
       <c r="J82" s="112">
         <f>J78+J80+J81</f>
         <v/>
@@ -10975,14 +10975,14 @@
           <t>GRAND TOTAL EQUIVALENT IN PHILIPPINE PESO (PHP @ 55.00 FX BASELINE)</t>
         </is>
       </c>
-      <c r="B83" s="111" t="n"/>
-      <c r="C83" s="111" t="n"/>
-      <c r="D83" s="111" t="n"/>
-      <c r="E83" s="111" t="n"/>
-      <c r="F83" s="111" t="n"/>
-      <c r="G83" s="111" t="n"/>
-      <c r="H83" s="111" t="n"/>
-      <c r="I83" s="111" t="n"/>
+      <c r="B83" s="134" t="n"/>
+      <c r="C83" s="134" t="n"/>
+      <c r="D83" s="134" t="n"/>
+      <c r="E83" s="134" t="n"/>
+      <c r="F83" s="134" t="n"/>
+      <c r="G83" s="134" t="n"/>
+      <c r="H83" s="134" t="n"/>
+      <c r="I83" s="135" t="n"/>
       <c r="J83" s="115">
         <f>J82*55</f>
         <v/>
@@ -11011,34 +11011,34 @@
           <t>Cost Element / Procurement Scope</t>
         </is>
       </c>
-      <c r="B86" s="79" t="n"/>
-      <c r="C86" s="79" t="n"/>
-      <c r="D86" s="79" t="n"/>
+      <c r="B86" s="89" t="n"/>
+      <c r="C86" s="89" t="n"/>
+      <c r="D86" s="90" t="n"/>
       <c r="E86" s="123" t="inlineStr">
         <is>
           <t>Modular Lot Schedule (USD)</t>
         </is>
       </c>
-      <c r="F86" s="79" t="n"/>
+      <c r="F86" s="90" t="n"/>
       <c r="G86" s="123" t="inlineStr">
         <is>
           <t>Services SOW Schedule (USD)</t>
         </is>
       </c>
-      <c r="H86" s="79" t="n"/>
+      <c r="H86" s="90" t="n"/>
       <c r="I86" s="123" t="inlineStr">
         <is>
           <t>Variance (USD)</t>
         </is>
       </c>
-      <c r="J86" s="79" t="n"/>
+      <c r="J86" s="90" t="n"/>
       <c r="K86" s="123" t="inlineStr">
         <is>
           <t>Live Audit Status &amp; Governance Rule</t>
         </is>
       </c>
-      <c r="L86" s="79" t="n"/>
-      <c r="M86" s="79" t="n"/>
+      <c r="L86" s="89" t="n"/>
+      <c r="M86" s="90" t="n"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="124" t="inlineStr">
@@ -11046,30 +11046,30 @@
           <t>1. Turnkey Rollout Services (Phase 1: 1,000 Sites)</t>
         </is>
       </c>
-      <c r="B87" s="125" t="n"/>
-      <c r="C87" s="125" t="n"/>
-      <c r="D87" s="125" t="n"/>
+      <c r="B87" s="89" t="n"/>
+      <c r="C87" s="89" t="n"/>
+      <c r="D87" s="90" t="n"/>
       <c r="E87" s="126">
         <f>'Lot 1 - RAN &amp; Rollout'!H16</f>
         <v/>
       </c>
-      <c r="F87" s="125" t="n"/>
+      <c r="F87" s="90" t="n"/>
       <c r="G87" s="126">
         <f>J77</f>
         <v/>
       </c>
-      <c r="H87" s="125" t="n"/>
+      <c r="H87" s="90" t="n"/>
       <c r="I87" s="126">
         <f>ABS('Lot 1 - RAN &amp; Rollout'!H16-J77)</f>
         <v/>
       </c>
-      <c r="J87" s="125" t="n"/>
+      <c r="J87" s="90" t="n"/>
       <c r="K87" s="124">
         <f>IF(ABS('Lot 1 - RAN &amp; Rollout'!H16-J77)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 1 - RAN &amp; Rollout'!H16-J77), "$#,##0.00") &amp; ")")</f>
         <v/>
       </c>
-      <c r="L87" s="125" t="n"/>
-      <c r="M87" s="125" t="n"/>
+      <c r="L87" s="89" t="n"/>
+      <c r="M87" s="90" t="n"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="124" t="inlineStr">
@@ -11077,30 +11077,30 @@
           <t>2. 24/7 Managed Services Annual O&amp;M (12 Months / 1,000 Sites)</t>
         </is>
       </c>
-      <c r="B88" s="125" t="n"/>
-      <c r="C88" s="125" t="n"/>
-      <c r="D88" s="125" t="n"/>
+      <c r="B88" s="89" t="n"/>
+      <c r="C88" s="89" t="n"/>
+      <c r="D88" s="90" t="n"/>
       <c r="E88" s="126">
         <f>'Lot 6 - Managed Services'!G10*1000</f>
         <v/>
       </c>
-      <c r="F88" s="125" t="n"/>
+      <c r="F88" s="90" t="n"/>
       <c r="G88" s="126">
         <f>J79</f>
         <v/>
       </c>
-      <c r="H88" s="125" t="n"/>
+      <c r="H88" s="90" t="n"/>
       <c r="I88" s="126">
         <f>ABS('Lot 6 - Managed Services'!G10*1000-J79)</f>
         <v/>
       </c>
-      <c r="J88" s="125" t="n"/>
+      <c r="J88" s="90" t="n"/>
       <c r="K88" s="124">
         <f>IF(ABS('Lot 6 - Managed Services'!G10*1000-J79)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 6 - Managed Services'!G10*1000-J79), "$#,##0.00") &amp; ")")</f>
         <v/>
       </c>
-      <c r="L88" s="125" t="n"/>
-      <c r="M88" s="125" t="n"/>
+      <c r="L88" s="89" t="n"/>
+      <c r="M88" s="90" t="n"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="124" t="inlineStr">
@@ -11108,30 +11108,30 @@
           <t>3. 3-Year Contractual Managed Services O&amp;M Baseline</t>
         </is>
       </c>
-      <c r="B89" s="125" t="n"/>
-      <c r="C89" s="125" t="n"/>
-      <c r="D89" s="125" t="n"/>
+      <c r="B89" s="89" t="n"/>
+      <c r="C89" s="89" t="n"/>
+      <c r="D89" s="90" t="n"/>
       <c r="E89" s="126">
         <f>'Lot 6 - Managed Services'!G10*1000*3</f>
         <v/>
       </c>
-      <c r="F89" s="125" t="n"/>
+      <c r="F89" s="90" t="n"/>
       <c r="G89" s="126">
         <f>J80</f>
         <v/>
       </c>
-      <c r="H89" s="125" t="n"/>
+      <c r="H89" s="90" t="n"/>
       <c r="I89" s="126">
         <f>ABS('Lot 6 - Managed Services'!G10*1000*3-J80)</f>
         <v/>
       </c>
-      <c r="J89" s="125" t="n"/>
+      <c r="J89" s="90" t="n"/>
       <c r="K89" s="124">
         <f>IF(ABS('Lot 6 - Managed Services'!G10*1000*3-J80)&lt;1, "✓ RECONCILED / ZERO VARIANCE", "⚠️ VARIANCE DETECTED ($" &amp; TEXT(ABS('Lot 6 - Managed Services'!G10*1000*3-J80), "$#,##0.00") &amp; ")")</f>
         <v/>
       </c>
-      <c r="L89" s="125" t="n"/>
-      <c r="M89" s="125" t="n"/>
+      <c r="L89" s="89" t="n"/>
+      <c r="M89" s="90" t="n"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="124" t="inlineStr">
@@ -11139,31 +11139,31 @@
           <t>4. Tier 1 Co-Location SAA Support (Committed 897 Sites)</t>
         </is>
       </c>
-      <c r="B90" s="125" t="n"/>
-      <c r="C90" s="125" t="n"/>
-      <c r="D90" s="125" t="n"/>
+      <c r="B90" s="89" t="n"/>
+      <c r="C90" s="89" t="n"/>
+      <c r="D90" s="90" t="n"/>
       <c r="E90" s="126">
         <f>J75</f>
         <v/>
       </c>
-      <c r="F90" s="125" t="n"/>
+      <c r="F90" s="90" t="n"/>
       <c r="G90" s="126">
         <f>J75</f>
         <v/>
       </c>
-      <c r="H90" s="125" t="n"/>
+      <c r="H90" s="90" t="n"/>
       <c r="I90" s="126">
         <f>0</f>
         <v/>
       </c>
-      <c r="J90" s="125" t="n"/>
+      <c r="J90" s="90" t="n"/>
       <c r="K90" s="124" t="inlineStr">
         <is>
           <t>"✓ COMMITTED TIER 1 SAA SCOPE"</t>
         </is>
       </c>
-      <c r="L90" s="125" t="n"/>
-      <c r="M90" s="125" t="n"/>
+      <c r="L90" s="89" t="n"/>
+      <c r="M90" s="90" t="n"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="124" t="inlineStr">
@@ -11171,31 +11171,31 @@
           <t>5. Standby 10.3% Own-Build SAQ Basket (103 Sites)</t>
         </is>
       </c>
-      <c r="B91" s="125" t="n"/>
-      <c r="C91" s="125" t="n"/>
-      <c r="D91" s="125" t="n"/>
+      <c r="B91" s="89" t="n"/>
+      <c r="C91" s="89" t="n"/>
+      <c r="D91" s="90" t="n"/>
       <c r="E91" s="126">
         <f>J76</f>
         <v/>
       </c>
-      <c r="F91" s="125" t="n"/>
+      <c r="F91" s="90" t="n"/>
       <c r="G91" s="126">
         <f>J76</f>
         <v/>
       </c>
-      <c r="H91" s="125" t="n"/>
+      <c r="H91" s="90" t="n"/>
       <c r="I91" s="126">
         <f>0</f>
         <v/>
       </c>
-      <c r="J91" s="125" t="n"/>
+      <c r="J91" s="90" t="n"/>
       <c r="K91" s="124" t="inlineStr">
         <is>
           <t>"✓ STANDBY CONTINGENCY BASKET"</t>
         </is>
       </c>
-      <c r="L91" s="125" t="n"/>
-      <c r="M91" s="125" t="n"/>
+      <c r="L91" s="89" t="n"/>
+      <c r="M91" s="90" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="52">

--- a/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
+++ b/RFP_Tender_Package/06_RFP_Commercial_Price_Book_and_BoQ_Template.xlsx
@@ -259,7 +259,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -370,6 +370,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
         <bgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00203764"/>
+        <bgColor rgb="00203764"/>
       </patternFill>
     </fill>
   </fills>
@@ -582,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -899,6 +905,33 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6352,7 +6385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6870,7 +6903,265 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="136" t="inlineStr">
+        <is>
+          <t>TABLE 5B: SITING CONVERSION &amp; MILESTONE 1 TRUE-UP RATE SCHEDULE (TSSR RECONCILIATION)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="137" t="inlineStr">
+        <is>
+          <t>Contractual Siting Reconciliation Framework per Appendix D §1.1 Item 5 &amp; Bid Bulletin 01 §1.4. Rates derive dynamically from Table 5A unit prices to ensure mathematical certainty and transparent adjustments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="138" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="B18" s="138" t="inlineStr">
+        <is>
+          <t>Conversion Package Description</t>
+        </is>
+      </c>
+      <c r="C18" s="138" t="inlineStr">
+        <is>
+          <t>Governing Scope &amp; BoQ Formula Mapping</t>
+        </is>
+      </c>
+      <c r="D18" s="138" t="inlineStr">
+        <is>
+          <t>Site Sourcing Classification</t>
+        </is>
+      </c>
+      <c r="E18" s="138" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="F18" s="138" t="inlineStr">
+        <is>
+          <t>Evaluated Baseline Sites</t>
+        </is>
+      </c>
+      <c r="G18" s="138" t="inlineStr">
+        <is>
+          <t>Unit Rate (USD)</t>
+        </is>
+      </c>
+      <c r="H18" s="138" t="inlineStr">
+        <is>
+          <t>Unit Rate (PHP @ 55)</t>
+        </is>
+      </c>
+      <c r="I18" s="138" t="inlineStr">
+        <is>
+          <t>True-Up Differential vs. Co-Lo (USD)</t>
+        </is>
+      </c>
+      <c r="J18" s="138" t="inlineStr">
+        <is>
+          <t>Remarks / True-Up Administration Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="139" t="inlineStr">
+        <is>
+          <t>LOT5-COLO</t>
+        </is>
+      </c>
+      <c r="B19" s="140" t="inlineStr">
+        <is>
+          <t>Tier 1 Co-Location Civil Package</t>
+        </is>
+      </c>
+      <c r="C19" s="140" t="inlineStr">
+        <is>
+          <t>Equipment Pad Foundation &amp; Elevated Cable Gantry (=CIV-SVC-03)</t>
+        </is>
+      </c>
+      <c r="D19" s="140" t="inlineStr">
+        <is>
+          <t>Tier 1 Co-Location Baseline</t>
+        </is>
+      </c>
+      <c r="E19" s="141" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F19" s="142" t="n">
+        <v>897</v>
+      </c>
+      <c r="G19" s="143">
+        <f>G7</f>
+        <v/>
+      </c>
+      <c r="H19" s="144">
+        <f>H7</f>
+        <v/>
+      </c>
+      <c r="I19" s="143">
+        <f>G19-G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="140" t="inlineStr">
+        <is>
+          <t>Contract baseline civil allowance. Milestone 1 TSSR confirmation retains this rate ($0.00 contract variation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="139" t="inlineStr">
+        <is>
+          <t>LOT5-B2S</t>
+        </is>
+      </c>
+      <c r="B20" s="140" t="inlineStr">
+        <is>
+          <t>Tier 2 TowerCo Build-to-Suit (B2S) Civil Package</t>
+        </is>
+      </c>
+      <c r="C20" s="140" t="inlineStr">
+        <is>
+          <t>Equipment Pad Foundation &amp; Cable Gantry on TowerCo B2S facility (=CIV-SVC-03)</t>
+        </is>
+      </c>
+      <c r="D20" s="140" t="inlineStr">
+        <is>
+          <t>Tier 2 B2S Expansion Alternative</t>
+        </is>
+      </c>
+      <c r="E20" s="141" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F20" s="142" t="n">
+        <v>103</v>
+      </c>
+      <c r="G20" s="143">
+        <f>G7</f>
+        <v/>
+      </c>
+      <c r="H20" s="144">
+        <f>H7</f>
+        <v/>
+      </c>
+      <c r="I20" s="143">
+        <f>G20-G19</f>
+        <v/>
+      </c>
+      <c r="J20" s="140" t="inlineStr">
+        <is>
+          <t>TowerCo finances and constructs tower/compound turnkey under MLA. Operator civil scope identical to co-location; $0.00 civil variation differential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="139" t="inlineStr">
+        <is>
+          <t>LOT5-GF30</t>
+        </is>
+      </c>
+      <c r="B21" s="140" t="inlineStr">
+        <is>
+          <t>Tier 3 Operator Greenfield 30m Monopole Package</t>
+        </is>
+      </c>
+      <c r="C21" s="140" t="inlineStr">
+        <is>
+          <t>Compound civil slab, 8x8m fence/gravel, grounding grid, 30m monopole, &amp; SAQ permits (=CIV-SVC-02+CIV-SVC-04+CIV-SVC-05+CIV-SVC-06)</t>
+        </is>
+      </c>
+      <c r="D21" s="140" t="inlineStr">
+        <is>
+          <t>Tier 3 Greenfield Standard (Alt A)</t>
+        </is>
+      </c>
+      <c r="E21" s="141" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F21" s="142" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" s="143">
+        <f>G6+G8+G9+G10</f>
+        <v/>
+      </c>
+      <c r="H21" s="144">
+        <f>H6+H8+H9+H10</f>
+        <v/>
+      </c>
+      <c r="I21" s="143">
+        <f>G21-G19</f>
+        <v/>
+      </c>
+      <c r="J21" s="140" t="inlineStr">
+        <is>
+          <t>Net addition per site converted from Co-Lo to GF30: =(CIV-SVC-02+CIV-SVC-04+CIV-SVC-05+CIV-SVC-06)-CIV-SVC-03. Reverse conversion from GF30 to Co-Lo issues equivalent credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="139" t="inlineStr">
+        <is>
+          <t>LOT5-GF40</t>
+        </is>
+      </c>
+      <c r="B22" s="140" t="inlineStr">
+        <is>
+          <t>Tier 3 Operator Greenfield 40m Monopole Package</t>
+        </is>
+      </c>
+      <c r="C22" s="140" t="inlineStr">
+        <is>
+          <t>Compound civil slab, 8x8m fence/gravel, grounding grid, 40m monopole, &amp; SAQ permits (=CIV-SVC-02+CIV-SVC-04+CIV-SVC-05+CIV-SVC-07)</t>
+        </is>
+      </c>
+      <c r="D22" s="140" t="inlineStr">
+        <is>
+          <t>Tier 3 Greenfield High-Clearance (Alt B)</t>
+        </is>
+      </c>
+      <c r="E22" s="141" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F22" s="142" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="143">
+        <f>G6+G8+G9+G11</f>
+        <v/>
+      </c>
+      <c r="H22" s="144">
+        <f>H6+H8+H9+H11</f>
+        <v/>
+      </c>
+      <c r="I22" s="143">
+        <f>G22-G19</f>
+        <v/>
+      </c>
+      <c r="J22" s="140" t="inlineStr">
+        <is>
+          <t>Net addition per site converted from Co-Lo to GF40: =(CIV-SVC-02+CIV-SVC-04+CIV-SVC-05+CIV-SVC-07)-CIV-SVC-03. Reverse conversion from GF40 to Co-Lo issues equivalent credit.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A16:J16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
